--- a/technicals/exports/new-highs-history.xlsx
+++ b/technicals/exports/new-highs-history.xlsx
@@ -117,54 +117,64 @@
     <ns0:row r="2">
       <ns0:c r="A2" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B2" t="inlineStr">
         <ns0:is>
-          <ns0:t>AMD</ns0:t>
+          <ns0:t>A</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C2" t="inlineStr">
         <ns0:is>
-          <ns0:t>Advanced Micro Devices Inc</ns0:t>
+          <ns0:t>Agilent Technologies Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D2" t="inlineStr">
         <ns0:is>
-          <ns0:t/>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>전 세계 생명과학, 진단 및 응용화학 시장에 용도별 솔루션을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G2">
-        <ns0:v>630.6300048828125</ns0:v>
+        <ns0:v>175.2100067138672</ns0:v>
       </ns0:c>
       <ns0:c r="H2">
-        <ns0:v>0.21771526808096464</ns0:v>
+        <ns0:v>1.4005518385123983</ns0:v>
       </ns0:c>
       <ns0:c r="I2">
-        <ns0:v>630.7999877929688</ns0:v>
+        <ns0:v>174.77000427246094</ns0:v>
       </ns0:c>
       <ns0:c r="J2">
-        <ns0:v>-0.026947196170845622</ns0:v>
+        <ns0:v>0.25176084605473825</ns0:v>
       </ns0:c>
       <ns0:c r="K2">
-        <ns0:v>0.8157954096816155</ns0:v>
+        <ns0:v>0.8334500295959376</ns0:v>
       </ns0:c>
       <ns0:c r="L2">
-        <ns0:v>72.99571503316014</ns0:v>
+        <ns0:v>76.76689164314655</ns0:v>
       </ns0:c>
       <ns0:c r="M2">
-        <ns0:v>528.1040023803711</ns0:v>
+        <ns0:v>155.81499938964845</ns0:v>
       </ns0:c>
       <ns0:c r="N2">
-        <ns0:v>504.7130029296875</ns0:v>
+        <ns0:v>149.62200012207032</ns0:v>
       </ns0:c>
       <ns0:c r="O2">
-        <ns0:v>364.753550567627</ns0:v>
+        <ns0:v>132.25100002288818</ns0:v>
       </ns0:c>
       <ns0:c r="P2" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q2" t="inlineStr">
@@ -174,66 +184,81 @@
       </ns0:c>
       <ns0:c r="R2" t="inlineStr">
         <ns0:is>
-          <ns0:t>동종 반도체 기업 대비 주가 적정성, 애널리스트의 새 목표주가, 완성형 시스템 수요와 주가 상승을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>교환 제안과 반복 매출을 통한 가치평가, 실적 발표 후 9.6% 오른 주가의 지속 가능성이 다뤄졌다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S2" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://www.trefis.com/articles/616631/is-amd-stock-priced-right-against-its-chip-peers/2026-09-25</ns0:t>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/agilent-technologies-tests-valuation-exchange-061259408.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/A/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="3">
       <ns0:c r="A3" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B3" t="inlineStr">
         <ns0:is>
-          <ns0:t>HPE</ns0:t>
+          <ns0:t>ABCL</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C3" t="inlineStr">
         <ns0:is>
-          <ns0:t>Hewlett Packard Enterprise Co</ns0:t>
+          <ns0:t>AbCellera Biologics Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D3" t="inlineStr">
         <ns0:is>
-          <ns0:t/>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Biotechnology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미충족 의료 수요에 대응하는 항체 의약품을 개발하며, 비호르몬 치료제 ABCL635는 임상 2상 중.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G3">
-        <ns0:v>62.939998626708984</ns0:v>
+        <ns0:v>13.920000076293945</ns0:v>
       </ns0:c>
       <ns0:c r="H3">
-        <ns0:v>-0.9131011128382327</ns0:v>
+        <ns0:v>9.606301459459644</ns0:v>
       </ns0:c>
       <ns0:c r="I3">
-        <ns0:v>65.4800033569336</ns0:v>
+        <ns0:v>13.180000305175781</ns0:v>
       </ns0:c>
       <ns0:c r="J3">
-        <ns0:v>-3.8790540623203085</ns0:v>
+        <ns0:v>5.614565659968651</ns0:v>
       </ns0:c>
       <ns0:c r="K3">
-        <ns0:v>0.5506095863383583</ns0:v>
+        <ns0:v>1.8184038472561628</ns0:v>
       </ns0:c>
       <ns0:c r="L3">
-        <ns0:v>61.301337066088976</ns0:v>
+        <ns0:v>72.85483704220029</ns0:v>
       </ns0:c>
       <ns0:c r="M3">
-        <ns0:v>57.36350021362305</ns0:v>
+        <ns0:v>11.872999906539917</ns0:v>
       </ns0:c>
       <ns0:c r="N3">
-        <ns0:v>53.94500015258789</ns0:v>
+        <ns0:v>9.853899946212769</ns0:v>
       </ns0:c>
       <ns0:c r="O3">
-        <ns0:v>35.905800123214725</ns0:v>
+        <ns0:v>5.769699981212616</ns0:v>
       </ns0:c>
       <ns0:c r="P3" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q3" t="inlineStr">
@@ -243,19 +268,24 @@
       </ns0:c>
       <ns0:c r="R3" t="inlineStr">
         <ns0:is>
-          <ns0:t>네트워킹·양자 분야 제휴 확대, 주가의 52주 최고가 기록과 매도 여부, 긍정적 종목 평가를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>ABCL 주가가 3개월간 121% 상승했다는 보도가 나왔다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S3" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/technology/articles/hpe-expanded-networking-quantum-partnerships-131208305.html</ns0:t>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/abcl-stock-surges-121-3-141700425.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/ABCL/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="4">
       <ns0:c r="A4" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B4" t="inlineStr">
@@ -280,36 +310,36 @@
       </ns0:c>
       <ns0:c r="F4" t="inlineStr">
         <ns0:is>
-          <ns0:t>마케팅 전략·브랜딩·디지털 마케팅·온오프라인 판매·고객 서비스를 제공하는 브랜드 관리 기업.</ns0:t>
+          <ns0:t>중국 뷰티·개인관리 브랜드에 전략, 마케팅, 전 채널 판매, 고객 서비스 및 물류 등 브랜드 관리 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G4">
-        <ns0:v>1.2999999523162842</ns0:v>
+        <ns0:v>1.6649999618530273</ns0:v>
       </ns0:c>
       <ns0:c r="H4">
-        <ns0:v>14.035084967467881</ns0:v>
+        <ns0:v>28.07692484037416</ns0:v>
       </ns0:c>
       <ns0:c r="I4">
-        <ns0:v>1.2999999523162842</ns0:v>
+        <ns0:v>1.6200000047683716</ns0:v>
       </ns0:c>
       <ns0:c r="J4">
-        <ns0:v>0.0</ns0:v>
+        <ns0:v>2.7777751205062318</ns0:v>
       </ns0:c>
       <ns0:c r="L4">
-        <ns0:v>69.06584562985581</ns0:v>
+        <ns0:v>78.49285813061412</ns0:v>
       </ns0:c>
       <ns0:c r="M4">
-        <ns0:v>1.0067999958992004</ns0:v>
+        <ns0:v>1.0310999929904938</ns0:v>
       </ns0:c>
       <ns0:c r="N4">
-        <ns0:v>0.9164199948310852</ns0:v>
+        <ns0:v>0.9295199942588807</ns0:v>
       </ns0:c>
       <ns0:c r="O4">
-        <ns0:v>0.847754997909069</ns0:v>
+        <ns0:v>0.8514999976754188</ns0:v>
       </ns0:c>
       <ns0:c r="P4" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q4" t="inlineStr">
@@ -324,67 +354,67 @@
       </ns0:c>
       <ns0:c r="T4" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finviz.com/quote.ashx?t=ABLV</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ABLV/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="5">
       <ns0:c r="A5" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B5" t="inlineStr">
         <ns0:is>
-          <ns0:t>ADPT</ns0:t>
+          <ns0:t>AERT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Adaptive Biotechnologies Corp</ns0:t>
+          <ns0:t>Aeries Technology Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Diagnostics &amp; Research</ns0:t>
+          <ns0:t>Consulting Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F5" t="inlineStr">
         <ns0:is>
-          <ns0:t>면역 의학 플랫폼 개발 기업.</ns0:t>
+          <ns0:t>북미·아시아태평양 등에서 전문·기술 컨설팅과 운영 모델 설계 관련 자문을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G5">
-        <ns0:v>29.43000030517578</ns0:v>
+        <ns0:v>7.224999904632568</ns0:v>
       </ns0:c>
       <ns0:c r="H5">
-        <ns0:v>-0.47345076460363344</ns0:v>
+        <ns0:v>1.760563403929627</ns0:v>
       </ns0:c>
       <ns0:c r="I5">
-        <ns0:v>29.579999923706055</ns0:v>
+        <ns0:v>7.650000095367432</ns0:v>
       </ns0:c>
       <ns0:c r="J5">
-        <ns0:v>-0.5070981031682131</ns0:v>
+        <ns0:v>-5.555557979564318</ns0:v>
       </ns0:c>
       <ns0:c r="K5">
-        <ns0:v>0.7562478403496726</ns0:v>
+        <ns0:v>1.5298320610687024</ns0:v>
       </ns0:c>
       <ns0:c r="L5">
-        <ns0:v>71.62183423491359</ns0:v>
+        <ns0:v>57.008305318372415</ns0:v>
       </ns0:c>
       <ns0:c r="M5">
-        <ns0:v>26.21250009536743</ns0:v>
+        <ns0:v>7.022749948501587</ns0:v>
       </ns0:c>
       <ns0:c r="N5">
-        <ns0:v>24.984800071716307</ns0:v>
+        <ns0:v>6.855399971008301</ns0:v>
       </ns0:c>
       <ns0:c r="O5">
-        <ns0:v>18.33455002307892</ns0:v>
+        <ns0:v>5.222569983005524</ns0:v>
       </ns0:c>
       <ns0:c r="P5" t="inlineStr">
         <ns0:is>
@@ -403,67 +433,67 @@
       </ns0:c>
       <ns0:c r="T5" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finviz.com/quote.ashx?t=ADPT</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/AERT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="6">
       <ns0:c r="A6" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B6" t="inlineStr">
         <ns0:is>
-          <ns0:t>AOUT</ns0:t>
+          <ns0:t>AGEN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C6" t="inlineStr">
         <ns0:is>
-          <ns0:t>American Outdoor Brands Inc</ns0:t>
+          <ns0:t>Agenus Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D6" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E6" t="inlineStr">
         <ns0:is>
-          <ns0:t>Leisure</ns0:t>
+          <ns0:t>Biotechnology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F6" t="inlineStr">
         <ns0:is>
-          <ns0:t>아웃도어 생활용품과 사격 스포츠 액세서리 제공 기업.</ns0:t>
+          <ns0:t>암·감염병 면역치료제를 발굴·개발하고 항체 발현 플랫폼을 제공하는 임상 단계 바이오 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G6">
-        <ns0:v>17.549999237060547</ns0:v>
+        <ns0:v>9.430000305175781</ns0:v>
       </ns0:c>
       <ns0:c r="H6">
-        <ns0:v>3.0534264794411126</ns0:v>
+        <ns0:v>10.421549734171665</ns0:v>
       </ns0:c>
       <ns0:c r="I6">
-        <ns0:v>17.30500030517578</ns0:v>
+        <ns0:v>8.850000381469727</ns0:v>
       </ns0:c>
       <ns0:c r="J6">
-        <ns0:v>1.4157695900848255</ns0:v>
+        <ns0:v>6.553671171816755</ns0:v>
       </ns0:c>
       <ns0:c r="K6">
-        <ns0:v>0.4236343366778149</ns0:v>
+        <ns0:v>3.044905541804711</ns0:v>
       </ns0:c>
       <ns0:c r="L6">
-        <ns0:v>77.62393708899921</ns0:v>
+        <ns0:v>70.26638200302364</ns0:v>
       </ns0:c>
       <ns0:c r="M6">
-        <ns0:v>14.439499998092652</ns0:v>
+        <ns0:v>7.837999939918518</ns0:v>
       </ns0:c>
       <ns0:c r="N6">
-        <ns0:v>13.202200012207031</ns0:v>
+        <ns0:v>7.428999986648559</ns0:v>
       </ns0:c>
       <ns0:c r="O6">
-        <ns0:v>10.425400035381317</ns0:v>
+        <ns0:v>4.493799998760223</ns0:v>
       </ns0:c>
       <ns0:c r="P6" t="inlineStr">
         <ns0:is>
@@ -477,77 +507,77 @@
       </ns0:c>
       <ns0:c r="R6" t="inlineStr">
         <ns0:is>
-          <ns0:t>2027 회계연도 1분기 실적 전망과 실적 발표에서 언급된 강한 매출 성장을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>임상시험 업데이트와 신규 자금 조달 이후 아제너스 주식의 적정가치 평가가 높아졌다는 보도다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S6" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/american-outdoor-brands-inc-aout-050058077.html</ns0:t>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/agenus-agen-stock-fair-value-020946866.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T6" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finviz.com/quote.ashx?t=AOUT</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/AGEN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="7">
       <ns0:c r="A7" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B7" t="inlineStr">
         <ns0:is>
-          <ns0:t>AVT</ns0:t>
+          <ns0:t>AMC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C7" t="inlineStr">
         <ns0:is>
-          <ns0:t>Avnet Inc</ns0:t>
+          <ns0:t>AMC Entertainment Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D7" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Communication Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E7" t="inlineStr">
         <ns0:is>
-          <ns0:t>Electronics &amp; Computer Distribution</ns0:t>
+          <ns0:t>Entertainment</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F7" t="inlineStr">
         <ns0:is>
-          <ns0:t>전자부품·파넬 부문을 통해 전 세계에 반도체·연결 부품·수동 및 전기기계 부품을 유통하는 기업.</ns0:t>
+          <ns0:t>미국과 해외에서 영화관을 소유·운영하거나 지분을 보유하는 영화 상영 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G7">
-        <ns0:v>103.08000183105469</ns0:v>
+        <ns0:v>3.2899999618530273</ns0:v>
       </ns0:c>
       <ns0:c r="H7">
-        <ns0:v>2.1504291846142554</ns0:v>
+        <ns0:v>11.904758429272476</ns0:v>
       </ns0:c>
       <ns0:c r="I7">
-        <ns0:v>102.69999694824219</ns0:v>
+        <ns0:v>3.180000066757202</ns0:v>
       </ns0:c>
       <ns0:c r="J7">
-        <ns0:v>0.3700145025359758</ns0:v>
+        <ns0:v>3.4591161253652913</ns0:v>
       </ns0:c>
       <ns0:c r="K7">
-        <ns0:v>0.9112713466733859</ns0:v>
+        <ns0:v>2.6765690252030154</ns0:v>
       </ns0:c>
       <ns0:c r="L7">
-        <ns0:v>67.41626269872638</ns0:v>
+        <ns0:v>72.7262509751873</ns0:v>
       </ns0:c>
       <ns0:c r="M7">
-        <ns0:v>94.15149993896485</ns0:v>
+        <ns0:v>2.694000017642975</ns0:v>
       </ns0:c>
       <ns0:c r="N7">
-        <ns0:v>92.2543994140625</ns0:v>
+        <ns0:v>2.6056000137329103</ns0:v>
       </ns0:c>
       <ns0:c r="O7">
-        <ns0:v>75.15899978637695</ns0:v>
+        <ns0:v>1.8283500012755394</ns0:v>
       </ns0:c>
       <ns0:c r="P7" t="inlineStr">
         <ns0:is>
@@ -561,81 +591,81 @@
       </ns0:c>
       <ns0:c r="R7" t="inlineStr">
         <ns0:is>
-          <ns0:t>AI 공급망 확대 속 매수 지점 근접 평가, 이익 확대의 세 동력, SMCI와의 투자 매력 비교를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>기업 동향 관련 기사 제목 3건 확인. 주가 상승과의 인과는 미확인입니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S7" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://www.investors.com/news/xmtr-stock-buy-point-avnet-xometry-ai-supply-chains/</ns0:t>
+          <ns0:t>https://247wallst.com/investing/2026/09/28/amc-spikes-13-as-refinancing-rally-extends-cinemark-and-imax-edge-higher/</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T7" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/AVT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/AMC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="8">
       <ns0:c r="A8" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B8" t="inlineStr">
         <ns0:is>
-          <ns0:t>CDNA</ns0:t>
+          <ns0:t>ATKR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C8" t="inlineStr">
         <ns0:is>
-          <ns0:t>Caredx Inc</ns0:t>
+          <ns0:t>Atkore Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D8" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E8" t="inlineStr">
         <ns0:is>
-          <ns0:t>Diagnostics &amp; Research</ns0:t>
+          <ns0:t>Electrical Equipment &amp; Parts</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F8" t="inlineStr">
         <ns0:is>
-          <ns0:t>이식 환자의 치료 결과와 장기 건강 개선을 위한 신장·심장 이식 검사 솔루션 제공 기업.</ns0:t>
+          <ns0:t>미국과 해외에서 전기·기계·안전·인프라 제품 및 솔루션을 제조·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G8">
-        <ns0:v>63.68000030517578</ns0:v>
+        <ns0:v>94.5999984741211</ns0:v>
       </ns0:c>
       <ns0:c r="H8">
-        <ns0:v>3.7640564013287747</ns0:v>
+        <ns0:v>0.0317212428821767</ns0:v>
       </ns0:c>
       <ns0:c r="I8">
-        <ns0:v>63.09000015258789</ns0:v>
+        <ns0:v>94.6500015258789</ns0:v>
       </ns0:c>
       <ns0:c r="J8">
-        <ns0:v>0.9351722161371478</ns0:v>
+        <ns0:v>-0.052829425199896196</ns0:v>
       </ns0:c>
       <ns0:c r="K8">
-        <ns0:v>1.9321999054334642</ns0:v>
+        <ns0:v>2.6473284431878885</ns0:v>
       </ns0:c>
       <ns0:c r="L8">
-        <ns0:v>79.29981082915883</ns0:v>
+        <ns0:v>72.0161227040802</ns0:v>
       </ns0:c>
       <ns0:c r="M8">
-        <ns0:v>52.834000205993654</ns0:v>
+        <ns0:v>94.18950080871582</ns0:v>
       </ns0:c>
       <ns0:c r="N8">
-        <ns0:v>47.554400024414065</ns0:v>
+        <ns0:v>89.9072004699707</ns0:v>
       </ns0:c>
       <ns0:c r="O8">
-        <ns0:v>27.618324937820436</ns0:v>
+        <ns0:v>74.7904501914978</ns0:v>
       </ns0:c>
       <ns0:c r="P8" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q8" t="inlineStr">
@@ -645,34 +675,34 @@
       </ns0:c>
       <ns0:c r="R8" t="inlineStr">
         <ns0:is>
-          <ns0:t>주가 급등과 상승 지속 여부, 애널리스트의 새 목표주가 74달러가 보도됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>AI 데이터센터 분야에서 앳코어가 주목받는 이유와 전기 시스템 업종 내 우수한 2분기 실적이 다뤄졌다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S8" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/caredx-cdna-stock-jumps-13-071800723.html</ns0:t>
+          <ns0:t>https://finance.yahoo.com/technology/ai/articles/why-atkore-belden-flex-stock-181008775.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T8" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CDNA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ATKR/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="9">
       <ns0:c r="A9" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B9" t="inlineStr">
         <ns0:is>
-          <ns0:t>CNET</ns0:t>
+          <ns0:t>BATRA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C9" t="inlineStr">
         <ns0:is>
-          <ns0:t>ZW Data Action Technologies Inc</ns0:t>
+          <ns0:t>Atlanta Braves Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D9" t="inlineStr">
@@ -682,116 +712,124 @@
       </ns0:c>
       <ns0:c r="E9" t="inlineStr">
         <ns0:is>
-          <ns0:t>Advertising Agencies</ns0:t>
+          <ns0:t>Entertainment</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F9" t="inlineStr">
         <ns0:is>
-          <ns0:t>온오프라인 통합 광고와 정밀 마케팅 원스톱 서비스를 운영하는 지주회사.</ns0:t>
+          <ns0:t>자회사를 통해 MLB 애틀랜타 브레이브스 구단과 구장을 소유·운영하며 복합개발 사업을 영위.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G9">
-        <ns0:v>1.850000023841858</ns0:v>
+        <ns0:v>59.61000061035156</ns0:v>
       </ns0:c>
       <ns0:c r="H9">
-        <ns0:v>35.036497620643495</ns0:v>
+        <ns0:v>0.9825543673534831</ns0:v>
       </ns0:c>
       <ns0:c r="I9">
-        <ns0:v>2.5999999046325684</ns0:v>
+        <ns0:v>59.20000076293945</ns0:v>
       </ns0:c>
       <ns0:c r="J9">
-        <ns0:v>-28.846150319251663</ns0:v>
+        <ns0:v>0.6925673008922884</ns0:v>
+      </ns0:c>
+      <ns0:c r="K9">
+        <ns0:v>0.8367511944138184</ns0:v>
       </ns0:c>
       <ns0:c r="L9">
-        <ns0:v>74.31481219388311</ns0:v>
+        <ns0:v>70.4415132890224</ns0:v>
       </ns0:c>
       <ns0:c r="M9">
-        <ns0:v>1.3279999852180482</ns0:v>
+        <ns0:v>56.406249618530275</ns0:v>
       </ns0:c>
       <ns0:c r="N9">
-        <ns0:v>1.317599993944168</ns0:v>
+        <ns0:v>55.826899719238284</ns0:v>
       </ns0:c>
       <ns0:c r="O9">
-        <ns0:v>1.0263999977707863</ns0:v>
+        <ns0:v>51.050174922943114</ns0:v>
       </ns0:c>
       <ns0:c r="P9" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q9" t="inlineStr">
         <ns0:is>
-          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+          <ns0:t>보도된 해석</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R9" t="inlineStr">
         <ns0:is>
-          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+          <ns0:t>애틀랜타 브레이브스 주주가 가치 실현을 위한 매각과 구단 인수자 물색을 촉구했다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://www.cfo.com/news/why-an-atlanta-braves-shareholder-breach-inlet-capital-management-is-pushing-for-a-sale/830641/</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T9" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finviz.com/quote.ashx?t=CNET</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/BATRA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="10">
       <ns0:c r="A10" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B10" t="inlineStr">
         <ns0:is>
-          <ns0:t>CNXN</ns0:t>
+          <ns0:t>BATRK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C10" t="inlineStr">
         <ns0:is>
-          <ns0:t>PC Connection Inc</ns0:t>
+          <ns0:t>Atlanta Braves Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D10" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Communication Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E10" t="inlineStr">
         <ns0:is>
-          <ns0:t>Electronics &amp; Computer Distribution</ns0:t>
+          <ns0:t>Entertainment</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F10" t="inlineStr">
         <ns0:is>
-          <ns0:t>대기업·일반 기업·공공 부문에 컴퓨터 시스템·데이터센터 등 IT 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>자회사를 통해 MLB 애틀랜타 브레이브스 구단과 구장을 소유·운영하며 복합개발 사업을 영위.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G10">
-        <ns0:v>89.31999969482422</ns0:v>
+        <ns0:v>54.290000915527344</ns0:v>
       </ns0:c>
       <ns0:c r="H10">
-        <ns0:v>0.3370063615714347</ns0:v>
+        <ns0:v>0.05529412997093974</ns0:v>
       </ns0:c>
       <ns0:c r="I10">
-        <ns0:v>89.62999725341797</ns0:v>
+        <ns0:v>54.459999084472656</ns0:v>
       </ns0:c>
       <ns0:c r="J10">
-        <ns0:v>-0.3458636261220338</ns0:v>
+        <ns0:v>-0.31215235365984473</ns0:v>
       </ns0:c>
       <ns0:c r="K10">
-        <ns0:v>0.614054054054054</ns0:v>
+        <ns0:v>1.053047233227975</ns0:v>
       </ns0:c>
       <ns0:c r="L10">
-        <ns0:v>70.67524063679258</ns0:v>
+        <ns0:v>67.7011601315167</ns0:v>
       </ns0:c>
       <ns0:c r="M10">
-        <ns0:v>84.70199966430664</ns0:v>
+        <ns0:v>51.207749938964845</ns0:v>
       </ns0:c>
       <ns0:c r="N10">
-        <ns0:v>82.63219985961913</ns0:v>
+        <ns0:v>51.28290031433105</ns0:v>
       </ns0:c>
       <ns0:c r="O10">
-        <ns0:v>68.51559993743896</ns0:v>
+        <ns0:v>46.800375099182126</ns0:v>
       </ns0:c>
       <ns0:c r="P10" t="inlineStr">
         <ns0:is>
@@ -805,34 +843,34 @@
       </ns0:c>
       <ns0:c r="R10" t="inlineStr">
         <ns0:is>
-          <ns0:t>퍼트리샤 갤럽 회장의 14,284주 매도와 올해 유통·도매 업종 대비 주가 성과를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>애틀랜타 브레이브스 주주가 가치 실현을 위한 매각과 구단 인수자 물색을 촉구했다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S10" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://www.fool.com/coverage/filings/2026/09/23/pc-connection-chairman-patricia-gallup-sells-14-284-shares/</ns0:t>
+          <ns0:t>https://www.cfo.com/news/why-an-atlanta-braves-shareholder-breach-inlet-capital-management-is-pushing-for-a-sale/830641/</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T10" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CNXN/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/BATRK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="11">
       <ns0:c r="A11" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B11" t="inlineStr">
         <ns0:is>
-          <ns0:t>CYPH</ns0:t>
+          <ns0:t>BDSX</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C11" t="inlineStr">
         <ns0:is>
-          <ns0:t>Cypherpunk Technologies Inc</ns0:t>
+          <ns0:t>Biodesix Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D11" t="inlineStr">
@@ -842,40 +880,40 @@
       </ns0:c>
       <ns0:c r="E11" t="inlineStr">
         <ns0:is>
-          <ns0:t>Biotechnology</ns0:t>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F11" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 프라이버시 강화 기술을 개발·투자·인수하고 지캐시 중심 디지털 자산 전략을 추진하는 기업.</ns0:t>
+          <ns0:t>폐암 위험 평가를 위한 혈액 기반 폐결절 검사 등 진단 솔루션을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G11">
-        <ns0:v>4.119999885559082</ns0:v>
+        <ns0:v>30.420000076293945</ns0:v>
       </ns0:c>
       <ns0:c r="H11">
-        <ns0:v>0.9803912402207571</ns0:v>
+        <ns0:v>4.536081366049638</ns0:v>
       </ns0:c>
       <ns0:c r="I11">
-        <ns0:v>4.139999866485596</ns0:v>
+        <ns0:v>31.350000381469727</ns0:v>
       </ns0:c>
       <ns0:c r="J11">
-        <ns0:v>-0.4830913423070071</ns0:v>
+        <ns0:v>-2.9665081143842142</ns0:v>
       </ns0:c>
       <ns0:c r="K11">
-        <ns0:v>1.1282711540469825</ns0:v>
+        <ns0:v>2.6174168797953965</ns0:v>
       </ns0:c>
       <ns0:c r="L11">
-        <ns0:v>76.32780306551894</ns0:v>
+        <ns0:v>64.4240859960014</ns0:v>
       </ns0:c>
       <ns0:c r="M11">
-        <ns0:v>2.7005000054836272</ns0:v>
+        <ns0:v>27.720250034332274</ns0:v>
       </ns0:c>
       <ns0:c r="N11">
-        <ns0:v>1.599020003080368</ns0:v>
+        <ns0:v>25.254799995422363</ns0:v>
       </ns0:c>
       <ns0:c r="O11">
-        <ns0:v>1.0564350017905235</ns0:v>
+        <ns0:v>16.511275005340575</ns0:v>
       </ns0:c>
       <ns0:c r="P11" t="inlineStr">
         <ns0:is>
@@ -884,156 +922,166 @@
       </ns0:c>
       <ns0:c r="Q11" t="inlineStr">
         <ns0:is>
-          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+          <ns0:t>보도된 해석</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R11" t="inlineStr">
         <ns0:is>
-          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+          <ns0:t>종양 정보 활용·비활용 방식으로 MRD 검사를 확대하고 바이오래드·써모피셔와 모니터링 프로그램을 추진했다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/healthcare/articles/biodesix-expands-mrd-testing-tumor-140300637.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T11" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CYPH/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/BDSX/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="12">
       <ns0:c r="A12" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B12" t="inlineStr">
         <ns0:is>
-          <ns0:t>FBLA</ns0:t>
+          <ns0:t>BIIB</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C12" t="inlineStr">
         <ns0:is>
-          <ns0:t>FB Bancorp Inc</ns0:t>
+          <ns0:t>Biogen Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D12" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E12" t="inlineStr">
         <ns0:is>
-          <ns0:t>Banks - Regional</ns0:t>
+          <ns0:t>Drug Manufacturers - General</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F12" t="inlineStr">
         <ns0:is>
-          <ns0:t>개인·기업·지역사회에 예금 등 은행 상품과 서비스를 제공하는 피델리티 은행의 지주회사.</ns0:t>
+          <ns0:t>다발성경화증, 척수성 근위축증, 프리드라이히 운동실조증 등의 치료제를 발굴·개발·제조·공급.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G12">
-        <ns0:v>16.469999313354492</ns0:v>
+        <ns0:v>228.69000244140625</ns0:v>
       </ns0:c>
       <ns0:c r="H12">
-        <ns0:v>1.2915072663999494</ns0:v>
+        <ns0:v>0.4789087472145681</ns0:v>
       </ns0:c>
       <ns0:c r="I12">
-        <ns0:v>16.389999389648438</ns0:v>
+        <ns0:v>229.19000244140625</ns0:v>
       </ns0:c>
       <ns0:c r="J12">
-        <ns0:v>0.48810205421105923</ns0:v>
+        <ns0:v>-0.21815960324352845</ns0:v>
       </ns0:c>
       <ns0:c r="K12">
-        <ns0:v>0.6699306405548756</ns0:v>
+        <ns0:v>1.4025676339333375</ns0:v>
       </ns0:c>
       <ns0:c r="L12">
-        <ns0:v>68.11235557900213</ns0:v>
+        <ns0:v>63.86767526487981</ns0:v>
       </ns0:c>
       <ns0:c r="M12">
-        <ns0:v>16.005249977111816</ns0:v>
+        <ns0:v>219.76049880981446</ns0:v>
       </ns0:c>
       <ns0:c r="N12">
-        <ns0:v>15.769099998474122</ns0:v>
+        <ns0:v>213.41139953613282</ns0:v>
       </ns0:c>
       <ns0:c r="O12">
-        <ns0:v>14.236925020217896</ns0:v>
+        <ns0:v>194.21255027770997</ns0:v>
       </ns0:c>
       <ns0:c r="P12" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q12" t="inlineStr">
         <ns0:is>
-          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+          <ns0:t>보도된 해석</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R12" t="inlineStr">
         <ns0:is>
-          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+          <ns0:t>성장 제품군과 기존 다발성경화증 약물의 실적 비교, 2분기 실적, 가정용 레켐비 펜·신장질환 데이터가 다뤄졌다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/healthcare/articles/biogens-growth-portfolio-maintain-lead-134100370.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T12" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/FBLA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/BIIB/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="13">
       <ns0:c r="A13" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B13" t="inlineStr">
         <ns0:is>
-          <ns0:t>FLXS</ns0:t>
+          <ns0:t>BLFS</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C13" t="inlineStr">
         <ns0:is>
-          <ns0:t>Flexsteel Industries Inc</ns0:t>
+          <ns0:t>Biolife Solutions Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D13" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E13" t="inlineStr">
         <ns0:is>
-          <ns0:t>Furnishings, Fixtures &amp; Appliances</ns0:t>
+          <ns0:t>Medical Instruments &amp; Supplies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F13" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 소파·의자·침실·식탁 가구 등 주거용 가구를 제조·유통·수입·판매하는 기업.</ns0:t>
+          <ns0:t>세포·유전자 치료 산업용 바이오 생산 제품과 서비스를 개발·제조·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G13">
-        <ns0:v>89.37000274658203</ns0:v>
+        <ns0:v>39.150001525878906</ns0:v>
       </ns0:c>
       <ns0:c r="H13">
-        <ns0:v>1.1316057133863522</ns0:v>
+        <ns0:v>1.7147306277758512</ns0:v>
       </ns0:c>
       <ns0:c r="I13">
-        <ns0:v>88.48999786376953</ns0:v>
+        <ns0:v>38.88999938964844</ns0:v>
       </ns0:c>
       <ns0:c r="J13">
-        <ns0:v>0.9944681930801558</ns0:v>
+        <ns0:v>0.6685578305760442</ns0:v>
       </ns0:c>
       <ns0:c r="K13">
-        <ns0:v>1.3992468042221398</ns0:v>
+        <ns0:v>1.384801016088061</ns0:v>
       </ns0:c>
       <ns0:c r="L13">
-        <ns0:v>72.0103378205649</ns0:v>
+        <ns0:v>71.9441288779734</ns0:v>
       </ns0:c>
       <ns0:c r="M13">
-        <ns0:v>82.44100151062011</ns0:v>
+        <ns0:v>36.50500011444092</ns0:v>
       </ns0:c>
       <ns0:c r="N13">
-        <ns0:v>78.87920028686523</ns0:v>
+        <ns0:v>34.883600120544436</ns0:v>
       </ns0:c>
       <ns0:c r="O13">
-        <ns0:v>58.46914999008179</ns0:v>
+        <ns0:v>26.28395004272461</ns0:v>
       </ns0:c>
       <ns0:c r="P13" t="inlineStr">
         <ns0:is>
@@ -1047,77 +1095,77 @@
       </ns0:c>
       <ns0:c r="R13" t="inlineStr">
         <ns0:is>
-          <ns0:t>올해 경기소비재 종목 대비 플렉스스틸의 주가 성과를 비교하는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>다이아몬드힐이 바이오라이프 솔루션스의 높은 전환 비용에 주목해 투자했다는 보도다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S13" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/consumer-discretionary-stocks-lagging-flexsteel-124002018.html</ns0:t>
+          <ns0:t>https://finance.yahoo.com/healthcare/articles/diamond-hill-bets-biolife-solutions-143150003.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T13" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/FLXS/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/BLFS/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="14">
       <ns0:c r="A14" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B14" t="inlineStr">
         <ns0:is>
-          <ns0:t>FRHC</ns0:t>
+          <ns0:t>CDNA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C14" t="inlineStr">
         <ns0:is>
-          <ns0:t>Freedom Holding Corp</ns0:t>
+          <ns0:t>Caredx Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D14" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E14" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial Conglomerates</ns0:t>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F14" t="inlineStr">
         <ns0:is>
-          <ns0:t>증권 중개와 금융 서비스를 제공하는 투자회사.</ns0:t>
+          <ns0:t>이식 환자의 치료 결과와 장기 건강 개선을 위한 신장·심장 이식 검사 솔루션 등을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G14">
-        <ns0:v>172.0800018310547</ns0:v>
+        <ns0:v>64.5999984741211</ns0:v>
       </ns0:c>
       <ns0:c r="H14">
-        <ns0:v>-2.43238272092845</ns0:v>
+        <ns0:v>1.4447207357669134</ns0:v>
       </ns0:c>
       <ns0:c r="I14">
-        <ns0:v>177.5</ns0:v>
+        <ns0:v>65.19000244140625</ns0:v>
       </ns0:c>
       <ns0:c r="J14">
-        <ns0:v>-3.053520095180462</ns0:v>
+        <ns0:v>-0.9050528381487011</ns0:v>
       </ns0:c>
       <ns0:c r="K14">
-        <ns0:v>1.0334690185436455</ns0:v>
+        <ns0:v>0.8505367757264863</ns0:v>
       </ns0:c>
       <ns0:c r="L14">
-        <ns0:v>57.30277041476822</ns0:v>
+        <ns0:v>80.21957113564521</ns0:v>
       </ns0:c>
       <ns0:c r="M14">
-        <ns0:v>167.90299911499022</ns0:v>
+        <ns0:v>53.57450008392334</ns0:v>
       </ns0:c>
       <ns0:c r="N14">
-        <ns0:v>160.60280029296874</ns0:v>
+        <ns0:v>48.05180000305176</ns0:v>
       </ns0:c>
       <ns0:c r="O14">
-        <ns0:v>143.52400005340576</ns0:v>
+        <ns0:v>27.84507493019104</ns0:v>
       </ns0:c>
       <ns0:c r="P14" t="inlineStr">
         <ns0:is>
@@ -1126,318 +1174,321 @@
       </ns0:c>
       <ns0:c r="Q14" t="inlineStr">
         <ns0:is>
-          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+          <ns0:t>보도된 해석</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R14" t="inlineStr">
         <ns0:is>
-          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+          <ns0:t>주가 급등과 상승 지속 여부, 애널리스트의 새 목표주가 74달러가 보도됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/caredx-cdna-stock-jumps-13-071800723.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T14" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finviz.com/quote.ashx?t=FRHC</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CDNA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="15">
       <ns0:c r="A15" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B15" t="inlineStr">
         <ns0:is>
-          <ns0:t>FSEA</ns0:t>
+          <ns0:t>CNK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C15" t="inlineStr">
         <ns0:is>
-          <ns0:t>First Seacoast Bancorp Inc</ns0:t>
+          <ns0:t>Cinemark Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D15" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Communication Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E15" t="inlineStr">
         <ns0:is>
-          <ns0:t>Banks - Regional</ns0:t>
+          <ns0:t>Entertainment</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F15" t="inlineStr">
         <ns0:is>
-          <ns0:t>개인·기업에 예금·은행·자산관리 서비스를 제공하는 퍼스트 시코스트 은행의 지주회사.</ns0:t>
+          <ns0:t>자회사와 함께 미국 및 라틴아메리카에서 영화관을 운영하는 영화 상영 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G15">
-        <ns0:v>17.239999771118164</ns0:v>
+        <ns0:v>38.380001068115234</ns0:v>
       </ns0:c>
       <ns0:c r="H15">
-        <ns0:v>0.349240191365463</ns0:v>
+        <ns0:v>1.6150399866520893</ns0:v>
       </ns0:c>
       <ns0:c r="I15">
-        <ns0:v>17.209999084472656</ns0:v>
+        <ns0:v>38.97999954223633</ns0:v>
       </ns0:c>
       <ns0:c r="J15">
-        <ns0:v>0.17432125648730867</ns0:v>
+        <ns0:v>-1.539247001455124</ns0:v>
+      </ns0:c>
+      <ns0:c r="K15">
+        <ns0:v>1.1149760159570008</ns0:v>
       </ns0:c>
       <ns0:c r="L15">
-        <ns0:v>71.12660333038355</ns0:v>
+        <ns0:v>66.4260720946335</ns0:v>
       </ns0:c>
       <ns0:c r="M15">
-        <ns0:v>17.181650161743164</ns0:v>
+        <ns0:v>35.53550033569336</ns0:v>
       </ns0:c>
       <ns0:c r="N15">
-        <ns0:v>17.089760131835938</ns0:v>
+        <ns0:v>35.88600025177002</ns0:v>
       </ns0:c>
       <ns0:c r="O15">
-        <ns0:v>14.798694977760315</ns0:v>
+        <ns0:v>29.533450078964233</ns0:v>
       </ns0:c>
       <ns0:c r="P15" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q15" t="inlineStr">
         <ns0:is>
-          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+          <ns0:t>보도된 해석</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R15" t="inlineStr">
         <ns0:is>
-          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+          <ns0:t>AMC 주가가 13% 상승한 가운데 시네마크와 아이맥스도 소폭 올랐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://247wallst.com/investing/2026/09/28/amc-spikes-13-as-refinancing-rally-extends-cinemark-and-imax-edge-higher/</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T15" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/FSEA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CNK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="16">
       <ns0:c r="A16" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B16" t="inlineStr">
         <ns0:is>
-          <ns0:t>GRAL</ns0:t>
+          <ns0:t>COLA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C16" t="inlineStr">
         <ns0:is>
-          <ns0:t>GRAIL Inc</ns0:t>
+          <ns0:t>Columbus Acquisition Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D16" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E16" t="inlineStr">
         <ns0:is>
-          <ns0:t>Diagnostics &amp; Research</ns0:t>
+          <ns0:t>Shell Companies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F16" t="inlineStr">
         <ns0:is>
-          <ns0:t>다중암 조기 발견 검사·서비스를 제공하고 50세 초과 무증상자용 갈레리 암 선별검사를 판매하는 기업.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병, 주식 교환, 자산 인수, 자본 재편 등 기업결합을 추진.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G16">
-        <ns0:v>126.88999938964844</ns0:v>
+        <ns0:v>10.637800216674805</ns0:v>
       </ns0:c>
       <ns0:c r="H16">
-        <ns0:v>1.3417461204854542</ns0:v>
+        <ns0:v>1.7971331180615113</ns0:v>
       </ns0:c>
       <ns0:c r="I16">
-        <ns0:v>126.80999755859375</ns0:v>
+        <ns0:v>12.84000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="J16">
-        <ns0:v>0.0630879525233885</ns0:v>
+        <ns0:v>-17.15108963973988</ns0:v>
       </ns0:c>
       <ns0:c r="L16">
-        <ns0:v>87.1102910918771</ns0:v>
+        <ns0:v>50.66089826432414</ns0:v>
       </ns0:c>
       <ns0:c r="M16">
-        <ns0:v>87.77049942016602</ns0:v>
+        <ns0:v>10.509639978408813</ns0:v>
       </ns0:c>
       <ns0:c r="N16">
-        <ns0:v>78.23519966125488</ns0:v>
+        <ns0:v>10.620756015777587</ns0:v>
       </ns0:c>
       <ns0:c r="O16">
-        <ns0:v>72.60579992294312</ns0:v>
+        <ns0:v>10.576838974952699</ns0:v>
       </ns0:c>
       <ns0:c r="P16" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q16" t="inlineStr">
         <ns0:is>
-          <ns0:t>보도된 해석</ns0:t>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R16" t="inlineStr">
         <ns0:is>
-          <ns0:t>주간 주가 55% 급등, 암 발견 혈액검사에 대한 FDA 자문위원 지지와 고평가 여부를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="S16" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://www.fool.com/investing/2026/09/25/heres-why-grail-stock-surged-55-this-week/</ns0:t>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T16" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/GRAL/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/COLA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="17">
       <ns0:c r="A17" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B17" t="inlineStr">
         <ns0:is>
-          <ns0:t>HBB</ns0:t>
+          <ns0:t>DMAA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C17" t="inlineStr">
         <ns0:is>
-          <ns0:t>Hamilton Beach Brands Holding Co</ns0:t>
+          <ns0:t>Drugs Made In America Acquisition Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D17" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E17" t="inlineStr">
         <ns0:is>
-          <ns0:t>Furnishings, Fixtures &amp; Appliances</ns0:t>
+          <ns0:t>Shell Companies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F17" t="inlineStr">
         <ns0:is>
-          <ns0:t>브랜드 소형 가전과 특수 가정용 기기를 설계·마케팅·유통하는 기업.</ns0:t>
+          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G17">
-        <ns0:v>37.2599983215332</ns0:v>
+        <ns0:v>10.880000114440918</ns0:v>
       </ns0:c>
       <ns0:c r="H17">
-        <ns0:v>-0.1340205036647557</ns0:v>
+        <ns0:v>0.36900333293332643</ns0:v>
       </ns0:c>
       <ns0:c r="I17">
-        <ns0:v>37.4900016784668</ns0:v>
+        <ns0:v>10.854999542236328</ns0:v>
       </ns0:c>
       <ns0:c r="J17">
-        <ns0:v>-0.613505859258745</ns0:v>
+        <ns0:v>0.2303138946004868</ns0:v>
       </ns0:c>
       <ns0:c r="K17">
-        <ns0:v>0.7961282516636419</ns0:v>
+        <ns0:v>0.007169949834821975</ns0:v>
       </ns0:c>
       <ns0:c r="L17">
-        <ns0:v>78.31067831420646</ns0:v>
+        <ns0:v>84.52732616037332</ns0:v>
       </ns0:c>
       <ns0:c r="M17">
-        <ns0:v>32.03000011444092</ns0:v>
+        <ns0:v>10.813750171661377</ns0:v>
       </ns0:c>
       <ns0:c r="N17">
-        <ns0:v>29.699799957275392</ns0:v>
+        <ns0:v>10.756100082397461</ns0:v>
       </ns0:c>
       <ns0:c r="O17">
-        <ns0:v>21.689400019645692</ns0:v>
+        <ns0:v>10.571860027313232</ns0:v>
       </ns0:c>
       <ns0:c r="P17" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q17" t="inlineStr">
         <ns0:is>
-          <ns0:t>보도된 해석</ns0:t>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R17" t="inlineStr">
         <ns0:is>
-          <ns0:t>핵심 사업 회복, 고급화와 인접 분야 성장을 다룬 신규 분석 보고서 소개. (기사 제목 요약·주가 인과 미확정)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="S17" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://finance.yahoo.com/small-business/articles/hamilton-beach-brand-core-recovery-210954378.html</ns0:t>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T17" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finviz.com/quote.ashx?t=HBB</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/DMAA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="18">
       <ns0:c r="A18" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B18" t="inlineStr">
         <ns0:is>
-          <ns0:t>HLP</ns0:t>
+          <ns0:t>FLXS</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C18" t="inlineStr">
         <ns0:is>
-          <ns0:t>Hongli Group Inc</ns0:t>
+          <ns0:t>Flexsteel Industries Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D18" t="inlineStr">
         <ns0:is>
-          <ns0:t>Basic Materials</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E18" t="inlineStr">
         <ns0:is>
-          <ns0:t>Steel</ns0:t>
+          <ns0:t>Furnishings, Fixtures &amp; Appliances</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F18" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국과 해외에서 다양한 맞춤형 냉간 성형 강재를 제조·판매한다.</ns0:t>
+          <ns0:t>미국에서 소파, 의자, 침실·식당 가구 등 주거용 가구를 제조·유통·수입·판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G18">
-        <ns0:v>2.2100000381469727</ns0:v>
+        <ns0:v>87.52999877929688</ns0:v>
       </ns0:c>
       <ns0:c r="H18">
-        <ns0:v>0.4545450112051208</ns0:v>
+        <ns0:v>-2.058860815415531</ns0:v>
       </ns0:c>
       <ns0:c r="I18">
-        <ns0:v>2.2799999713897705</ns0:v>
+        <ns0:v>90.0</ns0:v>
       </ns0:c>
       <ns0:c r="J18">
-        <ns0:v>-3.0701725491746212</ns0:v>
+        <ns0:v>-2.744445800781248</ns0:v>
       </ns0:c>
       <ns0:c r="K18">
-        <ns0:v>1.4768460575719649</ns0:v>
+        <ns0:v>0.9353096383672203</ns0:v>
       </ns0:c>
       <ns0:c r="L18">
-        <ns0:v>79.58984529123182</ns0:v>
+        <ns0:v>65.11493121052999</ns0:v>
       </ns0:c>
       <ns0:c r="M18">
-        <ns0:v>1.6622500002384186</ns0:v>
+        <ns0:v>82.72750129699708</ns0:v>
       </ns0:c>
       <ns0:c r="N18">
-        <ns0:v>1.39889999628067</ns0:v>
+        <ns0:v>79.1702001953125</ns0:v>
       </ns0:c>
       <ns0:c r="O18">
-        <ns0:v>1.0203249956667424</ns0:v>
+        <ns0:v>58.70494998931885</ns0:v>
       </ns0:c>
       <ns0:c r="P18" t="inlineStr">
         <ns0:is>
@@ -1446,77 +1497,79 @@
       </ns0:c>
       <ns0:c r="Q18" t="inlineStr">
         <ns0:is>
-          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+          <ns0:t>보도된 해석</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R18" t="inlineStr">
         <ns0:is>
-          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+          <ns0:t>신고가 경신 후 추가 상승 여력과 올해 경기소비재 업종 대비 주가 성과를 점검하는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/flexsteel-industries-inc-flxs-hits-121501829.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T18" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/HLP/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/FLXS/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="19">
       <ns0:c r="A19" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B19" t="inlineStr">
         <ns0:is>
-          <ns0:t>HQI</ns0:t>
+          <ns0:t>FSEA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C19" t="inlineStr">
         <ns0:is>
-          <ns0:t>HireQuest Inc</ns0:t>
+          <ns0:t>First Seacoast Bancorp Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D19" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E19" t="inlineStr">
         <ns0:is>
-          <ns0:t>Staffing &amp; Employment Services</ns0:t>
+          <ns0:t>Banks - Regional</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F19" t="inlineStr">
         <ns0:is>
-          <ns0:t>인력 공급 서비스를 제공한다.</ns0:t>
+          <ns0:t>개인과 기업에 예금·은행·자산관리 서비스를 제공하는 퍼스트 시코스트 은행의 지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G19">
-        <ns0:v>20.040000915527344</ns0:v>
+        <ns0:v>17.25</ns0:v>
       </ns0:c>
       <ns0:c r="H19">
-        <ns0:v>6.880004882812507</ns0:v>
+        <ns0:v>0.0580059687621981</ns0:v>
       </ns0:c>
       <ns0:c r="I19">
-        <ns0:v>19.010000228881836</ns0:v>
+        <ns0:v>17.239999771118164</ns0:v>
       </ns0:c>
       <ns0:c r="J19">
-        <ns0:v>5.4182044936571305</ns0:v>
-      </ns0:c>
-      <ns0:c r="K19">
-        <ns0:v>5.929465301478953</ns0:v>
+        <ns0:v>0.0580059687621981</ns0:v>
       </ns0:c>
       <ns0:c r="L19">
-        <ns0:v>76.14050493519318</ns0:v>
+        <ns0:v>72.40475799962326</ns0:v>
       </ns0:c>
       <ns0:c r="M19">
-        <ns0:v>16.861499881744386</ns0:v>
+        <ns0:v>17.184950160980225</ns0:v>
       </ns0:c>
       <ns0:c r="N19">
-        <ns0:v>15.602599925994873</ns0:v>
+        <ns0:v>17.096960144042967</ns0:v>
       </ns0:c>
       <ns0:c r="O19">
-        <ns0:v>12.330849959850312</ns0:v>
+        <ns0:v>14.822844977378844</ns0:v>
       </ns0:c>
       <ns0:c r="P19" t="inlineStr">
         <ns0:is>
@@ -1535,71 +1588,71 @@
       </ns0:c>
       <ns0:c r="T19" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finviz.com/quote.ashx?t=HQI</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/FSEA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="20">
       <ns0:c r="A20" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B20" t="inlineStr">
         <ns0:is>
-          <ns0:t>IBEX</ns0:t>
+          <ns0:t>GIC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C20" t="inlineStr">
         <ns0:is>
-          <ns0:t>IBEX Ltd</ns0:t>
+          <ns0:t>Global Industrial Co</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D20" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E20" t="inlineStr">
         <ns0:is>
-          <ns0:t>Information Technology Services</ns0:t>
+          <ns0:t>Industrial Distribution</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F20" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술 기반 고객 생애주기 경험 솔루션을 제공하는 업무 프로세스 아웃소싱 기업이다.</ns0:t>
+          <ns0:t>미국과 캐나다에서 보관·선반, 안전·보안 등 산업용 및 유지보수·수리·운영 제품을 유통한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G20">
-        <ns0:v>44.529998779296875</ns0:v>
+        <ns0:v>42.31999969482422</ns0:v>
       </ns0:c>
       <ns0:c r="H20">
-        <ns0:v>3.0309984303430237</ns0:v>
+        <ns0:v>1.9759028790945043</ns0:v>
       </ns0:c>
       <ns0:c r="I20">
-        <ns0:v>43.36000061035156</ns0:v>
+        <ns0:v>42.400001525878906</ns0:v>
       </ns0:c>
       <ns0:c r="J20">
-        <ns0:v>2.698335222499959</ns0:v>
+        <ns0:v>-0.18868355701793238</ns0:v>
       </ns0:c>
       <ns0:c r="K20">
-        <ns0:v>1.2209933405697186</ns0:v>
+        <ns0:v>1.2807647180619781</ns0:v>
       </ns0:c>
       <ns0:c r="L20">
-        <ns0:v>75.84561878827314</ns0:v>
+        <ns0:v>72.05921403434327</ns0:v>
       </ns0:c>
       <ns0:c r="M20">
-        <ns0:v>39.928999710083005</ns0:v>
+        <ns0:v>40.0854995727539</ns0:v>
       </ns0:c>
       <ns0:c r="N20">
-        <ns0:v>37.41349983215332</ns0:v>
+        <ns0:v>38.680199737548826</ns0:v>
       </ns0:c>
       <ns0:c r="O20">
-        <ns0:v>33.32537502288818</ns0:v>
+        <ns0:v>33.345349884033205</ns0:v>
       </ns0:c>
       <ns0:c r="P20" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q20" t="inlineStr">
@@ -1609,81 +1662,81 @@
       </ns0:c>
       <ns0:c r="R20" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026년 4분기 실적 발표에서 사상 최대 매출과 AI 기반 성장세가 부각됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>컨퍼런스 참석 이후 기업가치의 주가 반영 여부와 투자 회피 사유를 검토하는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S20" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/ibex-ltd-ibex-q4-2026-070056480.html</ns0:t>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/global-industrial-gic-fully-priced-001121519.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T20" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finviz.com/quote.ashx?t=IBEX</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/GIC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="21">
       <ns0:c r="A21" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B21" t="inlineStr">
         <ns0:is>
-          <ns0:t>IMAX</ns0:t>
+          <ns0:t>GMAB</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C21" t="inlineStr">
         <ns0:is>
-          <ns0:t>Imax Corp</ns0:t>
+          <ns0:t>Genmab ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D21" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Services</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E21" t="inlineStr">
         <ns0:is>
-          <ns0:t>Entertainment</ns0:t>
+          <ns0:t>Biotechnology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F21" t="inlineStr">
         <ns0:is>
-          <ns0:t>콘텐츠 솔루션과 기술 제품으로 전 세계 엔터테인먼트·이벤트 기술 플랫폼을 운영한다.</ns0:t>
+          <ns0:t>덴마크 바이오기업으로 암 등 질환 치료용 항체 의약품을 개발하며 EPKINLY·TEPKINLY를 판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G21">
-        <ns0:v>56.04999923706055</ns0:v>
+        <ns0:v>35.36000061035156</ns0:v>
       </ns0:c>
       <ns0:c r="H21">
-        <ns0:v>1.613486932760022</ns0:v>
+        <ns0:v>0.11325287619752267</ns0:v>
       </ns0:c>
       <ns0:c r="I21">
-        <ns0:v>55.56999969482422</ns0:v>
+        <ns0:v>35.65999984741211</ns0:v>
       </ns0:c>
       <ns0:c r="J21">
-        <ns0:v>0.8637745993744117</ns0:v>
+        <ns0:v>-0.8412766078077172</ns0:v>
       </ns0:c>
       <ns0:c r="K21">
-        <ns0:v>1.144834436724647</ns0:v>
+        <ns0:v>1.392098433335824</ns0:v>
       </ns0:c>
       <ns0:c r="L21">
-        <ns0:v>66.18047681710634</ns0:v>
+        <ns0:v>65.98848894978688</ns0:v>
       </ns0:c>
       <ns0:c r="M21">
-        <ns0:v>52.532999992370605</ns0:v>
+        <ns0:v>34.02950038909912</ns0:v>
       </ns0:c>
       <ns0:c r="N21">
-        <ns0:v>50.307799911499025</ns0:v>
+        <ns0:v>32.14550022125244</ns0:v>
       </ns0:c>
       <ns0:c r="O21">
-        <ns0:v>40.93200012207031</ns0:v>
+        <ns0:v>29.555325031280518</ns0:v>
       </ns0:c>
       <ns0:c r="P21" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q21" t="inlineStr">
@@ -1693,77 +1746,74 @@
       </ns0:c>
       <ns0:c r="R21" t="inlineStr">
         <ns0:is>
-          <ns0:t>모건스탠리는 추가 상승 가능성을 제시했고, 영화 ‘오디세이’의 관람 경험 변화와 연초 이후 업종 대비 성과가 조명됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>기업 동향 관련 기사 제목 2건 확인. 주가 상승과의 인과는 미확인입니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S21" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://stocktwits.com/news-articles/markets/equity/imax-stock-rally-may-be-just-the-start-morgan-stanley-says-why-the-odyssey-is-reshaping-the-moviegoing-experience/cZMJI4BRB9n</ns0:t>
+          <ns0:t>https://www.marketbeat.com/instant-alerts/event-genmab-eyes-three-pivotal-phase-iii-cancer-readouts-in-q4-2026-09-26/</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T21" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/IMAX/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/GMAB/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="22">
       <ns0:c r="A22" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B22" t="inlineStr">
         <ns0:is>
-          <ns0:t>IOSP</ns0:t>
+          <ns0:t>GRAL</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C22" t="inlineStr">
         <ns0:is>
-          <ns0:t>Innospec Inc</ns0:t>
+          <ns0:t>GRAIL Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D22" t="inlineStr">
         <ns0:is>
-          <ns0:t>Basic Materials</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E22" t="inlineStr">
         <ns0:is>
-          <ns0:t>Specialty Chemicals</ns0:t>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F22" t="inlineStr">
         <ns0:is>
-          <ns0:t>특수화학 제품을 개발·제조·혼합·판매하며 기능성 화학, 연료 특수제품, 유전서비스 사업을 한다.</ns0:t>
+          <ns0:t>다중암 조기 발견 검사·서비스를 제공하며, 50세 초과 무증상자를 위한 갈레리 암 선별검사를 판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G22">
-        <ns0:v>98.72000122070312</ns0:v>
+        <ns0:v>132.6300048828125</ns0:v>
       </ns0:c>
       <ns0:c r="H22">
-        <ns0:v>1.909774359107641</ns0:v>
+        <ns0:v>4.523607471647861</ns0:v>
       </ns0:c>
       <ns0:c r="I22">
-        <ns0:v>98.0</ns0:v>
+        <ns0:v>127.66999816894531</ns0:v>
       </ns0:c>
       <ns0:c r="J22">
-        <ns0:v>0.7346951231664622</ns0:v>
-      </ns0:c>
-      <ns0:c r="K22">
-        <ns0:v>1.2925987089025672</ns0:v>
+        <ns0:v>3.885021371507835</ns0:v>
       </ns0:c>
       <ns0:c r="L22">
-        <ns0:v>72.51896023763308</ns0:v>
+        <ns0:v>88.4116636319506</ns0:v>
       </ns0:c>
       <ns0:c r="M22">
-        <ns0:v>93.99000053405761</ns0:v>
+        <ns0:v>90.40199966430664</ns0:v>
       </ns0:c>
       <ns0:c r="N22">
-        <ns0:v>91.57660018920899</ns0:v>
+        <ns0:v>79.4353997039795</ns0:v>
       </ns0:c>
       <ns0:c r="O22">
-        <ns0:v>81.94405040740966</ns0:v>
+        <ns0:v>72.78164995193481</ns0:v>
       </ns0:c>
       <ns0:c r="P22" t="inlineStr">
         <ns0:is>
@@ -1777,77 +1827,74 @@
       </ns0:c>
       <ns0:c r="R22" t="inlineStr">
         <ns0:is>
-          <ns0:t>실적 발표 이후 주가가 2% 오른 가운데, 견조한 분기 실적에 가려진 현금흐름 문제가 지적됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>주간 주가 55% 급등, 암 탐지 혈액검사에 대한 FDA 자문위원 지지, 고평가 여부가 보도됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S22" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/innospec-iosp-2-since-last-153015757.html</ns0:t>
+          <ns0:t>https://www.fool.com/investing/2026/09/25/heres-why-grail-stock-surged-55-this-week/</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T22" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/IOSP/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/GRAL/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="23">
       <ns0:c r="A23" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B23" t="inlineStr">
         <ns0:is>
-          <ns0:t>IOVA</ns0:t>
+          <ns0:t>GTERA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C23" t="inlineStr">
         <ns0:is>
-          <ns0:t>Iovance Biotherapeutics Inc</ns0:t>
+          <ns0:t>Globa Terra Acquisition Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D23" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E23" t="inlineStr">
         <ns0:is>
-          <ns0:t>Biotechnology</ns0:t>
+          <ns0:t>Shell Companies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F23" t="inlineStr">
         <ns0:is>
-          <ns0:t>전이성 흑색종 등 고형암 치료용 자가 종양침윤림프구 세포치료제를 개발·상용화한다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G23">
-        <ns0:v>11.0</ns0:v>
+        <ns0:v>10.449999809265137</ns0:v>
       </ns0:c>
       <ns0:c r="H23">
-        <ns0:v>1.8518500530834592</ns0:v>
+        <ns0:v>0.28790530471725084</ns0:v>
       </ns0:c>
       <ns0:c r="I23">
-        <ns0:v>10.979999542236328</ns0:v>
+        <ns0:v>10.4350004196167</ns0:v>
       </ns0:c>
       <ns0:c r="J23">
-        <ns0:v>0.1821535391393958</ns0:v>
-      </ns0:c>
-      <ns0:c r="K23">
-        <ns0:v>0.9366111879724249</ns0:v>
+        <ns0:v>0.14374115040991509</ns0:v>
       </ns0:c>
       <ns0:c r="L23">
-        <ns0:v>74.35970596617581</ns0:v>
+        <ns0:v>77.57171193099609</ns0:v>
       </ns0:c>
       <ns0:c r="M23">
-        <ns0:v>9.301000022888184</ns0:v>
+        <ns0:v>10.418499994277955</ns0:v>
       </ns0:c>
       <ns0:c r="N23">
-        <ns0:v>7.413400011062622</ns0:v>
+        <ns0:v>10.394400062561035</ns0:v>
       </ns0:c>
       <ns0:c r="O23">
-        <ns0:v>4.444150003194809</ns0:v>
+        <ns0:v>10.256945018768311</ns0:v>
       </ns0:c>
       <ns0:c r="P23" t="inlineStr">
         <ns0:is>
@@ -1856,166 +1903,156 @@
       </ns0:c>
       <ns0:c r="Q23" t="inlineStr">
         <ns0:is>
-          <ns0:t>보도된 해석</ns0:t>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R23" t="inlineStr">
         <ns0:is>
-          <ns0:t>주가 19.2% 상승과 함께 2분기 암타그비 매출 신기록 및 종양침윤림프구 치료제 개발 확대가 보도됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="S23" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://www.fool.com/investing/2026/09/24/why-iovance-biotherapeutics-stock-was-on-fire-toda/</ns0:t>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T23" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/IOVA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/GTERA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="24">
       <ns0:c r="A24" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B24" t="inlineStr">
         <ns0:is>
-          <ns0:t>JILL</ns0:t>
+          <ns0:t>HLP</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C24" t="inlineStr">
         <ns0:is>
-          <ns0:t>J.Jill Inc</ns0:t>
+          <ns0:t>Hongli Group Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D24" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Basic Materials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E24" t="inlineStr">
         <ns0:is>
-          <ns0:t>Apparel Retail</ns0:t>
+          <ns0:t>Steel</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F24" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 온·오프라인 채널에서 여성 의류·신발·보석·가방 등 액세서리를 판매한다.</ns0:t>
+          <ns0:t>중국과 해외에서 다양한 형태의 맞춤형 냉간 성형 강재를 제조·판매하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G24">
-        <ns0:v>24.6299991607666</ns0:v>
+        <ns0:v>2.390000104904175</ns0:v>
       </ns0:c>
       <ns0:c r="H24">
-        <ns0:v>2.411642170916517</ns0:v>
+        <ns0:v>8.144799260190405</ns0:v>
       </ns0:c>
       <ns0:c r="I24">
-        <ns0:v>24.690000534057617</ns0:v>
+        <ns0:v>2.299999952316284</ns0:v>
       </ns0:c>
       <ns0:c r="J24">
-        <ns0:v>-0.24301892261301417</ns0:v>
+        <ns0:v>3.913050193642542</ns0:v>
       </ns0:c>
       <ns0:c r="K24">
-        <ns0:v>0.7047716969668645</ns0:v>
+        <ns0:v>1.336378466557912</ns0:v>
       </ns0:c>
       <ns0:c r="L24">
-        <ns0:v>74.65046572429807</ns0:v>
+        <ns0:v>82.90310868752772</ns0:v>
       </ns0:c>
       <ns0:c r="M24">
-        <ns0:v>22.3229998588562</ns0:v>
+        <ns0:v>1.7177500069141387</ns0:v>
       </ns0:c>
       <ns0:c r="N24">
-        <ns0:v>20.070999946594238</ns0:v>
+        <ns0:v>1.4232999992370605</ns0:v>
       </ns0:c>
       <ns0:c r="O24">
-        <ns0:v>15.965500016212463</ns0:v>
+        <ns0:v>1.0255249960720538</ns0:v>
       </ns0:c>
       <ns0:c r="P24" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q24" t="inlineStr">
         <ns0:is>
-          <ns0:t>보도된 해석</ns0:t>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R24" t="inlineStr">
         <ns0:is>
-          <ns0:t>실적·전망 관련 기사 제목 1건 확인. 주가 상승과의 인과는 미확인입니다.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="S24" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/j-jill-jill-four-analysts-190634876.html</ns0:t>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T24" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/JILL/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/HLP/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="25">
       <ns0:c r="A25" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B25" t="inlineStr">
         <ns0:is>
-          <ns0:t>MASS</ns0:t>
+          <ns0:t>HQI</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C25" t="inlineStr">
         <ns0:is>
-          <ns0:t>908 Devices Inc</ns0:t>
+          <ns0:t>HireQuest Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D25" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E25" t="inlineStr">
         <ns0:is>
-          <ns0:t>Medical Devices</ns0:t>
+          <ns0:t>Staffing &amp; Employment Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F25" t="inlineStr">
         <ns0:is>
-          <ns0:t>보건·안전 분야용 휴대용 질량분석기와 푸리에 변환 적외선 장비를 제공한다.</ns0:t>
+          <ns0:t>미국에서 임원 채용, 산업·건설·사무 인력 공급, 정규직 채용 등 인력 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G25">
-        <ns0:v>11.4399995803833</ns0:v>
+        <ns0:v>19.729999542236328</ns0:v>
       </ns0:c>
       <ns0:c r="H25">
-        <ns0:v>-0.6944520329984494</ns0:v>
+        <ns0:v>-1.5469129697036177</ns0:v>
       </ns0:c>
       <ns0:c r="I25">
-        <ns0:v>11.529999732971191</ns0:v>
+        <ns0:v>20.229999542236328</ns0:v>
       </ns0:c>
       <ns0:c r="J25">
-        <ns0:v>-0.7805737612510577</ns0:v>
+        <ns0:v>-2.471576921967278</ns0:v>
       </ns0:c>
       <ns0:c r="K25">
-        <ns0:v>0.8057695112089194</ns0:v>
+        <ns0:v>1.099556048834628</ns0:v>
       </ns0:c>
       <ns0:c r="L25">
-        <ns0:v>64.45950942237641</ns0:v>
+        <ns0:v>72.4803786838045</ns0:v>
       </ns0:c>
       <ns0:c r="M25">
-        <ns0:v>10.396499967575073</ns0:v>
+        <ns0:v>17.028999900817873</ns0:v>
       </ns0:c>
       <ns0:c r="N25">
-        <ns0:v>9.498000011444091</ns0:v>
+        <ns0:v>15.754999923706055</ns0:v>
       </ns0:c>
       <ns0:c r="O25">
-        <ns0:v>7.574825010299683</ns0:v>
+        <ns0:v>12.388349959850311</ns0:v>
       </ns0:c>
       <ns0:c r="P25" t="inlineStr">
         <ns0:is>
@@ -2029,77 +2066,77 @@
       </ns0:c>
       <ns0:c r="R25" t="inlineStr">
         <ns0:is>
-          <ns0:t>휴대용 탐지기 수요가 빠르게 늘어나는 가운데 2026년 전망을 상향했다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>주가 6.9% 상승과 상승세 지속 가능성을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S25" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://www.marketbeat.com/instant-alerts/event-908-devices-raises-2026-outlook-as-handheld-detection-demand-accelerates-2026-08-29/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/hirequest-hqi-stock-jumps-6-122000853.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T25" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MASS/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/HQI/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="26">
       <ns0:c r="A26" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B26" t="inlineStr">
         <ns0:is>
-          <ns0:t>MG</ns0:t>
+          <ns0:t>IMAX</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C26" t="inlineStr">
         <ns0:is>
-          <ns0:t>Mistras Group Inc</ns0:t>
+          <ns0:t>Imax Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D26" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Communication Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E26" t="inlineStr">
         <ns0:is>
-          <ns0:t>Security &amp; Protection Services</ns0:t>
+          <ns0:t>Entertainment</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F26" t="inlineStr">
         <ns0:is>
-          <ns0:t>산업 자산 건전성·실험실 시험 솔루션과 비파괴 검사, 배관 검사, 유지보수 계획 등을 제공한다.</ns0:t>
+          <ns0:t>미국·캐나다·중화권 등 전 세계에서 엔터테인먼트와 이벤트용 기술 플랫폼을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G26">
-        <ns0:v>21.520000457763672</ns0:v>
+        <ns0:v>56.130001068115234</ns0:v>
       </ns0:c>
       <ns0:c r="H26">
-        <ns0:v>0.6548236786368955</ns0:v>
+        <ns0:v>0.1427329743865391</ns0:v>
       </ns0:c>
       <ns0:c r="I26">
-        <ns0:v>21.56999969482422</ns0:v>
+        <ns0:v>56.68000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="J26">
-        <ns0:v>-0.23179989693066227</ns0:v>
+        <ns0:v>-0.9703585640424284</ns0:v>
       </ns0:c>
       <ns0:c r="K26">
-        <ns0:v>0.7671278790862338</ns0:v>
+        <ns0:v>1.504673744174003</ns0:v>
       </ns0:c>
       <ns0:c r="L26">
-        <ns0:v>70.07932732899262</ns0:v>
+        <ns0:v>66.4131568083092</ns0:v>
       </ns0:c>
       <ns0:c r="M26">
-        <ns0:v>19.839000034332276</ns0:v>
+        <ns0:v>52.82049999237061</ns0:v>
       </ns0:c>
       <ns0:c r="N26">
-        <ns0:v>18.090000057220458</ns0:v>
+        <ns0:v>50.64539993286133</ns0:v>
       </ns0:c>
       <ns0:c r="O26">
-        <ns0:v>16.361300024986267</ns0:v>
+        <ns0:v>41.02240013122559</ns0:v>
       </ns0:c>
       <ns0:c r="P26" t="inlineStr">
         <ns0:is>
@@ -2113,156 +2150,161 @@
       </ns0:c>
       <ns0:c r="R26" t="inlineStr">
         <ns0:is>
-          <ns0:t>계약·사업 관련 기사 제목 1건 확인. 주가 상승과의 인과는 미확인입니다.</ns0:t>
+          <ns0:t>IMAX 주가 상승과 업종 대비 성과를 점검하고, 모건스탠리의 추가 상승 전망 및 ‘오디세이’의 영향을 조명. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S26" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/mistras-group-shares-jump-following-151628366.html</ns0:t>
+          <ns0:t>https://247wallst.com/investing/2026/09/28/amc-spikes-13-as-refinancing-rally-extends-cinemark-and-imax-edge-higher/</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T26" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MG/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/IMAX/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="27">
       <ns0:c r="A27" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B27" t="inlineStr">
         <ns0:is>
-          <ns0:t>MGLD</ns0:t>
+          <ns0:t>IOSP</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C27" t="inlineStr">
         <ns0:is>
-          <ns0:t>Marygold Companies Inc</ns0:t>
+          <ns0:t>Innospec Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D27" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Basic Materials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E27" t="inlineStr">
         <ns0:is>
-          <ns0:t>Asset Management</ns0:t>
+          <ns0:t>Specialty Chemicals</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F27" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다·영국에서 상장지수상품을 운용하며 보안시스템·미용제품·금융 사업도 한다.</ns0:t>
+          <ns0:t>특수화학 제품을 개발·제조·혼합·판매하며 기능성 화학, 연료 특수제품, 유전서비스 사업을 한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G27">
-        <ns0:v>1.9299999475479126</ns0:v>
+        <ns0:v>97.87999725341797</ns0:v>
       </ns0:c>
       <ns0:c r="H27">
-        <ns0:v>92.99999475479126</ns0:v>
+        <ns0:v>-0.8508954182518735</ns0:v>
       </ns0:c>
       <ns0:c r="I27">
-        <ns0:v>1.3799999952316284</ns0:v>
+        <ns0:v>98.7699966430664</ns0:v>
       </ns0:c>
       <ns0:c r="J27">
-        <ns0:v>39.85506914613928</ns0:v>
+        <ns0:v>-0.901082737569292</ns0:v>
       </ns0:c>
       <ns0:c r="K27">
-        <ns0:v>1144.4698085419734</ns0:v>
+        <ns0:v>1.4019108593942378</ns0:v>
       </ns0:c>
       <ns0:c r="L27">
-        <ns0:v>84.26943360820123</ns0:v>
+        <ns0:v>67.45662382210412</ns0:v>
       </ns0:c>
       <ns0:c r="M27">
-        <ns0:v>1.0444499909877778</ns0:v>
+        <ns0:v>94.11500053405761</ns0:v>
       </ns0:c>
       <ns0:c r="N27">
-        <ns0:v>1.062079997062683</ns0:v>
+        <ns0:v>91.84920013427734</ns0:v>
       </ns0:c>
       <ns0:c r="O27">
-        <ns0:v>1.0786599957942962</ns0:v>
+        <ns0:v>82.05360038757324</ns0:v>
       </ns0:c>
       <ns0:c r="P27" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q27" t="inlineStr">
         <ns0:is>
-          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+          <ns0:t>보도된 해석</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R27" t="inlineStr">
         <ns0:is>
-          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+          <ns0:t>실적 발표 이후 주가 2% 상승과 지속 가능성, 양호한 분기 실적 속 현금흐름 문제가 다뤄졌다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/innospec-iosp-2-since-last-153015757.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T27" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MGLD/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/IOSP/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="28">
       <ns0:c r="A28" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B28" t="inlineStr">
         <ns0:is>
-          <ns0:t>MNTK</ns0:t>
+          <ns0:t>IOVA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C28" t="inlineStr">
         <ns0:is>
-          <ns0:t>Montauk Renewables Inc</ns0:t>
+          <ns0:t>Iovance Biotherapeutics Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D28" t="inlineStr">
         <ns0:is>
-          <ns0:t>Basic Materials</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E28" t="inlineStr">
         <ns0:is>
-          <ns0:t>Specialty Chemicals</ns0:t>
+          <ns0:t>Biotechnology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F28" t="inlineStr">
         <ns0:is>
-          <ns0:t>매립지 등 비화석 원천의 바이오가스를 회수·처리하며 재생 천연가스와 재생 전력 사업을 한다.</ns0:t>
+          <ns0:t>자가 종양침윤림프구를 활용해 전이성 흑색종 등 고형암 치료용 세포치료제를 개발·상용화한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G28">
-        <ns0:v>2.930000066757202</ns0:v>
+        <ns0:v>10.989999771118164</ns0:v>
       </ns0:c>
       <ns0:c r="H28">
-        <ns0:v>1.7361093864397548</ns0:v>
+        <ns0:v>-0.09091117165305196</ns0:v>
       </ns0:c>
       <ns0:c r="I28">
-        <ns0:v>2.9700000286102295</ns0:v>
+        <ns0:v>11.130000114440918</ns0:v>
       </ns0:c>
       <ns0:c r="J28">
-        <ns0:v>-1.3468000494176735</ns0:v>
+        <ns0:v>-1.2578647069473647</ns0:v>
       </ns0:c>
       <ns0:c r="K28">
-        <ns0:v>3.2764470552488985</ns0:v>
+        <ns0:v>0.8889542502460457</ns0:v>
       </ns0:c>
       <ns0:c r="L28">
-        <ns0:v>67.57522095471995</ns0:v>
+        <ns0:v>74.17911377395171</ns0:v>
       </ns0:c>
       <ns0:c r="M28">
-        <ns0:v>2.3115000128746033</ns0:v>
+        <ns0:v>9.45</ns0:v>
       </ns0:c>
       <ns0:c r="N28">
-        <ns0:v>1.998900008201599</ns0:v>
+        <ns0:v>7.533200006484986</ns0:v>
       </ns0:c>
       <ns0:c r="O28">
-        <ns0:v>1.6531250017881394</ns0:v>
+        <ns0:v>4.4878500020504</ns0:v>
       </ns0:c>
       <ns0:c r="P28" t="inlineStr">
         <ns0:is>
@@ -2276,81 +2318,81 @@
       </ns0:c>
       <ns0:c r="R28" t="inlineStr">
         <ns0:is>
-          <ns0:t>올해 주가 성과가 다른 석유·에너지 종목을 웃도는지 비교하는 기사가 나왔다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>당일 주가 급등의 배경을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S28" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/energy/articles/montauk-renewables-mntk-outperforming-other-134004370.html</ns0:t>
+          <ns0:t>https://www.fool.com/investing/2026/09/24/why-iovance-biotherapeutics-stock-was-on-fire-toda/</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T28" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MNTK/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/IOVA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="29">
       <ns0:c r="A29" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B29" t="inlineStr">
         <ns0:is>
-          <ns0:t>MRNA</ns0:t>
+          <ns0:t>JILL</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C29" t="inlineStr">
         <ns0:is>
-          <ns0:t>Moderna Inc</ns0:t>
+          <ns0:t>J.Jill Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D29" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E29" t="inlineStr">
         <ns0:is>
-          <ns0:t>Biotechnology</ns0:t>
+          <ns0:t>Apparel Retail</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F29" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·유럽 등에서 메신저 RNA 의약품과 호흡기·잠복 바이러스 관련 백신을 제공한다.</ns0:t>
+          <ns0:t>미국에서 온·오프라인 채널로 여성 의류·신발·보석·가방 등 액세서리를 판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G29">
-        <ns0:v>198.8800048828125</ns0:v>
+        <ns0:v>24.219999313354492</ns0:v>
       </ns0:c>
       <ns0:c r="H29">
-        <ns0:v>2.0839736197304948</ns0:v>
+        <ns0:v>-1.6646360592054044</ns0:v>
       </ns0:c>
       <ns0:c r="I29">
-        <ns0:v>195.70899963378906</ns0:v>
+        <ns0:v>24.729999542236328</ns0:v>
       </ns0:c>
       <ns0:c r="J29">
-        <ns0:v>1.62026542210989</ns0:v>
+        <ns0:v>-2.0622735071660903</ns0:v>
       </ns0:c>
       <ns0:c r="K29">
-        <ns0:v>0.8444472924254605</ns0:v>
+        <ns0:v>0.5800915491321421</ns0:v>
       </ns0:c>
       <ns0:c r="L29">
-        <ns0:v>76.07055815922786</ns0:v>
+        <ns0:v>69.12971845747131</ns0:v>
       </ns0:c>
       <ns0:c r="M29">
-        <ns0:v>155.69300079345703</ns0:v>
+        <ns0:v>22.543999862670898</ns0:v>
       </ns0:c>
       <ns0:c r="N29">
-        <ns0:v>110.10980087280274</ns0:v>
+        <ns0:v>20.223199920654295</ns0:v>
       </ns0:c>
       <ns0:c r="O29">
-        <ns0:v>64.25587517738342</ns0:v>
+        <ns0:v>16.004150013923645</ns0:v>
       </ns0:c>
       <ns0:c r="P29" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q29" t="inlineStr">
@@ -2360,77 +2402,77 @@
       </ns0:c>
       <ns0:c r="R29" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업 동향 관련 기사 제목 3건 확인. 주가 상승과의 인과는 미확인입니다.</ns0:t>
+          <ns0:t>실적·전망 관련 기사 제목 1건 확인. 주가 상승과의 인과는 미확인입니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S29" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://stocktwits.com/news-articles/markets/equity/mrna-pgen-stocks-hit-multi-year-highs-what-s-driving-the-momentum-today/cZMOKrcRBOS</ns0:t>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/j-jill-jill-four-analysts-190634876.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T29" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MRNA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/JILL/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="30">
       <ns0:c r="A30" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B30" t="inlineStr">
         <ns0:is>
-          <ns0:t>MTLS</ns0:t>
+          <ns0:t>JRSH</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C30" t="inlineStr">
         <ns0:is>
-          <ns0:t>Materialise Nv ADR</ns0:t>
+          <ns0:t>Jerash holdings (US) Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D30" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E30" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Apparel Manufacturing</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F30" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 적층 제조·의료 소프트웨어 도구와 3D 프린팅 서비스를 제공한다.</ns0:t>
+          <ns0:t>편직물 기반 맞춤형 기성 스포츠웨어·겉옷과 개인보호장비를 제조·수출한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G30">
-        <ns0:v>8.430000305175781</ns0:v>
+        <ns0:v>5.900000095367432</ns0:v>
       </ns0:c>
       <ns0:c r="H30">
-        <ns0:v>5.243446495538695</ns0:v>
+        <ns0:v>3.8732442548886192</ns0:v>
       </ns0:c>
       <ns0:c r="I30">
-        <ns0:v>8.079999923706055</ns0:v>
+        <ns0:v>5.809999942779541</ns0:v>
       </ns0:c>
       <ns0:c r="J30">
-        <ns0:v>4.331687930377992</ns0:v>
+        <ns0:v>1.5490559978359242</ns0:v>
       </ns0:c>
       <ns0:c r="K30">
-        <ns0:v>2.6649794028162948</ns0:v>
+        <ns0:v>1.7194330981557124</ns0:v>
       </ns0:c>
       <ns0:c r="L30">
-        <ns0:v>79.00927204347606</ns0:v>
+        <ns0:v>65.65575171955388</ns0:v>
       </ns0:c>
       <ns0:c r="M30">
-        <ns0:v>7.573000025749207</ns0:v>
+        <ns0:v>5.52425000667572</ns0:v>
       </ns0:c>
       <ns0:c r="N30">
-        <ns0:v>7.016600017547607</ns0:v>
+        <ns0:v>5.2459999942779545</ns0:v>
       </ns0:c>
       <ns0:c r="O30">
-        <ns0:v>6.067700004577636</ns0:v>
+        <ns0:v>3.8576249825954436</ns0:v>
       </ns0:c>
       <ns0:c r="P30" t="inlineStr">
         <ns0:is>
@@ -2439,39 +2481,34 @@
       </ns0:c>
       <ns0:c r="Q30" t="inlineStr">
         <ns0:is>
-          <ns0:t>보도된 해석</ns0:t>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R30" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026년 2분기 실적 발표에서 의료 부문 성장과 항공우주 부문 급성장이 부각됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="S30" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://www.fool.com/earnings/call-transcripts/2026/08/31/materialise-mtls-q2-2026-earnings-call-transcript/</ns0:t>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T30" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MTLS/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/JRSH/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="31">
       <ns0:c r="A31" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B31" t="inlineStr">
         <ns0:is>
-          <ns0:t>NTRA</ns0:t>
+          <ns0:t>KOD</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C31" t="inlineStr">
         <ns0:is>
-          <ns0:t>Natera Inc</ns0:t>
+          <ns0:t>Kodiak Sciences Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D31" t="inlineStr">
@@ -2481,44 +2518,44 @@
       </ns0:c>
       <ns0:c r="E31" t="inlineStr">
         <ns0:is>
-          <ns0:t>Diagnostics &amp; Research</ns0:t>
+          <ns0:t>Biotechnology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F31" t="inlineStr">
         <ns0:is>
-          <ns0:t>분자검사를 개발·상용화하며 잔존질환·재발 감시·치료 반응 평가용 혈액검사를 제공한다.</ns0:t>
+          <ns0:t>망막질환 치료제를 연구·개발·상용화하는 임상 단계 바이오기업으로, 주요 후보는 KSI-301이다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G31">
-        <ns0:v>412.55999755859375</ns0:v>
+        <ns0:v>89.91999816894531</ns0:v>
       </ns0:c>
       <ns0:c r="H31">
-        <ns0:v>0.9222312030303881</ns0:v>
+        <ns0:v>177.95982197921361</ns0:v>
       </ns0:c>
       <ns0:c r="I31">
-        <ns0:v>412.92498779296875</ns0:v>
+        <ns0:v>47.84000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="J31">
-        <ns0:v>-0.08839141373493398</ns0:v>
+        <ns0:v>87.95986179377367</ns0:v>
       </ns0:c>
       <ns0:c r="K31">
-        <ns0:v>1.1464325073767287</ns0:v>
+        <ns0:v>44.96979083711997</ns0:v>
       </ns0:c>
       <ns0:c r="L31">
-        <ns0:v>83.75044912642949</ns0:v>
+        <ns0:v>89.7762461305292</ns0:v>
       </ns0:c>
       <ns0:c r="M31">
-        <ns0:v>350.34025421142576</ns0:v>
+        <ns0:v>36.79649963378906</ns0:v>
       </ns0:c>
       <ns0:c r="N31">
-        <ns0:v>316.5035021972656</ns0:v>
+        <ns0:v>39.39859992980957</ns0:v>
       </ns0:c>
       <ns0:c r="O31">
-        <ns0:v>244.5601505279541</ns0:v>
+        <ns0:v>34.21389994621277</ns0:v>
       </ns0:c>
       <ns0:c r="P31" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q31" t="inlineStr">
@@ -2528,77 +2565,74 @@
       </ns0:c>
       <ns0:c r="R31" t="inlineStr">
         <ns0:is>
-          <ns0:t>시그나테라가 일본 PMDA의 방광암 동반진단 승인을 받았으며, 주가 급등을 다룬 기사도 나왔다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>승인·임상 관련 기사 제목 3건 확인. 주가 상승과의 인과는 미확인입니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S31" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/stocks-making-big-moves-yesterday-170902420.html</ns0:t>
+          <ns0:t>https://www.barrons.com/articles/kodiak-sciences-stock-eye-disease-drugs-a958d76d</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T31" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/NTRA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/KOD/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="32">
       <ns0:c r="A32" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B32" t="inlineStr">
         <ns0:is>
-          <ns0:t>NTRB</ns0:t>
+          <ns0:t>KOYN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C32" t="inlineStr">
         <ns0:is>
-          <ns0:t>Nutriband Inc</ns0:t>
+          <ns0:t>CSLM Digital Asset Acquisition Corp III Ltd</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D32" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E32" t="inlineStr">
         <ns0:is>
-          <ns0:t>Biotechnology</ns0:t>
+          <ns0:t>Shell Companies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F32" t="inlineStr">
         <ns0:is>
-          <ns0:t>경피 약물을 개발하며 주요 제품은 만성 통증 치료용 남용 억제 펜타닐 패치 AVERSA다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G32">
-        <ns0:v>8.0</ns0:v>
+        <ns0:v>10.244999885559082</ns0:v>
       </ns0:c>
       <ns0:c r="H32">
-        <ns0:v>-11.012233551981831</ns0:v>
+        <ns0:v>0.1466309285823808</ns0:v>
       </ns0:c>
       <ns0:c r="I32">
-        <ns0:v>9.0</ns0:v>
+        <ns0:v>10.244999885559082</ns0:v>
       </ns0:c>
       <ns0:c r="J32">
-        <ns0:v>-11.111111111111116</ns0:v>
-      </ns0:c>
-      <ns0:c r="K32">
-        <ns0:v>3.902578796561605</ns0:v>
+        <ns0:v>0.0</ns0:v>
       </ns0:c>
       <ns0:c r="L32">
-        <ns0:v>63.78414033666717</ns0:v>
+        <ns0:v>62.6088426064023</ns0:v>
       </ns0:c>
       <ns0:c r="M32">
-        <ns0:v>6.492350006103516</ns0:v>
+        <ns0:v>10.232499694824218</ns0:v>
       </ns0:c>
       <ns0:c r="N32">
-        <ns0:v>4.617459998130799</ns0:v>
+        <ns0:v>10.213199882507324</ns0:v>
       </ns0:c>
       <ns0:c r="O32">
-        <ns0:v>4.122244991064072</ns0:v>
+        <ns0:v>10.098429980278015</ns0:v>
       </ns0:c>
       <ns0:c r="P32" t="inlineStr">
         <ns0:is>
@@ -2617,24 +2651,24 @@
       </ns0:c>
       <ns0:c r="T32" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/NTRB/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/KOYN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="33">
       <ns0:c r="A33" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B33" t="inlineStr">
         <ns0:is>
-          <ns0:t>OPRT</ns0:t>
+          <ns0:t>MGLD</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C33" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oportun Financial Corp</ns0:t>
+          <ns0:t>Marygold Companies Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D33" t="inlineStr">
@@ -2644,157 +2678,160 @@
       </ns0:c>
       <ns0:c r="E33" t="inlineStr">
         <ns0:is>
-          <ns0:t>Credit Services</ns0:t>
+          <ns0:t>Asset Management</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F33" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 온라인·전화·매장·제휴사를 통해 개인대출과 신용카드 등 금융서비스를 제공한다.</ns0:t>
+          <ns0:t>미국·캐나다·영국에서 상장지수상품 운용 서비스를 제공하며 보안시스템·미용제품·금융 사업도 한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G33">
-        <ns0:v>8.550000190734863</ns0:v>
+        <ns0:v>1.9700000286102295</ns0:v>
       </ns0:c>
       <ns0:c r="H33">
-        <ns0:v>3.012048123553912</ns0:v>
+        <ns0:v>2.0725431165496966</ns0:v>
       </ns0:c>
       <ns0:c r="I33">
-        <ns0:v>8.54699993133545</ns0:v>
+        <ns0:v>1.9600000381469727</ns0:v>
       </ns0:c>
       <ns0:c r="J33">
-        <ns0:v>0.035103070358233346</ns0:v>
+        <ns0:v>0.5102035851341613</ns0:v>
       </ns0:c>
       <ns0:c r="K33">
-        <ns0:v>1.4042638192779835</ns0:v>
+        <ns0:v>3.1962488598358165</ns0:v>
       </ns0:c>
       <ns0:c r="L33">
-        <ns0:v>66.494637639649</ns0:v>
+        <ns0:v>84.75633492300662</ns0:v>
       </ns0:c>
       <ns0:c r="M33">
-        <ns0:v>7.8879999876022335</ns0:v>
+        <ns0:v>1.088949990272522</ns0:v>
       </ns0:c>
       <ns0:c r="N33">
-        <ns0:v>7.197400007247925</ns0:v>
+        <ns0:v>1.0782799983024598</ns0:v>
       </ns0:c>
       <ns0:c r="O33">
-        <ns0:v>5.769125013351441</ns0:v>
+        <ns0:v>1.0839599958062172</ns0:v>
       </ns0:c>
       <ns0:c r="P33" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q33" t="inlineStr">
         <ns0:is>
-          <ns0:t>보도된 해석</ns0:t>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R33" t="inlineStr">
         <ns0:is>
-          <ns0:t>잭스 투자전략 기사에서 주목받았으며, 빠른 주가 움직임과 가치투자 관점의 매력을 다룬 평가가 나왔다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="S33" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/zacks-approach-beat-markets-oportun-123300876.html</ns0:t>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T33" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/OPRT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MGLD/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="34">
       <ns0:c r="A34" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B34" t="inlineStr">
         <ns0:is>
-          <ns0:t>PACH</ns0:t>
+          <ns0:t>MTD</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C34" t="inlineStr">
         <ns0:is>
-          <ns0:t>Pioneer Acquisition I Corp</ns0:t>
+          <ns0:t>Mettler-Toledo International Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D34" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E34" t="inlineStr">
         <ns0:is>
-          <ns0:t>Shell Companies</ns0:t>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F34" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 헬스케어 및 관련 산업 기업과의 합병·주식 교환·인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>미주·유럽·아시아 등 전 세계에서 실험실 기기 등 정밀기기를 제조·공급하고 관련 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G34">
-        <ns0:v>10.329999923706055</ns0:v>
+        <ns0:v>1545.260009765625</ns0:v>
       </ns0:c>
       <ns0:c r="H34">
-        <ns0:v>-0.1932411306909687</ns0:v>
+        <ns0:v>2.224074170529722</ns0:v>
       </ns0:c>
       <ns0:c r="I34">
-        <ns0:v>10.350000381469727</ns0:v>
+        <ns0:v>1541.02001953125</ns0:v>
       </ns0:c>
       <ns0:c r="J34">
-        <ns0:v>-0.1932411306909687</ns0:v>
+        <ns0:v>0.27514180092642615</ns0:v>
+      </ns0:c>
+      <ns0:c r="K34">
+        <ns0:v>0.8457360974606295</ns0:v>
       </ns0:c>
       <ns0:c r="L34">
-        <ns0:v>54.228792426741094</ns0:v>
+        <ns0:v>73.41375599066843</ns0:v>
       </ns0:c>
       <ns0:c r="M34">
-        <ns0:v>10.330500030517578</ns0:v>
+        <ns0:v>1391.3749877929688</ns0:v>
       </ns0:c>
       <ns0:c r="N34">
-        <ns0:v>10.304320087432862</ns0:v>
+        <ns0:v>1391.956201171875</ns0:v>
       </ns0:c>
       <ns0:c r="O34">
-        <ns0:v>10.19614001750946</ns0:v>
+        <ns0:v>1316.6934979248047</ns0:v>
       </ns0:c>
       <ns0:c r="P34" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q34" t="inlineStr">
         <ns0:is>
-          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+          <ns0:t>보도된 해석</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R34" t="inlineStr">
         <ns0:is>
-          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+          <ns0:t>메틀러톨레도가 새롭게 주목받는 배경을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S34" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/mettler-toledo-international-mtd-why-121037566.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T34" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PACH/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MTD/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="35">
       <ns0:c r="A35" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B35" t="inlineStr">
         <ns0:is>
-          <ns0:t>PAYO</ns0:t>
+          <ns0:t>MTLS</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C35" t="inlineStr">
         <ns0:is>
-          <ns0:t>Payoneer Global Inc</ns0:t>
+          <ns0:t>Materialise Nv ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D35" t="inlineStr">
@@ -2804,76 +2841,81 @@
       </ns0:c>
       <ns0:c r="E35" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Infrastructure</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F35" t="inlineStr">
         <ns0:is>
-          <ns0:t>국경 간 대금 수취·지급용 다중통화 계좌와 결제 인프라를 제공하는 핀테크 기업.</ns0:t>
+          <ns0:t>미주·유럽·아프리카·아시아태평양에서 적층제조·의료 소프트웨어와 3D 프린팅 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G35">
-        <ns0:v>7.170000076293945</ns0:v>
+        <ns0:v>8.579999923706055</ns0:v>
       </ns0:c>
       <ns0:c r="H35">
-        <ns0:v>0.5610092736466177</ns0:v>
+        <ns0:v>1.7793548410452331</ns0:v>
       </ns0:c>
       <ns0:c r="I35">
-        <ns0:v>7.179999828338623</ns0:v>
+        <ns0:v>8.550000190734863</ns0:v>
       </ns0:c>
       <ns0:c r="J35">
-        <ns0:v>-0.13927231592972822</ns0:v>
+        <ns0:v>0.3508740620111306</ns0:v>
       </ns0:c>
       <ns0:c r="K35">
-        <ns0:v>1.2451037407510133</ns0:v>
+        <ns0:v>1.7492950912472707</ns0:v>
       </ns0:c>
       <ns0:c r="L35">
-        <ns0:v>59.71264589115707</ns0:v>
+        <ns0:v>80.7843805118834</ns0:v>
       </ns0:c>
       <ns0:c r="M35">
-        <ns0:v>7.130500030517578</ns0:v>
+        <ns0:v>7.651000022888184</ns0:v>
       </ns0:c>
       <ns0:c r="N35">
-        <ns0:v>7.124200019836426</ns0:v>
+        <ns0:v>7.057400016784668</ns0:v>
       </ns0:c>
       <ns0:c r="O35">
-        <ns0:v>5.939300003051758</ns0:v>
+        <ns0:v>6.081650004386902</ns0:v>
       </ns0:c>
       <ns0:c r="P35" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q35" t="inlineStr">
         <ns0:is>
-          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+          <ns0:t>보도된 해석</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R35" t="inlineStr">
         <ns0:is>
-          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+          <ns0:t>2026년 2분기 실적 발표 콘퍼런스콜 기록. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S35" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://www.fool.com/earnings/call-transcripts/2026/08/31/materialise-mtls-q2-2026-earnings-call-transcript/</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T35" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PAYO/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MTLS/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="36">
       <ns0:c r="A36" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B36" t="inlineStr">
         <ns0:is>
-          <ns0:t>PGEN</ns0:t>
+          <ns0:t>NTRA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C36" t="inlineStr">
         <ns0:is>
-          <ns0:t>Precigen Inc</ns0:t>
+          <ns0:t>Natera Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D36" t="inlineStr">
@@ -2883,40 +2925,40 @@
       </ns0:c>
       <ns0:c r="E36" t="inlineStr">
         <ns0:is>
-          <ns0:t>Biotechnology</ns0:t>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F36" t="inlineStr">
         <ns0:is>
-          <ns0:t>암 면역치료·자가면역·감염병 대상 유전자·세포 치료제를 개발하는 임상 단계 바이오 기업.</ns0:t>
+          <ns0:t>분자검사 서비스를 개발·상용화하며 잔존질환 평가·재발 감시·치료 반응 평가용 혈액검사를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G36">
-        <ns0:v>7.75</ns0:v>
+        <ns0:v>411.7699890136719</ns0:v>
       </ns0:c>
       <ns0:c r="H36">
-        <ns0:v>0.6493531425117771</ns0:v>
+        <ns0:v>-0.19148937114527032</ns0:v>
       </ns0:c>
       <ns0:c r="I36">
-        <ns0:v>8.039999961853027</ns0:v>
+        <ns0:v>415.75</ns0:v>
       </ns0:c>
       <ns0:c r="J36">
-        <ns0:v>-3.6069647167782937</ns0:v>
+        <ns0:v>-0.9573087158937121</ns0:v>
       </ns0:c>
       <ns0:c r="K36">
-        <ns0:v>1.563899849411944</ns0:v>
+        <ns0:v>1.1248105838636067</ns0:v>
       </ns0:c>
       <ns0:c r="L36">
-        <ns0:v>61.1915127132687</ns0:v>
+        <ns0:v>83.04975323859827</ns0:v>
       </ns0:c>
       <ns0:c r="M36">
-        <ns0:v>7.230499958992004</ns0:v>
+        <ns0:v>354.6157531738281</ns0:v>
       </ns0:c>
       <ns0:c r="N36">
-        <ns0:v>6.732399988174438</ns0:v>
+        <ns0:v>319.3111016845703</ns0:v>
       </ns0:c>
       <ns0:c r="O36">
-        <ns0:v>4.889199995994568</ns0:v>
+        <ns0:v>245.441350479126</ns0:v>
       </ns0:c>
       <ns0:c r="P36" t="inlineStr">
         <ns0:is>
@@ -2930,34 +2972,34 @@
       </ns0:c>
       <ns0:c r="R36" t="inlineStr">
         <ns0:is>
-          <ns0:t>다년래 신고가 기록, AdenoVerse의 FDA 플랫폼 지위 확보와 Papzimeos 외 성장 가능성을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>시그나테라의 방광암 동반진단 일본 PMDA 승인과 주가 급등이 보도됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S36" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://stocktwits.com/news-articles/markets/equity/mrna-pgen-stocks-hit-multi-year-highs-what-s-driving-the-momentum-today/cZMOKrcRBOS</ns0:t>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/stocks-making-big-moves-yesterday-170902420.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T36" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PGEN/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/NTRA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="37">
       <ns0:c r="A37" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B37" t="inlineStr">
         <ns0:is>
-          <ns0:t>PRLB</ns0:t>
+          <ns0:t>OESX</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C37" t="inlineStr">
         <ns0:is>
-          <ns0:t>Proto Labs Inc</ns0:t>
+          <ns0:t>Orion Energy Systems Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D37" t="inlineStr">
@@ -2967,44 +3009,44 @@
       </ns0:c>
       <ns0:c r="E37" t="inlineStr">
         <ns0:is>
-          <ns0:t>Metal Fabrication</ns0:t>
+          <ns0:t>Electrical Equipment &amp; Parts</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F37" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·유럽에서 성형·CNC 가공·3D 프린팅·판금 등 맞춤형 부품 제조 서비스를 제공.</ns0:t>
+          <ns0:t>북미와 독일에서 상업·산업·정부용 에너지 관리 시스템을 연구·설계·제조·판매·설치한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G37">
-        <ns0:v>96.25</ns0:v>
+        <ns0:v>30.459999084472656</ns0:v>
       </ns0:c>
       <ns0:c r="H37">
-        <ns0:v>3.5280184319998353</ns0:v>
+        <ns0:v>-0.4249789717776009</ns0:v>
       </ns0:c>
       <ns0:c r="I37">
-        <ns0:v>95.98999786376953</ns0:v>
+        <ns0:v>31.0</ns0:v>
       </ns0:c>
       <ns0:c r="J37">
-        <ns0:v>0.2708637795778124</ns0:v>
+        <ns0:v>-1.7419384371849755</ns0:v>
       </ns0:c>
       <ns0:c r="K37">
-        <ns0:v>1.1808118081180812</ns0:v>
+        <ns0:v>0.5204168485377565</ns0:v>
       </ns0:c>
       <ns0:c r="L37">
-        <ns0:v>73.89166461580626</ns0:v>
+        <ns0:v>66.14750631962619</ns0:v>
       </ns0:c>
       <ns0:c r="M37">
-        <ns0:v>83.58549919128419</ns0:v>
+        <ns0:v>26.954500007629395</ns0:v>
       </ns0:c>
       <ns0:c r="N37">
-        <ns0:v>82.76739990234375</ns0:v>
+        <ns0:v>20.672800045013428</ns0:v>
       </ns0:c>
       <ns0:c r="O37">
-        <ns0:v>68.56205001831054</ns0:v>
+        <ns0:v>13.997650027275085</ns0:v>
       </ns0:c>
       <ns0:c r="P37" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q37" t="inlineStr">
@@ -3014,77 +3056,77 @@
       </ns0:c>
       <ns0:c r="R37" t="inlineStr">
         <ns0:is>
-          <ns0:t>향후 사업 전개가 드러나지 않은 모험적 선택에 달렸는지 살펴보는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>실적 전망 상향과 소매업체 대상 사업 기회의 확실성을 점검하는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S37" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/protolabs-prlb-next-chapter-hinged-133431215.html</ns0:t>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/orion-energy-oesx-raises-guidance-195100572.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T37" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PRLB/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/OESX/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="38">
       <ns0:c r="A38" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B38" t="inlineStr">
         <ns0:is>
-          <ns0:t>QMCO</ns0:t>
+          <ns0:t>PRLB</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C38" t="inlineStr">
         <ns0:is>
-          <ns0:t>Quantum Corp</ns0:t>
+          <ns0:t>Proto Labs Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D38" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E38" t="inlineStr">
         <ns0:is>
-          <ns0:t>Computer Hardware</ns0:t>
+          <ns0:t>Metal Fabrication</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F38" t="inlineStr">
         <ns0:is>
-          <ns0:t>비정형 데이터 관리 솔루션과 영상 편집 등에 쓰이는 저장장치 소프트웨어·시스템을 제공.</ns0:t>
+          <ns0:t>미국과 유럽에서 금형 성형, CNC 가공, 3D 프린팅, 판금 등 맞춤형 부품 제조 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G38">
-        <ns0:v>31.68000030517578</ns0:v>
+        <ns0:v>96.9000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="H38">
-        <ns0:v>7.426248053763818</ns0:v>
+        <ns0:v>0.6753262606534083</ns0:v>
       </ns0:c>
       <ns0:c r="I38">
-        <ns0:v>32.08000183105469</ns0:v>
+        <ns0:v>96.91999816894531</ns0:v>
       </ns0:c>
       <ns0:c r="J38">
-        <ns0:v>-1.2468874783282846</ns0:v>
+        <ns0:v>-0.02063211250948882</ns0:v>
       </ns0:c>
       <ns0:c r="K38">
-        <ns0:v>3.081698823734679</ns0:v>
+        <ns0:v>1.2885937323226608</ns0:v>
       </ns0:c>
       <ns0:c r="L38">
-        <ns0:v>77.484675074693</ns0:v>
+        <ns0:v>74.57919618183305</ns0:v>
       </ns0:c>
       <ns0:c r="M38">
-        <ns0:v>24.835999965667725</ns0:v>
+        <ns0:v>84.44349937438965</ns0:v>
       </ns0:c>
       <ns0:c r="N38">
-        <ns0:v>19.671999988555907</ns0:v>
+        <ns0:v>83.15299987792969</ns0:v>
       </ns0:c>
       <ns0:c r="O38">
-        <ns0:v>10.913549993038178</ns0:v>
+        <ns0:v>68.79040002822876</ns0:v>
       </ns0:c>
       <ns0:c r="P38" t="inlineStr">
         <ns0:is>
@@ -3098,34 +3140,34 @@
       </ns0:c>
       <ns0:c r="R38" t="inlineStr">
         <ns0:is>
-          <ns0:t>주가 13.6% 상승의 지속 가능성, IBM과의 비교, S&amp;P 지수 편입 후 기대 반영 여부를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>매도를 주장하는 근거와 향후 사업 전개에 숨은 위험을 짚는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S38" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/strength-seen-quantum-corp-qmco-110300189.html</ns0:t>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/3-reasons-sell-prlb-1-002437847.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T38" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/QMCO/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PRLB/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="39">
       <ns0:c r="A39" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B39" t="inlineStr">
         <ns0:is>
-          <ns0:t>RCEL</ns0:t>
+          <ns0:t>RGEN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C39" t="inlineStr">
         <ns0:is>
-          <ns0:t>AVITA Medical Inc</ns0:t>
+          <ns0:t>Repligen Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D39" t="inlineStr">
@@ -3135,40 +3177,40 @@
       </ns0:c>
       <ns0:c r="E39" t="inlineStr">
         <ns0:is>
-          <ns0:t>Medical Devices</ns0:t>
+          <ns0:t>Medical Instruments &amp; Supplies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F39" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·일본·유럽 등에서 급성 상처 치료 사업을 운영하며 세포 채취 장치 RECELL을 제공.</ns0:t>
+          <ns0:t>바이오 공정 기술과 시스템을 개발·상용화하며 중공사 소모품, 크로마토그래피 시스템 등을 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G39">
-        <ns0:v>11.84000015258789</ns0:v>
+        <ns0:v>194.08999633789062</ns0:v>
       </ns0:c>
       <ns0:c r="H39">
-        <ns0:v>2.245252423098676</ns0:v>
+        <ns0:v>2.3249703882303407</ns0:v>
       </ns0:c>
       <ns0:c r="I39">
-        <ns0:v>11.8100004196167</ns0:v>
+        <ns0:v>192.49000549316406</ns0:v>
       </ns0:c>
       <ns0:c r="J39">
-        <ns0:v>0.2540197451759596</ns0:v>
+        <ns0:v>0.8312072310597829</ns0:v>
       </ns0:c>
       <ns0:c r="K39">
-        <ns0:v>1.1741238779791587</ns0:v>
+        <ns0:v>1.5212774838615735</ns0:v>
       </ns0:c>
       <ns0:c r="L39">
-        <ns0:v>67.95000382706597</ns0:v>
+        <ns0:v>70.58733831498354</ns0:v>
       </ns0:c>
       <ns0:c r="M39">
-        <ns0:v>10.675999975204467</ns0:v>
+        <ns0:v>176.08599929809571</ns0:v>
       </ns0:c>
       <ns0:c r="N39">
-        <ns0:v>8.425600004196166</ns0:v>
+        <ns0:v>165.95399963378907</ns0:v>
       </ns0:c>
       <ns0:c r="O39">
-        <ns0:v>5.2528000104427335</ns0:v>
+        <ns0:v>142.99584972381592</ns0:v>
       </ns0:c>
       <ns0:c r="P39" t="inlineStr">
         <ns0:is>
@@ -3182,34 +3224,34 @@
       </ns0:c>
       <ns0:c r="R39" t="inlineStr">
         <ns0:is>
-          <ns0:t>아비타 메디컬의 투자의견이 매수로 상향된 내용을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>투자 회피 근거를 제시하는 의견과 최근 반등 후 적정 가치에 근접했다는 평가. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S39" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/know-avita-medical-rcel-rating-160002727.html</ns0:t>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/3-reasons-avoid-rgen-1-191438284.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T39" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/RCEL/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/RGEN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="40">
       <ns0:c r="A40" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B40" t="inlineStr">
         <ns0:is>
-          <ns0:t>RDVT</ns0:t>
+          <ns0:t>SAIH</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C40" t="inlineStr">
         <ns0:is>
-          <ns0:t>Red Violet Inc</ns0:t>
+          <ns0:t>SAIHEAT Ltd</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D40" t="inlineStr">
@@ -3219,40 +3261,40 @@
       </ns0:c>
       <ns0:c r="E40" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Information Technology Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F40" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 자체 기술·분석 역량을 활용한 신원 정보 및 조사 솔루션 idiCORE를 제공.</ns0:t>
+          <ns0:t>암호화폐 채굴용 액체냉각 기술을 개발하며, 비트코인 채굴기 냉각 전환 캐비닛과 실외 인프라 제품을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G40">
-        <ns0:v>78.55000305175781</ns0:v>
+        <ns0:v>31.700000762939453</ns0:v>
       </ns0:c>
       <ns0:c r="H40">
-        <ns0:v>-0.6450727581391202</ns0:v>
+        <ns0:v>3.781308507973802</ns0:v>
       </ns0:c>
       <ns0:c r="I40">
-        <ns0:v>80.29000091552734</ns0:v>
+        <ns0:v>32.5</ns0:v>
       </ns0:c>
       <ns0:c r="J40">
-        <ns0:v>-2.1671414172733328</ns0:v>
+        <ns0:v>-2.4615361140324477</ns0:v>
       </ns0:c>
       <ns0:c r="K40">
-        <ns0:v>1.0711910941421248</ns0:v>
+        <ns0:v>0.6713690913543963</ns0:v>
       </ns0:c>
       <ns0:c r="L40">
-        <ns0:v>61.02085313027524</ns0:v>
+        <ns0:v>78.16976590185384</ns0:v>
       </ns0:c>
       <ns0:c r="M40">
-        <ns0:v>75.45250053405762</ns0:v>
+        <ns0:v>26.098499965667724</ns0:v>
       </ns0:c>
       <ns0:c r="N40">
-        <ns0:v>70.86650039672851</ns0:v>
+        <ns0:v>22.32663999557495</ns0:v>
       </ns0:c>
       <ns0:c r="O40">
-        <ns0:v>53.92812496185303</ns0:v>
+        <ns0:v>12.81882000207901</ns0:v>
       </ns0:c>
       <ns0:c r="P40" t="inlineStr">
         <ns0:is>
@@ -3261,82 +3303,77 @@
       </ns0:c>
       <ns0:c r="Q40" t="inlineStr">
         <ns0:is>
-          <ns0:t>보도된 해석</ns0:t>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R40" t="inlineStr">
         <ns0:is>
-          <ns0:t>높은 주가수익비율 속 6% 저평가 가능성과 성장주·모멘텀 종목으로서의 평가를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="S40" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/red-violet-rdvt-could-6-090857658.html</ns0:t>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T40" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/RDVT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SAIH/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="41">
       <ns0:c r="A41" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B41" t="inlineStr">
         <ns0:is>
-          <ns0:t>RSKD</ns0:t>
+          <ns0:t>SBFG</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C41" t="inlineStr">
         <ns0:is>
-          <ns0:t>Riskified Ltd</ns0:t>
+          <ns0:t>SB Financial Group Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D41" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E41" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Banks - Regional</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F41" t="inlineStr">
         <ns0:is>
-          <ns0:t>온라인 판매자·소비자의 신뢰 구축을 지원하는 전자상거래 위험 분석 플랫폼을 개발·제공.</ns0:t>
+          <ns0:t>주로 오하이오의 개인·기업에 상업은행·신탁·자산관리·권원보험을 제공하는 State Bank and Trust의 지주사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G41">
-        <ns0:v>7.78000020980835</ns0:v>
+        <ns0:v>29.989999771118164</ns0:v>
       </ns0:c>
       <ns0:c r="H41">
-        <ns0:v>-1.643484704317555</ns0:v>
+        <ns0:v>0.4353622173789651</ns0:v>
       </ns0:c>
       <ns0:c r="I41">
-        <ns0:v>8.020000457763672</ns0:v>
+        <ns0:v>30.84000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="J41">
-        <ns0:v>-2.9925216241477037</ns0:v>
+        <ns0:v>-2.7561620533857245</ns0:v>
       </ns0:c>
       <ns0:c r="K41">
-        <ns0:v>1.3970272771819023</ns0:v>
+        <ns0:v>0.5506940253470127</ns0:v>
       </ns0:c>
       <ns0:c r="L41">
-        <ns0:v>73.60458049582746</ns0:v>
+        <ns0:v>61.170719432302356</ns0:v>
       </ns0:c>
       <ns0:c r="M41">
-        <ns0:v>6.524499988555908</ns0:v>
+        <ns0:v>29.335499954223632</ns0:v>
       </ns0:c>
       <ns0:c r="N41">
-        <ns0:v>5.95959997177124</ns0:v>
+        <ns0:v>27.85879997253418</ns0:v>
       </ns0:c>
       <ns0:c r="O41">
-        <ns0:v>4.9680499947071075</ns0:v>
+        <ns0:v>23.589499950408936</ns0:v>
       </ns0:c>
       <ns0:c r="P41" t="inlineStr">
         <ns0:is>
@@ -3350,77 +3387,77 @@
       </ns0:c>
       <ns0:c r="R41" t="inlineStr">
         <ns0:is>
-          <ns0:t>주가 10.4% 상승과 추가 상승 가능성을 살펴보는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>투자 매력과 저평가 여부, 주가 신고점 이후 추가 상승 여력을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S41" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/riskified-rskd-stock-jumps-10-175800513.html</ns0:t>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/sb-financial-group-inc-sbfg-154503016.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T41" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/RSKD/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SBFG/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="42">
       <ns0:c r="A42" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B42" t="inlineStr">
         <ns0:is>
-          <ns0:t>SAIH</ns0:t>
+          <ns0:t>SGHT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C42" t="inlineStr">
         <ns0:is>
-          <ns0:t>SAIHEAT Ltd</ns0:t>
+          <ns0:t>Sight Sciences Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D42" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E42" t="inlineStr">
         <ns0:is>
-          <ns0:t>Information Technology Services</ns0:t>
+          <ns0:t>Medical Devices</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F42" t="inlineStr">
         <ns0:is>
-          <ns0:t>암호화폐 채굴용 액체냉각 기술과 비트코인 채굴기 냉각 전환 캐비닛·실외 인프라 제품을 제공.</ns0:t>
+          <ns0:t>미국에서 주요 안질환 치료를 위한 수술·비수술 기술을 개발하고 상용화하는 안과 의료기기 기업이다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G42">
-        <ns0:v>30.545000076293945</ns0:v>
+        <ns0:v>9.270000457763672</ns0:v>
       </ns0:c>
       <ns0:c r="H42">
-        <ns0:v>1.8166669209798147</ns0:v>
+        <ns0:v>3.807392396065512</ns0:v>
       </ns0:c>
       <ns0:c r="I42">
-        <ns0:v>30.299999237060547</ns0:v>
+        <ns0:v>9.236000061035156</ns0:v>
       </ns0:c>
       <ns0:c r="J42">
-        <ns0:v>0.80858364819274</ns0:v>
+        <ns0:v>0.36812902234546474</ns0:v>
       </ns0:c>
       <ns0:c r="K42">
-        <ns0:v>0.6383513445589344</ns0:v>
+        <ns0:v>2.293816098707403</ns0:v>
       </ns0:c>
       <ns0:c r="L42">
-        <ns0:v>75.79990055678368</ns0:v>
+        <ns0:v>76.00181961463866</ns0:v>
       </ns0:c>
       <ns0:c r="M42">
-        <ns0:v>25.70099992752075</ns0:v>
+        <ns0:v>8.353750133514405</ns0:v>
       </ns0:c>
       <ns0:c r="N42">
-        <ns0:v>21.95523998260498</ns0:v>
+        <ns0:v>7.455700054168701</ns0:v>
       </ns0:c>
       <ns0:c r="O42">
-        <ns0:v>12.701919996738434</ns0:v>
+        <ns0:v>5.882875022888183</ns0:v>
       </ns0:c>
       <ns0:c r="P42" t="inlineStr">
         <ns0:is>
@@ -3439,24 +3476,24 @@
       </ns0:c>
       <ns0:c r="T42" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SAIH/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SGHT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="43">
       <ns0:c r="A43" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B43" t="inlineStr">
         <ns0:is>
-          <ns0:t>SBFG</ns0:t>
+          <ns0:t>SVRN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C43" t="inlineStr">
         <ns0:is>
-          <ns0:t>SB Financial Group Inc</ns0:t>
+          <ns0:t>SVRN Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D43" t="inlineStr">
@@ -3466,124 +3503,119 @@
       </ns0:c>
       <ns0:c r="E43" t="inlineStr">
         <ns0:is>
-          <ns0:t>Banks - Regional</ns0:t>
+          <ns0:t>Asset Management</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F43" t="inlineStr">
         <ns0:is>
-          <ns0:t>오하이오 개인·기업에 은행·신탁·자산관리·권원보험을 제공하는 State Bank and Trust의 지주사.</ns0:t>
+          <ns0:t>AI 에이전트 경제의 기반 인프라를 개발하며 개인의 자산·데이터·AI 에이전트 통제를 지원한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G43">
-        <ns0:v>29.860000610351562</ns0:v>
+        <ns0:v>52.05500030517578</ns0:v>
       </ns0:c>
       <ns0:c r="H43">
-        <ns0:v>-2.8311062311895285</ns0:v>
+        <ns0:v>10.14600540402013</ns0:v>
       </ns0:c>
       <ns0:c r="I43">
-        <ns0:v>30.729999542236328</ns0:v>
+        <ns0:v>52.0</ns0:v>
       </ns0:c>
       <ns0:c r="J43">
-        <ns0:v>-2.8311062311895285</ns0:v>
+        <ns0:v>0.10576981764574</ns0:v>
       </ns0:c>
       <ns0:c r="K43">
-        <ns0:v>0.997229916897507</ns0:v>
+        <ns0:v>1.2829654408819995</ns0:v>
       </ns0:c>
       <ns0:c r="L43">
-        <ns0:v>60.13029726061827</ns0:v>
+        <ns0:v>92.78688862330982</ns0:v>
       </ns0:c>
       <ns0:c r="M43">
-        <ns0:v>29.21899995803833</ns0:v>
+        <ns0:v>20.021749830245973</ns0:v>
       </ns0:c>
       <ns0:c r="N43">
-        <ns0:v>27.80059997558594</ns0:v>
+        <ns0:v>12.251099967956543</ns0:v>
       </ns0:c>
       <ns0:c r="O43">
-        <ns0:v>23.548649950027468</ns0:v>
+        <ns0:v>12.43597000837326</ns0:v>
       </ns0:c>
       <ns0:c r="P43" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q43" t="inlineStr">
         <ns0:is>
-          <ns0:t>보도된 해석</ns0:t>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R43" t="inlineStr">
         <ns0:is>
-          <ns0:t>투자 매력과 저평가 여부, 신고가 기록 이후 추가 상승 여력을 살펴보는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="S43" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/sb-financial-group-inc-sbfg-154503016.html</ns0:t>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T43" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SBFG/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SVRN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="44">
       <ns0:c r="A44" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B44" t="inlineStr">
         <ns0:is>
-          <ns0:t>SILC</ns0:t>
+          <ns0:t>TWST</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C44" t="inlineStr">
         <ns0:is>
-          <ns0:t>Silicom Ltd</ns0:t>
+          <ns0:t>Twist Bioscience Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D44" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E44" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Equipment</ns0:t>
+          <ns0:t>Biotechnology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F44" t="inlineStr">
         <ns0:is>
-          <ns0:t>서버 네트워크 인터페이스 카드와 암호화·압축용 카드 등 네트워크·데이터 인프라 솔루션을 제공.</ns0:t>
+          <ns0:t>치료제, 진단, 화학·소재, 식품·농업, 데이터 저장과 학술 연구에 쓰이는 합성 DNA 제품을 제조·판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G44">
-        <ns0:v>52.779998779296875</ns0:v>
+        <ns0:v>179.60000610351562</ns0:v>
       </ns0:c>
       <ns0:c r="H44">
-        <ns0:v>2.2471907621361753</ns0:v>
+        <ns0:v>-1.766666135311734</ns0:v>
       </ns0:c>
       <ns0:c r="I44">
-        <ns0:v>52.95000076293945</ns0:v>
+        <ns0:v>186.1999969482422</ns0:v>
       </ns0:c>
       <ns0:c r="J44">
-        <ns0:v>-0.32106134314083823</ns0:v>
+        <ns0:v>-3.5445708662181996</ns0:v>
       </ns0:c>
       <ns0:c r="K44">
-        <ns0:v>0.6873830862439624</ns0:v>
+        <ns0:v>1.1176667217848102</ns0:v>
       </ns0:c>
       <ns0:c r="L44">
-        <ns0:v>66.51640959102025</ns0:v>
+        <ns0:v>70.53102389721931</ns0:v>
       </ns0:c>
       <ns0:c r="M44">
-        <ns0:v>44.19300003051758</ns0:v>
+        <ns0:v>146.8500015258789</ns0:v>
       </ns0:c>
       <ns0:c r="N44">
-        <ns0:v>43.617800064086914</ns0:v>
+        <ns0:v>127.99180084228516</ns0:v>
       </ns0:c>
       <ns0:c r="O44">
-        <ns0:v>31.80054995059967</ns0:v>
+        <ns0:v>73.91230013847351</ns0:v>
       </ns0:c>
       <ns0:c r="P44" t="inlineStr">
         <ns0:is>
@@ -3592,34 +3624,39 @@
       </ns0:c>
       <ns0:c r="Q44" t="inlineStr">
         <ns0:is>
-          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+          <ns0:t>보도된 해석</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R44" t="inlineStr">
         <ns0:is>
-          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+          <ns0:t>투자 판단 조건, 급등과 앤트로픽의 연관성에 대한 리링크의 해석, 릴리 TuneLab과의 AI 신약 개발 협력을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S44" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://www.trefis.com/articles/616634/what-needs-to-be-true-to-buy-twist-bioscience-stock-now/2026-09-25</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T44" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SILC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/TWST/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="45">
       <ns0:c r="A45" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B45" t="inlineStr">
         <ns0:is>
-          <ns0:t>SRZN</ns0:t>
+          <ns0:t>TXG</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C45" t="inlineStr">
         <ns0:is>
-          <ns0:t>Surrozen Inc</ns0:t>
+          <ns0:t>10x Genomics Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D45" t="inlineStr">
@@ -3629,119 +3666,121 @@
       </ns0:c>
       <ns0:c r="E45" t="inlineStr">
         <ns0:is>
-          <ns0:t>Biotechnology</ns0:t>
+          <ns0:t>Medical Devices</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F45" t="inlineStr">
         <ns0:is>
-          <ns0:t>조직 복구를 위해 Wnt 경로를 선택적으로 조절하는 항체 기반 치료제 후보를 발굴·개발.</ns0:t>
+          <ns0:t>생물학적 시스템 분석용 장비, 소모품, 소프트웨어를 개발·판매하며 Chromium 플랫폼을 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G45">
-        <ns0:v>29.540000915527344</ns0:v>
+        <ns0:v>88.5</ns0:v>
       </ns0:c>
       <ns0:c r="H45">
-        <ns0:v>-12.29215959660256</ns0:v>
+        <ns0:v>3.2551638610771816</ns0:v>
       </ns0:c>
       <ns0:c r="I45">
-        <ns0:v>35.86000061035156</ns0:v>
+        <ns0:v>86.16000366210938</ns0:v>
       </ns0:c>
       <ns0:c r="J45">
-        <ns0:v>-17.624092546724192</ns0:v>
+        <ns0:v>2.715873071532471</ns0:v>
       </ns0:c>
       <ns0:c r="K45">
-        <ns0:v>2.5624605573454677</ns0:v>
+        <ns0:v>1.1965389698985247</ns0:v>
       </ns0:c>
       <ns0:c r="L45">
-        <ns0:v>65.57668098652911</ns0:v>
+        <ns0:v>75.94420555196685</ns0:v>
       </ns0:c>
       <ns0:c r="M45">
-        <ns0:v>20.662000370025634</ns0:v>
+        <ns0:v>72.11499977111816</ns0:v>
       </ns0:c>
       <ns0:c r="N45">
-        <ns0:v>21.875000076293944</ns0:v>
+        <ns0:v>61.261199951171875</ns0:v>
       </ns0:c>
       <ns0:c r="O45">
-        <ns0:v>24.363800010681153</ns0:v>
+        <ns0:v>33.261000032424924</ns0:v>
       </ns0:c>
       <ns0:c r="P45" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q45" t="inlineStr">
         <ns0:is>
-          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+          <ns0:t>보도된 해석</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R45" t="inlineStr">
         <ns0:is>
-          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+          <ns0:t>의료·생명과학 종목들과 동반 하락한 흐름 및 동종 기업 대비 2분기 실적을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S45" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/healthcare/articles/surgery-partners-10x-genomics-quidelortho-213005328.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T45" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SRZN/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/TXG/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="46">
       <ns0:c r="A46" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B46" t="inlineStr">
         <ns0:is>
-          <ns0:t>TBBB</ns0:t>
+          <ns0:t>VNME</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C46" t="inlineStr">
         <ns0:is>
-          <ns0:t>BBB Foods Inc</ns0:t>
+          <ns0:t>Vendome Acquisition Corp I</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D46" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Defensive</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E46" t="inlineStr">
         <ns0:is>
-          <ns0:t>Discount Stores</ns0:t>
+          <ns0:t>Shell Companies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F46" t="inlineStr">
         <ns0:is>
-          <ns0:t>멕시코 식료품 소매 체인으로 식품·의류·전자제품·생활용품과 브랜드·자체상표 상품을 판매.</ns0:t>
+          <ns0:t>현재 유의미한 사업 운영 없이 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G46">
-        <ns0:v>53.560001373291016</ns0:v>
+        <ns0:v>10.3100004196167</ns0:v>
       </ns0:c>
       <ns0:c r="H46">
-        <ns0:v>1.0184853090627888</ns0:v>
+        <ns0:v>0.38948354498649085</ns0:v>
       </ns0:c>
       <ns0:c r="I46">
-        <ns0:v>53.33000183105469</ns0:v>
+        <ns0:v>10.300000190734863</ns0:v>
       </ns0:c>
       <ns0:c r="J46">
-        <ns0:v>0.43127608164152953</ns0:v>
-      </ns0:c>
-      <ns0:c r="K46">
-        <ns0:v>1.8259554721309765</ns0:v>
+        <ns0:v>0.09708959899661362</ns0:v>
       </ns0:c>
       <ns0:c r="L46">
-        <ns0:v>67.7936821600555</ns0:v>
+        <ns0:v>67.43826925531627</ns0:v>
       </ns0:c>
       <ns0:c r="M46">
-        <ns0:v>50.878000259399414</ns0:v>
+        <ns0:v>10.285000085830688</ns0:v>
       </ns0:c>
       <ns0:c r="N46">
-        <ns0:v>46.77760025024414</ns0:v>
+        <ns0:v>10.255160083770752</ns0:v>
       </ns0:c>
       <ns0:c r="O46">
-        <ns0:v>39.159450149536134</ns0:v>
+        <ns0:v>10.152619972229004</ns0:v>
       </ns0:c>
       <ns0:c r="P46" t="inlineStr">
         <ns0:is>
@@ -3750,161 +3789,161 @@
       </ns0:c>
       <ns0:c r="Q46" t="inlineStr">
         <ns0:is>
-          <ns0:t>보도된 해석</ns0:t>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R46" t="inlineStr">
         <ns0:is>
-          <ns0:t>주가 98% 상승 이후 BBB Foods 이사가 보유 지분 전량을 매각했다는 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="S46" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://www.fool.com/coverage/filings/2026/09/15/bbb-foods-director-sells-full-stake-after-98-stock-gain/</ns0:t>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T46" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/TBBB/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/VNME/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="47">
       <ns0:c r="A47" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B47" t="inlineStr">
         <ns0:is>
-          <ns0:t>TJGC</ns0:t>
+          <ns0:t>WAT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C47" t="inlineStr">
         <ns0:is>
-          <ns0:t>TJGC Group Ltd</ns0:t>
+          <ns0:t>Waters Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D47" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Services</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E47" t="inlineStr">
         <ns0:is>
-          <ns0:t>Advertising Agencies</ns0:t>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F47" t="inlineStr">
         <ns0:is>
-          <ns0:t>자회사 Ctrl Media를 통해 홍콩에서 모바일 게임 앱 개발사 등에 통합 마케팅·광고를 제공.</ns0:t>
+          <ns0:t>분석 업무 솔루션을 제공하며 액체 크로마토그래피와 질량분석 시스템을 설계·제조·판매·서비스한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G47">
-        <ns0:v>26.239999771118164</ns0:v>
+        <ns0:v>442.94000244140625</ns0:v>
       </ns0:c>
       <ns0:c r="H47">
-        <ns0:v>-6.9503579389867625</ns0:v>
+        <ns0:v>2.1681952556197315</ns0:v>
       </ns0:c>
       <ns0:c r="I47">
-        <ns0:v>28.549999237060547</ns0:v>
+        <ns0:v>436.3399963378906</ns0:v>
       </ns0:c>
       <ns0:c r="J47">
-        <ns0:v>-8.091066646838252</ns0:v>
+        <ns0:v>1.5125833430141844</ns0:v>
       </ns0:c>
       <ns0:c r="K47">
-        <ns0:v>0.06470879504473334</ns0:v>
+        <ns0:v>1.4940341687730305</ns0:v>
       </ns0:c>
       <ns0:c r="L47">
-        <ns0:v>84.33039935941575</ns0:v>
+        <ns0:v>68.6476043243118</ns0:v>
       </ns0:c>
       <ns0:c r="M47">
-        <ns0:v>13.842500019073487</ns0:v>
+        <ns0:v>417.3705032348633</ns0:v>
       </ns0:c>
       <ns0:c r="N47">
-        <ns0:v>8.431300005912782</ns0:v>
+        <ns0:v>405.08220153808594</ns0:v>
       </ns0:c>
       <ns0:c r="O47">
-        <ns0:v>4.797375011444092</ns0:v>
+        <ns0:v>362.6722007751465</ns0:v>
       </ns0:c>
       <ns0:c r="P47" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q47" t="inlineStr">
         <ns0:is>
-          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+          <ns0:t>보도된 해석</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R47" t="inlineStr">
         <ns0:is>
-          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+          <ns0:t>가정용 HPV 검사·세포 분석 확대, AI 수요와 BD 통합을 배경으로 한 성장 전망 상회, 견조한 실적을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S47" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/healthcare/articles/bull-case-waters-wat-could-231014773.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T47" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/TJGC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/WAT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="48">
       <ns0:c r="A48" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B48" t="inlineStr">
         <ns0:is>
-          <ns0:t>TKNO</ns0:t>
+          <ns0:t>XRPN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C48" t="inlineStr">
         <ns0:is>
-          <ns0:t>Alpha Teknova Inc</ns0:t>
+          <ns0:t>Armada Acquisition Corp II</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D48" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E48" t="inlineStr">
         <ns0:is>
-          <ns0:t>Drug Manufacturers - Specialty &amp; Generic</ns0:t>
+          <ns0:t>Shell Companies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F48" t="inlineStr">
         <ns0:is>
-          <ns0:t>치료제·백신·분자진단의 발굴·개발·상용화용 시약과 세포 배양·복제용 배지 등을 생산.</ns0:t>
+          <ns0:t>기술 서비스 분야 기업과 합병, 주식 교환, 자산 인수, 자본 재편 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G48">
-        <ns0:v>9.329999923706055</ns0:v>
+        <ns0:v>10.574999809265137</ns0:v>
       </ns0:c>
       <ns0:c r="H48">
-        <ns0:v>0.43057009706433114</ns0:v>
+        <ns0:v>-0.04726006121904547</ns0:v>
       </ns0:c>
       <ns0:c r="I48">
-        <ns0:v>9.40999984741211</ns0:v>
+        <ns0:v>10.906000137329102</ns0:v>
       </ns0:c>
       <ns0:c r="J48">
-        <ns0:v>-0.8501586078989765</ns0:v>
+        <ns0:v>-3.03502956075542</ns0:v>
       </ns0:c>
       <ns0:c r="K48">
-        <ns0:v>1.287419205400278</ns0:v>
+        <ns0:v>1.8376434617929587</ns0:v>
       </ns0:c>
       <ns0:c r="L48">
-        <ns0:v>80.51748329392791</ns0:v>
+        <ns0:v>65.78657988578104</ns0:v>
       </ns0:c>
       <ns0:c r="M48">
-        <ns0:v>7.557750010490418</ns0:v>
+        <ns0:v>10.548499965667725</ns0:v>
       </ns0:c>
       <ns0:c r="N48">
-        <ns0:v>6.754900007247925</ns0:v>
+        <ns0:v>10.508999977111817</ns0:v>
       </ns0:c>
       <ns0:c r="O48">
-        <ns0:v>4.4307499957084655</ns0:v>
+        <ns0:v>10.372494988441467</ns0:v>
       </ns0:c>
       <ns0:c r="P48" t="inlineStr">
         <ns0:is>
@@ -3918,17 +3957,17 @@
       </ns0:c>
       <ns0:c r="R48" t="inlineStr">
         <ns0:is>
-          <ns0:t>주가 7.1% 상승과 상승세 지속 가능성을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>에버노스의 XRP 재무자산 보유 종목 XRPN이 나스닥 진출까지 표결 하나를 남겨뒀다는 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S48" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/alpha-teknova-tkno-moves-7-125300864.html</ns0:t>
+          <ns0:t>https://www.ccn.com/news/crypto/evernorth-xrp-treasury-xrpn-nasdaq-vote/</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T48" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/TKNO/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/XRPN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3940,55 +3979,45 @@
       </ns0:c>
       <ns0:c r="B49" t="inlineStr">
         <ns0:is>
-          <ns0:t>TWIN</ns0:t>
+          <ns0:t>AMD</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C49" t="inlineStr">
         <ns0:is>
-          <ns0:t>Twin Disc Incorporated</ns0:t>
+          <ns0:t>Advanced Micro Devices Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D49" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E49" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Specialty Industrial Machinery</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F49" t="inlineStr">
-        <ns0:is>
-          <ns0:t>선박·중장비용 동력전달 장비를 설계·제조·판매하며 제조와 유통 부문을 운영.</ns0:t>
+          <ns0:t/>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G49">
-        <ns0:v>26.1299991607666</ns0:v>
+        <ns0:v>630.6300048828125</ns0:v>
       </ns0:c>
       <ns0:c r="H49">
-        <ns0:v>0.7324542127881806</ns0:v>
+        <ns0:v>0.21771526808096464</ns0:v>
       </ns0:c>
       <ns0:c r="I49">
-        <ns0:v>26.18000030517578</ns0:v>
+        <ns0:v>630.7999877929688</ns0:v>
       </ns0:c>
       <ns0:c r="J49">
-        <ns0:v>-0.1909898541876398</ns0:v>
+        <ns0:v>-0.026947196170845622</ns0:v>
       </ns0:c>
       <ns0:c r="K49">
-        <ns0:v>0.6961598922075005</ns0:v>
+        <ns0:v>0.8157954096816155</ns0:v>
       </ns0:c>
       <ns0:c r="L49">
-        <ns0:v>66.17698878916215</ns0:v>
+        <ns0:v>72.99571503316014</ns0:v>
       </ns0:c>
       <ns0:c r="M49">
-        <ns0:v>24.394500160217284</ns0:v>
+        <ns0:v>528.1040023803711</ns0:v>
       </ns0:c>
       <ns0:c r="N49">
-        <ns0:v>23.876800117492675</ns0:v>
+        <ns0:v>504.7130029296875</ns0:v>
       </ns0:c>
       <ns0:c r="O49">
-        <ns0:v>19.330750093460082</ns0:v>
+        <ns0:v>364.753550567627</ns0:v>
       </ns0:c>
       <ns0:c r="P49" t="inlineStr">
         <ns0:is>
@@ -4002,17 +4031,12 @@
       </ns0:c>
       <ns0:c r="R49" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업 동향 관련 기사 제목 2건 확인. 주가 상승과의 인과는 미확인입니다.</ns0:t>
+          <ns0:t>동종 반도체 기업 대비 주가 적정성, 애널리스트의 새 목표주가, 완성형 시스템 수요와 주가 상승을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S49" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://www.marketbeat.com/instant-alerts/event-twin-disc-targets-500m-as-defense-electrification-drive-record-growth-2026-08-28/</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="T49" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/TWIN/profile/</ns0:t>
+          <ns0:t>https://www.trefis.com/articles/616631/is-amd-stock-priced-right-against-its-chip-peers/2026-09-25</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4024,55 +4048,45 @@
       </ns0:c>
       <ns0:c r="B50" t="inlineStr">
         <ns0:is>
-          <ns0:t>TWST</ns0:t>
+          <ns0:t>HPE</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C50" t="inlineStr">
         <ns0:is>
-          <ns0:t>Twist Bioscience Corp</ns0:t>
+          <ns0:t>Hewlett Packard Enterprise Co</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D50" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E50" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Biotechnology</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F50" t="inlineStr">
-        <ns0:is>
-          <ns0:t>치료제·진단·화학소재·농식품·데이터 저장·학술연구용 합성 DNA·유전자·유전자 조각을 제조·판매.</ns0:t>
+          <ns0:t/>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G50">
-        <ns0:v>182.8300018310547</ns0:v>
+        <ns0:v>62.939998626708984</ns0:v>
       </ns0:c>
       <ns0:c r="H50">
-        <ns0:v>-0.652065943705904</ns0:v>
+        <ns0:v>-0.9131011128382327</ns0:v>
       </ns0:c>
       <ns0:c r="I50">
-        <ns0:v>185.22000122070312</ns0:v>
+        <ns0:v>65.4800033569336</ns0:v>
       </ns0:c>
       <ns0:c r="J50">
-        <ns0:v>-1.2903570747743287</ns0:v>
+        <ns0:v>-3.8790540623203085</ns0:v>
       </ns0:c>
       <ns0:c r="K50">
-        <ns0:v>1.4297526119057997</ns0:v>
+        <ns0:v>0.5506095863383583</ns0:v>
       </ns0:c>
       <ns0:c r="L50">
-        <ns0:v>73.35930688123281</ns0:v>
+        <ns0:v>61.301337066088976</ns0:v>
       </ns0:c>
       <ns0:c r="M50">
-        <ns0:v>144.93900146484376</ns0:v>
+        <ns0:v>57.36350021362305</ns0:v>
       </ns0:c>
       <ns0:c r="N50">
-        <ns0:v>126.27680068969727</ns0:v>
+        <ns0:v>53.94500015258789</ns0:v>
       </ns0:c>
       <ns0:c r="O50">
-        <ns0:v>73.17220010757447</ns0:v>
+        <ns0:v>35.905800123214725</ns0:v>
       </ns0:c>
       <ns0:c r="P50" t="inlineStr">
         <ns0:is>
@@ -4086,17 +4100,12 @@
       </ns0:c>
       <ns0:c r="R50" t="inlineStr">
         <ns0:is>
-          <ns0:t>주가 16% 급등을 Anthropic과 연결한 Leerink의 해석과 Lilly TuneLab 제휴를 통한 AI 신약개발 확대 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>네트워킹·양자 분야 제휴 확대, 주가의 52주 최고가 기록과 매도 여부, 긍정적 종목 평가를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S50" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://www.tikr.com/blog/twist-bioscience-stock-jumped-16-thursday-leerink-says-anthropic-made-it-happen</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="T50" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/TWST/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/technology/articles/hpe-expanded-networking-quantum-partnerships-131208305.html</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4108,55 +4117,52 @@
       </ns0:c>
       <ns0:c r="B51" t="inlineStr">
         <ns0:is>
-          <ns0:t>TXG</ns0:t>
+          <ns0:t>ABLV</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C51" t="inlineStr">
         <ns0:is>
-          <ns0:t>10x Genomics Inc</ns0:t>
+          <ns0:t>Able View Global Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D51" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E51" t="inlineStr">
         <ns0:is>
-          <ns0:t>Medical Devices</ns0:t>
+          <ns0:t>Specialty Retail</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F51" t="inlineStr">
         <ns0:is>
-          <ns0:t>생물학적 시스템 분석용 장비·소모품·소프트웨어를 개발·판매하며 Chromium 플랫폼 등을 제공.</ns0:t>
+          <ns0:t>마케팅 전략·브랜딩·디지털 마케팅·온오프라인 판매·고객 서비스를 제공하는 브랜드 관리 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G51">
-        <ns0:v>85.70999908447266</ns0:v>
+        <ns0:v>1.2999999523162842</ns0:v>
       </ns0:c>
       <ns0:c r="H51">
-        <ns0:v>1.9022690078594362</ns0:v>
+        <ns0:v>14.035084967467881</ns0:v>
       </ns0:c>
       <ns0:c r="I51">
-        <ns0:v>85.93000030517578</ns0:v>
+        <ns0:v>1.2999999523162842</ns0:v>
       </ns0:c>
       <ns0:c r="J51">
-        <ns0:v>-0.2560237634374518</ns0:v>
-      </ns0:c>
-      <ns0:c r="K51">
-        <ns0:v>1.228051116591165</ns0:v>
+        <ns0:v>0.0</ns0:v>
       </ns0:c>
       <ns0:c r="L51">
-        <ns0:v>73.93009622870196</ns0:v>
+        <ns0:v>69.06584562985581</ns0:v>
       </ns0:c>
       <ns0:c r="M51">
-        <ns0:v>70.76699981689453</ns0:v>
+        <ns0:v>1.0067999958992004</ns0:v>
       </ns0:c>
       <ns0:c r="N51">
-        <ns0:v>60.36599998474121</ns0:v>
+        <ns0:v>0.9164199948310852</ns0:v>
       </ns0:c>
       <ns0:c r="O51">
-        <ns0:v>32.907700033187865</ns0:v>
+        <ns0:v>0.847754997909069</ns0:v>
       </ns0:c>
       <ns0:c r="P51" t="inlineStr">
         <ns0:is>
@@ -4165,22 +4171,17 @@
       </ns0:c>
       <ns0:c r="Q51" t="inlineStr">
         <ns0:is>
-          <ns0:t>보도된 해석</ns0:t>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="R51" t="inlineStr">
         <ns0:is>
-          <ns0:t>주가 하락, 동종 생명과학 도구·서비스 기업과의 2분기 비교, 종양학 AI 소식 속 고평가 가능성 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="S51" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://finance.yahoo.com/healthcare/articles/surgery-partners-10x-genomics-quidelortho-213005328.html</ns0:t>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T51" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/TXG/profile/</ns0:t>
+          <ns0:t>https://finviz.com/quote.ashx?t=ABLV</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4192,55 +4193,55 @@
       </ns0:c>
       <ns0:c r="B52" t="inlineStr">
         <ns0:is>
-          <ns0:t>VEON</ns0:t>
+          <ns0:t>ADPT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C52" t="inlineStr">
         <ns0:is>
-          <ns0:t>VEON Ltd ADR</ns0:t>
+          <ns0:t>Adaptive Biotechnologies Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D52" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Services</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E52" t="inlineStr">
         <ns0:is>
-          <ns0:t>Telecom Services</ns0:t>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F52" t="inlineStr">
         <ns0:is>
-          <ns0:t>파키스탄·우크라이나·카자흐스탄·방글라데시·우즈베키스탄에서 이동통신·디지털 서비스 제공.</ns0:t>
+          <ns0:t>면역 의학 플랫폼 개발 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G52">
-        <ns0:v>73.5199966430664</ns0:v>
+        <ns0:v>29.43000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="H52">
-        <ns0:v>1.3509728634829576</ns0:v>
+        <ns0:v>-0.47345076460363344</ns0:v>
       </ns0:c>
       <ns0:c r="I52">
-        <ns0:v>73.79000091552734</ns0:v>
+        <ns0:v>29.579999923706055</ns0:v>
       </ns0:c>
       <ns0:c r="J52">
-        <ns0:v>-0.3659090244083729</ns0:v>
+        <ns0:v>-0.5070981031682131</ns0:v>
       </ns0:c>
       <ns0:c r="K52">
-        <ns0:v>1.0945415219989754</ns0:v>
+        <ns0:v>0.7562478403496726</ns0:v>
       </ns0:c>
       <ns0:c r="L52">
-        <ns0:v>79.3841757869804</ns0:v>
+        <ns0:v>71.62183423491359</ns0:v>
       </ns0:c>
       <ns0:c r="M52">
-        <ns0:v>67.35550003051758</ns0:v>
+        <ns0:v>26.21250009536743</ns0:v>
       </ns0:c>
       <ns0:c r="N52">
-        <ns0:v>60.14280014038086</ns0:v>
+        <ns0:v>24.984800071716307</ns0:v>
       </ns0:c>
       <ns0:c r="O52">
-        <ns0:v>54.30535001754761</ns0:v>
+        <ns0:v>18.33455002307892</ns0:v>
       </ns0:c>
       <ns0:c r="P52" t="inlineStr">
         <ns0:is>
@@ -4259,7 +4260,7 @@
       </ns0:c>
       <ns0:c r="T52" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/VEON/profile/</ns0:t>
+          <ns0:t>https://finviz.com/quote.ashx?t=ADPT</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4271,12 +4272,12 @@
       </ns0:c>
       <ns0:c r="B53" t="inlineStr">
         <ns0:is>
-          <ns0:t>VNCE</ns0:t>
+          <ns0:t>AOUT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C53" t="inlineStr">
         <ns0:is>
-          <ns0:t>Vince Holding Corp</ns0:t>
+          <ns0:t>American Outdoor Brands Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D53" t="inlineStr">
@@ -4286,44 +4287,44 @@
       </ns0:c>
       <ns0:c r="E53" t="inlineStr">
         <ns0:is>
-          <ns0:t>Apparel Manufacturing</ns0:t>
+          <ns0:t>Leisure</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F53" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 Vince 도매·소비자 직접 판매를 통해 캐시미어 스웨터·실크 블라우스 등 여성복 판매.</ns0:t>
+          <ns0:t>아웃도어 생활용품과 사격 스포츠 액세서리 제공 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G53">
-        <ns0:v>11.5</ns0:v>
+        <ns0:v>17.549999237060547</ns0:v>
       </ns0:c>
       <ns0:c r="H53">
-        <ns0:v>3.2315946641153115</ns0:v>
+        <ns0:v>3.0534264794411126</ns0:v>
       </ns0:c>
       <ns0:c r="I53">
-        <ns0:v>11.979999542236328</ns0:v>
+        <ns0:v>17.30500030517578</ns0:v>
       </ns0:c>
       <ns0:c r="J53">
-        <ns0:v>-4.006674128359156</ns0:v>
+        <ns0:v>1.4157695900848255</ns0:v>
       </ns0:c>
       <ns0:c r="K53">
-        <ns0:v>1.1962751979682897</ns0:v>
+        <ns0:v>0.4236343366778149</ns0:v>
       </ns0:c>
       <ns0:c r="L53">
-        <ns0:v>70.42947865305948</ns0:v>
+        <ns0:v>77.62393708899921</ns0:v>
       </ns0:c>
       <ns0:c r="M53">
-        <ns0:v>8.061500000953675</ns0:v>
+        <ns0:v>14.439499998092652</ns0:v>
       </ns0:c>
       <ns0:c r="N53">
-        <ns0:v>7.029200019836426</ns0:v>
+        <ns0:v>13.202200012207031</ns0:v>
       </ns0:c>
       <ns0:c r="O53">
-        <ns0:v>4.685350006818771</ns0:v>
+        <ns0:v>10.425400035381317</ns0:v>
       </ns0:c>
       <ns0:c r="P53" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q53" t="inlineStr">
@@ -4333,17 +4334,17 @@
       </ns0:c>
       <ns0:c r="R53" t="inlineStr">
         <ns0:is>
-          <ns0:t>주가 추세의 지속 가능성과 가격 매력을 조명한 기사, 2분기 실적 발표의 OVO 규모·전망 상향 관련 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>2027 회계연도 1분기 실적 전망과 실적 발표에서 언급된 강한 매출 성장을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S53" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/vince-holding-vnce-move-heres-125501304.html</ns0:t>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/american-outdoor-brands-inc-aout-050058077.html</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="T53" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/VNCE/profile/</ns0:t>
+          <ns0:t>https://finviz.com/quote.ashx?t=AOUT</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4355,165 +4356,4101 @@
       </ns0:c>
       <ns0:c r="B54" t="inlineStr">
         <ns0:is>
+          <ns0:t>AVT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C54" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Avnet Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D54" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Technology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E54" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Electronics &amp; Computer Distribution</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F54" t="inlineStr">
+        <ns0:is>
+          <ns0:t>전자부품·파넬 부문을 통해 전 세계에 반도체·연결 부품·수동 및 전기기계 부품을 유통하는 기업.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G54">
+        <ns0:v>103.08000183105469</ns0:v>
+      </ns0:c>
+      <ns0:c r="H54">
+        <ns0:v>2.1504291846142554</ns0:v>
+      </ns0:c>
+      <ns0:c r="I54">
+        <ns0:v>102.69999694824219</ns0:v>
+      </ns0:c>
+      <ns0:c r="J54">
+        <ns0:v>0.3700145025359758</ns0:v>
+      </ns0:c>
+      <ns0:c r="K54">
+        <ns0:v>0.9112713466733859</ns0:v>
+      </ns0:c>
+      <ns0:c r="L54">
+        <ns0:v>67.41626269872638</ns0:v>
+      </ns0:c>
+      <ns0:c r="M54">
+        <ns0:v>94.15149993896485</ns0:v>
+      </ns0:c>
+      <ns0:c r="N54">
+        <ns0:v>92.2543994140625</ns0:v>
+      </ns0:c>
+      <ns0:c r="O54">
+        <ns0:v>75.15899978637695</ns0:v>
+      </ns0:c>
+      <ns0:c r="P54" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q54" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R54" t="inlineStr">
+        <ns0:is>
+          <ns0:t>AI 공급망 확대 속 매수 지점 근접 평가, 이익 확대의 세 동력, SMCI와의 투자 매력 비교를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S54" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://www.investors.com/news/xmtr-stock-buy-point-avnet-xometry-ai-supply-chains/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T54" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/AVT/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="55">
+      <ns0:c r="A55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CDNA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Caredx Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>이식 환자의 치료 결과와 장기 건강 개선을 위한 신장·심장 이식 검사 솔루션 제공 기업.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G55">
+        <ns0:v>63.68000030517578</ns0:v>
+      </ns0:c>
+      <ns0:c r="H55">
+        <ns0:v>3.7640564013287747</ns0:v>
+      </ns0:c>
+      <ns0:c r="I55">
+        <ns0:v>63.09000015258789</ns0:v>
+      </ns0:c>
+      <ns0:c r="J55">
+        <ns0:v>0.9351722161371478</ns0:v>
+      </ns0:c>
+      <ns0:c r="K55">
+        <ns0:v>1.9321999054334642</ns0:v>
+      </ns0:c>
+      <ns0:c r="L55">
+        <ns0:v>79.29981082915883</ns0:v>
+      </ns0:c>
+      <ns0:c r="M55">
+        <ns0:v>52.834000205993654</ns0:v>
+      </ns0:c>
+      <ns0:c r="N55">
+        <ns0:v>47.554400024414065</ns0:v>
+      </ns0:c>
+      <ns0:c r="O55">
+        <ns0:v>27.618324937820436</ns0:v>
+      </ns0:c>
+      <ns0:c r="P55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>주가 급등과 상승 지속 여부, 애널리스트의 새 목표주가 74달러가 보도됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/caredx-cdna-stock-jumps-13-071800723.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/CDNA/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="56">
+      <ns0:c r="A56" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B56" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CNET</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C56" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ZW Data Action Technologies Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D56" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Communication Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E56" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Advertising Agencies</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F56" t="inlineStr">
+        <ns0:is>
+          <ns0:t>온오프라인 통합 광고와 정밀 마케팅 원스톱 서비스를 운영하는 지주회사.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G56">
+        <ns0:v>1.850000023841858</ns0:v>
+      </ns0:c>
+      <ns0:c r="H56">
+        <ns0:v>35.036497620643495</ns0:v>
+      </ns0:c>
+      <ns0:c r="I56">
+        <ns0:v>2.5999999046325684</ns0:v>
+      </ns0:c>
+      <ns0:c r="J56">
+        <ns0:v>-28.846150319251663</ns0:v>
+      </ns0:c>
+      <ns0:c r="L56">
+        <ns0:v>74.31481219388311</ns0:v>
+      </ns0:c>
+      <ns0:c r="M56">
+        <ns0:v>1.3279999852180482</ns0:v>
+      </ns0:c>
+      <ns0:c r="N56">
+        <ns0:v>1.317599993944168</ns0:v>
+      </ns0:c>
+      <ns0:c r="O56">
+        <ns0:v>1.0263999977707863</ns0:v>
+      </ns0:c>
+      <ns0:c r="P56" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q56" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R56" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T56" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finviz.com/quote.ashx?t=CNET</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="57">
+      <ns0:c r="A57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CNXN</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PC Connection Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Technology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Electronics &amp; Computer Distribution</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>대기업·일반 기업·공공 부문에 컴퓨터 시스템·데이터센터 등 IT 솔루션을 제공하는 기업.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G57">
+        <ns0:v>89.31999969482422</ns0:v>
+      </ns0:c>
+      <ns0:c r="H57">
+        <ns0:v>0.3370063615714347</ns0:v>
+      </ns0:c>
+      <ns0:c r="I57">
+        <ns0:v>89.62999725341797</ns0:v>
+      </ns0:c>
+      <ns0:c r="J57">
+        <ns0:v>-0.3458636261220338</ns0:v>
+      </ns0:c>
+      <ns0:c r="K57">
+        <ns0:v>0.614054054054054</ns0:v>
+      </ns0:c>
+      <ns0:c r="L57">
+        <ns0:v>70.67524063679258</ns0:v>
+      </ns0:c>
+      <ns0:c r="M57">
+        <ns0:v>84.70199966430664</ns0:v>
+      </ns0:c>
+      <ns0:c r="N57">
+        <ns0:v>82.63219985961913</ns0:v>
+      </ns0:c>
+      <ns0:c r="O57">
+        <ns0:v>68.51559993743896</ns0:v>
+      </ns0:c>
+      <ns0:c r="P57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>퍼트리샤 갤럽 회장의 14,284주 매도와 올해 유통·도매 업종 대비 주가 성과를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://www.fool.com/coverage/filings/2026/09/23/pc-connection-chairman-patricia-gallup-sells-14-284-shares/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/CNXN/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="58">
+      <ns0:c r="A58" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B58" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CYPH</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C58" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Cypherpunk Technologies Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D58" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E58" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Biotechnology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F58" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국에서 프라이버시 강화 기술을 개발·투자·인수하고 지캐시 중심 디지털 자산 전략을 추진하는 기업.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G58">
+        <ns0:v>4.119999885559082</ns0:v>
+      </ns0:c>
+      <ns0:c r="H58">
+        <ns0:v>0.9803912402207571</ns0:v>
+      </ns0:c>
+      <ns0:c r="I58">
+        <ns0:v>4.139999866485596</ns0:v>
+      </ns0:c>
+      <ns0:c r="J58">
+        <ns0:v>-0.4830913423070071</ns0:v>
+      </ns0:c>
+      <ns0:c r="K58">
+        <ns0:v>1.1282711540469825</ns0:v>
+      </ns0:c>
+      <ns0:c r="L58">
+        <ns0:v>76.32780306551894</ns0:v>
+      </ns0:c>
+      <ns0:c r="M58">
+        <ns0:v>2.7005000054836272</ns0:v>
+      </ns0:c>
+      <ns0:c r="N58">
+        <ns0:v>1.599020003080368</ns0:v>
+      </ns0:c>
+      <ns0:c r="O58">
+        <ns0:v>1.0564350017905235</ns0:v>
+      </ns0:c>
+      <ns0:c r="P58" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q58" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R58" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T58" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/CYPH/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="59">
+      <ns0:c r="A59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FBLA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FB Bancorp Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Financial</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Banks - Regional</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>개인·기업·지역사회에 예금 등 은행 상품과 서비스를 제공하는 피델리티 은행의 지주회사.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G59">
+        <ns0:v>16.469999313354492</ns0:v>
+      </ns0:c>
+      <ns0:c r="H59">
+        <ns0:v>1.2915072663999494</ns0:v>
+      </ns0:c>
+      <ns0:c r="I59">
+        <ns0:v>16.389999389648438</ns0:v>
+      </ns0:c>
+      <ns0:c r="J59">
+        <ns0:v>0.48810205421105923</ns0:v>
+      </ns0:c>
+      <ns0:c r="K59">
+        <ns0:v>0.6699306405548756</ns0:v>
+      </ns0:c>
+      <ns0:c r="L59">
+        <ns0:v>68.11235557900213</ns0:v>
+      </ns0:c>
+      <ns0:c r="M59">
+        <ns0:v>16.005249977111816</ns0:v>
+      </ns0:c>
+      <ns0:c r="N59">
+        <ns0:v>15.769099998474122</ns0:v>
+      </ns0:c>
+      <ns0:c r="O59">
+        <ns0:v>14.236925020217896</ns0:v>
+      </ns0:c>
+      <ns0:c r="P59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/FBLA/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="60">
+      <ns0:c r="A60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FLXS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Flexsteel Industries Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Consumer Cyclical</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Furnishings, Fixtures &amp; Appliances</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국에서 소파·의자·침실·식탁 가구 등 주거용 가구를 제조·유통·수입·판매하는 기업.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G60">
+        <ns0:v>89.37000274658203</ns0:v>
+      </ns0:c>
+      <ns0:c r="H60">
+        <ns0:v>1.1316057133863522</ns0:v>
+      </ns0:c>
+      <ns0:c r="I60">
+        <ns0:v>88.48999786376953</ns0:v>
+      </ns0:c>
+      <ns0:c r="J60">
+        <ns0:v>0.9944681930801558</ns0:v>
+      </ns0:c>
+      <ns0:c r="K60">
+        <ns0:v>1.3992468042221398</ns0:v>
+      </ns0:c>
+      <ns0:c r="L60">
+        <ns0:v>72.0103378205649</ns0:v>
+      </ns0:c>
+      <ns0:c r="M60">
+        <ns0:v>82.44100151062011</ns0:v>
+      </ns0:c>
+      <ns0:c r="N60">
+        <ns0:v>78.87920028686523</ns0:v>
+      </ns0:c>
+      <ns0:c r="O60">
+        <ns0:v>58.46914999008179</ns0:v>
+      </ns0:c>
+      <ns0:c r="P60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>올해 경기소비재 종목 대비 플렉스스틸의 주가 성과를 비교하는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/consumer-discretionary-stocks-lagging-flexsteel-124002018.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/FLXS/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="61">
+      <ns0:c r="A61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FRHC</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Freedom Holding Corp</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Financial</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Financial Conglomerates</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>증권 중개와 금융 서비스를 제공하는 투자회사.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G61">
+        <ns0:v>172.0800018310547</ns0:v>
+      </ns0:c>
+      <ns0:c r="H61">
+        <ns0:v>-2.43238272092845</ns0:v>
+      </ns0:c>
+      <ns0:c r="I61">
+        <ns0:v>177.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="J61">
+        <ns0:v>-3.053520095180462</ns0:v>
+      </ns0:c>
+      <ns0:c r="K61">
+        <ns0:v>1.0334690185436455</ns0:v>
+      </ns0:c>
+      <ns0:c r="L61">
+        <ns0:v>57.30277041476822</ns0:v>
+      </ns0:c>
+      <ns0:c r="M61">
+        <ns0:v>167.90299911499022</ns0:v>
+      </ns0:c>
+      <ns0:c r="N61">
+        <ns0:v>160.60280029296874</ns0:v>
+      </ns0:c>
+      <ns0:c r="O61">
+        <ns0:v>143.52400005340576</ns0:v>
+      </ns0:c>
+      <ns0:c r="P61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finviz.com/quote.ashx?t=FRHC</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="62">
+      <ns0:c r="A62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FSEA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>First Seacoast Bancorp Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Financial</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Banks - Regional</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>개인·기업에 예금·은행·자산관리 서비스를 제공하는 퍼스트 시코스트 은행의 지주회사.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G62">
+        <ns0:v>17.239999771118164</ns0:v>
+      </ns0:c>
+      <ns0:c r="H62">
+        <ns0:v>0.349240191365463</ns0:v>
+      </ns0:c>
+      <ns0:c r="I62">
+        <ns0:v>17.209999084472656</ns0:v>
+      </ns0:c>
+      <ns0:c r="J62">
+        <ns0:v>0.17432125648730867</ns0:v>
+      </ns0:c>
+      <ns0:c r="L62">
+        <ns0:v>71.12660333038355</ns0:v>
+      </ns0:c>
+      <ns0:c r="M62">
+        <ns0:v>17.181650161743164</ns0:v>
+      </ns0:c>
+      <ns0:c r="N62">
+        <ns0:v>17.089760131835938</ns0:v>
+      </ns0:c>
+      <ns0:c r="O62">
+        <ns0:v>14.798694977760315</ns0:v>
+      </ns0:c>
+      <ns0:c r="P62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/FSEA/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="63">
+      <ns0:c r="A63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>GRAL</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>GRAIL Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>다중암 조기 발견 검사·서비스를 제공하고 50세 초과 무증상자용 갈레리 암 선별검사를 판매하는 기업.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G63">
+        <ns0:v>126.88999938964844</ns0:v>
+      </ns0:c>
+      <ns0:c r="H63">
+        <ns0:v>1.3417461204854542</ns0:v>
+      </ns0:c>
+      <ns0:c r="I63">
+        <ns0:v>126.80999755859375</ns0:v>
+      </ns0:c>
+      <ns0:c r="J63">
+        <ns0:v>0.0630879525233885</ns0:v>
+      </ns0:c>
+      <ns0:c r="L63">
+        <ns0:v>87.1102910918771</ns0:v>
+      </ns0:c>
+      <ns0:c r="M63">
+        <ns0:v>87.77049942016602</ns0:v>
+      </ns0:c>
+      <ns0:c r="N63">
+        <ns0:v>78.23519966125488</ns0:v>
+      </ns0:c>
+      <ns0:c r="O63">
+        <ns0:v>72.60579992294312</ns0:v>
+      </ns0:c>
+      <ns0:c r="P63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>주간 주가 55% 급등, 암 발견 혈액검사에 대한 FDA 자문위원 지지와 고평가 여부를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://www.fool.com/investing/2026/09/25/heres-why-grail-stock-surged-55-this-week/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/GRAL/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="64">
+      <ns0:c r="A64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>HBB</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Hamilton Beach Brands Holding Co</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Consumer Cyclical</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Furnishings, Fixtures &amp; Appliances</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>브랜드 소형 가전과 특수 가정용 기기를 설계·마케팅·유통하는 기업.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G64">
+        <ns0:v>37.2599983215332</ns0:v>
+      </ns0:c>
+      <ns0:c r="H64">
+        <ns0:v>-0.1340205036647557</ns0:v>
+      </ns0:c>
+      <ns0:c r="I64">
+        <ns0:v>37.4900016784668</ns0:v>
+      </ns0:c>
+      <ns0:c r="J64">
+        <ns0:v>-0.613505859258745</ns0:v>
+      </ns0:c>
+      <ns0:c r="K64">
+        <ns0:v>0.7961282516636419</ns0:v>
+      </ns0:c>
+      <ns0:c r="L64">
+        <ns0:v>78.31067831420646</ns0:v>
+      </ns0:c>
+      <ns0:c r="M64">
+        <ns0:v>32.03000011444092</ns0:v>
+      </ns0:c>
+      <ns0:c r="N64">
+        <ns0:v>29.699799957275392</ns0:v>
+      </ns0:c>
+      <ns0:c r="O64">
+        <ns0:v>21.689400019645692</ns0:v>
+      </ns0:c>
+      <ns0:c r="P64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>핵심 사업 회복, 고급화와 인접 분야 성장을 다룬 신규 분석 보고서 소개. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/small-business/articles/hamilton-beach-brand-core-recovery-210954378.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finviz.com/quote.ashx?t=HBB</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="65">
+      <ns0:c r="A65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>HLP</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Hongli Group Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Basic Materials</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Steel</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>중국과 해외에서 다양한 맞춤형 냉간 성형 강재를 제조·판매한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G65">
+        <ns0:v>2.2100000381469727</ns0:v>
+      </ns0:c>
+      <ns0:c r="H65">
+        <ns0:v>0.4545450112051208</ns0:v>
+      </ns0:c>
+      <ns0:c r="I65">
+        <ns0:v>2.2799999713897705</ns0:v>
+      </ns0:c>
+      <ns0:c r="J65">
+        <ns0:v>-3.0701725491746212</ns0:v>
+      </ns0:c>
+      <ns0:c r="K65">
+        <ns0:v>1.4768460575719649</ns0:v>
+      </ns0:c>
+      <ns0:c r="L65">
+        <ns0:v>79.58984529123182</ns0:v>
+      </ns0:c>
+      <ns0:c r="M65">
+        <ns0:v>1.6622500002384186</ns0:v>
+      </ns0:c>
+      <ns0:c r="N65">
+        <ns0:v>1.39889999628067</ns0:v>
+      </ns0:c>
+      <ns0:c r="O65">
+        <ns0:v>1.0203249956667424</ns0:v>
+      </ns0:c>
+      <ns0:c r="P65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/HLP/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="66">
+      <ns0:c r="A66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>HQI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>HireQuest Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Industrials</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Staffing &amp; Employment Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>인력 공급 서비스를 제공한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G66">
+        <ns0:v>20.040000915527344</ns0:v>
+      </ns0:c>
+      <ns0:c r="H66">
+        <ns0:v>6.880004882812507</ns0:v>
+      </ns0:c>
+      <ns0:c r="I66">
+        <ns0:v>19.010000228881836</ns0:v>
+      </ns0:c>
+      <ns0:c r="J66">
+        <ns0:v>5.4182044936571305</ns0:v>
+      </ns0:c>
+      <ns0:c r="K66">
+        <ns0:v>5.929465301478953</ns0:v>
+      </ns0:c>
+      <ns0:c r="L66">
+        <ns0:v>76.14050493519318</ns0:v>
+      </ns0:c>
+      <ns0:c r="M66">
+        <ns0:v>16.861499881744386</ns0:v>
+      </ns0:c>
+      <ns0:c r="N66">
+        <ns0:v>15.602599925994873</ns0:v>
+      </ns0:c>
+      <ns0:c r="O66">
+        <ns0:v>12.330849959850312</ns0:v>
+      </ns0:c>
+      <ns0:c r="P66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finviz.com/quote.ashx?t=HQI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="67">
+      <ns0:c r="A67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IBEX</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IBEX Ltd</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Technology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Information Technology Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>기술 기반 고객 생애주기 경험 솔루션을 제공하는 업무 프로세스 아웃소싱 기업이다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G67">
+        <ns0:v>44.529998779296875</ns0:v>
+      </ns0:c>
+      <ns0:c r="H67">
+        <ns0:v>3.0309984303430237</ns0:v>
+      </ns0:c>
+      <ns0:c r="I67">
+        <ns0:v>43.36000061035156</ns0:v>
+      </ns0:c>
+      <ns0:c r="J67">
+        <ns0:v>2.698335222499959</ns0:v>
+      </ns0:c>
+      <ns0:c r="K67">
+        <ns0:v>1.2209933405697186</ns0:v>
+      </ns0:c>
+      <ns0:c r="L67">
+        <ns0:v>75.84561878827314</ns0:v>
+      </ns0:c>
+      <ns0:c r="M67">
+        <ns0:v>39.928999710083005</ns0:v>
+      </ns0:c>
+      <ns0:c r="N67">
+        <ns0:v>37.41349983215332</ns0:v>
+      </ns0:c>
+      <ns0:c r="O67">
+        <ns0:v>33.32537502288818</ns0:v>
+      </ns0:c>
+      <ns0:c r="P67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026년 4분기 실적 발표에서 사상 최대 매출과 AI 기반 성장세가 부각됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/ibex-ltd-ibex-q4-2026-070056480.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finviz.com/quote.ashx?t=IBEX</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="68">
+      <ns0:c r="A68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IMAX</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Imax Corp</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Communication Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Entertainment</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>콘텐츠 솔루션과 기술 제품으로 전 세계 엔터테인먼트·이벤트 기술 플랫폼을 운영한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G68">
+        <ns0:v>56.04999923706055</ns0:v>
+      </ns0:c>
+      <ns0:c r="H68">
+        <ns0:v>1.613486932760022</ns0:v>
+      </ns0:c>
+      <ns0:c r="I68">
+        <ns0:v>55.56999969482422</ns0:v>
+      </ns0:c>
+      <ns0:c r="J68">
+        <ns0:v>0.8637745993744117</ns0:v>
+      </ns0:c>
+      <ns0:c r="K68">
+        <ns0:v>1.144834436724647</ns0:v>
+      </ns0:c>
+      <ns0:c r="L68">
+        <ns0:v>66.18047681710634</ns0:v>
+      </ns0:c>
+      <ns0:c r="M68">
+        <ns0:v>52.532999992370605</ns0:v>
+      </ns0:c>
+      <ns0:c r="N68">
+        <ns0:v>50.307799911499025</ns0:v>
+      </ns0:c>
+      <ns0:c r="O68">
+        <ns0:v>40.93200012207031</ns0:v>
+      </ns0:c>
+      <ns0:c r="P68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>모건스탠리는 추가 상승 가능성을 제시했고, 영화 ‘오디세이’의 관람 경험 변화와 연초 이후 업종 대비 성과가 조명됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://stocktwits.com/news-articles/markets/equity/imax-stock-rally-may-be-just-the-start-morgan-stanley-says-why-the-odyssey-is-reshaping-the-moviegoing-experience/cZMJI4BRB9n</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/IMAX/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="69">
+      <ns0:c r="A69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IOSP</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Innospec Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Basic Materials</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Specialty Chemicals</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특수화학 제품을 개발·제조·혼합·판매하며 기능성 화학, 연료 특수제품, 유전서비스 사업을 한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G69">
+        <ns0:v>98.72000122070312</ns0:v>
+      </ns0:c>
+      <ns0:c r="H69">
+        <ns0:v>1.909774359107641</ns0:v>
+      </ns0:c>
+      <ns0:c r="I69">
+        <ns0:v>98.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="J69">
+        <ns0:v>0.7346951231664622</ns0:v>
+      </ns0:c>
+      <ns0:c r="K69">
+        <ns0:v>1.2925987089025672</ns0:v>
+      </ns0:c>
+      <ns0:c r="L69">
+        <ns0:v>72.51896023763308</ns0:v>
+      </ns0:c>
+      <ns0:c r="M69">
+        <ns0:v>93.99000053405761</ns0:v>
+      </ns0:c>
+      <ns0:c r="N69">
+        <ns0:v>91.57660018920899</ns0:v>
+      </ns0:c>
+      <ns0:c r="O69">
+        <ns0:v>81.94405040740966</ns0:v>
+      </ns0:c>
+      <ns0:c r="P69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>실적 발표 이후 주가가 2% 오른 가운데, 견조한 분기 실적에 가려진 현금흐름 문제가 지적됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/innospec-iosp-2-since-last-153015757.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/IOSP/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="70">
+      <ns0:c r="A70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IOVA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Iovance Biotherapeutics Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Biotechnology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>전이성 흑색종 등 고형암 치료용 자가 종양침윤림프구 세포치료제를 개발·상용화한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G70">
+        <ns0:v>11.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H70">
+        <ns0:v>1.8518500530834592</ns0:v>
+      </ns0:c>
+      <ns0:c r="I70">
+        <ns0:v>10.979999542236328</ns0:v>
+      </ns0:c>
+      <ns0:c r="J70">
+        <ns0:v>0.1821535391393958</ns0:v>
+      </ns0:c>
+      <ns0:c r="K70">
+        <ns0:v>0.9366111879724249</ns0:v>
+      </ns0:c>
+      <ns0:c r="L70">
+        <ns0:v>74.35970596617581</ns0:v>
+      </ns0:c>
+      <ns0:c r="M70">
+        <ns0:v>9.301000022888184</ns0:v>
+      </ns0:c>
+      <ns0:c r="N70">
+        <ns0:v>7.413400011062622</ns0:v>
+      </ns0:c>
+      <ns0:c r="O70">
+        <ns0:v>4.444150003194809</ns0:v>
+      </ns0:c>
+      <ns0:c r="P70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>주가 19.2% 상승과 함께 2분기 암타그비 매출 신기록 및 종양침윤림프구 치료제 개발 확대가 보도됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://www.fool.com/investing/2026/09/24/why-iovance-biotherapeutics-stock-was-on-fire-toda/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/IOVA/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="71">
+      <ns0:c r="A71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>JILL</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>J.Jill Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Consumer Cyclical</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Apparel Retail</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국 온·오프라인 채널에서 여성 의류·신발·보석·가방 등 액세서리를 판매한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G71">
+        <ns0:v>24.6299991607666</ns0:v>
+      </ns0:c>
+      <ns0:c r="H71">
+        <ns0:v>2.411642170916517</ns0:v>
+      </ns0:c>
+      <ns0:c r="I71">
+        <ns0:v>24.690000534057617</ns0:v>
+      </ns0:c>
+      <ns0:c r="J71">
+        <ns0:v>-0.24301892261301417</ns0:v>
+      </ns0:c>
+      <ns0:c r="K71">
+        <ns0:v>0.7047716969668645</ns0:v>
+      </ns0:c>
+      <ns0:c r="L71">
+        <ns0:v>74.65046572429807</ns0:v>
+      </ns0:c>
+      <ns0:c r="M71">
+        <ns0:v>22.3229998588562</ns0:v>
+      </ns0:c>
+      <ns0:c r="N71">
+        <ns0:v>20.070999946594238</ns0:v>
+      </ns0:c>
+      <ns0:c r="O71">
+        <ns0:v>15.965500016212463</ns0:v>
+      </ns0:c>
+      <ns0:c r="P71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>실적·전망 관련 기사 제목 1건 확인. 주가 상승과의 인과는 미확인입니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/j-jill-jill-four-analysts-190634876.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/JILL/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="72">
+      <ns0:c r="A72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>MASS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>908 Devices Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Medical Devices</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보건·안전 분야용 휴대용 질량분석기와 푸리에 변환 적외선 장비를 제공한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G72">
+        <ns0:v>11.4399995803833</ns0:v>
+      </ns0:c>
+      <ns0:c r="H72">
+        <ns0:v>-0.6944520329984494</ns0:v>
+      </ns0:c>
+      <ns0:c r="I72">
+        <ns0:v>11.529999732971191</ns0:v>
+      </ns0:c>
+      <ns0:c r="J72">
+        <ns0:v>-0.7805737612510577</ns0:v>
+      </ns0:c>
+      <ns0:c r="K72">
+        <ns0:v>0.8057695112089194</ns0:v>
+      </ns0:c>
+      <ns0:c r="L72">
+        <ns0:v>64.45950942237641</ns0:v>
+      </ns0:c>
+      <ns0:c r="M72">
+        <ns0:v>10.396499967575073</ns0:v>
+      </ns0:c>
+      <ns0:c r="N72">
+        <ns0:v>9.498000011444091</ns0:v>
+      </ns0:c>
+      <ns0:c r="O72">
+        <ns0:v>7.574825010299683</ns0:v>
+      </ns0:c>
+      <ns0:c r="P72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>휴대용 탐지기 수요가 빠르게 늘어나는 가운데 2026년 전망을 상향했다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://www.marketbeat.com/instant-alerts/event-908-devices-raises-2026-outlook-as-handheld-detection-demand-accelerates-2026-08-29/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/MASS/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="73">
+      <ns0:c r="A73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>MG</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Mistras Group Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Industrials</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Security &amp; Protection Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>산업 자산 건전성·실험실 시험 솔루션과 비파괴 검사, 배관 검사, 유지보수 계획 등을 제공한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G73">
+        <ns0:v>21.520000457763672</ns0:v>
+      </ns0:c>
+      <ns0:c r="H73">
+        <ns0:v>0.6548236786368955</ns0:v>
+      </ns0:c>
+      <ns0:c r="I73">
+        <ns0:v>21.56999969482422</ns0:v>
+      </ns0:c>
+      <ns0:c r="J73">
+        <ns0:v>-0.23179989693066227</ns0:v>
+      </ns0:c>
+      <ns0:c r="K73">
+        <ns0:v>0.7671278790862338</ns0:v>
+      </ns0:c>
+      <ns0:c r="L73">
+        <ns0:v>70.07932732899262</ns0:v>
+      </ns0:c>
+      <ns0:c r="M73">
+        <ns0:v>19.839000034332276</ns0:v>
+      </ns0:c>
+      <ns0:c r="N73">
+        <ns0:v>18.090000057220458</ns0:v>
+      </ns0:c>
+      <ns0:c r="O73">
+        <ns0:v>16.361300024986267</ns0:v>
+      </ns0:c>
+      <ns0:c r="P73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>계약·사업 관련 기사 제목 1건 확인. 주가 상승과의 인과는 미확인입니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/mistras-group-shares-jump-following-151628366.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/MG/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="74">
+      <ns0:c r="A74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>MGLD</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Marygold Companies Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Financial</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Asset Management</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국·캐나다·영국에서 상장지수상품을 운용하며 보안시스템·미용제품·금융 사업도 한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G74">
+        <ns0:v>1.9299999475479126</ns0:v>
+      </ns0:c>
+      <ns0:c r="H74">
+        <ns0:v>92.99999475479126</ns0:v>
+      </ns0:c>
+      <ns0:c r="I74">
+        <ns0:v>1.3799999952316284</ns0:v>
+      </ns0:c>
+      <ns0:c r="J74">
+        <ns0:v>39.85506914613928</ns0:v>
+      </ns0:c>
+      <ns0:c r="K74">
+        <ns0:v>1144.4698085419734</ns0:v>
+      </ns0:c>
+      <ns0:c r="L74">
+        <ns0:v>84.26943360820123</ns0:v>
+      </ns0:c>
+      <ns0:c r="M74">
+        <ns0:v>1.0444499909877778</ns0:v>
+      </ns0:c>
+      <ns0:c r="N74">
+        <ns0:v>1.062079997062683</ns0:v>
+      </ns0:c>
+      <ns0:c r="O74">
+        <ns0:v>1.0786599957942962</ns0:v>
+      </ns0:c>
+      <ns0:c r="P74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/MGLD/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="75">
+      <ns0:c r="A75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>MNTK</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Montauk Renewables Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Basic Materials</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Specialty Chemicals</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>매립지 등 비화석 원천의 바이오가스를 회수·처리하며 재생 천연가스와 재생 전력 사업을 한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G75">
+        <ns0:v>2.930000066757202</ns0:v>
+      </ns0:c>
+      <ns0:c r="H75">
+        <ns0:v>1.7361093864397548</ns0:v>
+      </ns0:c>
+      <ns0:c r="I75">
+        <ns0:v>2.9700000286102295</ns0:v>
+      </ns0:c>
+      <ns0:c r="J75">
+        <ns0:v>-1.3468000494176735</ns0:v>
+      </ns0:c>
+      <ns0:c r="K75">
+        <ns0:v>3.2764470552488985</ns0:v>
+      </ns0:c>
+      <ns0:c r="L75">
+        <ns0:v>67.57522095471995</ns0:v>
+      </ns0:c>
+      <ns0:c r="M75">
+        <ns0:v>2.3115000128746033</ns0:v>
+      </ns0:c>
+      <ns0:c r="N75">
+        <ns0:v>1.998900008201599</ns0:v>
+      </ns0:c>
+      <ns0:c r="O75">
+        <ns0:v>1.6531250017881394</ns0:v>
+      </ns0:c>
+      <ns0:c r="P75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>올해 주가 성과가 다른 석유·에너지 종목을 웃도는지 비교하는 기사가 나왔다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/energy/articles/montauk-renewables-mntk-outperforming-other-134004370.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/MNTK/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="76">
+      <ns0:c r="A76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>MRNA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Moderna Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Biotechnology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국·유럽 등에서 메신저 RNA 의약품과 호흡기·잠복 바이러스 관련 백신을 제공한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G76">
+        <ns0:v>198.8800048828125</ns0:v>
+      </ns0:c>
+      <ns0:c r="H76">
+        <ns0:v>2.0839736197304948</ns0:v>
+      </ns0:c>
+      <ns0:c r="I76">
+        <ns0:v>195.70899963378906</ns0:v>
+      </ns0:c>
+      <ns0:c r="J76">
+        <ns0:v>1.62026542210989</ns0:v>
+      </ns0:c>
+      <ns0:c r="K76">
+        <ns0:v>0.8444472924254605</ns0:v>
+      </ns0:c>
+      <ns0:c r="L76">
+        <ns0:v>76.07055815922786</ns0:v>
+      </ns0:c>
+      <ns0:c r="M76">
+        <ns0:v>155.69300079345703</ns0:v>
+      </ns0:c>
+      <ns0:c r="N76">
+        <ns0:v>110.10980087280274</ns0:v>
+      </ns0:c>
+      <ns0:c r="O76">
+        <ns0:v>64.25587517738342</ns0:v>
+      </ns0:c>
+      <ns0:c r="P76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>기업 동향 관련 기사 제목 3건 확인. 주가 상승과의 인과는 미확인입니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://stocktwits.com/news-articles/markets/equity/mrna-pgen-stocks-hit-multi-year-highs-what-s-driving-the-momentum-today/cZMOKrcRBOS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/MRNA/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="77">
+      <ns0:c r="A77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>MTLS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Materialise Nv ADR</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Technology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Software - Application</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>전 세계에서 적층 제조·의료 소프트웨어 도구와 3D 프린팅 서비스를 제공한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G77">
+        <ns0:v>8.430000305175781</ns0:v>
+      </ns0:c>
+      <ns0:c r="H77">
+        <ns0:v>5.243446495538695</ns0:v>
+      </ns0:c>
+      <ns0:c r="I77">
+        <ns0:v>8.079999923706055</ns0:v>
+      </ns0:c>
+      <ns0:c r="J77">
+        <ns0:v>4.331687930377992</ns0:v>
+      </ns0:c>
+      <ns0:c r="K77">
+        <ns0:v>2.6649794028162948</ns0:v>
+      </ns0:c>
+      <ns0:c r="L77">
+        <ns0:v>79.00927204347606</ns0:v>
+      </ns0:c>
+      <ns0:c r="M77">
+        <ns0:v>7.573000025749207</ns0:v>
+      </ns0:c>
+      <ns0:c r="N77">
+        <ns0:v>7.016600017547607</ns0:v>
+      </ns0:c>
+      <ns0:c r="O77">
+        <ns0:v>6.067700004577636</ns0:v>
+      </ns0:c>
+      <ns0:c r="P77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026년 2분기 실적 발표에서 의료 부문 성장과 항공우주 부문 급성장이 부각됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://www.fool.com/earnings/call-transcripts/2026/08/31/materialise-mtls-q2-2026-earnings-call-transcript/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/MTLS/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="78">
+      <ns0:c r="A78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NTRA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Natera Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>분자검사를 개발·상용화하며 잔존질환·재발 감시·치료 반응 평가용 혈액검사를 제공한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G78">
+        <ns0:v>412.55999755859375</ns0:v>
+      </ns0:c>
+      <ns0:c r="H78">
+        <ns0:v>0.9222312030303881</ns0:v>
+      </ns0:c>
+      <ns0:c r="I78">
+        <ns0:v>412.92498779296875</ns0:v>
+      </ns0:c>
+      <ns0:c r="J78">
+        <ns0:v>-0.08839141373493398</ns0:v>
+      </ns0:c>
+      <ns0:c r="K78">
+        <ns0:v>1.1464325073767287</ns0:v>
+      </ns0:c>
+      <ns0:c r="L78">
+        <ns0:v>83.75044912642949</ns0:v>
+      </ns0:c>
+      <ns0:c r="M78">
+        <ns0:v>350.34025421142576</ns0:v>
+      </ns0:c>
+      <ns0:c r="N78">
+        <ns0:v>316.5035021972656</ns0:v>
+      </ns0:c>
+      <ns0:c r="O78">
+        <ns0:v>244.5601505279541</ns0:v>
+      </ns0:c>
+      <ns0:c r="P78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>시그나테라가 일본 PMDA의 방광암 동반진단 승인을 받았으며, 주가 급등을 다룬 기사도 나왔다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/stocks-making-big-moves-yesterday-170902420.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/NTRA/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="79">
+      <ns0:c r="A79" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B79" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NTRB</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C79" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Nutriband Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D79" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E79" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Biotechnology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F79" t="inlineStr">
+        <ns0:is>
+          <ns0:t>경피 약물을 개발하며 주요 제품은 만성 통증 치료용 남용 억제 펜타닐 패치 AVERSA다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G79">
+        <ns0:v>8.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H79">
+        <ns0:v>-11.012233551981831</ns0:v>
+      </ns0:c>
+      <ns0:c r="I79">
+        <ns0:v>9.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="J79">
+        <ns0:v>-11.111111111111116</ns0:v>
+      </ns0:c>
+      <ns0:c r="K79">
+        <ns0:v>3.902578796561605</ns0:v>
+      </ns0:c>
+      <ns0:c r="L79">
+        <ns0:v>63.78414033666717</ns0:v>
+      </ns0:c>
+      <ns0:c r="M79">
+        <ns0:v>6.492350006103516</ns0:v>
+      </ns0:c>
+      <ns0:c r="N79">
+        <ns0:v>4.617459998130799</ns0:v>
+      </ns0:c>
+      <ns0:c r="O79">
+        <ns0:v>4.122244991064072</ns0:v>
+      </ns0:c>
+      <ns0:c r="P79" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q79" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R79" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T79" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/NTRB/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="80">
+      <ns0:c r="A80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OPRT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Oportun Financial Corp</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Financial</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Credit Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국에서 온라인·전화·매장·제휴사를 통해 개인대출과 신용카드 등 금융서비스를 제공한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G80">
+        <ns0:v>8.550000190734863</ns0:v>
+      </ns0:c>
+      <ns0:c r="H80">
+        <ns0:v>3.012048123553912</ns0:v>
+      </ns0:c>
+      <ns0:c r="I80">
+        <ns0:v>8.54699993133545</ns0:v>
+      </ns0:c>
+      <ns0:c r="J80">
+        <ns0:v>0.035103070358233346</ns0:v>
+      </ns0:c>
+      <ns0:c r="K80">
+        <ns0:v>1.4042638192779835</ns0:v>
+      </ns0:c>
+      <ns0:c r="L80">
+        <ns0:v>66.494637639649</ns0:v>
+      </ns0:c>
+      <ns0:c r="M80">
+        <ns0:v>7.8879999876022335</ns0:v>
+      </ns0:c>
+      <ns0:c r="N80">
+        <ns0:v>7.197400007247925</ns0:v>
+      </ns0:c>
+      <ns0:c r="O80">
+        <ns0:v>5.769125013351441</ns0:v>
+      </ns0:c>
+      <ns0:c r="P80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>잭스 투자전략 기사에서 주목받았으며, 빠른 주가 움직임과 가치투자 관점의 매력을 다룬 평가가 나왔다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/zacks-approach-beat-markets-oportun-123300876.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/OPRT/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="81">
+      <ns0:c r="A81" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B81" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PACH</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C81" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Pioneer Acquisition I Corp</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D81" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Financial</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E81" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Shell Companies</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F81" t="inlineStr">
+        <ns0:is>
+          <ns0:t>주요 영업활동 없이 헬스케어 및 관련 산업 기업과의 합병·주식 교환·인수 등 기업결합을 추진한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G81">
+        <ns0:v>10.329999923706055</ns0:v>
+      </ns0:c>
+      <ns0:c r="H81">
+        <ns0:v>-0.1932411306909687</ns0:v>
+      </ns0:c>
+      <ns0:c r="I81">
+        <ns0:v>10.350000381469727</ns0:v>
+      </ns0:c>
+      <ns0:c r="J81">
+        <ns0:v>-0.1932411306909687</ns0:v>
+      </ns0:c>
+      <ns0:c r="L81">
+        <ns0:v>54.228792426741094</ns0:v>
+      </ns0:c>
+      <ns0:c r="M81">
+        <ns0:v>10.330500030517578</ns0:v>
+      </ns0:c>
+      <ns0:c r="N81">
+        <ns0:v>10.304320087432862</ns0:v>
+      </ns0:c>
+      <ns0:c r="O81">
+        <ns0:v>10.19614001750946</ns0:v>
+      </ns0:c>
+      <ns0:c r="P81" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q81" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R81" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T81" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/PACH/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="82">
+      <ns0:c r="A82" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B82" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PAYO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C82" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Payoneer Global Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D82" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Technology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E82" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Software - Infrastructure</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F82" t="inlineStr">
+        <ns0:is>
+          <ns0:t>국경 간 대금 수취·지급용 다중통화 계좌와 결제 인프라를 제공하는 핀테크 기업.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G82">
+        <ns0:v>7.170000076293945</ns0:v>
+      </ns0:c>
+      <ns0:c r="H82">
+        <ns0:v>0.5610092736466177</ns0:v>
+      </ns0:c>
+      <ns0:c r="I82">
+        <ns0:v>7.179999828338623</ns0:v>
+      </ns0:c>
+      <ns0:c r="J82">
+        <ns0:v>-0.13927231592972822</ns0:v>
+      </ns0:c>
+      <ns0:c r="K82">
+        <ns0:v>1.2451037407510133</ns0:v>
+      </ns0:c>
+      <ns0:c r="L82">
+        <ns0:v>59.71264589115707</ns0:v>
+      </ns0:c>
+      <ns0:c r="M82">
+        <ns0:v>7.130500030517578</ns0:v>
+      </ns0:c>
+      <ns0:c r="N82">
+        <ns0:v>7.124200019836426</ns0:v>
+      </ns0:c>
+      <ns0:c r="O82">
+        <ns0:v>5.939300003051758</ns0:v>
+      </ns0:c>
+      <ns0:c r="P82" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q82" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R82" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T82" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/PAYO/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="83">
+      <ns0:c r="A83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PGEN</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Precigen Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Biotechnology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>암 면역치료·자가면역·감염병 대상 유전자·세포 치료제를 개발하는 임상 단계 바이오 기업.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G83">
+        <ns0:v>7.75</ns0:v>
+      </ns0:c>
+      <ns0:c r="H83">
+        <ns0:v>0.6493531425117771</ns0:v>
+      </ns0:c>
+      <ns0:c r="I83">
+        <ns0:v>8.039999961853027</ns0:v>
+      </ns0:c>
+      <ns0:c r="J83">
+        <ns0:v>-3.6069647167782937</ns0:v>
+      </ns0:c>
+      <ns0:c r="K83">
+        <ns0:v>1.563899849411944</ns0:v>
+      </ns0:c>
+      <ns0:c r="L83">
+        <ns0:v>61.1915127132687</ns0:v>
+      </ns0:c>
+      <ns0:c r="M83">
+        <ns0:v>7.230499958992004</ns0:v>
+      </ns0:c>
+      <ns0:c r="N83">
+        <ns0:v>6.732399988174438</ns0:v>
+      </ns0:c>
+      <ns0:c r="O83">
+        <ns0:v>4.889199995994568</ns0:v>
+      </ns0:c>
+      <ns0:c r="P83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>다년래 신고가 기록, AdenoVerse의 FDA 플랫폼 지위 확보와 Papzimeos 외 성장 가능성을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://stocktwits.com/news-articles/markets/equity/mrna-pgen-stocks-hit-multi-year-highs-what-s-driving-the-momentum-today/cZMOKrcRBOS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/PGEN/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="84">
+      <ns0:c r="A84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PRLB</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Proto Labs Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Industrials</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Metal Fabrication</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국·유럽에서 성형·CNC 가공·3D 프린팅·판금 등 맞춤형 부품 제조 서비스를 제공.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G84">
+        <ns0:v>96.25</ns0:v>
+      </ns0:c>
+      <ns0:c r="H84">
+        <ns0:v>3.5280184319998353</ns0:v>
+      </ns0:c>
+      <ns0:c r="I84">
+        <ns0:v>95.98999786376953</ns0:v>
+      </ns0:c>
+      <ns0:c r="J84">
+        <ns0:v>0.2708637795778124</ns0:v>
+      </ns0:c>
+      <ns0:c r="K84">
+        <ns0:v>1.1808118081180812</ns0:v>
+      </ns0:c>
+      <ns0:c r="L84">
+        <ns0:v>73.89166461580626</ns0:v>
+      </ns0:c>
+      <ns0:c r="M84">
+        <ns0:v>83.58549919128419</ns0:v>
+      </ns0:c>
+      <ns0:c r="N84">
+        <ns0:v>82.76739990234375</ns0:v>
+      </ns0:c>
+      <ns0:c r="O84">
+        <ns0:v>68.56205001831054</ns0:v>
+      </ns0:c>
+      <ns0:c r="P84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>향후 사업 전개가 드러나지 않은 모험적 선택에 달렸는지 살펴보는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/protolabs-prlb-next-chapter-hinged-133431215.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/PRLB/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="85">
+      <ns0:c r="A85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>QMCO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Quantum Corp</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Technology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Computer Hardware</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>비정형 데이터 관리 솔루션과 영상 편집 등에 쓰이는 저장장치 소프트웨어·시스템을 제공.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G85">
+        <ns0:v>31.68000030517578</ns0:v>
+      </ns0:c>
+      <ns0:c r="H85">
+        <ns0:v>7.426248053763818</ns0:v>
+      </ns0:c>
+      <ns0:c r="I85">
+        <ns0:v>32.08000183105469</ns0:v>
+      </ns0:c>
+      <ns0:c r="J85">
+        <ns0:v>-1.2468874783282846</ns0:v>
+      </ns0:c>
+      <ns0:c r="K85">
+        <ns0:v>3.081698823734679</ns0:v>
+      </ns0:c>
+      <ns0:c r="L85">
+        <ns0:v>77.484675074693</ns0:v>
+      </ns0:c>
+      <ns0:c r="M85">
+        <ns0:v>24.835999965667725</ns0:v>
+      </ns0:c>
+      <ns0:c r="N85">
+        <ns0:v>19.671999988555907</ns0:v>
+      </ns0:c>
+      <ns0:c r="O85">
+        <ns0:v>10.913549993038178</ns0:v>
+      </ns0:c>
+      <ns0:c r="P85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>주가 13.6% 상승의 지속 가능성, IBM과의 비교, S&amp;P 지수 편입 후 기대 반영 여부를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/strength-seen-quantum-corp-qmco-110300189.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/QMCO/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="86">
+      <ns0:c r="A86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>RCEL</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>AVITA Medical Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Medical Devices</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국·일본·유럽 등에서 급성 상처 치료 사업을 운영하며 세포 채취 장치 RECELL을 제공.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G86">
+        <ns0:v>11.84000015258789</ns0:v>
+      </ns0:c>
+      <ns0:c r="H86">
+        <ns0:v>2.245252423098676</ns0:v>
+      </ns0:c>
+      <ns0:c r="I86">
+        <ns0:v>11.8100004196167</ns0:v>
+      </ns0:c>
+      <ns0:c r="J86">
+        <ns0:v>0.2540197451759596</ns0:v>
+      </ns0:c>
+      <ns0:c r="K86">
+        <ns0:v>1.1741238779791587</ns0:v>
+      </ns0:c>
+      <ns0:c r="L86">
+        <ns0:v>67.95000382706597</ns0:v>
+      </ns0:c>
+      <ns0:c r="M86">
+        <ns0:v>10.675999975204467</ns0:v>
+      </ns0:c>
+      <ns0:c r="N86">
+        <ns0:v>8.425600004196166</ns0:v>
+      </ns0:c>
+      <ns0:c r="O86">
+        <ns0:v>5.2528000104427335</ns0:v>
+      </ns0:c>
+      <ns0:c r="P86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>아비타 메디컬의 투자의견이 매수로 상향된 내용을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/know-avita-medical-rcel-rating-160002727.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/RCEL/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="87">
+      <ns0:c r="A87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>RDVT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Red Violet Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Technology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Software - Application</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국에서 자체 기술·분석 역량을 활용한 신원 정보 및 조사 솔루션 idiCORE를 제공.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G87">
+        <ns0:v>78.55000305175781</ns0:v>
+      </ns0:c>
+      <ns0:c r="H87">
+        <ns0:v>-0.6450727581391202</ns0:v>
+      </ns0:c>
+      <ns0:c r="I87">
+        <ns0:v>80.29000091552734</ns0:v>
+      </ns0:c>
+      <ns0:c r="J87">
+        <ns0:v>-2.1671414172733328</ns0:v>
+      </ns0:c>
+      <ns0:c r="K87">
+        <ns0:v>1.0711910941421248</ns0:v>
+      </ns0:c>
+      <ns0:c r="L87">
+        <ns0:v>61.02085313027524</ns0:v>
+      </ns0:c>
+      <ns0:c r="M87">
+        <ns0:v>75.45250053405762</ns0:v>
+      </ns0:c>
+      <ns0:c r="N87">
+        <ns0:v>70.86650039672851</ns0:v>
+      </ns0:c>
+      <ns0:c r="O87">
+        <ns0:v>53.92812496185303</ns0:v>
+      </ns0:c>
+      <ns0:c r="P87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>높은 주가수익비율 속 6% 저평가 가능성과 성장주·모멘텀 종목으로서의 평가를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/red-violet-rdvt-could-6-090857658.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/RDVT/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="88">
+      <ns0:c r="A88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>RSKD</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Riskified Ltd</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Technology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Software - Application</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>온라인 판매자·소비자의 신뢰 구축을 지원하는 전자상거래 위험 분석 플랫폼을 개발·제공.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G88">
+        <ns0:v>7.78000020980835</ns0:v>
+      </ns0:c>
+      <ns0:c r="H88">
+        <ns0:v>-1.643484704317555</ns0:v>
+      </ns0:c>
+      <ns0:c r="I88">
+        <ns0:v>8.020000457763672</ns0:v>
+      </ns0:c>
+      <ns0:c r="J88">
+        <ns0:v>-2.9925216241477037</ns0:v>
+      </ns0:c>
+      <ns0:c r="K88">
+        <ns0:v>1.3970272771819023</ns0:v>
+      </ns0:c>
+      <ns0:c r="L88">
+        <ns0:v>73.60458049582746</ns0:v>
+      </ns0:c>
+      <ns0:c r="M88">
+        <ns0:v>6.524499988555908</ns0:v>
+      </ns0:c>
+      <ns0:c r="N88">
+        <ns0:v>5.95959997177124</ns0:v>
+      </ns0:c>
+      <ns0:c r="O88">
+        <ns0:v>4.9680499947071075</ns0:v>
+      </ns0:c>
+      <ns0:c r="P88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>주가 10.4% 상승과 추가 상승 가능성을 살펴보는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/riskified-rskd-stock-jumps-10-175800513.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/RSKD/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="89">
+      <ns0:c r="A89" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B89" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SAIH</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C89" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SAIHEAT Ltd</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D89" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Technology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E89" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Information Technology Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F89" t="inlineStr">
+        <ns0:is>
+          <ns0:t>암호화폐 채굴용 액체냉각 기술과 비트코인 채굴기 냉각 전환 캐비닛·실외 인프라 제품을 제공.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G89">
+        <ns0:v>30.545000076293945</ns0:v>
+      </ns0:c>
+      <ns0:c r="H89">
+        <ns0:v>1.8166669209798147</ns0:v>
+      </ns0:c>
+      <ns0:c r="I89">
+        <ns0:v>30.299999237060547</ns0:v>
+      </ns0:c>
+      <ns0:c r="J89">
+        <ns0:v>0.80858364819274</ns0:v>
+      </ns0:c>
+      <ns0:c r="K89">
+        <ns0:v>0.6383513445589344</ns0:v>
+      </ns0:c>
+      <ns0:c r="L89">
+        <ns0:v>75.79990055678368</ns0:v>
+      </ns0:c>
+      <ns0:c r="M89">
+        <ns0:v>25.70099992752075</ns0:v>
+      </ns0:c>
+      <ns0:c r="N89">
+        <ns0:v>21.95523998260498</ns0:v>
+      </ns0:c>
+      <ns0:c r="O89">
+        <ns0:v>12.701919996738434</ns0:v>
+      </ns0:c>
+      <ns0:c r="P89" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q89" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R89" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T89" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/SAIH/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="90">
+      <ns0:c r="A90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SBFG</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SB Financial Group Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Financial</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Banks - Regional</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>오하이오 개인·기업에 은행·신탁·자산관리·권원보험을 제공하는 State Bank and Trust의 지주사.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G90">
+        <ns0:v>29.860000610351562</ns0:v>
+      </ns0:c>
+      <ns0:c r="H90">
+        <ns0:v>-2.8311062311895285</ns0:v>
+      </ns0:c>
+      <ns0:c r="I90">
+        <ns0:v>30.729999542236328</ns0:v>
+      </ns0:c>
+      <ns0:c r="J90">
+        <ns0:v>-2.8311062311895285</ns0:v>
+      </ns0:c>
+      <ns0:c r="K90">
+        <ns0:v>0.997229916897507</ns0:v>
+      </ns0:c>
+      <ns0:c r="L90">
+        <ns0:v>60.13029726061827</ns0:v>
+      </ns0:c>
+      <ns0:c r="M90">
+        <ns0:v>29.21899995803833</ns0:v>
+      </ns0:c>
+      <ns0:c r="N90">
+        <ns0:v>27.80059997558594</ns0:v>
+      </ns0:c>
+      <ns0:c r="O90">
+        <ns0:v>23.548649950027468</ns0:v>
+      </ns0:c>
+      <ns0:c r="P90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>투자 매력과 저평가 여부, 신고가 기록 이후 추가 상승 여력을 살펴보는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/sb-financial-group-inc-sbfg-154503016.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/SBFG/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="91">
+      <ns0:c r="A91" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B91" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SILC</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C91" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Silicom Ltd</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D91" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Technology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E91" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Communication Equipment</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F91" t="inlineStr">
+        <ns0:is>
+          <ns0:t>서버 네트워크 인터페이스 카드와 암호화·압축용 카드 등 네트워크·데이터 인프라 솔루션을 제공.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G91">
+        <ns0:v>52.779998779296875</ns0:v>
+      </ns0:c>
+      <ns0:c r="H91">
+        <ns0:v>2.2471907621361753</ns0:v>
+      </ns0:c>
+      <ns0:c r="I91">
+        <ns0:v>52.95000076293945</ns0:v>
+      </ns0:c>
+      <ns0:c r="J91">
+        <ns0:v>-0.32106134314083823</ns0:v>
+      </ns0:c>
+      <ns0:c r="K91">
+        <ns0:v>0.6873830862439624</ns0:v>
+      </ns0:c>
+      <ns0:c r="L91">
+        <ns0:v>66.51640959102025</ns0:v>
+      </ns0:c>
+      <ns0:c r="M91">
+        <ns0:v>44.19300003051758</ns0:v>
+      </ns0:c>
+      <ns0:c r="N91">
+        <ns0:v>43.617800064086914</ns0:v>
+      </ns0:c>
+      <ns0:c r="O91">
+        <ns0:v>31.80054995059967</ns0:v>
+      </ns0:c>
+      <ns0:c r="P91" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q91" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R91" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T91" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/SILC/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="92">
+      <ns0:c r="A92" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B92" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SRZN</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C92" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Surrozen Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D92" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E92" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Biotechnology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F92" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조직 복구를 위해 Wnt 경로를 선택적으로 조절하는 항체 기반 치료제 후보를 발굴·개발.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G92">
+        <ns0:v>29.540000915527344</ns0:v>
+      </ns0:c>
+      <ns0:c r="H92">
+        <ns0:v>-12.29215959660256</ns0:v>
+      </ns0:c>
+      <ns0:c r="I92">
+        <ns0:v>35.86000061035156</ns0:v>
+      </ns0:c>
+      <ns0:c r="J92">
+        <ns0:v>-17.624092546724192</ns0:v>
+      </ns0:c>
+      <ns0:c r="K92">
+        <ns0:v>2.5624605573454677</ns0:v>
+      </ns0:c>
+      <ns0:c r="L92">
+        <ns0:v>65.57668098652911</ns0:v>
+      </ns0:c>
+      <ns0:c r="M92">
+        <ns0:v>20.662000370025634</ns0:v>
+      </ns0:c>
+      <ns0:c r="N92">
+        <ns0:v>21.875000076293944</ns0:v>
+      </ns0:c>
+      <ns0:c r="O92">
+        <ns0:v>24.363800010681153</ns0:v>
+      </ns0:c>
+      <ns0:c r="P92" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q92" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R92" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T92" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/SRZN/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="93">
+      <ns0:c r="A93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>TBBB</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>BBB Foods Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Consumer Defensive</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Discount Stores</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>멕시코 식료품 소매 체인으로 식품·의류·전자제품·생활용품과 브랜드·자체상표 상품을 판매.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G93">
+        <ns0:v>53.560001373291016</ns0:v>
+      </ns0:c>
+      <ns0:c r="H93">
+        <ns0:v>1.0184853090627888</ns0:v>
+      </ns0:c>
+      <ns0:c r="I93">
+        <ns0:v>53.33000183105469</ns0:v>
+      </ns0:c>
+      <ns0:c r="J93">
+        <ns0:v>0.43127608164152953</ns0:v>
+      </ns0:c>
+      <ns0:c r="K93">
+        <ns0:v>1.8259554721309765</ns0:v>
+      </ns0:c>
+      <ns0:c r="L93">
+        <ns0:v>67.7936821600555</ns0:v>
+      </ns0:c>
+      <ns0:c r="M93">
+        <ns0:v>50.878000259399414</ns0:v>
+      </ns0:c>
+      <ns0:c r="N93">
+        <ns0:v>46.77760025024414</ns0:v>
+      </ns0:c>
+      <ns0:c r="O93">
+        <ns0:v>39.159450149536134</ns0:v>
+      </ns0:c>
+      <ns0:c r="P93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>주가 98% 상승 이후 BBB Foods 이사가 보유 지분 전량을 매각했다는 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://www.fool.com/coverage/filings/2026/09/15/bbb-foods-director-sells-full-stake-after-98-stock-gain/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/TBBB/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="94">
+      <ns0:c r="A94" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B94" t="inlineStr">
+        <ns0:is>
+          <ns0:t>TJGC</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C94" t="inlineStr">
+        <ns0:is>
+          <ns0:t>TJGC Group Ltd</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D94" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Communication Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E94" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Advertising Agencies</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F94" t="inlineStr">
+        <ns0:is>
+          <ns0:t>자회사 Ctrl Media를 통해 홍콩에서 모바일 게임 앱 개발사 등에 통합 마케팅·광고를 제공.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G94">
+        <ns0:v>26.239999771118164</ns0:v>
+      </ns0:c>
+      <ns0:c r="H94">
+        <ns0:v>-6.9503579389867625</ns0:v>
+      </ns0:c>
+      <ns0:c r="I94">
+        <ns0:v>28.549999237060547</ns0:v>
+      </ns0:c>
+      <ns0:c r="J94">
+        <ns0:v>-8.091066646838252</ns0:v>
+      </ns0:c>
+      <ns0:c r="K94">
+        <ns0:v>0.06470879504473334</ns0:v>
+      </ns0:c>
+      <ns0:c r="L94">
+        <ns0:v>84.33039935941575</ns0:v>
+      </ns0:c>
+      <ns0:c r="M94">
+        <ns0:v>13.842500019073487</ns0:v>
+      </ns0:c>
+      <ns0:c r="N94">
+        <ns0:v>8.431300005912782</ns0:v>
+      </ns0:c>
+      <ns0:c r="O94">
+        <ns0:v>4.797375011444092</ns0:v>
+      </ns0:c>
+      <ns0:c r="P94" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q94" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R94" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T94" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/TJGC/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="95">
+      <ns0:c r="A95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>TKNO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Alpha Teknova Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Drug Manufacturers - Specialty &amp; Generic</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>치료제·백신·분자진단의 발굴·개발·상용화용 시약과 세포 배양·복제용 배지 등을 생산.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G95">
+        <ns0:v>9.329999923706055</ns0:v>
+      </ns0:c>
+      <ns0:c r="H95">
+        <ns0:v>0.43057009706433114</ns0:v>
+      </ns0:c>
+      <ns0:c r="I95">
+        <ns0:v>9.40999984741211</ns0:v>
+      </ns0:c>
+      <ns0:c r="J95">
+        <ns0:v>-0.8501586078989765</ns0:v>
+      </ns0:c>
+      <ns0:c r="K95">
+        <ns0:v>1.287419205400278</ns0:v>
+      </ns0:c>
+      <ns0:c r="L95">
+        <ns0:v>80.51748329392791</ns0:v>
+      </ns0:c>
+      <ns0:c r="M95">
+        <ns0:v>7.557750010490418</ns0:v>
+      </ns0:c>
+      <ns0:c r="N95">
+        <ns0:v>6.754900007247925</ns0:v>
+      </ns0:c>
+      <ns0:c r="O95">
+        <ns0:v>4.4307499957084655</ns0:v>
+      </ns0:c>
+      <ns0:c r="P95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>주가 7.1% 상승과 상승세 지속 가능성을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/alpha-teknova-tkno-moves-7-125300864.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/TKNO/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="96">
+      <ns0:c r="A96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>TWIN</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Twin Disc Incorporated</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Industrials</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Specialty Industrial Machinery</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>선박·중장비용 동력전달 장비를 설계·제조·판매하며 제조와 유통 부문을 운영.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G96">
+        <ns0:v>26.1299991607666</ns0:v>
+      </ns0:c>
+      <ns0:c r="H96">
+        <ns0:v>0.7324542127881806</ns0:v>
+      </ns0:c>
+      <ns0:c r="I96">
+        <ns0:v>26.18000030517578</ns0:v>
+      </ns0:c>
+      <ns0:c r="J96">
+        <ns0:v>-0.1909898541876398</ns0:v>
+      </ns0:c>
+      <ns0:c r="K96">
+        <ns0:v>0.6961598922075005</ns0:v>
+      </ns0:c>
+      <ns0:c r="L96">
+        <ns0:v>66.17698878916215</ns0:v>
+      </ns0:c>
+      <ns0:c r="M96">
+        <ns0:v>24.394500160217284</ns0:v>
+      </ns0:c>
+      <ns0:c r="N96">
+        <ns0:v>23.876800117492675</ns0:v>
+      </ns0:c>
+      <ns0:c r="O96">
+        <ns0:v>19.330750093460082</ns0:v>
+      </ns0:c>
+      <ns0:c r="P96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>기업 동향 관련 기사 제목 2건 확인. 주가 상승과의 인과는 미확인입니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://www.marketbeat.com/instant-alerts/event-twin-disc-targets-500m-as-defense-electrification-drive-record-growth-2026-08-28/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/TWIN/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="97">
+      <ns0:c r="A97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>TWST</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Twist Bioscience Corp</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Biotechnology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>치료제·진단·화학소재·농식품·데이터 저장·학술연구용 합성 DNA·유전자·유전자 조각을 제조·판매.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G97">
+        <ns0:v>182.8300018310547</ns0:v>
+      </ns0:c>
+      <ns0:c r="H97">
+        <ns0:v>-0.652065943705904</ns0:v>
+      </ns0:c>
+      <ns0:c r="I97">
+        <ns0:v>185.22000122070312</ns0:v>
+      </ns0:c>
+      <ns0:c r="J97">
+        <ns0:v>-1.2903570747743287</ns0:v>
+      </ns0:c>
+      <ns0:c r="K97">
+        <ns0:v>1.4297526119057997</ns0:v>
+      </ns0:c>
+      <ns0:c r="L97">
+        <ns0:v>73.35930688123281</ns0:v>
+      </ns0:c>
+      <ns0:c r="M97">
+        <ns0:v>144.93900146484376</ns0:v>
+      </ns0:c>
+      <ns0:c r="N97">
+        <ns0:v>126.27680068969727</ns0:v>
+      </ns0:c>
+      <ns0:c r="O97">
+        <ns0:v>73.17220010757447</ns0:v>
+      </ns0:c>
+      <ns0:c r="P97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>주가 16% 급등을 Anthropic과 연결한 Leerink의 해석과 Lilly TuneLab 제휴를 통한 AI 신약개발 확대 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://www.tikr.com/blog/twist-bioscience-stock-jumped-16-thursday-leerink-says-anthropic-made-it-happen</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/TWST/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="98">
+      <ns0:c r="A98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>TXG</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>10x Genomics Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Healthcare</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Medical Devices</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>생물학적 시스템 분석용 장비·소모품·소프트웨어를 개발·판매하며 Chromium 플랫폼 등을 제공.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G98">
+        <ns0:v>85.70999908447266</ns0:v>
+      </ns0:c>
+      <ns0:c r="H98">
+        <ns0:v>1.9022690078594362</ns0:v>
+      </ns0:c>
+      <ns0:c r="I98">
+        <ns0:v>85.93000030517578</ns0:v>
+      </ns0:c>
+      <ns0:c r="J98">
+        <ns0:v>-0.2560237634374518</ns0:v>
+      </ns0:c>
+      <ns0:c r="K98">
+        <ns0:v>1.228051116591165</ns0:v>
+      </ns0:c>
+      <ns0:c r="L98">
+        <ns0:v>73.93009622870196</ns0:v>
+      </ns0:c>
+      <ns0:c r="M98">
+        <ns0:v>70.76699981689453</ns0:v>
+      </ns0:c>
+      <ns0:c r="N98">
+        <ns0:v>60.36599998474121</ns0:v>
+      </ns0:c>
+      <ns0:c r="O98">
+        <ns0:v>32.907700033187865</ns0:v>
+      </ns0:c>
+      <ns0:c r="P98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>주가 하락, 동종 생명과학 도구·서비스 기업과의 2분기 비교, 종양학 AI 소식 속 고평가 가능성 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/healthcare/articles/surgery-partners-10x-genomics-quidelortho-213005328.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/TXG/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="99">
+      <ns0:c r="A99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>VEON</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>VEON Ltd ADR</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Communication Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Telecom Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>파키스탄·우크라이나·카자흐스탄·방글라데시·우즈베키스탄에서 이동통신·디지털 서비스 제공.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G99">
+        <ns0:v>73.5199966430664</ns0:v>
+      </ns0:c>
+      <ns0:c r="H99">
+        <ns0:v>1.3509728634829576</ns0:v>
+      </ns0:c>
+      <ns0:c r="I99">
+        <ns0:v>73.79000091552734</ns0:v>
+      </ns0:c>
+      <ns0:c r="J99">
+        <ns0:v>-0.3659090244083729</ns0:v>
+      </ns0:c>
+      <ns0:c r="K99">
+        <ns0:v>1.0945415219989754</ns0:v>
+      </ns0:c>
+      <ns0:c r="L99">
+        <ns0:v>79.3841757869804</ns0:v>
+      </ns0:c>
+      <ns0:c r="M99">
+        <ns0:v>67.35550003051758</ns0:v>
+      </ns0:c>
+      <ns0:c r="N99">
+        <ns0:v>60.14280014038086</ns0:v>
+      </ns0:c>
+      <ns0:c r="O99">
+        <ns0:v>54.30535001754761</ns0:v>
+      </ns0:c>
+      <ns0:c r="P99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>특정 재료 확인 안 됨</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/VEON/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="100">
+      <ns0:c r="A100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>VNCE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Vince Holding Corp</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Consumer Cyclical</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Apparel Manufacturing</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국과 해외에서 Vince 도매·소비자 직접 판매를 통해 캐시미어 스웨터·실크 블라우스 등 여성복 판매.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G100">
+        <ns0:v>11.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="H100">
+        <ns0:v>3.2315946641153115</ns0:v>
+      </ns0:c>
+      <ns0:c r="I100">
+        <ns0:v>11.979999542236328</ns0:v>
+      </ns0:c>
+      <ns0:c r="J100">
+        <ns0:v>-4.006674128359156</ns0:v>
+      </ns0:c>
+      <ns0:c r="K100">
+        <ns0:v>1.1962751979682897</ns0:v>
+      </ns0:c>
+      <ns0:c r="L100">
+        <ns0:v>70.42947865305948</ns0:v>
+      </ns0:c>
+      <ns0:c r="M100">
+        <ns0:v>8.061500000953675</ns0:v>
+      </ns0:c>
+      <ns0:c r="N100">
+        <ns0:v>7.029200019836426</ns0:v>
+      </ns0:c>
+      <ns0:c r="O100">
+        <ns0:v>4.685350006818771</ns0:v>
+      </ns0:c>
+      <ns0:c r="P100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보도된 해석</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>주가 추세의 지속 가능성과 가격 매력을 조명한 기사, 2분기 실적 발표의 OVO 규모·전망 상향 관련 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/markets/stocks/articles/vince-holding-vnce-move-heres-125501304.html</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/VNCE/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="101">
+      <ns0:c r="A101" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B101" t="inlineStr">
+        <ns0:is>
           <ns0:t>WEYS</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="C54" t="inlineStr">
+      <ns0:c r="C101" t="inlineStr">
         <ns0:is>
           <ns0:t>Weyco Group Inc</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="D54" t="inlineStr">
+      <ns0:c r="D101" t="inlineStr">
         <ns0:is>
           <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E54" t="inlineStr">
+      <ns0:c r="E101" t="inlineStr">
         <ns0:is>
           <ns0:t>Footwear &amp; Accessories</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F54" t="inlineStr">
+      <ns0:c r="F101" t="inlineStr">
         <ns0:is>
           <ns0:t>미국·캐나다·호주·아시아·남아프리카에서 남성·여성·아동용 신발을 디자인·마케팅·유통.</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G54">
+      <ns0:c r="G101">
         <ns0:v>47.439998626708984</ns0:v>
       </ns0:c>
-      <ns0:c r="H54">
+      <ns0:c r="H101">
         <ns0:v>0.042177263888576455</ns0:v>
       </ns0:c>
-      <ns0:c r="I54">
+      <ns0:c r="I101">
         <ns0:v>48.68000030517578</ns0:v>
       </ns0:c>
-      <ns0:c r="J54">
+      <ns0:c r="J101">
         <ns0:v>-2.547250761489739</ns0:v>
       </ns0:c>
-      <ns0:c r="K54">
+      <ns0:c r="K101">
         <ns0:v>0.9512362637362637</ns0:v>
       </ns0:c>
-      <ns0:c r="L54">
+      <ns0:c r="L101">
         <ns0:v>64.62781339120424</ns0:v>
       </ns0:c>
-      <ns0:c r="M54">
+      <ns0:c r="M101">
         <ns0:v>45.063500213623044</ns0:v>
       </ns0:c>
-      <ns0:c r="N54">
+      <ns0:c r="N101">
         <ns0:v>43.64900024414062</ns0:v>
       </ns0:c>
-      <ns0:c r="O54">
+      <ns0:c r="O101">
         <ns0:v>36.159800090789794</ns0:v>
       </ns0:c>
-      <ns0:c r="P54" t="inlineStr">
+      <ns0:c r="P101" t="inlineStr">
         <ns0:is>
           <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="Q54" t="inlineStr">
+      <ns0:c r="Q101" t="inlineStr">
         <ns0:is>
           <ns0:t>특정 재료 확인 안 됨</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="R54" t="inlineStr">
+      <ns0:c r="R101" t="inlineStr">
         <ns0:is>
           <ns0:t>조회한 자료에서 기준일 이전의 관련 재료를 확인하지 못했습니다.</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="T54" t="inlineStr">
+      <ns0:c r="T101" t="inlineStr">
         <ns0:is>
           <ns0:t>https://finance.yahoo.com/quote/WEYS/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>
-  <ns0:autoFilter ref="A1:T54"/>
+  <ns0:autoFilter ref="A1:T101"/>
   <ns0:hyperlinks>
     <ns0:hyperlink ref="S2" ns1:id="rId1"/>
-    <ns0:hyperlink ref="S3" ns1:id="rId2"/>
-    <ns0:hyperlink ref="T4" ns1:id="rId3"/>
-    <ns0:hyperlink ref="T5" ns1:id="rId4"/>
-    <ns0:hyperlink ref="S6" ns1:id="rId5"/>
-    <ns0:hyperlink ref="T6" ns1:id="rId6"/>
-    <ns0:hyperlink ref="S7" ns1:id="rId7"/>
-    <ns0:hyperlink ref="T7" ns1:id="rId8"/>
-    <ns0:hyperlink ref="S8" ns1:id="rId9"/>
-    <ns0:hyperlink ref="T8" ns1:id="rId10"/>
-    <ns0:hyperlink ref="T9" ns1:id="rId11"/>
-    <ns0:hyperlink ref="S10" ns1:id="rId12"/>
-    <ns0:hyperlink ref="T10" ns1:id="rId13"/>
-    <ns0:hyperlink ref="T11" ns1:id="rId14"/>
-    <ns0:hyperlink ref="T12" ns1:id="rId15"/>
-    <ns0:hyperlink ref="S13" ns1:id="rId16"/>
-    <ns0:hyperlink ref="T13" ns1:id="rId17"/>
-    <ns0:hyperlink ref="T14" ns1:id="rId18"/>
-    <ns0:hyperlink ref="T15" ns1:id="rId19"/>
-    <ns0:hyperlink ref="S16" ns1:id="rId20"/>
-    <ns0:hyperlink ref="T16" ns1:id="rId21"/>
-    <ns0:hyperlink ref="S17" ns1:id="rId22"/>
-    <ns0:hyperlink ref="T17" ns1:id="rId23"/>
-    <ns0:hyperlink ref="T18" ns1:id="rId24"/>
-    <ns0:hyperlink ref="T19" ns1:id="rId25"/>
-    <ns0:hyperlink ref="S20" ns1:id="rId26"/>
-    <ns0:hyperlink ref="T20" ns1:id="rId27"/>
-    <ns0:hyperlink ref="S21" ns1:id="rId28"/>
-    <ns0:hyperlink ref="T21" ns1:id="rId29"/>
-    <ns0:hyperlink ref="S22" ns1:id="rId30"/>
-    <ns0:hyperlink ref="T22" ns1:id="rId31"/>
-    <ns0:hyperlink ref="S23" ns1:id="rId32"/>
-    <ns0:hyperlink ref="T23" ns1:id="rId33"/>
-    <ns0:hyperlink ref="S24" ns1:id="rId34"/>
-    <ns0:hyperlink ref="T24" ns1:id="rId35"/>
-    <ns0:hyperlink ref="S25" ns1:id="rId36"/>
-    <ns0:hyperlink ref="T25" ns1:id="rId37"/>
-    <ns0:hyperlink ref="S26" ns1:id="rId38"/>
-    <ns0:hyperlink ref="T26" ns1:id="rId39"/>
-    <ns0:hyperlink ref="T27" ns1:id="rId40"/>
-    <ns0:hyperlink ref="S28" ns1:id="rId41"/>
-    <ns0:hyperlink ref="T28" ns1:id="rId42"/>
-    <ns0:hyperlink ref="S29" ns1:id="rId43"/>
-    <ns0:hyperlink ref="T29" ns1:id="rId44"/>
-    <ns0:hyperlink ref="S30" ns1:id="rId45"/>
-    <ns0:hyperlink ref="T30" ns1:id="rId46"/>
-    <ns0:hyperlink ref="S31" ns1:id="rId47"/>
-    <ns0:hyperlink ref="T31" ns1:id="rId48"/>
-    <ns0:hyperlink ref="T32" ns1:id="rId49"/>
-    <ns0:hyperlink ref="S33" ns1:id="rId50"/>
-    <ns0:hyperlink ref="T33" ns1:id="rId51"/>
-    <ns0:hyperlink ref="T34" ns1:id="rId52"/>
-    <ns0:hyperlink ref="T35" ns1:id="rId53"/>
-    <ns0:hyperlink ref="S36" ns1:id="rId54"/>
-    <ns0:hyperlink ref="T36" ns1:id="rId55"/>
-    <ns0:hyperlink ref="S37" ns1:id="rId56"/>
-    <ns0:hyperlink ref="T37" ns1:id="rId57"/>
-    <ns0:hyperlink ref="S38" ns1:id="rId58"/>
-    <ns0:hyperlink ref="T38" ns1:id="rId59"/>
-    <ns0:hyperlink ref="S39" ns1:id="rId60"/>
-    <ns0:hyperlink ref="T39" ns1:id="rId61"/>
-    <ns0:hyperlink ref="S40" ns1:id="rId62"/>
-    <ns0:hyperlink ref="T40" ns1:id="rId63"/>
-    <ns0:hyperlink ref="S41" ns1:id="rId64"/>
-    <ns0:hyperlink ref="T41" ns1:id="rId65"/>
-    <ns0:hyperlink ref="T42" ns1:id="rId66"/>
-    <ns0:hyperlink ref="S43" ns1:id="rId67"/>
-    <ns0:hyperlink ref="T43" ns1:id="rId68"/>
-    <ns0:hyperlink ref="T44" ns1:id="rId69"/>
-    <ns0:hyperlink ref="T45" ns1:id="rId70"/>
-    <ns0:hyperlink ref="S46" ns1:id="rId71"/>
-    <ns0:hyperlink ref="T46" ns1:id="rId72"/>
-    <ns0:hyperlink ref="T47" ns1:id="rId73"/>
-    <ns0:hyperlink ref="S48" ns1:id="rId74"/>
-    <ns0:hyperlink ref="T48" ns1:id="rId75"/>
-    <ns0:hyperlink ref="S49" ns1:id="rId76"/>
-    <ns0:hyperlink ref="T49" ns1:id="rId77"/>
-    <ns0:hyperlink ref="S50" ns1:id="rId78"/>
-    <ns0:hyperlink ref="T50" ns1:id="rId79"/>
-    <ns0:hyperlink ref="S51" ns1:id="rId80"/>
-    <ns0:hyperlink ref="T51" ns1:id="rId81"/>
-    <ns0:hyperlink ref="T52" ns1:id="rId82"/>
-    <ns0:hyperlink ref="S53" ns1:id="rId83"/>
-    <ns0:hyperlink ref="T53" ns1:id="rId84"/>
-    <ns0:hyperlink ref="T54" ns1:id="rId85"/>
+    <ns0:hyperlink ref="T2" ns1:id="rId2"/>
+    <ns0:hyperlink ref="S3" ns1:id="rId3"/>
+    <ns0:hyperlink ref="T3" ns1:id="rId4"/>
+    <ns0:hyperlink ref="T4" ns1:id="rId5"/>
+    <ns0:hyperlink ref="T5" ns1:id="rId6"/>
+    <ns0:hyperlink ref="S6" ns1:id="rId7"/>
+    <ns0:hyperlink ref="T6" ns1:id="rId8"/>
+    <ns0:hyperlink ref="S7" ns1:id="rId9"/>
+    <ns0:hyperlink ref="T7" ns1:id="rId10"/>
+    <ns0:hyperlink ref="S8" ns1:id="rId11"/>
+    <ns0:hyperlink ref="T8" ns1:id="rId12"/>
+    <ns0:hyperlink ref="S9" ns1:id="rId13"/>
+    <ns0:hyperlink ref="T9" ns1:id="rId14"/>
+    <ns0:hyperlink ref="S10" ns1:id="rId15"/>
+    <ns0:hyperlink ref="T10" ns1:id="rId16"/>
+    <ns0:hyperlink ref="S11" ns1:id="rId17"/>
+    <ns0:hyperlink ref="T11" ns1:id="rId18"/>
+    <ns0:hyperlink ref="S12" ns1:id="rId19"/>
+    <ns0:hyperlink ref="T12" ns1:id="rId20"/>
+    <ns0:hyperlink ref="S13" ns1:id="rId21"/>
+    <ns0:hyperlink ref="T13" ns1:id="rId22"/>
+    <ns0:hyperlink ref="S14" ns1:id="rId23"/>
+    <ns0:hyperlink ref="T14" ns1:id="rId24"/>
+    <ns0:hyperlink ref="S15" ns1:id="rId25"/>
+    <ns0:hyperlink ref="T15" ns1:id="rId26"/>
+    <ns0:hyperlink ref="T16" ns1:id="rId27"/>
+    <ns0:hyperlink ref="T17" ns1:id="rId28"/>
+    <ns0:hyperlink ref="S18" ns1:id="rId29"/>
+    <ns0:hyperlink ref="T18" ns1:id="rId30"/>
+    <ns0:hyperlink ref="T19" ns1:id="rId31"/>
+    <ns0:hyperlink ref="S20" ns1:id="rId32"/>
+    <ns0:hyperlink ref="T20" ns1:id="rId33"/>
+    <ns0:hyperlink ref="S21" ns1:id="rId34"/>
+    <ns0:hyperlink ref="T21" ns1:id="rId35"/>
+    <ns0:hyperlink ref="S22" ns1:id="rId36"/>
+    <ns0:hyperlink ref="T22" ns1:id="rId37"/>
+    <ns0:hyperlink ref="T23" ns1:id="rId38"/>
+    <ns0:hyperlink ref="T24" ns1:id="rId39"/>
+    <ns0:hyperlink ref="S25" ns1:id="rId40"/>
+    <ns0:hyperlink ref="T25" ns1:id="rId41"/>
+    <ns0:hyperlink ref="S26" ns1:id="rId42"/>
+    <ns0:hyperlink ref="T26" ns1:id="rId43"/>
+    <ns0:hyperlink ref="S27" ns1:id="rId44"/>
+    <ns0:hyperlink ref="T27" ns1:id="rId45"/>
+    <ns0:hyperlink ref="S28" ns1:id="rId46"/>
+    <ns0:hyperlink ref="T28" ns1:id="rId47"/>
+    <ns0:hyperlink ref="S29" ns1:id="rId48"/>
+    <ns0:hyperlink ref="T29" ns1:id="rId49"/>
+    <ns0:hyperlink ref="T30" ns1:id="rId50"/>
+    <ns0:hyperlink ref="S31" ns1:id="rId51"/>
+    <ns0:hyperlink ref="T31" ns1:id="rId52"/>
+    <ns0:hyperlink ref="T32" ns1:id="rId53"/>
+    <ns0:hyperlink ref="T33" ns1:id="rId54"/>
+    <ns0:hyperlink ref="S34" ns1:id="rId55"/>
+    <ns0:hyperlink ref="T34" ns1:id="rId56"/>
+    <ns0:hyperlink ref="S35" ns1:id="rId57"/>
+    <ns0:hyperlink ref="T35" ns1:id="rId58"/>
+    <ns0:hyperlink ref="S36" ns1:id="rId59"/>
+    <ns0:hyperlink ref="T36" ns1:id="rId60"/>
+    <ns0:hyperlink ref="S37" ns1:id="rId61"/>
+    <ns0:hyperlink ref="T37" ns1:id="rId62"/>
+    <ns0:hyperlink ref="S38" ns1:id="rId63"/>
+    <ns0:hyperlink ref="T38" ns1:id="rId64"/>
+    <ns0:hyperlink ref="S39" ns1:id="rId65"/>
+    <ns0:hyperlink ref="T39" ns1:id="rId66"/>
+    <ns0:hyperlink ref="T40" ns1:id="rId67"/>
+    <ns0:hyperlink ref="S41" ns1:id="rId68"/>
+    <ns0:hyperlink ref="T41" ns1:id="rId69"/>
+    <ns0:hyperlink ref="T42" ns1:id="rId70"/>
+    <ns0:hyperlink ref="T43" ns1:id="rId71"/>
+    <ns0:hyperlink ref="S44" ns1:id="rId72"/>
+    <ns0:hyperlink ref="T44" ns1:id="rId73"/>
+    <ns0:hyperlink ref="S45" ns1:id="rId74"/>
+    <ns0:hyperlink ref="T45" ns1:id="rId75"/>
+    <ns0:hyperlink ref="T46" ns1:id="rId76"/>
+    <ns0:hyperlink ref="S47" ns1:id="rId77"/>
+    <ns0:hyperlink ref="T47" ns1:id="rId78"/>
+    <ns0:hyperlink ref="S48" ns1:id="rId79"/>
+    <ns0:hyperlink ref="T48" ns1:id="rId80"/>
+    <ns0:hyperlink ref="S49" ns1:id="rId81"/>
+    <ns0:hyperlink ref="S50" ns1:id="rId82"/>
+    <ns0:hyperlink ref="T51" ns1:id="rId83"/>
+    <ns0:hyperlink ref="T52" ns1:id="rId84"/>
+    <ns0:hyperlink ref="S53" ns1:id="rId85"/>
+    <ns0:hyperlink ref="T53" ns1:id="rId86"/>
+    <ns0:hyperlink ref="S54" ns1:id="rId87"/>
+    <ns0:hyperlink ref="T54" ns1:id="rId88"/>
+    <ns0:hyperlink ref="S55" ns1:id="rId89"/>
+    <ns0:hyperlink ref="T55" ns1:id="rId90"/>
+    <ns0:hyperlink ref="T56" ns1:id="rId91"/>
+    <ns0:hyperlink ref="S57" ns1:id="rId92"/>
+    <ns0:hyperlink ref="T57" ns1:id="rId93"/>
+    <ns0:hyperlink ref="T58" ns1:id="rId94"/>
+    <ns0:hyperlink ref="T59" ns1:id="rId95"/>
+    <ns0:hyperlink ref="S60" ns1:id="rId96"/>
+    <ns0:hyperlink ref="T60" ns1:id="rId97"/>
+    <ns0:hyperlink ref="T61" ns1:id="rId98"/>
+    <ns0:hyperlink ref="T62" ns1:id="rId99"/>
+    <ns0:hyperlink ref="S63" ns1:id="rId100"/>
+    <ns0:hyperlink ref="T63" ns1:id="rId101"/>
+    <ns0:hyperlink ref="S64" ns1:id="rId102"/>
+    <ns0:hyperlink ref="T64" ns1:id="rId103"/>
+    <ns0:hyperlink ref="T65" ns1:id="rId104"/>
+    <ns0:hyperlink ref="T66" ns1:id="rId105"/>
+    <ns0:hyperlink ref="S67" ns1:id="rId106"/>
+    <ns0:hyperlink ref="T67" ns1:id="rId107"/>
+    <ns0:hyperlink ref="S68" ns1:id="rId108"/>
+    <ns0:hyperlink ref="T68" ns1:id="rId109"/>
+    <ns0:hyperlink ref="S69" ns1:id="rId110"/>
+    <ns0:hyperlink ref="T69" ns1:id="rId111"/>
+    <ns0:hyperlink ref="S70" ns1:id="rId112"/>
+    <ns0:hyperlink ref="T70" ns1:id="rId113"/>
+    <ns0:hyperlink ref="S71" ns1:id="rId114"/>
+    <ns0:hyperlink ref="T71" ns1:id="rId115"/>
+    <ns0:hyperlink ref="S72" ns1:id="rId116"/>
+    <ns0:hyperlink ref="T72" ns1:id="rId117"/>
+    <ns0:hyperlink ref="S73" ns1:id="rId118"/>
+    <ns0:hyperlink ref="T73" ns1:id="rId119"/>
+    <ns0:hyperlink ref="T74" ns1:id="rId120"/>
+    <ns0:hyperlink ref="S75" ns1:id="rId121"/>
+    <ns0:hyperlink ref="T75" ns1:id="rId122"/>
+    <ns0:hyperlink ref="S76" ns1:id="rId123"/>
+    <ns0:hyperlink ref="T76" ns1:id="rId124"/>
+    <ns0:hyperlink ref="S77" ns1:id="rId125"/>
+    <ns0:hyperlink ref="T77" ns1:id="rId126"/>
+    <ns0:hyperlink ref="S78" ns1:id="rId127"/>
+    <ns0:hyperlink ref="T78" ns1:id="rId128"/>
+    <ns0:hyperlink ref="T79" ns1:id="rId129"/>
+    <ns0:hyperlink ref="S80" ns1:id="rId130"/>
+    <ns0:hyperlink ref="T80" ns1:id="rId131"/>
+    <ns0:hyperlink ref="T81" ns1:id="rId132"/>
+    <ns0:hyperlink ref="T82" ns1:id="rId133"/>
+    <ns0:hyperlink ref="S83" ns1:id="rId134"/>
+    <ns0:hyperlink ref="T83" ns1:id="rId135"/>
+    <ns0:hyperlink ref="S84" ns1:id="rId136"/>
+    <ns0:hyperlink ref="T84" ns1:id="rId137"/>
+    <ns0:hyperlink ref="S85" ns1:id="rId138"/>
+    <ns0:hyperlink ref="T85" ns1:id="rId139"/>
+    <ns0:hyperlink ref="S86" ns1:id="rId140"/>
+    <ns0:hyperlink ref="T86" ns1:id="rId141"/>
+    <ns0:hyperlink ref="S87" ns1:id="rId142"/>
+    <ns0:hyperlink ref="T87" ns1:id="rId143"/>
+    <ns0:hyperlink ref="S88" ns1:id="rId144"/>
+    <ns0:hyperlink ref="T88" ns1:id="rId145"/>
+    <ns0:hyperlink ref="T89" ns1:id="rId146"/>
+    <ns0:hyperlink ref="S90" ns1:id="rId147"/>
+    <ns0:hyperlink ref="T90" ns1:id="rId148"/>
+    <ns0:hyperlink ref="T91" ns1:id="rId149"/>
+    <ns0:hyperlink ref="T92" ns1:id="rId150"/>
+    <ns0:hyperlink ref="S93" ns1:id="rId151"/>
+    <ns0:hyperlink ref="T93" ns1:id="rId152"/>
+    <ns0:hyperlink ref="T94" ns1:id="rId153"/>
+    <ns0:hyperlink ref="S95" ns1:id="rId154"/>
+    <ns0:hyperlink ref="T95" ns1:id="rId155"/>
+    <ns0:hyperlink ref="S96" ns1:id="rId156"/>
+    <ns0:hyperlink ref="T96" ns1:id="rId157"/>
+    <ns0:hyperlink ref="S97" ns1:id="rId158"/>
+    <ns0:hyperlink ref="T97" ns1:id="rId159"/>
+    <ns0:hyperlink ref="S98" ns1:id="rId160"/>
+    <ns0:hyperlink ref="T98" ns1:id="rId161"/>
+    <ns0:hyperlink ref="T99" ns1:id="rId162"/>
+    <ns0:hyperlink ref="S100" ns1:id="rId163"/>
+    <ns0:hyperlink ref="T100" ns1:id="rId164"/>
+    <ns0:hyperlink ref="T101" ns1:id="rId165"/>
   </ns0:hyperlinks>
 </ns0:worksheet>
 </file>
@@ -4541,7 +8478,7 @@
     <ns0:row r="2">
       <ns0:c r="A2" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B2" t="inlineStr">
@@ -4550,18 +8487,18 @@
         </ns0:is>
       </ns0:c>
       <ns0:c r="C2">
-        <ns0:v>15</ns0:v>
+        <ns0:v>18</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="3">
       <ns0:c r="A3" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B3" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C3">
@@ -4571,42 +8508,42 @@
     <ns0:row r="4">
       <ns0:c r="A4" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B4" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C4">
-        <ns0:v>7</ns0:v>
+        <ns0:v>6</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="5">
       <ns0:c r="A5" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Communication Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C5">
-        <ns0:v>7</ns0:v>
+        <ns0:v>5</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="6">
       <ns0:c r="A6" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B6" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Services</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C6">
@@ -4616,31 +8553,31 @@
     <ns0:row r="7">
       <ns0:c r="A7" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B7" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Basic Materials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C7">
-        <ns0:v>4</ns0:v>
+        <ns0:v>2</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="8">
       <ns0:c r="A8" t="inlineStr">
         <ns0:is>
-          <ns0:t>2026-09-25</ns0:t>
+          <ns0:t>2026-09-28</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B8" t="inlineStr">
         <ns0:is>
-          <ns0:t>Basic Materials</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C8">
-        <ns0:v>3</ns0:v>
+        <ns0:v>2</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="9">
@@ -4651,11 +8588,11 @@
       </ns0:c>
       <ns0:c r="B9" t="inlineStr">
         <ns0:is>
-          <ns0:t>미분류</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C9">
-        <ns0:v>2</ns0:v>
+        <ns0:v>15</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="10">
@@ -4666,15 +8603,120 @@
       </ns0:c>
       <ns0:c r="B10" t="inlineStr">
         <ns0:is>
+          <ns0:t>Technology</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C10">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Consumer Cyclical</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C11">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="12">
+      <ns0:c r="A12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Financial</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C12">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="13">
+      <ns0:c r="A13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Communication Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C13">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="14">
+      <ns0:c r="A14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Industrials</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C14">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="15">
+      <ns0:c r="A15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Basic Materials</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C15">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="16">
+      <ns0:c r="A16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미분류</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C16">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="17">
+      <ns0:c r="A17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-25</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B17" t="inlineStr">
+        <ns0:is>
           <ns0:t>Consumer Defensive</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="C10">
+      <ns0:c r="C17">
         <ns0:v>1</ns0:v>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>
-  <ns0:autoFilter ref="A1:C10"/>
+  <ns0:autoFilter ref="A1:C17"/>
 </ns0:worksheet>
 </file>
 
@@ -4706,24 +8748,44 @@
     <ns0:row r="2">
       <ns0:c r="A2" t="inlineStr">
         <ns0:is>
+          <ns0:t>2026-09-28</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>partial</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C2">
+        <ns0:v>47</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Finviz 신고가 후보 중 검증된 미국 종목 · 분할조정 일봉 · 직전 252거래일 최고가와 비교</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" t="inlineStr">
+        <ns0:is>
           <ns0:t>2026-09-25</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="B2" t="inlineStr">
+      <ns0:c r="B3" t="inlineStr">
         <ns0:is>
           <ns0:t>partial</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="C2">
+      <ns0:c r="C3">
         <ns0:v>53</ns0:v>
       </ns0:c>
-      <ns0:c r="D2" t="inlineStr">
+      <ns0:c r="D3" t="inlineStr">
         <ns0:is>
           <ns0:t>Finviz 신고가 후보 중 검증된 미국 종목 · 분할조정 일봉 · 직전 252거래일 최고가와 비교</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>
-  <ns0:autoFilter ref="A1:D2"/>
+  <ns0:autoFilter ref="A1:D3"/>
 </ns0:worksheet>
 </file>
--- a/technicals/exports/new-highs-history.xlsx
+++ b/technicals/exports/new-highs-history.xlsx
@@ -142,7 +142,7 @@
       </ns0:c>
       <ns0:c r="F2" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계 생명과학, 진단 및 응용화학 시장에 용도별 솔루션을 제공.</ns0:t>
+          <ns0:t>전 세계 생명과학·진단·응용화학 시장에 용도별 솔루션을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G2">
@@ -184,7 +184,7 @@
       </ns0:c>
       <ns0:c r="R2" t="inlineStr">
         <ns0:is>
-          <ns0:t>교환 제안과 반복 매출을 통한 가치평가, 실적 발표 후 9.6% 오른 주가의 지속 가능성이 다뤄졌다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>교환 제안·반복 매출을 둘러싼 기업가치 평가와 최근 실적 발표 이후 주가 9.6% 상승의 지속 가능성 조명. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S2" t="inlineStr">
@@ -226,7 +226,7 @@
       </ns0:c>
       <ns0:c r="F3" t="inlineStr">
         <ns0:is>
-          <ns0:t>미충족 의료 수요에 대응하는 항체 의약품을 개발하며, 비호르몬 치료제 ABCL635는 임상 2상 중.</ns0:t>
+          <ns0:t>미충족 의료 수요에 대응하는 항체 의약품 개발사로, 비호르몬 치료제 ABCL635는 임상 2상 중.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G3">
@@ -268,7 +268,7 @@
       </ns0:c>
       <ns0:c r="R3" t="inlineStr">
         <ns0:is>
-          <ns0:t>ABCL 주가가 3개월간 121% 상승했다는 보도가 나왔다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>애브셀라 주가의 최근 3개월간 121% 상승을 조명. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S3" t="inlineStr">
@@ -310,7 +310,7 @@
       </ns0:c>
       <ns0:c r="F4" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국 뷰티·개인관리 브랜드에 전략, 마케팅, 전 채널 판매, 고객 서비스 및 물류 등 브랜드 관리 제공.</ns0:t>
+          <ns0:t>중국 뷰티·개인관리 브랜드에 전략·마케팅·전 채널 판매·고객 서비스·물류 등 브랜드 관리 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G4">
@@ -386,7 +386,7 @@
       </ns0:c>
       <ns0:c r="F5" t="inlineStr">
         <ns0:is>
-          <ns0:t>북미·아시아태평양 등에서 전문·기술 컨설팅과 운영 모델 설계 관련 자문을 제공.</ns0:t>
+          <ns0:t>북미·아시아태평양 등에서 전문·기술 컨설팅과 운영 모델 설계 자문 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G5">
@@ -507,7 +507,7 @@
       </ns0:c>
       <ns0:c r="R6" t="inlineStr">
         <ns0:is>
-          <ns0:t>임상시험 업데이트와 신규 자금 조달 이후 아제너스 주식의 적정가치 평가가 높아졌다는 보도다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>임상 진행 소식과 신규 자금 조달 이후 아제너스 주식의 적정가치 평가 상향 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S6" t="inlineStr">
@@ -675,7 +675,7 @@
       </ns0:c>
       <ns0:c r="R8" t="inlineStr">
         <ns0:is>
-          <ns0:t>AI 데이터센터 분야에서 앳코어가 주목받는 이유와 전기 시스템 업종 내 우수한 2분기 실적이 다뤄졌다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>AI 데이터센터 관련 기업으로 아트코어가 주목받으며, 전기 시스템 업종 2분기 실적 비교에서 우수 평가. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S8" t="inlineStr">
@@ -717,7 +717,7 @@
       </ns0:c>
       <ns0:c r="F9" t="inlineStr">
         <ns0:is>
-          <ns0:t>자회사를 통해 MLB 애틀랜타 브레이브스 구단과 구장을 소유·운영하며 복합개발 사업을 영위.</ns0:t>
+          <ns0:t>자회사를 통해 MLB 애틀랜타 브레이브스 구단·구장을 소유·운영하고 복합개발 사업 영위.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G9">
@@ -759,7 +759,7 @@
       </ns0:c>
       <ns0:c r="R9" t="inlineStr">
         <ns0:is>
-          <ns0:t>애틀랜타 브레이브스 주주가 가치 실현을 위한 매각과 구단 인수자 물색을 촉구했다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>주주 브리치 인렛이 기업가치 실현을 위한 애틀랜타 브레이브스 매각과 구단 인수자 물색을 촉구. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S9" t="inlineStr">
@@ -801,7 +801,7 @@
       </ns0:c>
       <ns0:c r="F10" t="inlineStr">
         <ns0:is>
-          <ns0:t>자회사를 통해 MLB 애틀랜타 브레이브스 구단과 구장을 소유·운영하며 복합개발 사업을 영위.</ns0:t>
+          <ns0:t>자회사를 통해 MLB 애틀랜타 브레이브스 구단·구장을 소유·운영하고 복합개발 사업 영위.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G10">
@@ -843,7 +843,7 @@
       </ns0:c>
       <ns0:c r="R10" t="inlineStr">
         <ns0:is>
-          <ns0:t>애틀랜타 브레이브스 주주가 가치 실현을 위한 매각과 구단 인수자 물색을 촉구했다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>주주 브리치 인렛이 기업가치 실현을 위한 애틀랜타 브레이브스 매각과 구단 인수자 물색을 촉구. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S10" t="inlineStr">
@@ -885,7 +885,7 @@
       </ns0:c>
       <ns0:c r="F11" t="inlineStr">
         <ns0:is>
-          <ns0:t>폐암 위험 평가를 위한 혈액 기반 폐결절 검사 등 진단 솔루션을 제공.</ns0:t>
+          <ns0:t>폐암 위험 평가를 위한 혈액 기반 폐결절 검사 등 진단 솔루션 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G11">
@@ -927,7 +927,7 @@
       </ns0:c>
       <ns0:c r="R11" t="inlineStr">
         <ns0:is>
-          <ns0:t>종양 정보 활용·비활용 방식으로 MRD 검사를 확대하고 바이오래드·써모피셔와 모니터링 프로그램을 추진했다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>종양 정보 활용·비활용 방식으로 MRD 검사를 확대하고 바이오래드·써모 피셔와 모니터링 프로그램 추진. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S11" t="inlineStr">
@@ -969,7 +969,7 @@
       </ns0:c>
       <ns0:c r="F12" t="inlineStr">
         <ns0:is>
-          <ns0:t>다발성경화증, 척수성 근위축증, 프리드라이히 운동실조증 등의 치료제를 발굴·개발·제조·공급.</ns0:t>
+          <ns0:t>다발성경화증·척수성 근위축증·프리드라이히 운동실조증 등의 치료제를 발굴·개발·제조·공급.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G12">
@@ -1011,7 +1011,7 @@
       </ns0:c>
       <ns0:c r="R12" t="inlineStr">
         <ns0:is>
-          <ns0:t>성장 제품군과 기존 다발성경화증 약물의 실적 비교, 2분기 실적, 가정용 레켐비 펜·신장질환 데이터가 다뤄졌다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>성장 제품군과 기존 다발성경화증 약물의 성과 비교, 2분기 실적, 가정용 레켐비 펜·신장질환 데이터 진전 조명. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S12" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </ns0:c>
       <ns0:c r="R13" t="inlineStr">
         <ns0:is>
-          <ns0:t>다이아몬드힐이 바이오라이프 솔루션스의 높은 전환 비용에 주목해 투자했다는 보도다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>다이아몬드 힐이 바이오라이프 솔루션스의 높은 전환 비용에 주목해 투자. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S13" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </ns0:c>
       <ns0:c r="F14" t="inlineStr">
         <ns0:is>
-          <ns0:t>이식 환자의 치료 결과와 장기 건강 개선을 위한 신장·심장 이식 검사 솔루션 등을 제공하는 기업.</ns0:t>
+          <ns0:t>이식 환자의 치료 결과와 장기 건강 개선을 위한 신장·심장 이식 검사 솔루션 제공 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G14">
@@ -1221,7 +1221,7 @@
       </ns0:c>
       <ns0:c r="F15" t="inlineStr">
         <ns0:is>
-          <ns0:t>자회사와 함께 미국 및 라틴아메리카에서 영화관을 운영하는 영화 상영 기업.</ns0:t>
+          <ns0:t>자회사와 함께 미국·라틴아메리카에서 영화관을 운영하는 영화 상영 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G15">
@@ -1263,7 +1263,7 @@
       </ns0:c>
       <ns0:c r="R15" t="inlineStr">
         <ns0:is>
-          <ns0:t>AMC 주가가 13% 상승한 가운데 시네마크와 아이맥스도 소폭 올랐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>AMC의 차환 관련 랠리와 13% 상승이 보도된 가운데 시네마크와 IMAX도 소폭 상승. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S15" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </ns0:c>
       <ns0:c r="F16" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 합병, 주식 교환, 자산 인수, 자본 재편 등 기업결합을 추진.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병·주식 교환·자산 인수·자본 재편 등 기업결합 추진.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G16">
@@ -1381,7 +1381,7 @@
       </ns0:c>
       <ns0:c r="F17" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병·주식 교환·자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G17">
@@ -1460,7 +1460,7 @@
       </ns0:c>
       <ns0:c r="F18" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 소파, 의자, 침실·식당 가구 등 주거용 가구를 제조·유통·수입·판매한다.</ns0:t>
+          <ns0:t>미국에서 소파·의자·침실·식당용 주거 가구를 제조·유통·수입·판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G18">
@@ -1502,7 +1502,7 @@
       </ns0:c>
       <ns0:c r="R18" t="inlineStr">
         <ns0:is>
-          <ns0:t>신고가 경신 후 추가 상승 여력과 올해 경기소비재 업종 대비 주가 성과를 점검하는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>신고가 경신 후 추가 상승 여력과 올해 경기소비재 종목 대비 수익률을 점검한 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S18" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </ns0:c>
       <ns0:c r="F19" t="inlineStr">
         <ns0:is>
-          <ns0:t>개인과 기업에 예금·은행·자산관리 서비스를 제공하는 퍼스트 시코스트 은행의 지주회사.</ns0:t>
+          <ns0:t>개인·기업에 예금·은행·자산관리 서비스를 제공하는 퍼스트 시코스트 은행의 지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G19">
@@ -1620,7 +1620,7 @@
       </ns0:c>
       <ns0:c r="F20" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 캐나다에서 보관·선반, 안전·보안 등 산업용 및 유지보수·수리·운영 제품을 유통한다.</ns0:t>
+          <ns0:t>미국·캐나다에서 보관·선반·안전·보안 등 산업용 및 유지보수·수리·운영 제품을 유통한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G20">
@@ -1662,7 +1662,7 @@
       </ns0:c>
       <ns0:c r="R20" t="inlineStr">
         <ns0:is>
-          <ns0:t>컨퍼런스 참석 이후 기업가치의 주가 반영 여부와 투자 회피 사유를 검토하는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>컨퍼런스 참석 후 주가의 가치 반영 수준을 점검하고 투자 회피 논거를 제시한 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S20" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </ns0:c>
       <ns0:c r="F21" t="inlineStr">
         <ns0:is>
-          <ns0:t>덴마크 바이오기업으로 암 등 질환 치료용 항체 의약품을 개발하며 EPKINLY·TEPKINLY를 판매한다.</ns0:t>
+          <ns0:t>암 등 질환 치료용 항체 의약품을 개발하고 EPKINLY·TEPKINLY를 판매하는 덴마크 바이오기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G21">
@@ -1788,7 +1788,7 @@
       </ns0:c>
       <ns0:c r="F22" t="inlineStr">
         <ns0:is>
-          <ns0:t>다중암 조기 발견 검사·서비스를 제공하며, 50세 초과 무증상자를 위한 갈레리 암 선별검사를 판매하는 기업.</ns0:t>
+          <ns0:t>다중암 조기 발견 검사·서비스를 제공하고 50세 초과 무증상자용 갈레리 암 선별검사를 판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G22">
@@ -1827,7 +1827,7 @@
       </ns0:c>
       <ns0:c r="R22" t="inlineStr">
         <ns0:is>
-          <ns0:t>주간 주가 55% 급등, 암 탐지 혈액검사에 대한 FDA 자문위원 지지, 고평가 여부가 보도됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>주간 주가 55% 급등, 암 발견 혈액검사에 대한 FDA 자문위원 지지와 고평가 여부를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S22" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </ns0:c>
       <ns0:c r="F23" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병·주식 교환·자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G23">
@@ -1945,7 +1945,7 @@
       </ns0:c>
       <ns0:c r="F24" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국과 해외에서 다양한 형태의 맞춤형 냉간 성형 강재를 제조·판매하는 회사.</ns0:t>
+          <ns0:t>중국과 해외에서 다양한 맞춤형 냉간 성형 강재를 제조·판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G24">
@@ -2024,7 +2024,7 @@
       </ns0:c>
       <ns0:c r="F25" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 임원 채용, 산업·건설·사무 인력 공급, 정규직 채용 등 인력 서비스를 제공한다.</ns0:t>
+          <ns0:t>미국에서 임원·정규직 채용과 산업·건설·사무 인력 공급 등 인력 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G25">
@@ -2066,7 +2066,7 @@
       </ns0:c>
       <ns0:c r="R25" t="inlineStr">
         <ns0:is>
-          <ns0:t>주가 6.9% 상승과 상승세 지속 가능성을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>주가 6.9% 상승과 추가 상승 가능성을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S25" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </ns0:c>
       <ns0:c r="F26" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다·중화권 등 전 세계에서 엔터테인먼트와 이벤트용 기술 플랫폼을 운영한다.</ns0:t>
+          <ns0:t>미국·캐나다·중화권 등 전 세계에서 엔터테인먼트·이벤트용 기술 플랫폼을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G26">
@@ -2150,7 +2150,7 @@
       </ns0:c>
       <ns0:c r="R26" t="inlineStr">
         <ns0:is>
-          <ns0:t>IMAX 주가 상승과 업종 대비 성과를 점검하고, 모건스탠리의 추가 상승 전망 및 ‘오디세이’의 영향을 조명. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>IMAX 주가 상승과 경기소비재 대비 성과를 점검하고, 모건스탠리의 추가 상승 전망 및 ‘오디세이’ 영향을 소개. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S26" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </ns0:c>
       <ns0:c r="R27" t="inlineStr">
         <ns0:is>
-          <ns0:t>실적 발표 이후 주가 2% 상승과 지속 가능성, 양호한 분기 실적 속 현금흐름 문제가 다뤄졌다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>실적 발표 이후 주가가 2% 오른 가운데, 견조한 분기 실적에 가려진 현금흐름 문제가 지적됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S27" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </ns0:c>
       <ns0:c r="F28" t="inlineStr">
         <ns0:is>
-          <ns0:t>자가 종양침윤림프구를 활용해 전이성 흑색종 등 고형암 치료용 세포치료제를 개발·상용화한다.</ns0:t>
+          <ns0:t>자가 종양침윤림프구 기반으로 전이성 흑색종 등 고형암용 세포치료제를 개발·상용화한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G28">
@@ -2318,7 +2318,7 @@
       </ns0:c>
       <ns0:c r="R28" t="inlineStr">
         <ns0:is>
-          <ns0:t>당일 주가 급등의 배경을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>당일 주가 급등 배경을 다룬 기사로, 제목에는 구체적 배경이 제시되지 않음. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S28" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </ns0:c>
       <ns0:c r="F29" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 온·오프라인 채널로 여성 의류·신발·보석·가방 등 액세서리를 판매한다.</ns0:t>
+          <ns0:t>미국 온·오프라인 채널에서 여성 의류·신발·보석·가방 등 액세서리를 판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G29">
@@ -2607,7 +2607,7 @@
       </ns0:c>
       <ns0:c r="F32" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병·주식 교환·자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G32">
@@ -2683,7 +2683,7 @@
       </ns0:c>
       <ns0:c r="F33" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다·영국에서 상장지수상품 운용 서비스를 제공하며 보안시스템·미용제품·금융 사업도 한다.</ns0:t>
+          <ns0:t>미국·캐나다·영국에서 상장지수상품을 운용하며 보안시스템·미용제품·금융 사업도 한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G33">
@@ -2762,7 +2762,7 @@
       </ns0:c>
       <ns0:c r="F34" t="inlineStr">
         <ns0:is>
-          <ns0:t>미주·유럽·아시아 등 전 세계에서 실험실 기기 등 정밀기기를 제조·공급하고 관련 서비스를 제공한다.</ns0:t>
+          <ns0:t>전 세계에서 실험실 기기 등 정밀기기를 제조·공급하고 관련 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G34">
@@ -2804,7 +2804,7 @@
       </ns0:c>
       <ns0:c r="R34" t="inlineStr">
         <ns0:is>
-          <ns0:t>메틀러톨레도가 새롭게 주목받는 배경을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>메틀러토레도가 새롭게 주목받는 배경을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S34" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </ns0:c>
       <ns0:c r="F36" t="inlineStr">
         <ns0:is>
-          <ns0:t>분자검사 서비스를 개발·상용화하며 잔존질환 평가·재발 감시·치료 반응 평가용 혈액검사를 제공한다.</ns0:t>
+          <ns0:t>분자검사를 개발·상용화하며 잔존질환·재발 감시·치료 반응 평가용 혈액검사를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G36">
@@ -2972,7 +2972,7 @@
       </ns0:c>
       <ns0:c r="R36" t="inlineStr">
         <ns0:is>
-          <ns0:t>시그나테라의 방광암 동반진단 일본 PMDA 승인과 주가 급등이 보도됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>시그나테라가 일본 PMDA의 방광암 동반진단 승인을 받았으며, 주가 급등을 다룬 기사도 나왔다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S36" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </ns0:c>
       <ns0:c r="F37" t="inlineStr">
         <ns0:is>
-          <ns0:t>북미와 독일에서 상업·산업·정부용 에너지 관리 시스템을 연구·설계·제조·판매·설치한다.</ns0:t>
+          <ns0:t>북미·독일에서 상업·산업·정부용 에너지 관리 시스템을 연구·설계·제조·판매·설치한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G37">
@@ -3056,7 +3056,7 @@
       </ns0:c>
       <ns0:c r="R37" t="inlineStr">
         <ns0:is>
-          <ns0:t>실적 전망 상향과 소매업체 대상 사업 기회의 확실성을 점검하는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>실적 전망 상향과 소매업체 관련 사업 기회의 확실성을 점검한 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S37" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </ns0:c>
       <ns0:c r="F38" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 유럽에서 금형 성형, CNC 가공, 3D 프린팅, 판금 등 맞춤형 부품 제조 서비스를 제공한다.</ns0:t>
+          <ns0:t>미국·유럽에서 금형 성형, CNC 가공, 3D 프린팅, 판금 등 맞춤형 부품 제조 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G38">
@@ -3140,7 +3140,7 @@
       </ns0:c>
       <ns0:c r="R38" t="inlineStr">
         <ns0:is>
-          <ns0:t>매도를 주장하는 근거와 향후 사업 전개에 숨은 위험을 짚는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>매도 근거를 제시하는 기사와 향후 사업 전개에 숨은 위험을 묻는 기사가 나왔다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S38" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </ns0:c>
       <ns0:c r="F39" t="inlineStr">
         <ns0:is>
-          <ns0:t>바이오 공정 기술과 시스템을 개발·상용화하며 중공사 소모품, 크로마토그래피 시스템 등을 제공한다.</ns0:t>
+          <ns0:t>바이오 공정 기술·시스템을 개발·상용화하며 중공사 소모품과 크로마토그래피 시스템 등을 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G39">
@@ -3224,7 +3224,7 @@
       </ns0:c>
       <ns0:c r="R39" t="inlineStr">
         <ns0:is>
-          <ns0:t>투자 회피 근거를 제시하는 의견과 최근 반등 후 적정 가치에 근접했다는 평가. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>투자 회피 근거를 제시하는 기사와 최근 반등 후 주가가 적정 가치에 근접했다는 평가가 나왔다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S39" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </ns0:c>
       <ns0:c r="F40" t="inlineStr">
         <ns0:is>
-          <ns0:t>암호화폐 채굴용 액체냉각 기술을 개발하며, 비트코인 채굴기 냉각 전환 캐비닛과 실외 인프라 제품을 제공.</ns0:t>
+          <ns0:t>암호화폐 채굴용 액체냉각 기술과 비트코인 채굴기 냉각 전환 캐비닛·실외 인프라 제품을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G40">
@@ -3345,7 +3345,7 @@
       </ns0:c>
       <ns0:c r="F41" t="inlineStr">
         <ns0:is>
-          <ns0:t>주로 오하이오의 개인·기업에 상업은행·신탁·자산관리·권원보험을 제공하는 State Bank and Trust의 지주사.</ns0:t>
+          <ns0:t>오하이오 개인·기업에 은행·신탁·자산관리·권원보험을 제공하는 State Bank and Trust의 지주사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G41">
@@ -3387,7 +3387,7 @@
       </ns0:c>
       <ns0:c r="R41" t="inlineStr">
         <ns0:is>
-          <ns0:t>투자 매력과 저평가 여부, 주가 신고점 이후 추가 상승 여력을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>투자 매력과 저평가 여부, 신고가 기록 이후 추가 상승 여력을 살펴보는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S41" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </ns0:c>
       <ns0:c r="F42" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 주요 안질환 치료를 위한 수술·비수술 기술을 개발하고 상용화하는 안과 의료기기 기업이다.</ns0:t>
+          <ns0:t>미국에서 주요 안질환 치료용 수술·비수술 기술을 개발·상용화하는 안과 의료기기 기업이다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G42">
@@ -3587,7 +3587,7 @@
       </ns0:c>
       <ns0:c r="F44" t="inlineStr">
         <ns0:is>
-          <ns0:t>치료제, 진단, 화학·소재, 식품·농업, 데이터 저장과 학술 연구에 쓰이는 합성 DNA 제품을 제조·판매한다.</ns0:t>
+          <ns0:t>치료제·진단·화학·소재·식품·농업·데이터 저장·학술 연구용 합성 DNA 제품을 제조·판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G44">
@@ -3629,7 +3629,7 @@
       </ns0:c>
       <ns0:c r="R44" t="inlineStr">
         <ns0:is>
-          <ns0:t>투자 판단 조건, 급등과 앤트로픽의 연관성에 대한 리링크의 해석, 릴리 TuneLab과의 AI 신약 개발 협력을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>매수 판단 조건, 주가 급등과 앤트로픽의 연관성에 대한 리링크의 해석, 릴리 TuneLab 협력을 다뤘다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S44" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </ns0:c>
       <ns0:c r="F45" t="inlineStr">
         <ns0:is>
-          <ns0:t>생물학적 시스템 분석용 장비, 소모품, 소프트웨어를 개발·판매하며 Chromium 플랫폼을 제공한다.</ns0:t>
+          <ns0:t>생물학적 시스템 분석용 장비·소모품·소프트웨어를 개발·판매하며 Chromium 플랫폼을 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G45">
@@ -3713,7 +3713,7 @@
       </ns0:c>
       <ns0:c r="R45" t="inlineStr">
         <ns0:is>
-          <ns0:t>의료·생명과학 종목들과 동반 하락한 흐름 및 동종 기업 대비 2분기 실적을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>의료 관련 종목들과 동반 하락한 소식과 생명과학 도구·서비스 기업 간 2분기 실적 비교를 다뤘다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S45" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </ns0:c>
       <ns0:c r="F47" t="inlineStr">
         <ns0:is>
-          <ns0:t>분석 업무 솔루션을 제공하며 액체 크로마토그래피와 질량분석 시스템을 설계·제조·판매·서비스한다.</ns0:t>
+          <ns0:t>분석 업무 솔루션을 제공하며 액체 크로마토그래피·질량분석 시스템을 설계·제조·판매·서비스한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G47">
@@ -3873,7 +3873,7 @@
       </ns0:c>
       <ns0:c r="R47" t="inlineStr">
         <ns0:is>
-          <ns0:t>가정용 HPV 검사·세포 분석 확대, AI 수요와 BD 통합을 배경으로 한 성장 전망 상회, 견조한 실적을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>가정용 HPV·세포 분석 사업, AI 수요·BD 통합 관련 성장 전망 상회, 견조한 실적을 다뤘다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S47" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </ns0:c>
       <ns0:c r="F48" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술 서비스 분야 기업과 합병, 주식 교환, 자산 인수, 자본 재편 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>기술 서비스 기업과 합병, 주식 교환, 자산 인수, 자본 재편 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G48">
@@ -3957,7 +3957,7 @@
       </ns0:c>
       <ns0:c r="R48" t="inlineStr">
         <ns0:is>
-          <ns0:t>에버노스의 XRP 재무자산 보유 종목 XRPN이 나스닥 진출까지 표결 하나를 남겨뒀다는 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>에버노스의 XRP 재무자산 보유 주식 XRPN이 나스닥 진출까지 표결 한 차례를 남겼다는 기사다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S48" t="inlineStr">

--- a/technicals/exports/new-highs-history.xlsx
+++ b/technicals/exports/new-highs-history.xlsx
@@ -221,7 +221,7 @@
       </ns0:c>
       <ns0:c r="F3" t="inlineStr">
         <ns0:is>
-          <ns0:t>미충족 의료 수요를 위한 항체 의약품을 개발하며, 비호르몬성 혈관운동 증상 치료제를 임상 2상 중인 기업.</ns0:t>
+          <ns0:t>미충족 의료 수요 대상 항체 의약품을 개발하며 비호르몬성 혈관운동 증상 치료제 임상 2상을 진행하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G3">
@@ -300,7 +300,7 @@
       </ns0:c>
       <ns0:c r="F4" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국 뷰티·개인관리 브랜드에 전략, 마케팅, 전 채널 판매, 고객 서비스 및 물류 등 브랜드 관리 제공.</ns0:t>
+          <ns0:t>중국 뷰티·개인관리 브랜드에 전략·마케팅·전 채널 판매·고객 서비스·물류 등 브랜드 관리 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G4">
@@ -376,7 +376,7 @@
       </ns0:c>
       <ns0:c r="F5" t="inlineStr">
         <ns0:is>
-          <ns0:t>학교·가정·사무실·산업 시장 등에 절단·측정·응급처치·연마 제품을 공급하는 기업.</ns0:t>
+          <ns0:t>학교·가정·사무실·산업 시장에 절단·측정·응급처치·연마 제품을 공급하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G5">
@@ -455,7 +455,7 @@
       </ns0:c>
       <ns0:c r="F6" t="inlineStr">
         <ns0:is>
-          <ns0:t>북미·아시아태평양 등에서 전문·기술 컨설팅과 운영 모델 설계 관련 자문을 제공.</ns0:t>
+          <ns0:t>북미·아시아태평양 등에서 전문·기술 컨설팅과 운영 모델 설계 자문 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G6">
@@ -929,7 +929,7 @@
       </ns0:c>
       <ns0:c r="F12" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업·공공부문 등에 컴퓨터 시스템과 데이터센터를 포함한 다양한 IT 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>기업·공공부문에 컴퓨터 시스템·데이터센터 등 다양한 IT 솔루션을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G12">
@@ -1245,7 +1245,7 @@
       </ns0:c>
       <ns0:c r="F16" t="inlineStr">
         <ns0:is>
-          <ns0:t>다중암 조기 발견 검사·서비스를 제공하며, 50세 초과 무증상자 대상 암 선별검사 Galleri를 공급하는 기업.</ns0:t>
+          <ns0:t>다중암 조기 발견 검사·서비스와 50세 초과 무증상자 대상 암 선별검사 Galleri를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G16">
@@ -1400,7 +1400,7 @@
       </ns0:c>
       <ns0:c r="F18" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국과 해외에서 다양한 형태의 맞춤형 냉간 성형 강재를 제조·판매하는 회사.</ns0:t>
+          <ns0:t>중국과 해외에서 다양한 맞춤형 냉간 성형 강재를 제조·판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G18">
@@ -1479,7 +1479,7 @@
       </ns0:c>
       <ns0:c r="F19" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술로 의료 제공을 확장·자동화하며 급성 부상·만성 통증·수술 후 재활 등 근골격계 관리 플랫폼을 개발하는 기업.</ns0:t>
+          <ns0:t>급성 부상·만성 통증·수술 후 재활 등 근골격계 관리를 위한 의료 자동화 플랫폼 개발 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G19">
@@ -1558,7 +1558,7 @@
       </ns0:c>
       <ns0:c r="F20" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·영국 등에서 통신·결제 서비스를 제공하며 소매 솔루션·핀테크·Net2phone 사업 등을 운영하는 기업.</ns0:t>
+          <ns0:t>미국·영국 등에서 통신·결제 서비스를 제공하고 소매 솔루션·핀테크·Net2phone 사업 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G20">
@@ -1637,7 +1637,7 @@
       </ns0:c>
       <ns0:c r="F21" t="inlineStr">
         <ns0:is>
-          <ns0:t>유전·유전체 분석용 염기서열 분석 및 어레이 기반 장비와 소모품을 제공한다.</ns0:t>
+          <ns0:t>유전·유전체 분석용 염기서열 분석 및 어레이 기반 장비와 소모품 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G21">
@@ -1716,7 +1716,7 @@
       </ns0:c>
       <ns0:c r="F22" t="inlineStr">
         <ns0:is>
-          <ns0:t>전이성 흑색종과 기타 고형암 치료를 위한 자가 종양침윤림프구 기반 세포치료제를 개발·상용화한다.</ns0:t>
+          <ns0:t>전이성 흑색종·기타 고형암 치료용 자가 종양침윤림프구 기반 세포치료제 개발·상용화.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G22">
@@ -1795,7 +1795,7 @@
       </ns0:c>
       <ns0:c r="F23" t="inlineStr">
         <ns0:is>
-          <ns0:t>켄터키주에서 예금 등 다양한 은행 상품과 서비스를 제공하는 금융기관의 지주회사다.</ns0:t>
+          <ns0:t>켄터키주에서 예금 등 은행 상품과 서비스를 제공하는 금융기관의 지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G23">
@@ -1871,7 +1871,7 @@
       </ns0:c>
       <ns0:c r="F24" t="inlineStr">
         <ns0:is>
-          <ns0:t>보건·안전 분야에 사용하는 휴대용 질량분석기와 푸리에 변환 적외선 장비를 제공한다.</ns0:t>
+          <ns0:t>보건·안전 분야용 휴대용 질량분석기와 푸리에 변환 적외선 장비 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G24">
@@ -1950,7 +1950,7 @@
       </ns0:c>
       <ns0:c r="F25" t="inlineStr">
         <ns0:is>
-          <ns0:t>매립지 등 비화석연료원에서 바이오가스를 회수·처리하며 재생 천연가스와 재생 전력 사업을 한다.</ns0:t>
+          <ns0:t>매립지 등 비화석연료원의 바이오가스를 회수·처리하고 재생 천연가스·전력 사업 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G25">
@@ -2108,7 +2108,7 @@
       </ns0:c>
       <ns0:c r="F27" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 실험실용 기기 등 정밀기기를 제조·공급하고 관련 서비스를 제공한다.</ns0:t>
+          <ns0:t>전 세계에 실험실용 기기 등 정밀기기를 제조·공급하고 관련 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G27">
@@ -2187,7 +2187,7 @@
       </ns0:c>
       <ns0:c r="F28" t="inlineStr">
         <ns0:is>
-          <ns0:t>적층 제조 및 의료용 소프트웨어 도구와 3D 프린팅 서비스를 제공한다.</ns0:t>
+          <ns0:t>적층 제조·의료용 소프트웨어 도구와 3D 프린팅 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G28">
@@ -2266,7 +2266,7 @@
       </ns0:c>
       <ns0:c r="F29" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병·주식 교환·자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G29">
@@ -2342,7 +2342,7 @@
       </ns0:c>
       <ns0:c r="F30" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업의 데이터 인프라 전환을 위한 소프트웨어, 시스템 및 서비스를 제공한다.</ns0:t>
+          <ns0:t>기업의 데이터 인프라 전환을 위한 소프트웨어·시스템·서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G30">
@@ -2421,7 +2421,7 @@
       </ns0:c>
       <ns0:c r="F31" t="inlineStr">
         <ns0:is>
-          <ns0:t>분자검사 서비스를 개발·상용화하며 미세잔존질환 평가, 재발 감시, 치료 반응 평가용 혈액검사를 제공한다.</ns0:t>
+          <ns0:t>분자검사를 개발·상용화하고 미세잔존질환·재발·치료 반응 평가용 혈액검사 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G31">
@@ -2500,7 +2500,7 @@
       </ns0:c>
       <ns0:c r="F32" t="inlineStr">
         <ns0:is>
-          <ns0:t>데이터 저장·관리 기술과 제품, 서비스를 제공하며 데이터 축소·보호·암호화 소프트웨어를 공급한다.</ns0:t>
+          <ns0:t>데이터 저장·관리 기술과 제품·서비스, 데이터 축소·보호·암호화 소프트웨어 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G32">
@@ -2579,7 +2579,7 @@
       </ns0:c>
       <ns0:c r="F33" t="inlineStr">
         <ns0:is>
-          <ns0:t>맞춤형 부품의 디지털 제조업체로 성형, CNC 가공, 3D 프린팅, 판금 제조 서비스를 제공한다.</ns0:t>
+          <ns0:t>맞춤형 부품의 디지털 제조업체로 성형·CNC 가공·3D 프린팅·판금 제조 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G33">
@@ -2658,7 +2658,7 @@
       </ns0:c>
       <ns0:c r="F34" t="inlineStr">
         <ns0:is>
-          <ns0:t>비정형 데이터 관리 솔루션과 영상 편집·후반 제작 등에 쓰이는 저장 소프트웨어 및 시스템을 제공한다.</ns0:t>
+          <ns0:t>비정형 데이터 관리 솔루션과 영상 편집·후반 제작용 저장 소프트웨어·시스템 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G34">
@@ -2737,7 +2737,7 @@
       </ns0:c>
       <ns0:c r="F35" t="inlineStr">
         <ns0:is>
-          <ns0:t>건강과학 분야의 장비·시약·소프트웨어와 검출·영상 기술, 질환 조기 탐지 솔루션을 제공한다.</ns0:t>
+          <ns0:t>건강과학 분야 장비·시약·소프트웨어와 검출·영상 기술, 질환 조기 탐지 솔루션 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G35">
@@ -2816,7 +2816,7 @@
       </ns0:c>
       <ns0:c r="F36" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 주요 안질환 치료를 위한 수술·비수술 기술을 개발하고 상용화하는 안과 의료기기 기업이다.</ns0:t>
+          <ns0:t>미국에서 주요 안질환 치료용 수술·비수술 기술을 개발·상용화하는 안과 의료기기 기업이다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G36">
@@ -2895,7 +2895,7 @@
       </ns0:c>
       <ns0:c r="F37" t="inlineStr">
         <ns0:is>
-          <ns0:t>서버 네트워크 인터페이스 카드와 암호화·압축용 카드 등 네트워크·데이터 인프라 솔루션을 설계·제조·판매.</ns0:t>
+          <ns0:t>서버 네트워크 인터페이스 카드와 암호화·압축용 카드 등 네트워크·데이터 인프라 솔루션을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G37">
@@ -3053,7 +3053,7 @@
       </ns0:c>
       <ns0:c r="F39" t="inlineStr">
         <ns0:is>
-          <ns0:t>자회사 Ctrl Media를 통해 홍콩에서 모바일 게임 앱 개발사 등에 통합 마케팅·광고 서비스를 제공.</ns0:t>
+          <ns0:t>자회사 Ctrl Media를 통해 홍콩에서 모바일 게임 앱 개발사 등에 통합 마케팅·광고를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G39">
@@ -3132,7 +3132,7 @@
       </ns0:c>
       <ns0:c r="F40" t="inlineStr">
         <ns0:is>
-          <ns0:t>선박 및 대형 비도로용 동력전달 장비를 설계·제조·판매하며 제조와 유통 부문을 운영한다.</ns0:t>
+          <ns0:t>선박·대형 비도로용 동력전달 장비를 설계·제조·판매하고 제조·유통 부문 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G40">
@@ -3211,7 +3211,7 @@
       </ns0:c>
       <ns0:c r="F41" t="inlineStr">
         <ns0:is>
-          <ns0:t>치료제·진단·소재·농업·데이터 저장·학술 연구 등에 쓰이는 합성 DNA 제품을 제조·판매한다.</ns0:t>
+          <ns0:t>치료제·진단·소재·농업·데이터 저장·학술 연구용 합성 DNA 제품 제조·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G41">
@@ -3527,7 +3527,7 @@
       </ns0:c>
       <ns0:c r="F45" t="inlineStr">
         <ns0:is>
-          <ns0:t>유의미한 영업활동 없이 기업 합병·주식 교환·자산 인수 등 사업결합을 추진한다.</ns0:t>
+          <ns0:t>유의미한 영업활동 없이 합병·주식 교환·자산 인수 등 사업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G45">
@@ -3682,7 +3682,7 @@
       </ns0:c>
       <ns0:c r="F47" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술 서비스 분야 기업과의 합병·주식 교환·자산 인수 등 사업결합을 추진한다.</ns0:t>
+          <ns0:t>기술 서비스 기업과의 합병·주식 교환·자산 인수 등 사업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G47">

--- a/technicals/exports/new-highs-history.xlsx
+++ b/technicals/exports/new-highs-history.xlsx
@@ -135,11 +135,6 @@
           <ns0:t/>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>엣지부터 클라우드까지 IT 및 기업용 제품·솔루션·서비스를 제공하는 글로벌 기업.</ns0:t>
-        </ns0:is>
-      </ns0:c>
       <ns0:c r="G2">
         <ns0:v>63.88999938964844</ns0:v>
       </ns0:c>
@@ -187,11 +182,6 @@
           <ns0:t>https://finance.yahoo.com/technology/ai/articles/hpe-shares-jump-1-2-180808900.html</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="T2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>https://finviz.com/quote.ashx?t=HPE</ns0:t>
-        </ns0:is>
-      </ns0:c>
     </ns0:row>
     <ns0:row r="3">
       <ns0:c r="A3" t="inlineStr">
@@ -221,7 +211,7 @@
       </ns0:c>
       <ns0:c r="F3" t="inlineStr">
         <ns0:is>
-          <ns0:t>미충족 의료 수요를 위한 항체 의약품을 개발하며, 비호르몬성 ABCL635는 혈관운동 증상 대상 임상 2상 중.</ns0:t>
+          <ns0:t>미충족 의료 수요를 위한 항체 치료제 개발사. 비호르몬성 ABCL635는 혈관운동 증상 임상 2상 중.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G3">
@@ -263,7 +253,7 @@
       </ns0:c>
       <ns0:c r="R3" t="inlineStr">
         <ns0:is>
-          <ns0:t>ABCL을 포함한 종목들의 주가 급등과 52주 최고치 기록을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>ABCL 등 종목의 52주 신고가 기록과 급등 배경을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S3" t="inlineStr">
@@ -305,7 +295,7 @@
       </ns0:c>
       <ns0:c r="F4" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국 뷰티·개인관리 브랜드에 전략, 마케팅, 전 채널 판매, 고객 서비스 및 물류 등 브랜드 관리 제공.</ns0:t>
+          <ns0:t>중국 뷰티·개인관리 브랜드에 전략·마케팅·전 채널 판매·고객 서비스·물류 등 브랜드 관리 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G4">
@@ -423,7 +413,7 @@
       </ns0:c>
       <ns0:c r="R5" t="inlineStr">
         <ns0:is>
-          <ns0:t>임상시험 업데이트와 신규 자금 조달 이후 아제너스 주식의 적정가치 평가가 높아졌다는 보도다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>임상 진행 소식과 신규 자금 조달 이후 아제너스 주식의 적정가치 평가 상향 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S5" t="inlineStr">
@@ -507,7 +497,7 @@
       </ns0:c>
       <ns0:c r="R6" t="inlineStr">
         <ns0:is>
-          <ns0:t>올해 앳코어 주가가 산업재 동종 기업보다 높은 성과를 내는지 비교. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>올해 주가 성과가 산업재 동종 기업을 앞서는지 비교하는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S6" t="inlineStr">
@@ -591,7 +581,7 @@
       </ns0:c>
       <ns0:c r="R7" t="inlineStr">
         <ns0:is>
-          <ns0:t>AI 관련 반도체 수요를 전망하며 4분기 매출 반등을 목표로 한다는 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>AI 관련 반도체 수요 확대를 전망하며 4분기 매출 반등을 목표로 한다는 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S7" t="inlineStr">
@@ -633,7 +623,7 @@
       </ns0:c>
       <ns0:c r="F8" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 기업·비영리단체·기업가에게 은행 상품과 서비스를 제공하는 Capital Bank의 지주회사.</ns0:t>
+          <ns0:t>미국 기업·비영리단체·기업가에게 은행 서비스를 제공하는 Capital Bank의 지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G8">
@@ -675,7 +665,7 @@
       </ns0:c>
       <ns0:c r="R8" t="inlineStr">
         <ns0:is>
-          <ns0:t>매수 등급 상향 소식과 함께 가치투자 관점의 매수 적절성 및 저평가 여부를 다룬 분석. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>투자의견 매수 상향과 함께 가치투자 관점의 매수 적합성 및 저평가 여부를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S8" t="inlineStr">
@@ -717,7 +707,7 @@
       </ns0:c>
       <ns0:c r="F9" t="inlineStr">
         <ns0:is>
-          <ns0:t>이식 환자의 치료 결과와 장기 건강 개선을 위한 신장·심장 이식 검사 솔루션 등을 제공하는 기업.</ns0:t>
+          <ns0:t>이식 환자의 치료 결과와 장기 건강 개선을 위한 신장·심장 이식 검사 솔루션 제공 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G9">
@@ -801,7 +791,7 @@
       </ns0:c>
       <ns0:c r="F10" t="inlineStr">
         <ns0:is>
-          <ns0:t>Citizens and Farmers Bank의 은행지주사로 개인·기업 금융, 주택담보대출 및 소비자금융 제공.</ns0:t>
+          <ns0:t>Citizens and Farmers Bank의 지주사로 개인·기업 금융, 주택담보대출·소비자금융 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G10">
@@ -927,7 +917,7 @@
       </ns0:c>
       <ns0:c r="R11" t="inlineStr">
         <ns0:is>
-          <ns0:t>주가 2% 상승 보도와 변동성 대비 보상 분석, 팔로알토 네트웍스와의 투자 비교. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>주가 2% 상승 보도와 변동성 대비 수익 평가, 팔로알토네트웍스와의 투자 비교 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S11" t="inlineStr">
@@ -969,7 +959,7 @@
       </ns0:c>
       <ns0:c r="F12" t="inlineStr">
         <ns0:is>
-          <ns0:t>한국·미국 등에서 캐주얼 게임과 모바일 앱을 개발·배급하며 소셜 카지노와 iGaming 사업 운영.</ns0:t>
+          <ns0:t>한국·미국 등에서 캐주얼 게임·모바일 앱을 개발·배급하며 소셜 카지노와 iGaming 사업 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G12">
@@ -1011,7 +1001,7 @@
       </ns0:c>
       <ns0:c r="R12" t="inlineStr">
         <ns0:is>
-          <ns0:t>인수 제안이 미해결 상태인 가운데 이익이 급증했다는 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>이익 급증과 아직 결론 나지 않은 인수 제안을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S12" t="inlineStr">
@@ -1053,7 +1043,7 @@
       </ns0:c>
       <ns0:c r="F13" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 난치성 암 치료제를 발굴·개발·상용화하며 진행성 신세포암 치료제 CABOMETYX를 제공.</ns0:t>
+          <ns0:t>미국에서 난치성 암 치료제를 발굴·개발·상용화하며 진행성 신세포암 치료제 CABOMETYX 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G13">
@@ -1095,7 +1085,7 @@
       </ns0:c>
       <ns0:c r="R13" t="inlineStr">
         <ns0:is>
-          <ns0:t>잔잘린티닙의 FDA 지연이 성장 계획에 영향을 미칠 가능성을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>잔잘린티닙의 FDA 절차 지연이 성장 계획에 미칠 영향을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S13" t="inlineStr">
@@ -1216,7 +1206,7 @@
       </ns0:c>
       <ns0:c r="F15" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 다른 기업과의 합병·인수 등 사업결합을 추진하는 기업.</ns0:t>
+          <ns0:t>주요 영업활동 없이 다른 기업과 합병·인수 등 사업결합을 추진하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G15">
@@ -1334,7 +1324,7 @@
       </ns0:c>
       <ns0:c r="R16" t="inlineStr">
         <ns0:is>
-          <ns0:t>올해 포슬 그룹과 소매·도매 업종 주식의 성과를 비교한 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>올해 포실그룹과 소매·도매 업종의 주가 성과를 비교하는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S16" t="inlineStr">
@@ -1376,7 +1366,7 @@
       </ns0:c>
       <ns0:c r="F17" t="inlineStr">
         <ns0:is>
-          <ns0:t>덴마크 바이오기업으로 암 등 질환 치료용 항체 의약품을 개발하며 EPKINLY·TEPKINLY를 판매한다.</ns0:t>
+          <ns0:t>암 등 질환 치료용 항체 의약품을 개발하고 EPKINLY·TEPKINLY를 판매하는 덴마크 바이오기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G17">
@@ -1460,7 +1450,7 @@
       </ns0:c>
       <ns0:c r="F18" t="inlineStr">
         <ns0:is>
-          <ns0:t>다중암 조기검사 기업으로, 50세 초과 무증상자를 위한 암 선별검사 Galleri 등을 제공.</ns0:t>
+          <ns0:t>다중암 조기검사 기업으로 50세 초과 무증상자 대상 암 선별검사 Galleri 등을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G18">
@@ -1499,7 +1489,7 @@
       </ns0:c>
       <ns0:c r="R18" t="inlineStr">
         <ns0:is>
-          <ns0:t>6개월간 180%, 주간 약 70% 및 55%의 주가 상승을 각각 다룬 기사들이 추가 상승 여력과 관전 요소 조명. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>6개월간 180%, 주간 약 70% 및 55% 주가 급등을 각각 다루며 추가 상승 가능성과 향후 관전 포인트 제시. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S18" t="inlineStr">
@@ -1583,7 +1573,7 @@
       </ns0:c>
       <ns0:c r="R19" t="inlineStr">
         <ns0:is>
-          <ns0:t>Torm 지분을 19.85%로 확대한 뒤 주가가 하락했다는 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>Torm 지분을 19.85%로 확대한 이후 주가 하락 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S19" t="inlineStr">
@@ -1625,7 +1615,7 @@
       </ns0:c>
       <ns0:c r="F20" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 소형 가전 및 특수 가정용 기기를 설계·판매·유통한다.</ns0:t>
+          <ns0:t>미국과 해외에서 소형 가전 및 특수 가정용 기기를 설계·판매·유통.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G20">
@@ -1667,7 +1657,7 @@
       </ns0:c>
       <ns0:c r="R20" t="inlineStr">
         <ns0:is>
-          <ns0:t>동종업체 대비 주가 성과와 저평가 소비재 종목으로서의 투자 매력을 검토한 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>동종 기업 대비 주가 성과 우위와 저렴한 소비재 종목으로서의 매수 적합성을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S20" t="inlineStr">
@@ -1709,7 +1699,7 @@
       </ns0:c>
       <ns0:c r="F21" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국과 해외에서 다양한 형태의 맞춤형 냉간 성형 강재를 제조·판매하는 회사.</ns0:t>
+          <ns0:t>중국과 해외에서 다양한 맞춤형 냉간 성형 강재를 제조·판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G21">
@@ -1788,7 +1778,7 @@
       </ns0:c>
       <ns0:c r="F22" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술로 의료 제공을 자동화하며 급성 부상·만성 통증·수술 후 재활 등 근골격계 관리 플랫폼을 개발한다.</ns0:t>
+          <ns0:t>기술로 의료 제공을 자동화하며 급성 부상·만성 통증·수술 후 재활 등 근골격계 관리 플랫폼 개발.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G22">
@@ -1872,7 +1862,7 @@
       </ns0:c>
       <ns0:c r="F23" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·영국 등에서 통신·결제 서비스를 제공하며 소매 솔루션, 핀테크, 인터넷 전화 사업을 운영한다.</ns0:t>
+          <ns0:t>미국·영국 등에서 통신·결제 서비스를 제공하며 소매 솔루션·핀테크·인터넷 전화 사업 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G23">
@@ -1914,7 +1904,7 @@
       </ns0:c>
       <ns0:c r="R23" t="inlineStr">
         <ns0:is>
-          <ns0:t>주가 급등을 다룬 기사와 2026년 4분기 실적 발표 콘퍼런스콜 요약·전문. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>주가 급등 배경을 다룬 기사와 2026년 4분기 실적 발표 콘퍼런스콜 요약·전문. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S23" t="inlineStr">
@@ -1956,7 +1946,7 @@
       </ns0:c>
       <ns0:c r="F24" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 유전·유전체 분석용 시퀀싱 및 어레이 기반 장비와 시약 등 소모품을 제공한다.</ns0:t>
+          <ns0:t>전 세계에 유전·유전체 분석용 시퀀싱·어레이 장비와 시약 등 소모품을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G24">
@@ -1998,7 +1988,7 @@
       </ns0:c>
       <ns0:c r="R24" t="inlineStr">
         <ns0:is>
-          <ns0:t>매도 논거와 대체 종목, REGN 대비 가치평가, 옵션시장의 주가 급등 예측 가능성을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>매도 논거와 REGN 대비 가치평가 비교, 옵션시장의 주가 급등 예측 가능성을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S24" t="inlineStr">
@@ -2040,7 +2030,7 @@
       </ns0:c>
       <ns0:c r="F25" t="inlineStr">
         <ns0:is>
-          <ns0:t>원유와 석유제품의 국제 운송을 위한 원양 선박을 보유·운영하는 기업.</ns0:t>
+          <ns0:t>원유·석유제품의 국제 운송용 원양 선박을 보유·운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G25">
@@ -2082,7 +2072,7 @@
       </ns0:c>
       <ns0:c r="R25" t="inlineStr">
         <ns0:is>
-          <ns0:t>운송 차질에 따른 기록적 유조선 이익이 낙관론에 미칠 영향과 배당을 분석한 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>운송 차질 속 기록적 탱커 이익이 낙관론에 미칠 영향과 배당 분석을 다룸. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S25" t="inlineStr">
@@ -2124,7 +2114,7 @@
       </ns0:c>
       <ns0:c r="F26" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병·주식 교환·자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G26">
@@ -2200,7 +2190,7 @@
       </ns0:c>
       <ns0:c r="F27" t="inlineStr">
         <ns0:is>
-          <ns0:t>망막 질환 치료제를 연구·개발·상용화하는 임상 단계 바이오제약사로 주요 후보는 타르코시맙 테드로머.</ns0:t>
+          <ns0:t>망막 질환 치료제를 개발·상용화하는 임상 단계 바이오제약사. 주요 후보는 타르코시맙 테드로머.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G27">
@@ -2242,7 +2232,7 @@
       </ns0:c>
       <ns0:c r="R27" t="inlineStr">
         <ns0:is>
-          <ns0:t>긍정적인 습성 황반변성 데이터와 BLA 제출 임박 소식, 주가 178% 상승 및 52주 신고가 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>긍정적 습성 황반변성 데이터와 생물학적제제 허가신청 임박, 주가 급등 및 52주 신고가를 다룸. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S27" t="inlineStr">
@@ -2284,7 +2274,7 @@
       </ns0:c>
       <ns0:c r="F28" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병·주식 교환·자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G28">
@@ -2360,7 +2350,7 @@
       </ns0:c>
       <ns0:c r="F29" t="inlineStr">
         <ns0:is>
-          <ns0:t>보건·안전 분야에 사용하는 휴대용 질량분석기와 푸리에 변환 적외선 장비를 제공한다.</ns0:t>
+          <ns0:t>보건·안전 분야용 휴대용 질량분석기와 푸리에 변환 적외선 장비 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G29">
@@ -2439,7 +2429,7 @@
       </ns0:c>
       <ns0:c r="F30" t="inlineStr">
         <ns0:is>
-          <ns0:t>미주·유럽·아시아 등 전 세계에서 실험실 기기 등 정밀기기를 제조·공급하고 관련 서비스를 제공한다.</ns0:t>
+          <ns0:t>전 세계에서 실험실 기기 등 정밀기기를 제조·공급하고 관련 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G30">
@@ -2481,7 +2471,7 @@
       </ns0:c>
       <ns0:c r="R30" t="inlineStr">
         <ns0:is>
-          <ns0:t>메틀러톨레도가 새롭게 주목받는 배경을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>메틀러토레도가 새롭게 주목받는 배경을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S30" t="inlineStr">
@@ -2523,7 +2513,7 @@
       </ns0:c>
       <ns0:c r="F31" t="inlineStr">
         <ns0:is>
-          <ns0:t>일리노이주에서 당좌·저축·정기예금 등 은행 서비스를 제공하는 North Shore Trust and Savings의 지주회사.</ns0:t>
+          <ns0:t>일리노이주에서 당좌·저축·정기예금을 제공하는 North Shore Trust and Savings의 지주사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G31">
@@ -2602,7 +2592,7 @@
       </ns0:c>
       <ns0:c r="F32" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계 기업의 데이터 인프라 전환을 위한 소프트웨어·시스템·서비스를 제공한다.</ns0:t>
+          <ns0:t>기업의 데이터 인프라 전환을 위한 소프트웨어·시스템·서비스를 전 세계에 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G32">
@@ -2644,7 +2634,7 @@
       </ns0:c>
       <ns0:c r="R32" t="inlineStr">
         <ns0:is>
-          <ns0:t>유럽 규제 데이터 시장 공략과 AI 제휴 확대를 다뤘으며, BofA는 AI 성장 기회를 평가해 목표가를 상향. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>유럽 규제 데이터 시장 공략, AI 성장 기회에 대한 BofA 목표가 상향, 제휴를 통한 AI 전략 확대. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S32" t="inlineStr">
@@ -2686,7 +2676,7 @@
       </ns0:c>
       <ns0:c r="F33" t="inlineStr">
         <ns0:is>
-          <ns0:t>분자검사 서비스를 개발·상용화하며 잔존질환 평가·재발 감시·치료 반응 평가용 혈액검사를 제공한다.</ns0:t>
+          <ns0:t>분자검사를 개발·상용화하며 잔존질환·재발 감시·치료 반응 평가용 혈액검사를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G33">
@@ -2728,7 +2718,7 @@
       </ns0:c>
       <ns0:c r="R33" t="inlineStr">
         <ns0:is>
-          <ns0:t>시그나테라의 방광암 동반진단 일본 PMDA 승인과 주가 급등이 보도됐다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>시그나테라가 일본 PMDA의 방광암 동반진단 승인을 받았으며, 주가 급등을 다룬 기사도 나왔다. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S33" t="inlineStr">
@@ -2770,7 +2760,7 @@
       </ns0:c>
       <ns0:c r="F34" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 소비재·기술 분야 기업과의 합병·인수 등 사업결합을 추진하는 기업.</ns0:t>
+          <ns0:t>주요 영업활동 없이 소비재·기술 기업과의 합병·인수 등 사업결합을 추진.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G34">
@@ -2846,7 +2836,7 @@
       </ns0:c>
       <ns0:c r="F35" t="inlineStr">
         <ns0:is>
-          <ns0:t>북미와 독일에서 상업·산업·정부용 에너지 관리 시스템을 연구·설계·제조·판매·설치한다.</ns0:t>
+          <ns0:t>북미·독일에서 상업·산업·정부용 에너지 관리 시스템을 연구·설계·제조·판매·설치한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G35">
@@ -2888,7 +2878,7 @@
       </ns0:c>
       <ns0:c r="R35" t="inlineStr">
         <ns0:is>
-          <ns0:t>실적 전망 상향과 소매업체 대상 사업 기회의 확실성을 점검하는 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>실적 전망 상향과 소매업체 관련 사업 기회의 확실성을 점검한 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S35" t="inlineStr">
@@ -2930,7 +2920,7 @@
       </ns0:c>
       <ns0:c r="F36" t="inlineStr">
         <ns0:is>
-          <ns0:t>데이터 저장·관리 기술과 제품을 제공하며 Purity 소프트웨어로 데이터 축소·보호·암호화를 지원한다.</ns0:t>
+          <ns0:t>데이터 저장·관리 제품을 제공하며 Purity 소프트웨어로 데이터 축소·보호·암호화를 지원.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G36">
@@ -2972,7 +2962,7 @@
       </ns0:c>
       <ns0:c r="R36" t="inlineStr">
         <ns0:is>
-          <ns0:t>4배 상승 후 저평가 가능성, AI 플랫폼 개선, 애널리스트 목표가 상향과 잉여현금흐름 적자 전환을 다룸. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>주가 4배 상승 후 저평가 가능성, AI 플랫폼 개선, 분석가 목표가 상향과 잉여현금흐름 적자를 다룸. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S36" t="inlineStr">
@@ -3014,7 +3004,7 @@
       </ns0:c>
       <ns0:c r="F37" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 사이버보안 솔루션을 제공하며 보안 접속과 네트워크 보안 관리 제품을 운영하는 기업.</ns0:t>
+          <ns0:t>전 세계에 사이버보안 솔루션과 보안 접속·네트워크 보안 관리 제품을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G37">
@@ -3056,7 +3046,7 @@
       </ns0:c>
       <ns0:c r="R37" t="inlineStr">
         <ns0:is>
-          <ns0:t>AI 방어의 상시 서비스화와 주가 상승 보도, 크라우드스트라이크와의 투자 비교 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>AI 방어의 상시 서비스화와 주가 상승 동향, 크라우드스트라이크와의 투자 비교를 다룸. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S37" t="inlineStr">
@@ -3098,7 +3088,7 @@
       </ns0:c>
       <ns0:c r="F38" t="inlineStr">
         <ns0:is>
-          <ns0:t>암 치료 제품을 개발·상용화하는 바이오제약사로, 경구용 네라티닙 제품 NERLYNX를 제공.</ns0:t>
+          <ns0:t>암 치료제를 개발·상용화하며 경구용 네라티닙 제품 NERLYNX를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G38">
@@ -3182,7 +3172,7 @@
       </ns0:c>
       <ns0:c r="F39" t="inlineStr">
         <ns0:is>
-          <ns0:t>정밀 기술을 활용해 면역항암·자가면역·감염 질환 대상 유전자·세포 치료제를 개발.</ns0:t>
+          <ns0:t>정밀 기술을 활용해 면역항암·자가면역·감염 질환용 유전자·세포 치료제를 개발.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G39">
@@ -3224,7 +3214,7 @@
       </ns0:c>
       <ns0:c r="R39" t="inlineStr">
         <ns0:is>
-          <ns0:t>FDA의 플랫폼 인정과 신약 개발비 절감 가능성, 기업가치 평가 및 수년 내 주가 최고치 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>FDA의 플랫폼 인정과 신약 개발비 절감 가능성, 저평가 여부 및 다년 신고가 동향을 다룸. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S39" t="inlineStr">
@@ -3266,7 +3256,7 @@
       </ns0:c>
       <ns0:c r="F40" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업·클라우드·SaaS 데이터 보호, 위협 분석 및 신원 복구 등 데이터 보안 솔루션 제공.</ns0:t>
+          <ns0:t>기업·클라우드·SaaS 데이터 보호, 위협 분석, 신원 복구 등 데이터 보안 솔루션을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G40">
@@ -3350,7 +3340,7 @@
       </ns0:c>
       <ns0:c r="F41" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 독자 기술과 분석 역량으로 신원 정보 및 조사 솔루션 idiCORE를 제공.</ns0:t>
+          <ns0:t>미국에서 독자 기술과 분석 역량을 활용한 신원 정보·조사 솔루션 idiCORE를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G41">
@@ -3392,7 +3382,7 @@
       </ns0:c>
       <ns0:c r="R41" t="inlineStr">
         <ns0:is>
-          <ns0:t>높은 주가수익비율과 주가 모멘텀 속에서도 6% 저평가 가능성 제기. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>높은 주가수익비율과 주가 모멘텀 속에서도 6% 저평가됐을 가능성을 제시. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S41" t="inlineStr">
@@ -3434,7 +3424,7 @@
       </ns0:c>
       <ns0:c r="F42" t="inlineStr">
         <ns0:is>
-          <ns0:t>보건과학 분야의 장비·시약·소프트웨어·검사 플랫폼과 탐지·영상 기술 및 서비스를 제공한다.</ns0:t>
+          <ns0:t>보건과학용 장비·시약·소프트웨어·검사 플랫폼과 탐지·영상 기술 및 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G42">
@@ -3476,7 +3466,7 @@
       </ns0:c>
       <ns0:c r="R42" t="inlineStr">
         <ns0:is>
-          <ns0:t>2분기 실적 후 투자 판단과 보유 논거, 유럽 신생아 1형 당뇨병 탐지 키트 출시를 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>2분기 실적 후 투자 판단과 보유 논거, 유럽 내 신생아 제1형 당뇨병 탐지 키트 출시를 다룸. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S42" t="inlineStr">
@@ -3518,7 +3508,7 @@
       </ns0:c>
       <ns0:c r="F43" t="inlineStr">
         <ns0:is>
-          <ns0:t>신약 개발과 소재 응용을 위한 신규 분자 발굴용 물리학 기반 계산 플랫폼을 개발.</ns0:t>
+          <ns0:t>신약 개발·소재 응용을 위한 신규 분자 발굴용 물리학 기반 계산 플랫폼을 개발.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G43">
@@ -3602,7 +3592,7 @@
       </ns0:c>
       <ns0:c r="F44" t="inlineStr">
         <ns0:is>
-          <ns0:t>서버 네트워크 인터페이스 카드와 암호화·압축용 카드 등 네트워크·데이터 인프라 솔루션을 설계·제조·판매.</ns0:t>
+          <ns0:t>서버 네트워크 인터페이스 카드와 암호화·압축용 카드 등 네트워크·데이터 인프라 솔루션을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G44">
@@ -3839,7 +3829,7 @@
       </ns0:c>
       <ns0:c r="F47" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 생명과학 솔루션, 분석기기, 전문 진단, 실험실 제품 및 바이오제약 서비스를 제공.</ns0:t>
+          <ns0:t>전 세계에 생명과학 솔루션·분석기기·전문 진단·실험실 제품·바이오제약 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G47">
@@ -3881,7 +3871,7 @@
       </ns0:c>
       <ns0:c r="R47" t="inlineStr">
         <ns0:is>
-          <ns0:t>47% 상승 후 주가 적정성 평가, 혁신의 반복매출 전환과 수익성, 신규 CHO-K1 패널·MRD 행보 조명. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>47% 상승 후 가치평가, 혁신의 반복 매출 전환과 수익성, 신규 CHO-K1 패널·MRD 행보를 다룸. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S47" t="inlineStr">
@@ -3923,7 +3913,7 @@
       </ns0:c>
       <ns0:c r="F48" t="inlineStr">
         <ns0:is>
-          <ns0:t>석유제품 운반선을 보유·운영하며 휘발유·항공유 등 정제유 운송과 해양 엔지니어링 사업을 영위.</ns0:t>
+          <ns0:t>석유제품 운반선을 보유·운영하며 정제유 운송과 해양 엔지니어링 사업을 영위.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G48">
@@ -3965,7 +3955,7 @@
       </ns0:c>
       <ns0:c r="R48" t="inlineStr">
         <ns0:is>
-          <ns0:t>하프니아가 TORM 지분을 19.85%로 늘린 뒤 하프니아 주가 하락 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>하프니아가 Torm 지분을 19.85%로 늘린 뒤 하프니아 주가가 하락했다는 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S48" t="inlineStr">
@@ -4007,7 +3997,7 @@
       </ns0:c>
       <ns0:c r="F49" t="inlineStr">
         <ns0:is>
-          <ns0:t>치료제·진단·소재·식품·농업·데이터 저장·학술 연구 등에 쓰이는 합성 DNA 제품을 제조·판매한다.</ns0:t>
+          <ns0:t>치료제·진단·소재·식품·농업·데이터 저장·학술 연구용 합성 DNA 제품을 제조·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G49">
@@ -4049,7 +4039,7 @@
       </ns0:c>
       <ns0:c r="R49" t="inlineStr">
         <ns0:is>
-          <ns0:t>매수에 필요한 조건을 검토한 기사와 목요일 주가 16% 상승을 앤트로픽과 연관 지은 리링크의 평가. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>매수 판단 조건을 다룬 기사와 목요일 주가 16% 상승을 앤트로픽과 연결한 리링크의 해석 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S49" t="inlineStr">
@@ -4091,7 +4081,7 @@
       </ns0:c>
       <ns0:c r="F50" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 생물학적 시스템 분석용 장비·소모품·소프트웨어를 개발·판매하며 Chromium 플랫폼을 제공한다.</ns0:t>
+          <ns0:t>생물학적 시스템 분석용 장비·소모품·소프트웨어를 개발·판매하며 Chromium 플랫폼 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G50">
@@ -4133,7 +4123,7 @@
       </ns0:c>
       <ns0:c r="R50" t="inlineStr">
         <ns0:is>
-          <ns0:t>10x 지노믹스의 주가 상승을 다룬 기사와 여러 의료 관련 종목의 동반 하락을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>10x Genomics 주가 상승 보도와 여러 의료 관련 종목과 함께 하락했다는 보도가 각각 제시됨. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S50" t="inlineStr">
@@ -4175,7 +4165,7 @@
       </ns0:c>
       <ns0:c r="F51" t="inlineStr">
         <ns0:is>
-          <ns0:t>파키스탄·우크라이나·카자흐스탄·방글라데시·우즈베키스탄에서 통신·디지털 서비스를 제공.</ns0:t>
+          <ns0:t>파키스탄·우크라이나·카자흐스탄·방글라데시·우즈베키스탄에서 통신·디지털 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G51">
@@ -4217,7 +4207,7 @@
       </ns0:c>
       <ns0:c r="R51" t="inlineStr">
         <ns0:is>
-          <ns0:t>방글라데시 디지털은행 면허 취득과 기업가치 평가 논쟁 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>기업가치 평가 논쟁이 커지는 가운데 방글라데시 디지털 은행 면허를 취득했다는 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S51" t="inlineStr">
@@ -4335,7 +4325,7 @@
       </ns0:c>
       <ns0:c r="F53" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 여성 핸드백, 여행가방·용품, 패션·홈 액세서리 및 선물용품을 설계·제조.</ns0:t>
+          <ns0:t>미국에서 여성 핸드백, 여행가방·용품, 패션·홈 액세서리와 선물용품을 설계·제조.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G53">
@@ -4377,7 +4367,7 @@
       </ns0:c>
       <ns0:c r="R53" t="inlineStr">
         <ns0:is>
-          <ns0:t>빠른 주가 움직임을 보이는 베라 브래들리의 가치투자 매력을 평가한 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>빠른 주가 움직임을 보인 Vera Bradley의 가치투자 매력을 다룬 기사. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S53" t="inlineStr">
@@ -4419,7 +4409,7 @@
       </ns0:c>
       <ns0:c r="F54" t="inlineStr">
         <ns0:is>
-          <ns0:t>아시아·미주·유럽에서 분석 업무 솔루션과 액체크로마토그래피·질량분석 시스템을 제공.</ns0:t>
+          <ns0:t>아시아·미주·유럽에서 분석 업무 솔루션과 액체크로마토그래피·질량분석 시스템 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G54">
@@ -4461,7 +4451,7 @@
       </ns0:c>
       <ns0:c r="R54" t="inlineStr">
         <ns0:is>
-          <ns0:t>가정용 HPV 검사·세포 분석 진출이 낙관론에 미칠 영향과 성장 전망 상회, AI 수요·BD 통합 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
+          <ns0:t>가정용 HPV·세포 분석 추진이 낙관론에 미칠 영향과 AI 수요·BD 통합 속 성장 전망 상회 보도. (기사 제목 요약·주가 인과 미확정)</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="S54" t="inlineStr">
@@ -4503,7 +4493,7 @@
       </ns0:c>
       <ns0:c r="F55" t="inlineStr">
         <ns0:is>
-          <ns0:t>HBO Max·discovery+ 등 스트리밍, 스튜디오 및 글로벌 방송 네트워크를 운영하는 미디어 기업.</ns0:t>
+          <ns0:t>HBO Max·discovery+ 등 스트리밍, 스튜디오와 글로벌 방송 네트워크를 운영하는 미디어 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G55">
@@ -4666,7 +4656,7 @@
       </ns0:c>
       <ns0:c r="F57" t="inlineStr">
         <ns0:is>
-          <ns0:t>유의미한 영업활동 없이 기업 합병·주식 교환·자산 인수 등 사업결합을 추진한다.</ns0:t>
+          <ns0:t>유의미한 영업활동 없이 합병·주식 교환·자산 인수 등 사업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G57">
@@ -16506,313 +16496,312 @@
   <ns0:autoFilter ref="A1:T203"/>
   <ns0:hyperlinks>
     <ns0:hyperlink ref="S2" ns1:id="rId1"/>
-    <ns0:hyperlink ref="T2" ns1:id="rId2"/>
-    <ns0:hyperlink ref="S3" ns1:id="rId3"/>
-    <ns0:hyperlink ref="T3" ns1:id="rId4"/>
-    <ns0:hyperlink ref="T4" ns1:id="rId5"/>
-    <ns0:hyperlink ref="S5" ns1:id="rId6"/>
-    <ns0:hyperlink ref="T5" ns1:id="rId7"/>
-    <ns0:hyperlink ref="S6" ns1:id="rId8"/>
-    <ns0:hyperlink ref="T6" ns1:id="rId9"/>
-    <ns0:hyperlink ref="S7" ns1:id="rId10"/>
-    <ns0:hyperlink ref="T7" ns1:id="rId11"/>
-    <ns0:hyperlink ref="S8" ns1:id="rId12"/>
-    <ns0:hyperlink ref="T8" ns1:id="rId13"/>
-    <ns0:hyperlink ref="S9" ns1:id="rId14"/>
-    <ns0:hyperlink ref="T9" ns1:id="rId15"/>
-    <ns0:hyperlink ref="S10" ns1:id="rId16"/>
-    <ns0:hyperlink ref="T10" ns1:id="rId17"/>
-    <ns0:hyperlink ref="S11" ns1:id="rId18"/>
-    <ns0:hyperlink ref="T11" ns1:id="rId19"/>
-    <ns0:hyperlink ref="S12" ns1:id="rId20"/>
-    <ns0:hyperlink ref="T12" ns1:id="rId21"/>
-    <ns0:hyperlink ref="S13" ns1:id="rId22"/>
-    <ns0:hyperlink ref="T13" ns1:id="rId23"/>
-    <ns0:hyperlink ref="T14" ns1:id="rId24"/>
-    <ns0:hyperlink ref="T15" ns1:id="rId25"/>
-    <ns0:hyperlink ref="S16" ns1:id="rId26"/>
-    <ns0:hyperlink ref="T16" ns1:id="rId27"/>
-    <ns0:hyperlink ref="S17" ns1:id="rId28"/>
-    <ns0:hyperlink ref="T17" ns1:id="rId29"/>
-    <ns0:hyperlink ref="S18" ns1:id="rId30"/>
-    <ns0:hyperlink ref="T18" ns1:id="rId31"/>
-    <ns0:hyperlink ref="S19" ns1:id="rId32"/>
-    <ns0:hyperlink ref="T19" ns1:id="rId33"/>
-    <ns0:hyperlink ref="S20" ns1:id="rId34"/>
-    <ns0:hyperlink ref="T20" ns1:id="rId35"/>
-    <ns0:hyperlink ref="T21" ns1:id="rId36"/>
-    <ns0:hyperlink ref="S22" ns1:id="rId37"/>
-    <ns0:hyperlink ref="T22" ns1:id="rId38"/>
-    <ns0:hyperlink ref="S23" ns1:id="rId39"/>
-    <ns0:hyperlink ref="T23" ns1:id="rId40"/>
-    <ns0:hyperlink ref="S24" ns1:id="rId41"/>
-    <ns0:hyperlink ref="T24" ns1:id="rId42"/>
-    <ns0:hyperlink ref="S25" ns1:id="rId43"/>
-    <ns0:hyperlink ref="T25" ns1:id="rId44"/>
-    <ns0:hyperlink ref="T26" ns1:id="rId45"/>
-    <ns0:hyperlink ref="S27" ns1:id="rId46"/>
-    <ns0:hyperlink ref="T27" ns1:id="rId47"/>
-    <ns0:hyperlink ref="T28" ns1:id="rId48"/>
-    <ns0:hyperlink ref="T29" ns1:id="rId49"/>
-    <ns0:hyperlink ref="S30" ns1:id="rId50"/>
-    <ns0:hyperlink ref="T30" ns1:id="rId51"/>
-    <ns0:hyperlink ref="T31" ns1:id="rId52"/>
-    <ns0:hyperlink ref="S32" ns1:id="rId53"/>
-    <ns0:hyperlink ref="T32" ns1:id="rId54"/>
-    <ns0:hyperlink ref="S33" ns1:id="rId55"/>
-    <ns0:hyperlink ref="T33" ns1:id="rId56"/>
-    <ns0:hyperlink ref="T34" ns1:id="rId57"/>
-    <ns0:hyperlink ref="S35" ns1:id="rId58"/>
-    <ns0:hyperlink ref="T35" ns1:id="rId59"/>
-    <ns0:hyperlink ref="S36" ns1:id="rId60"/>
-    <ns0:hyperlink ref="T36" ns1:id="rId61"/>
-    <ns0:hyperlink ref="S37" ns1:id="rId62"/>
-    <ns0:hyperlink ref="T37" ns1:id="rId63"/>
-    <ns0:hyperlink ref="S38" ns1:id="rId64"/>
-    <ns0:hyperlink ref="T38" ns1:id="rId65"/>
-    <ns0:hyperlink ref="S39" ns1:id="rId66"/>
-    <ns0:hyperlink ref="T39" ns1:id="rId67"/>
-    <ns0:hyperlink ref="S40" ns1:id="rId68"/>
-    <ns0:hyperlink ref="T40" ns1:id="rId69"/>
-    <ns0:hyperlink ref="S41" ns1:id="rId70"/>
-    <ns0:hyperlink ref="T41" ns1:id="rId71"/>
-    <ns0:hyperlink ref="S42" ns1:id="rId72"/>
-    <ns0:hyperlink ref="T42" ns1:id="rId73"/>
-    <ns0:hyperlink ref="S43" ns1:id="rId74"/>
-    <ns0:hyperlink ref="T43" ns1:id="rId75"/>
-    <ns0:hyperlink ref="T44" ns1:id="rId76"/>
-    <ns0:hyperlink ref="T45" ns1:id="rId77"/>
-    <ns0:hyperlink ref="T46" ns1:id="rId78"/>
-    <ns0:hyperlink ref="S47" ns1:id="rId79"/>
-    <ns0:hyperlink ref="T47" ns1:id="rId80"/>
-    <ns0:hyperlink ref="S48" ns1:id="rId81"/>
-    <ns0:hyperlink ref="T48" ns1:id="rId82"/>
-    <ns0:hyperlink ref="S49" ns1:id="rId83"/>
-    <ns0:hyperlink ref="T49" ns1:id="rId84"/>
-    <ns0:hyperlink ref="S50" ns1:id="rId85"/>
-    <ns0:hyperlink ref="T50" ns1:id="rId86"/>
-    <ns0:hyperlink ref="S51" ns1:id="rId87"/>
-    <ns0:hyperlink ref="T51" ns1:id="rId88"/>
-    <ns0:hyperlink ref="T52" ns1:id="rId89"/>
-    <ns0:hyperlink ref="S53" ns1:id="rId90"/>
-    <ns0:hyperlink ref="T53" ns1:id="rId91"/>
-    <ns0:hyperlink ref="S54" ns1:id="rId92"/>
-    <ns0:hyperlink ref="T54" ns1:id="rId93"/>
-    <ns0:hyperlink ref="S55" ns1:id="rId94"/>
-    <ns0:hyperlink ref="T55" ns1:id="rId95"/>
-    <ns0:hyperlink ref="T56" ns1:id="rId96"/>
-    <ns0:hyperlink ref="T57" ns1:id="rId97"/>
-    <ns0:hyperlink ref="T58" ns1:id="rId98"/>
-    <ns0:hyperlink ref="T59" ns1:id="rId99"/>
-    <ns0:hyperlink ref="T60" ns1:id="rId100"/>
-    <ns0:hyperlink ref="T61" ns1:id="rId101"/>
-    <ns0:hyperlink ref="T62" ns1:id="rId102"/>
-    <ns0:hyperlink ref="T63" ns1:id="rId103"/>
-    <ns0:hyperlink ref="T64" ns1:id="rId104"/>
-    <ns0:hyperlink ref="T65" ns1:id="rId105"/>
-    <ns0:hyperlink ref="T66" ns1:id="rId106"/>
-    <ns0:hyperlink ref="T67" ns1:id="rId107"/>
-    <ns0:hyperlink ref="T68" ns1:id="rId108"/>
-    <ns0:hyperlink ref="T69" ns1:id="rId109"/>
-    <ns0:hyperlink ref="T70" ns1:id="rId110"/>
-    <ns0:hyperlink ref="T71" ns1:id="rId111"/>
-    <ns0:hyperlink ref="T72" ns1:id="rId112"/>
-    <ns0:hyperlink ref="T73" ns1:id="rId113"/>
-    <ns0:hyperlink ref="T74" ns1:id="rId114"/>
-    <ns0:hyperlink ref="T75" ns1:id="rId115"/>
-    <ns0:hyperlink ref="T76" ns1:id="rId116"/>
-    <ns0:hyperlink ref="T77" ns1:id="rId117"/>
-    <ns0:hyperlink ref="T78" ns1:id="rId118"/>
-    <ns0:hyperlink ref="T79" ns1:id="rId119"/>
-    <ns0:hyperlink ref="T80" ns1:id="rId120"/>
-    <ns0:hyperlink ref="T81" ns1:id="rId121"/>
-    <ns0:hyperlink ref="T82" ns1:id="rId122"/>
-    <ns0:hyperlink ref="T83" ns1:id="rId123"/>
-    <ns0:hyperlink ref="T84" ns1:id="rId124"/>
-    <ns0:hyperlink ref="T85" ns1:id="rId125"/>
-    <ns0:hyperlink ref="T86" ns1:id="rId126"/>
-    <ns0:hyperlink ref="T87" ns1:id="rId127"/>
-    <ns0:hyperlink ref="T88" ns1:id="rId128"/>
-    <ns0:hyperlink ref="T89" ns1:id="rId129"/>
-    <ns0:hyperlink ref="T90" ns1:id="rId130"/>
-    <ns0:hyperlink ref="T91" ns1:id="rId131"/>
-    <ns0:hyperlink ref="T92" ns1:id="rId132"/>
-    <ns0:hyperlink ref="T93" ns1:id="rId133"/>
-    <ns0:hyperlink ref="T94" ns1:id="rId134"/>
-    <ns0:hyperlink ref="T95" ns1:id="rId135"/>
-    <ns0:hyperlink ref="T96" ns1:id="rId136"/>
-    <ns0:hyperlink ref="T97" ns1:id="rId137"/>
-    <ns0:hyperlink ref="T98" ns1:id="rId138"/>
-    <ns0:hyperlink ref="T99" ns1:id="rId139"/>
-    <ns0:hyperlink ref="T100" ns1:id="rId140"/>
-    <ns0:hyperlink ref="T101" ns1:id="rId141"/>
-    <ns0:hyperlink ref="T102" ns1:id="rId142"/>
-    <ns0:hyperlink ref="T103" ns1:id="rId143"/>
-    <ns0:hyperlink ref="S104" ns1:id="rId144"/>
-    <ns0:hyperlink ref="T104" ns1:id="rId145"/>
-    <ns0:hyperlink ref="S105" ns1:id="rId146"/>
-    <ns0:hyperlink ref="T105" ns1:id="rId147"/>
-    <ns0:hyperlink ref="T106" ns1:id="rId148"/>
-    <ns0:hyperlink ref="T107" ns1:id="rId149"/>
-    <ns0:hyperlink ref="S108" ns1:id="rId150"/>
-    <ns0:hyperlink ref="T108" ns1:id="rId151"/>
-    <ns0:hyperlink ref="S109" ns1:id="rId152"/>
-    <ns0:hyperlink ref="T109" ns1:id="rId153"/>
-    <ns0:hyperlink ref="S110" ns1:id="rId154"/>
-    <ns0:hyperlink ref="T110" ns1:id="rId155"/>
-    <ns0:hyperlink ref="S111" ns1:id="rId156"/>
-    <ns0:hyperlink ref="T111" ns1:id="rId157"/>
-    <ns0:hyperlink ref="S112" ns1:id="rId158"/>
-    <ns0:hyperlink ref="T112" ns1:id="rId159"/>
-    <ns0:hyperlink ref="S113" ns1:id="rId160"/>
-    <ns0:hyperlink ref="T113" ns1:id="rId161"/>
-    <ns0:hyperlink ref="S114" ns1:id="rId162"/>
-    <ns0:hyperlink ref="T114" ns1:id="rId163"/>
-    <ns0:hyperlink ref="S115" ns1:id="rId164"/>
-    <ns0:hyperlink ref="T115" ns1:id="rId165"/>
-    <ns0:hyperlink ref="S116" ns1:id="rId166"/>
-    <ns0:hyperlink ref="T116" ns1:id="rId167"/>
-    <ns0:hyperlink ref="S117" ns1:id="rId168"/>
-    <ns0:hyperlink ref="T117" ns1:id="rId169"/>
-    <ns0:hyperlink ref="T118" ns1:id="rId170"/>
-    <ns0:hyperlink ref="T119" ns1:id="rId171"/>
-    <ns0:hyperlink ref="S120" ns1:id="rId172"/>
-    <ns0:hyperlink ref="T120" ns1:id="rId173"/>
-    <ns0:hyperlink ref="T121" ns1:id="rId174"/>
-    <ns0:hyperlink ref="S122" ns1:id="rId175"/>
-    <ns0:hyperlink ref="T122" ns1:id="rId176"/>
-    <ns0:hyperlink ref="S123" ns1:id="rId177"/>
-    <ns0:hyperlink ref="T123" ns1:id="rId178"/>
-    <ns0:hyperlink ref="S124" ns1:id="rId179"/>
-    <ns0:hyperlink ref="T124" ns1:id="rId180"/>
-    <ns0:hyperlink ref="T125" ns1:id="rId181"/>
-    <ns0:hyperlink ref="T126" ns1:id="rId182"/>
-    <ns0:hyperlink ref="S127" ns1:id="rId183"/>
-    <ns0:hyperlink ref="T127" ns1:id="rId184"/>
-    <ns0:hyperlink ref="S128" ns1:id="rId185"/>
-    <ns0:hyperlink ref="T128" ns1:id="rId186"/>
-    <ns0:hyperlink ref="S129" ns1:id="rId187"/>
-    <ns0:hyperlink ref="T129" ns1:id="rId188"/>
-    <ns0:hyperlink ref="S130" ns1:id="rId189"/>
-    <ns0:hyperlink ref="T130" ns1:id="rId190"/>
-    <ns0:hyperlink ref="S131" ns1:id="rId191"/>
-    <ns0:hyperlink ref="T131" ns1:id="rId192"/>
-    <ns0:hyperlink ref="T132" ns1:id="rId193"/>
-    <ns0:hyperlink ref="S133" ns1:id="rId194"/>
-    <ns0:hyperlink ref="T133" ns1:id="rId195"/>
-    <ns0:hyperlink ref="T134" ns1:id="rId196"/>
-    <ns0:hyperlink ref="T135" ns1:id="rId197"/>
-    <ns0:hyperlink ref="S136" ns1:id="rId198"/>
-    <ns0:hyperlink ref="T136" ns1:id="rId199"/>
-    <ns0:hyperlink ref="S137" ns1:id="rId200"/>
-    <ns0:hyperlink ref="T137" ns1:id="rId201"/>
-    <ns0:hyperlink ref="S138" ns1:id="rId202"/>
-    <ns0:hyperlink ref="T138" ns1:id="rId203"/>
-    <ns0:hyperlink ref="S139" ns1:id="rId204"/>
-    <ns0:hyperlink ref="T139" ns1:id="rId205"/>
-    <ns0:hyperlink ref="S140" ns1:id="rId206"/>
-    <ns0:hyperlink ref="T140" ns1:id="rId207"/>
-    <ns0:hyperlink ref="S141" ns1:id="rId208"/>
-    <ns0:hyperlink ref="T141" ns1:id="rId209"/>
-    <ns0:hyperlink ref="T142" ns1:id="rId210"/>
-    <ns0:hyperlink ref="S143" ns1:id="rId211"/>
-    <ns0:hyperlink ref="T143" ns1:id="rId212"/>
-    <ns0:hyperlink ref="T144" ns1:id="rId213"/>
-    <ns0:hyperlink ref="T145" ns1:id="rId214"/>
-    <ns0:hyperlink ref="S146" ns1:id="rId215"/>
-    <ns0:hyperlink ref="T146" ns1:id="rId216"/>
-    <ns0:hyperlink ref="S147" ns1:id="rId217"/>
-    <ns0:hyperlink ref="T147" ns1:id="rId218"/>
-    <ns0:hyperlink ref="T148" ns1:id="rId219"/>
-    <ns0:hyperlink ref="S149" ns1:id="rId220"/>
-    <ns0:hyperlink ref="T149" ns1:id="rId221"/>
-    <ns0:hyperlink ref="S150" ns1:id="rId222"/>
-    <ns0:hyperlink ref="T150" ns1:id="rId223"/>
-    <ns0:hyperlink ref="S151" ns1:id="rId224"/>
-    <ns0:hyperlink ref="S152" ns1:id="rId225"/>
-    <ns0:hyperlink ref="T153" ns1:id="rId226"/>
-    <ns0:hyperlink ref="T154" ns1:id="rId227"/>
-    <ns0:hyperlink ref="S155" ns1:id="rId228"/>
-    <ns0:hyperlink ref="T155" ns1:id="rId229"/>
-    <ns0:hyperlink ref="S156" ns1:id="rId230"/>
-    <ns0:hyperlink ref="T156" ns1:id="rId231"/>
-    <ns0:hyperlink ref="S157" ns1:id="rId232"/>
-    <ns0:hyperlink ref="T157" ns1:id="rId233"/>
-    <ns0:hyperlink ref="T158" ns1:id="rId234"/>
-    <ns0:hyperlink ref="S159" ns1:id="rId235"/>
-    <ns0:hyperlink ref="T159" ns1:id="rId236"/>
-    <ns0:hyperlink ref="T160" ns1:id="rId237"/>
-    <ns0:hyperlink ref="T161" ns1:id="rId238"/>
-    <ns0:hyperlink ref="S162" ns1:id="rId239"/>
-    <ns0:hyperlink ref="T162" ns1:id="rId240"/>
-    <ns0:hyperlink ref="T163" ns1:id="rId241"/>
-    <ns0:hyperlink ref="T164" ns1:id="rId242"/>
-    <ns0:hyperlink ref="S165" ns1:id="rId243"/>
-    <ns0:hyperlink ref="T165" ns1:id="rId244"/>
-    <ns0:hyperlink ref="S166" ns1:id="rId245"/>
-    <ns0:hyperlink ref="T166" ns1:id="rId246"/>
-    <ns0:hyperlink ref="T167" ns1:id="rId247"/>
-    <ns0:hyperlink ref="T168" ns1:id="rId248"/>
-    <ns0:hyperlink ref="S169" ns1:id="rId249"/>
-    <ns0:hyperlink ref="T169" ns1:id="rId250"/>
-    <ns0:hyperlink ref="S170" ns1:id="rId251"/>
-    <ns0:hyperlink ref="T170" ns1:id="rId252"/>
-    <ns0:hyperlink ref="S171" ns1:id="rId253"/>
-    <ns0:hyperlink ref="T171" ns1:id="rId254"/>
-    <ns0:hyperlink ref="S172" ns1:id="rId255"/>
-    <ns0:hyperlink ref="T172" ns1:id="rId256"/>
-    <ns0:hyperlink ref="S173" ns1:id="rId257"/>
-    <ns0:hyperlink ref="T173" ns1:id="rId258"/>
-    <ns0:hyperlink ref="S174" ns1:id="rId259"/>
-    <ns0:hyperlink ref="T174" ns1:id="rId260"/>
-    <ns0:hyperlink ref="S175" ns1:id="rId261"/>
-    <ns0:hyperlink ref="T175" ns1:id="rId262"/>
-    <ns0:hyperlink ref="T176" ns1:id="rId263"/>
-    <ns0:hyperlink ref="S177" ns1:id="rId264"/>
-    <ns0:hyperlink ref="T177" ns1:id="rId265"/>
-    <ns0:hyperlink ref="S178" ns1:id="rId266"/>
-    <ns0:hyperlink ref="T178" ns1:id="rId267"/>
-    <ns0:hyperlink ref="S179" ns1:id="rId268"/>
-    <ns0:hyperlink ref="T179" ns1:id="rId269"/>
-    <ns0:hyperlink ref="S180" ns1:id="rId270"/>
-    <ns0:hyperlink ref="T180" ns1:id="rId271"/>
-    <ns0:hyperlink ref="T181" ns1:id="rId272"/>
-    <ns0:hyperlink ref="S182" ns1:id="rId273"/>
-    <ns0:hyperlink ref="T182" ns1:id="rId274"/>
-    <ns0:hyperlink ref="T183" ns1:id="rId275"/>
-    <ns0:hyperlink ref="T184" ns1:id="rId276"/>
-    <ns0:hyperlink ref="S185" ns1:id="rId277"/>
-    <ns0:hyperlink ref="T185" ns1:id="rId278"/>
-    <ns0:hyperlink ref="S186" ns1:id="rId279"/>
-    <ns0:hyperlink ref="T186" ns1:id="rId280"/>
-    <ns0:hyperlink ref="S187" ns1:id="rId281"/>
-    <ns0:hyperlink ref="T187" ns1:id="rId282"/>
-    <ns0:hyperlink ref="S188" ns1:id="rId283"/>
-    <ns0:hyperlink ref="T188" ns1:id="rId284"/>
-    <ns0:hyperlink ref="S189" ns1:id="rId285"/>
-    <ns0:hyperlink ref="T189" ns1:id="rId286"/>
-    <ns0:hyperlink ref="S190" ns1:id="rId287"/>
-    <ns0:hyperlink ref="T190" ns1:id="rId288"/>
-    <ns0:hyperlink ref="T191" ns1:id="rId289"/>
-    <ns0:hyperlink ref="S192" ns1:id="rId290"/>
-    <ns0:hyperlink ref="T192" ns1:id="rId291"/>
-    <ns0:hyperlink ref="T193" ns1:id="rId292"/>
-    <ns0:hyperlink ref="T194" ns1:id="rId293"/>
-    <ns0:hyperlink ref="S195" ns1:id="rId294"/>
-    <ns0:hyperlink ref="T195" ns1:id="rId295"/>
-    <ns0:hyperlink ref="T196" ns1:id="rId296"/>
-    <ns0:hyperlink ref="S197" ns1:id="rId297"/>
-    <ns0:hyperlink ref="T197" ns1:id="rId298"/>
-    <ns0:hyperlink ref="S198" ns1:id="rId299"/>
-    <ns0:hyperlink ref="T198" ns1:id="rId300"/>
-    <ns0:hyperlink ref="S199" ns1:id="rId301"/>
-    <ns0:hyperlink ref="T199" ns1:id="rId302"/>
-    <ns0:hyperlink ref="S200" ns1:id="rId303"/>
-    <ns0:hyperlink ref="T200" ns1:id="rId304"/>
-    <ns0:hyperlink ref="T201" ns1:id="rId305"/>
-    <ns0:hyperlink ref="S202" ns1:id="rId306"/>
-    <ns0:hyperlink ref="T202" ns1:id="rId307"/>
-    <ns0:hyperlink ref="T203" ns1:id="rId308"/>
+    <ns0:hyperlink ref="S3" ns1:id="rId2"/>
+    <ns0:hyperlink ref="T3" ns1:id="rId3"/>
+    <ns0:hyperlink ref="T4" ns1:id="rId4"/>
+    <ns0:hyperlink ref="S5" ns1:id="rId5"/>
+    <ns0:hyperlink ref="T5" ns1:id="rId6"/>
+    <ns0:hyperlink ref="S6" ns1:id="rId7"/>
+    <ns0:hyperlink ref="T6" ns1:id="rId8"/>
+    <ns0:hyperlink ref="S7" ns1:id="rId9"/>
+    <ns0:hyperlink ref="T7" ns1:id="rId10"/>
+    <ns0:hyperlink ref="S8" ns1:id="rId11"/>
+    <ns0:hyperlink ref="T8" ns1:id="rId12"/>
+    <ns0:hyperlink ref="S9" ns1:id="rId13"/>
+    <ns0:hyperlink ref="T9" ns1:id="rId14"/>
+    <ns0:hyperlink ref="S10" ns1:id="rId15"/>
+    <ns0:hyperlink ref="T10" ns1:id="rId16"/>
+    <ns0:hyperlink ref="S11" ns1:id="rId17"/>
+    <ns0:hyperlink ref="T11" ns1:id="rId18"/>
+    <ns0:hyperlink ref="S12" ns1:id="rId19"/>
+    <ns0:hyperlink ref="T12" ns1:id="rId20"/>
+    <ns0:hyperlink ref="S13" ns1:id="rId21"/>
+    <ns0:hyperlink ref="T13" ns1:id="rId22"/>
+    <ns0:hyperlink ref="T14" ns1:id="rId23"/>
+    <ns0:hyperlink ref="T15" ns1:id="rId24"/>
+    <ns0:hyperlink ref="S16" ns1:id="rId25"/>
+    <ns0:hyperlink ref="T16" ns1:id="rId26"/>
+    <ns0:hyperlink ref="S17" ns1:id="rId27"/>
+    <ns0:hyperlink ref="T17" ns1:id="rId28"/>
+    <ns0:hyperlink ref="S18" ns1:id="rId29"/>
+    <ns0:hyperlink ref="T18" ns1:id="rId30"/>
+    <ns0:hyperlink ref="S19" ns1:id="rId31"/>
+    <ns0:hyperlink ref="T19" ns1:id="rId32"/>
+    <ns0:hyperlink ref="S20" ns1:id="rId33"/>
+    <ns0:hyperlink ref="T20" ns1:id="rId34"/>
+    <ns0:hyperlink ref="T21" ns1:id="rId35"/>
+    <ns0:hyperlink ref="S22" ns1:id="rId36"/>
+    <ns0:hyperlink ref="T22" ns1:id="rId37"/>
+    <ns0:hyperlink ref="S23" ns1:id="rId38"/>
+    <ns0:hyperlink ref="T23" ns1:id="rId39"/>
+    <ns0:hyperlink ref="S24" ns1:id="rId40"/>
+    <ns0:hyperlink ref="T24" ns1:id="rId41"/>
+    <ns0:hyperlink ref="S25" ns1:id="rId42"/>
+    <ns0:hyperlink ref="T25" ns1:id="rId43"/>
+    <ns0:hyperlink ref="T26" ns1:id="rId44"/>
+    <ns0:hyperlink ref="S27" ns1:id="rId45"/>
+    <ns0:hyperlink ref="T27" ns1:id="rId46"/>
+    <ns0:hyperlink ref="T28" ns1:id="rId47"/>
+    <ns0:hyperlink ref="T29" ns1:id="rId48"/>
+    <ns0:hyperlink ref="S30" ns1:id="rId49"/>
+    <ns0:hyperlink ref="T30" ns1:id="rId50"/>
+    <ns0:hyperlink ref="T31" ns1:id="rId51"/>
+    <ns0:hyperlink ref="S32" ns1:id="rId52"/>
+    <ns0:hyperlink ref="T32" ns1:id="rId53"/>
+    <ns0:hyperlink ref="S33" ns1:id="rId54"/>
+    <ns0:hyperlink ref="T33" ns1:id="rId55"/>
+    <ns0:hyperlink ref="T34" ns1:id="rId56"/>
+    <ns0:hyperlink ref="S35" ns1:id="rId57"/>
+    <ns0:hyperlink ref="T35" ns1:id="rId58"/>
+    <ns0:hyperlink ref="S36" ns1:id="rId59"/>
+    <ns0:hyperlink ref="T36" ns1:id="rId60"/>
+    <ns0:hyperlink ref="S37" ns1:id="rId61"/>
+    <ns0:hyperlink ref="T37" ns1:id="rId62"/>
+    <ns0:hyperlink ref="S38" ns1:id="rId63"/>
+    <ns0:hyperlink ref="T38" ns1:id="rId64"/>
+    <ns0:hyperlink ref="S39" ns1:id="rId65"/>
+    <ns0:hyperlink ref="T39" ns1:id="rId66"/>
+    <ns0:hyperlink ref="S40" ns1:id="rId67"/>
+    <ns0:hyperlink ref="T40" ns1:id="rId68"/>
+    <ns0:hyperlink ref="S41" ns1:id="rId69"/>
+    <ns0:hyperlink ref="T41" ns1:id="rId70"/>
+    <ns0:hyperlink ref="S42" ns1:id="rId71"/>
+    <ns0:hyperlink ref="T42" ns1:id="rId72"/>
+    <ns0:hyperlink ref="S43" ns1:id="rId73"/>
+    <ns0:hyperlink ref="T43" ns1:id="rId74"/>
+    <ns0:hyperlink ref="T44" ns1:id="rId75"/>
+    <ns0:hyperlink ref="T45" ns1:id="rId76"/>
+    <ns0:hyperlink ref="T46" ns1:id="rId77"/>
+    <ns0:hyperlink ref="S47" ns1:id="rId78"/>
+    <ns0:hyperlink ref="T47" ns1:id="rId79"/>
+    <ns0:hyperlink ref="S48" ns1:id="rId80"/>
+    <ns0:hyperlink ref="T48" ns1:id="rId81"/>
+    <ns0:hyperlink ref="S49" ns1:id="rId82"/>
+    <ns0:hyperlink ref="T49" ns1:id="rId83"/>
+    <ns0:hyperlink ref="S50" ns1:id="rId84"/>
+    <ns0:hyperlink ref="T50" ns1:id="rId85"/>
+    <ns0:hyperlink ref="S51" ns1:id="rId86"/>
+    <ns0:hyperlink ref="T51" ns1:id="rId87"/>
+    <ns0:hyperlink ref="T52" ns1:id="rId88"/>
+    <ns0:hyperlink ref="S53" ns1:id="rId89"/>
+    <ns0:hyperlink ref="T53" ns1:id="rId90"/>
+    <ns0:hyperlink ref="S54" ns1:id="rId91"/>
+    <ns0:hyperlink ref="T54" ns1:id="rId92"/>
+    <ns0:hyperlink ref="S55" ns1:id="rId93"/>
+    <ns0:hyperlink ref="T55" ns1:id="rId94"/>
+    <ns0:hyperlink ref="T56" ns1:id="rId95"/>
+    <ns0:hyperlink ref="T57" ns1:id="rId96"/>
+    <ns0:hyperlink ref="T58" ns1:id="rId97"/>
+    <ns0:hyperlink ref="T59" ns1:id="rId98"/>
+    <ns0:hyperlink ref="T60" ns1:id="rId99"/>
+    <ns0:hyperlink ref="T61" ns1:id="rId100"/>
+    <ns0:hyperlink ref="T62" ns1:id="rId101"/>
+    <ns0:hyperlink ref="T63" ns1:id="rId102"/>
+    <ns0:hyperlink ref="T64" ns1:id="rId103"/>
+    <ns0:hyperlink ref="T65" ns1:id="rId104"/>
+    <ns0:hyperlink ref="T66" ns1:id="rId105"/>
+    <ns0:hyperlink ref="T67" ns1:id="rId106"/>
+    <ns0:hyperlink ref="T68" ns1:id="rId107"/>
+    <ns0:hyperlink ref="T69" ns1:id="rId108"/>
+    <ns0:hyperlink ref="T70" ns1:id="rId109"/>
+    <ns0:hyperlink ref="T71" ns1:id="rId110"/>
+    <ns0:hyperlink ref="T72" ns1:id="rId111"/>
+    <ns0:hyperlink ref="T73" ns1:id="rId112"/>
+    <ns0:hyperlink ref="T74" ns1:id="rId113"/>
+    <ns0:hyperlink ref="T75" ns1:id="rId114"/>
+    <ns0:hyperlink ref="T76" ns1:id="rId115"/>
+    <ns0:hyperlink ref="T77" ns1:id="rId116"/>
+    <ns0:hyperlink ref="T78" ns1:id="rId117"/>
+    <ns0:hyperlink ref="T79" ns1:id="rId118"/>
+    <ns0:hyperlink ref="T80" ns1:id="rId119"/>
+    <ns0:hyperlink ref="T81" ns1:id="rId120"/>
+    <ns0:hyperlink ref="T82" ns1:id="rId121"/>
+    <ns0:hyperlink ref="T83" ns1:id="rId122"/>
+    <ns0:hyperlink ref="T84" ns1:id="rId123"/>
+    <ns0:hyperlink ref="T85" ns1:id="rId124"/>
+    <ns0:hyperlink ref="T86" ns1:id="rId125"/>
+    <ns0:hyperlink ref="T87" ns1:id="rId126"/>
+    <ns0:hyperlink ref="T88" ns1:id="rId127"/>
+    <ns0:hyperlink ref="T89" ns1:id="rId128"/>
+    <ns0:hyperlink ref="T90" ns1:id="rId129"/>
+    <ns0:hyperlink ref="T91" ns1:id="rId130"/>
+    <ns0:hyperlink ref="T92" ns1:id="rId131"/>
+    <ns0:hyperlink ref="T93" ns1:id="rId132"/>
+    <ns0:hyperlink ref="T94" ns1:id="rId133"/>
+    <ns0:hyperlink ref="T95" ns1:id="rId134"/>
+    <ns0:hyperlink ref="T96" ns1:id="rId135"/>
+    <ns0:hyperlink ref="T97" ns1:id="rId136"/>
+    <ns0:hyperlink ref="T98" ns1:id="rId137"/>
+    <ns0:hyperlink ref="T99" ns1:id="rId138"/>
+    <ns0:hyperlink ref="T100" ns1:id="rId139"/>
+    <ns0:hyperlink ref="T101" ns1:id="rId140"/>
+    <ns0:hyperlink ref="T102" ns1:id="rId141"/>
+    <ns0:hyperlink ref="T103" ns1:id="rId142"/>
+    <ns0:hyperlink ref="S104" ns1:id="rId143"/>
+    <ns0:hyperlink ref="T104" ns1:id="rId144"/>
+    <ns0:hyperlink ref="S105" ns1:id="rId145"/>
+    <ns0:hyperlink ref="T105" ns1:id="rId146"/>
+    <ns0:hyperlink ref="T106" ns1:id="rId147"/>
+    <ns0:hyperlink ref="T107" ns1:id="rId148"/>
+    <ns0:hyperlink ref="S108" ns1:id="rId149"/>
+    <ns0:hyperlink ref="T108" ns1:id="rId150"/>
+    <ns0:hyperlink ref="S109" ns1:id="rId151"/>
+    <ns0:hyperlink ref="T109" ns1:id="rId152"/>
+    <ns0:hyperlink ref="S110" ns1:id="rId153"/>
+    <ns0:hyperlink ref="T110" ns1:id="rId154"/>
+    <ns0:hyperlink ref="S111" ns1:id="rId155"/>
+    <ns0:hyperlink ref="T111" ns1:id="rId156"/>
+    <ns0:hyperlink ref="S112" ns1:id="rId157"/>
+    <ns0:hyperlink ref="T112" ns1:id="rId158"/>
+    <ns0:hyperlink ref="S113" ns1:id="rId159"/>
+    <ns0:hyperlink ref="T113" ns1:id="rId160"/>
+    <ns0:hyperlink ref="S114" ns1:id="rId161"/>
+    <ns0:hyperlink ref="T114" ns1:id="rId162"/>
+    <ns0:hyperlink ref="S115" ns1:id="rId163"/>
+    <ns0:hyperlink ref="T115" ns1:id="rId164"/>
+    <ns0:hyperlink ref="S116" ns1:id="rId165"/>
+    <ns0:hyperlink ref="T116" ns1:id="rId166"/>
+    <ns0:hyperlink ref="S117" ns1:id="rId167"/>
+    <ns0:hyperlink ref="T117" ns1:id="rId168"/>
+    <ns0:hyperlink ref="T118" ns1:id="rId169"/>
+    <ns0:hyperlink ref="T119" ns1:id="rId170"/>
+    <ns0:hyperlink ref="S120" ns1:id="rId171"/>
+    <ns0:hyperlink ref="T120" ns1:id="rId172"/>
+    <ns0:hyperlink ref="T121" ns1:id="rId173"/>
+    <ns0:hyperlink ref="S122" ns1:id="rId174"/>
+    <ns0:hyperlink ref="T122" ns1:id="rId175"/>
+    <ns0:hyperlink ref="S123" ns1:id="rId176"/>
+    <ns0:hyperlink ref="T123" ns1:id="rId177"/>
+    <ns0:hyperlink ref="S124" ns1:id="rId178"/>
+    <ns0:hyperlink ref="T124" ns1:id="rId179"/>
+    <ns0:hyperlink ref="T125" ns1:id="rId180"/>
+    <ns0:hyperlink ref="T126" ns1:id="rId181"/>
+    <ns0:hyperlink ref="S127" ns1:id="rId182"/>
+    <ns0:hyperlink ref="T127" ns1:id="rId183"/>
+    <ns0:hyperlink ref="S128" ns1:id="rId184"/>
+    <ns0:hyperlink ref="T128" ns1:id="rId185"/>
+    <ns0:hyperlink ref="S129" ns1:id="rId186"/>
+    <ns0:hyperlink ref="T129" ns1:id="rId187"/>
+    <ns0:hyperlink ref="S130" ns1:id="rId188"/>
+    <ns0:hyperlink ref="T130" ns1:id="rId189"/>
+    <ns0:hyperlink ref="S131" ns1:id="rId190"/>
+    <ns0:hyperlink ref="T131" ns1:id="rId191"/>
+    <ns0:hyperlink ref="T132" ns1:id="rId192"/>
+    <ns0:hyperlink ref="S133" ns1:id="rId193"/>
+    <ns0:hyperlink ref="T133" ns1:id="rId194"/>
+    <ns0:hyperlink ref="T134" ns1:id="rId195"/>
+    <ns0:hyperlink ref="T135" ns1:id="rId196"/>
+    <ns0:hyperlink ref="S136" ns1:id="rId197"/>
+    <ns0:hyperlink ref="T136" ns1:id="rId198"/>
+    <ns0:hyperlink ref="S137" ns1:id="rId199"/>
+    <ns0:hyperlink ref="T137" ns1:id="rId200"/>
+    <ns0:hyperlink ref="S138" ns1:id="rId201"/>
+    <ns0:hyperlink ref="T138" ns1:id="rId202"/>
+    <ns0:hyperlink ref="S139" ns1:id="rId203"/>
+    <ns0:hyperlink ref="T139" ns1:id="rId204"/>
+    <ns0:hyperlink ref="S140" ns1:id="rId205"/>
+    <ns0:hyperlink ref="T140" ns1:id="rId206"/>
+    <ns0:hyperlink ref="S141" ns1:id="rId207"/>
+    <ns0:hyperlink ref="T141" ns1:id="rId208"/>
+    <ns0:hyperlink ref="T142" ns1:id="rId209"/>
+    <ns0:hyperlink ref="S143" ns1:id="rId210"/>
+    <ns0:hyperlink ref="T143" ns1:id="rId211"/>
+    <ns0:hyperlink ref="T144" ns1:id="rId212"/>
+    <ns0:hyperlink ref="T145" ns1:id="rId213"/>
+    <ns0:hyperlink ref="S146" ns1:id="rId214"/>
+    <ns0:hyperlink ref="T146" ns1:id="rId215"/>
+    <ns0:hyperlink ref="S147" ns1:id="rId216"/>
+    <ns0:hyperlink ref="T147" ns1:id="rId217"/>
+    <ns0:hyperlink ref="T148" ns1:id="rId218"/>
+    <ns0:hyperlink ref="S149" ns1:id="rId219"/>
+    <ns0:hyperlink ref="T149" ns1:id="rId220"/>
+    <ns0:hyperlink ref="S150" ns1:id="rId221"/>
+    <ns0:hyperlink ref="T150" ns1:id="rId222"/>
+    <ns0:hyperlink ref="S151" ns1:id="rId223"/>
+    <ns0:hyperlink ref="S152" ns1:id="rId224"/>
+    <ns0:hyperlink ref="T153" ns1:id="rId225"/>
+    <ns0:hyperlink ref="T154" ns1:id="rId226"/>
+    <ns0:hyperlink ref="S155" ns1:id="rId227"/>
+    <ns0:hyperlink ref="T155" ns1:id="rId228"/>
+    <ns0:hyperlink ref="S156" ns1:id="rId229"/>
+    <ns0:hyperlink ref="T156" ns1:id="rId230"/>
+    <ns0:hyperlink ref="S157" ns1:id="rId231"/>
+    <ns0:hyperlink ref="T157" ns1:id="rId232"/>
+    <ns0:hyperlink ref="T158" ns1:id="rId233"/>
+    <ns0:hyperlink ref="S159" ns1:id="rId234"/>
+    <ns0:hyperlink ref="T159" ns1:id="rId235"/>
+    <ns0:hyperlink ref="T160" ns1:id="rId236"/>
+    <ns0:hyperlink ref="T161" ns1:id="rId237"/>
+    <ns0:hyperlink ref="S162" ns1:id="rId238"/>
+    <ns0:hyperlink ref="T162" ns1:id="rId239"/>
+    <ns0:hyperlink ref="T163" ns1:id="rId240"/>
+    <ns0:hyperlink ref="T164" ns1:id="rId241"/>
+    <ns0:hyperlink ref="S165" ns1:id="rId242"/>
+    <ns0:hyperlink ref="T165" ns1:id="rId243"/>
+    <ns0:hyperlink ref="S166" ns1:id="rId244"/>
+    <ns0:hyperlink ref="T166" ns1:id="rId245"/>
+    <ns0:hyperlink ref="T167" ns1:id="rId246"/>
+    <ns0:hyperlink ref="T168" ns1:id="rId247"/>
+    <ns0:hyperlink ref="S169" ns1:id="rId248"/>
+    <ns0:hyperlink ref="T169" ns1:id="rId249"/>
+    <ns0:hyperlink ref="S170" ns1:id="rId250"/>
+    <ns0:hyperlink ref="T170" ns1:id="rId251"/>
+    <ns0:hyperlink ref="S171" ns1:id="rId252"/>
+    <ns0:hyperlink ref="T171" ns1:id="rId253"/>
+    <ns0:hyperlink ref="S172" ns1:id="rId254"/>
+    <ns0:hyperlink ref="T172" ns1:id="rId255"/>
+    <ns0:hyperlink ref="S173" ns1:id="rId256"/>
+    <ns0:hyperlink ref="T173" ns1:id="rId257"/>
+    <ns0:hyperlink ref="S174" ns1:id="rId258"/>
+    <ns0:hyperlink ref="T174" ns1:id="rId259"/>
+    <ns0:hyperlink ref="S175" ns1:id="rId260"/>
+    <ns0:hyperlink ref="T175" ns1:id="rId261"/>
+    <ns0:hyperlink ref="T176" ns1:id="rId262"/>
+    <ns0:hyperlink ref="S177" ns1:id="rId263"/>
+    <ns0:hyperlink ref="T177" ns1:id="rId264"/>
+    <ns0:hyperlink ref="S178" ns1:id="rId265"/>
+    <ns0:hyperlink ref="T178" ns1:id="rId266"/>
+    <ns0:hyperlink ref="S179" ns1:id="rId267"/>
+    <ns0:hyperlink ref="T179" ns1:id="rId268"/>
+    <ns0:hyperlink ref="S180" ns1:id="rId269"/>
+    <ns0:hyperlink ref="T180" ns1:id="rId270"/>
+    <ns0:hyperlink ref="T181" ns1:id="rId271"/>
+    <ns0:hyperlink ref="S182" ns1:id="rId272"/>
+    <ns0:hyperlink ref="T182" ns1:id="rId273"/>
+    <ns0:hyperlink ref="T183" ns1:id="rId274"/>
+    <ns0:hyperlink ref="T184" ns1:id="rId275"/>
+    <ns0:hyperlink ref="S185" ns1:id="rId276"/>
+    <ns0:hyperlink ref="T185" ns1:id="rId277"/>
+    <ns0:hyperlink ref="S186" ns1:id="rId278"/>
+    <ns0:hyperlink ref="T186" ns1:id="rId279"/>
+    <ns0:hyperlink ref="S187" ns1:id="rId280"/>
+    <ns0:hyperlink ref="T187" ns1:id="rId281"/>
+    <ns0:hyperlink ref="S188" ns1:id="rId282"/>
+    <ns0:hyperlink ref="T188" ns1:id="rId283"/>
+    <ns0:hyperlink ref="S189" ns1:id="rId284"/>
+    <ns0:hyperlink ref="T189" ns1:id="rId285"/>
+    <ns0:hyperlink ref="S190" ns1:id="rId286"/>
+    <ns0:hyperlink ref="T190" ns1:id="rId287"/>
+    <ns0:hyperlink ref="T191" ns1:id="rId288"/>
+    <ns0:hyperlink ref="S192" ns1:id="rId289"/>
+    <ns0:hyperlink ref="T192" ns1:id="rId290"/>
+    <ns0:hyperlink ref="T193" ns1:id="rId291"/>
+    <ns0:hyperlink ref="T194" ns1:id="rId292"/>
+    <ns0:hyperlink ref="S195" ns1:id="rId293"/>
+    <ns0:hyperlink ref="T195" ns1:id="rId294"/>
+    <ns0:hyperlink ref="T196" ns1:id="rId295"/>
+    <ns0:hyperlink ref="S197" ns1:id="rId296"/>
+    <ns0:hyperlink ref="T197" ns1:id="rId297"/>
+    <ns0:hyperlink ref="S198" ns1:id="rId298"/>
+    <ns0:hyperlink ref="T198" ns1:id="rId299"/>
+    <ns0:hyperlink ref="S199" ns1:id="rId300"/>
+    <ns0:hyperlink ref="T199" ns1:id="rId301"/>
+    <ns0:hyperlink ref="S200" ns1:id="rId302"/>
+    <ns0:hyperlink ref="T200" ns1:id="rId303"/>
+    <ns0:hyperlink ref="T201" ns1:id="rId304"/>
+    <ns0:hyperlink ref="S202" ns1:id="rId305"/>
+    <ns0:hyperlink ref="T202" ns1:id="rId306"/>
+    <ns0:hyperlink ref="T203" ns1:id="rId307"/>
   </ns0:hyperlinks>
 </ns0:worksheet>
 </file>

--- a/technicals/exports/new-highs-history.xlsx
+++ b/technicals/exports/new-highs-history.xlsx
@@ -142,7 +142,7 @@
       </ns0:c>
       <ns0:c r="F2" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국 뷰티·개인관리 브랜드에 전략, 마케팅, 전 채널 판매, 고객 서비스 및 물류 등 브랜드 관리 제공.</ns0:t>
+          <ns0:t>중국 뷰티·개인관리 브랜드에 전략·마케팅·전 채널 판매·고객 서비스·물류 등 브랜드 관리 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G2">
@@ -297,7 +297,7 @@
       </ns0:c>
       <ns0:c r="F4" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업·컨택센터·통신사업자에 음성 통신 인프라·장비, 클라우드 관리 및 음성 AI 솔루션 제공.</ns0:t>
+          <ns0:t>기업·컨택센터·통신사업자에 음성 통신 인프라·장비, 클라우드 관리·음성 AI 솔루션 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G4">
@@ -376,7 +376,7 @@
       </ns0:c>
       <ns0:c r="F5" t="inlineStr">
         <ns0:is>
-          <ns0:t>이식 환자의 치료 결과와 장기 건강 개선을 위한 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>이식 환자의 치료 결과와 장기 건강 개선을 위한 솔루션 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G5">
@@ -455,7 +455,7 @@
       </ns0:c>
       <ns0:c r="F6" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업·공공부문 등에 컴퓨터 시스템과 데이터센터를 포함한 다양한 IT 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>기업·공공부문에 컴퓨터 시스템·데이터센터 등 다양한 IT 솔루션을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G6">
@@ -534,7 +534,7 @@
       </ns0:c>
       <ns0:c r="F7" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 하나 이상의 기업과 합병·주식교환·자산인수 등 기업결합을 추진.</ns0:t>
+          <ns0:t>주요 영업활동 없이 하나 이상의 기업과 합병·주식교환·자산인수 등 기업결합 추진.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G7">
@@ -768,7 +768,7 @@
       </ns0:c>
       <ns0:c r="F10" t="inlineStr">
         <ns0:is>
-          <ns0:t>자회사를 통해 원유 운반선을 소유·운영하며 기술 관리 서비스도 제공하는 기업.</ns0:t>
+          <ns0:t>자회사를 통해 원유 운반선을 소유·운영하고 기술 관리 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G10">
@@ -847,7 +847,7 @@
       </ns0:c>
       <ns0:c r="F11" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병·주식 교환·자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G11">
@@ -923,7 +923,7 @@
       </ns0:c>
       <ns0:c r="F12" t="inlineStr">
         <ns0:is>
-          <ns0:t>디지털 기업의 복잡한 디지털 환경을 위한 AI 기반 관측성 플랫폼을 제공하는 기업.</ns0:t>
+          <ns0:t>기업의 복잡한 디지털 환경을 위한 AI 기반 관측성 플랫폼 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G12">
@@ -1081,7 +1081,7 @@
       </ns0:c>
       <ns0:c r="F14" t="inlineStr">
         <ns0:is>
-          <ns0:t>시계·스마트워치·주얼리·핸드백·가죽 소품·벨트·선글라스 등 패션 액세서리를 설계·개발·유통.</ns0:t>
+          <ns0:t>시계·스마트워치·주얼리·핸드백·가죽 소품·벨트·선글라스 등 패션 액세서리 설계·개발·유통.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G14">
@@ -1239,7 +1239,7 @@
       </ns0:c>
       <ns0:c r="F16" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병·주식 교환·자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G16">
@@ -1315,7 +1315,7 @@
       </ns0:c>
       <ns0:c r="F17" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술로 의료 제공을 확장·자동화하며 급성 부상·만성 통증·수술 후 재활 등 근골격계 관리 플랫폼을 개발하는 기업.</ns0:t>
+          <ns0:t>급성 부상·만성 통증·수술 후 재활 등 근골격계 관리를 위한 의료 자동화 플랫폼 개발 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G17">
@@ -1394,7 +1394,7 @@
       </ns0:c>
       <ns0:c r="F18" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·영국 등에서 핀테크 및 통신 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>미국·영국 등에서 핀테크 및 통신 솔루션 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G18">
@@ -1473,7 +1473,7 @@
       </ns0:c>
       <ns0:c r="F19" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 전자 설계·시험용 소프트웨어, 계측기, 시스템 및 관련 서비스를 제공.</ns0:t>
+          <ns0:t>전 세계에 전자 설계·시험용 소프트웨어, 계측기·시스템 및 관련 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G19">
@@ -1710,7 +1710,7 @@
       </ns0:c>
       <ns0:c r="F22" t="inlineStr">
         <ns0:is>
-          <ns0:t>보건·안전 분야에 사용하는 휴대용 질량분석기와 푸리에 변환 적외선 장비를 제공한다.</ns0:t>
+          <ns0:t>보건·안전 분야용 휴대용 질량분석기와 푸리에 변환 적외선 장비 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G22">
@@ -1789,7 +1789,7 @@
       </ns0:c>
       <ns0:c r="F23" t="inlineStr">
         <ns0:is>
-          <ns0:t>자동차 금융·리스, 은행 및 금융서비스 산업용 기업 소프트웨어를 설계·개발·판매하는 회사.</ns0:t>
+          <ns0:t>자동차 금융·리스, 은행·금융서비스용 기업 소프트웨어를 설계·개발·판매하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G23">
@@ -1947,7 +1947,7 @@
       </ns0:c>
       <ns0:c r="F25" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 싱글 사인온과 위험 기반 다중요소 인증 등 신원·접근 보안 서비스를 제공하는 회사.</ns0:t>
+          <ns0:t>미국과 해외에서 싱글 사인온, 위험 기반 다중요소 인증 등 신원·접근 보안 서비스를 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G25">
@@ -2026,7 +2026,7 @@
       </ns0:c>
       <ns0:c r="F26" t="inlineStr">
         <ns0:is>
-          <ns0:t>데이터 저장·관리 기술과 제품, 서비스를 제공하며 데이터 축소·보호·암호화 소프트웨어를 공급한다.</ns0:t>
+          <ns0:t>데이터 저장·관리 기술과 제품·서비스, 데이터 축소·보호·암호화 소프트웨어 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G26">
@@ -2105,7 +2105,7 @@
       </ns0:c>
       <ns0:c r="F27" t="inlineStr">
         <ns0:is>
-          <ns0:t>선불카드, 환자 비용 부담 지원, 디지털뱅킹, 생명과학 소프트웨어 및 통합 결제처리를 제공하는 회사.</ns0:t>
+          <ns0:t>선불카드, 환자 비용 지원, 디지털뱅킹, 생명과학 소프트웨어 및 통합 결제처리를 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G27">
@@ -2184,7 +2184,7 @@
       </ns0:c>
       <ns0:c r="F28" t="inlineStr">
         <ns0:is>
-          <ns0:t>p53 변이 및 관련 암을 표적으로 하는 저분자 치료제를 발굴·개발하는 미국 정밀항암 기업.</ns0:t>
+          <ns0:t>p53 변이 및 관련 암을 표적으로 저분자 치료제를 발굴·개발하는 미국 정밀항암 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G28">
@@ -2418,7 +2418,7 @@
       </ns0:c>
       <ns0:c r="F31" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업·클라우드·SaaS 데이터 보호, 데이터 위협 분석 및 신원 복구 등 보안 솔루션을 제공하는 회사.</ns0:t>
+          <ns0:t>기업·클라우드·SaaS 데이터 보호, 데이터 위협 분석 및 신원 복구 보안 솔루션을 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G31">
@@ -2576,7 +2576,7 @@
       </ns0:c>
       <ns0:c r="F33" t="inlineStr">
         <ns0:is>
-          <ns0:t>독자 기술과 분석 역량으로 신원 정보를 제공하며, 조사 솔루션 idiCORE를 운영하는 미국 기업.</ns0:t>
+          <ns0:t>독자 기술과 분석으로 신원 정보를 제공하고 조사 솔루션 idiCORE를 운영하는 미국 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G33">
@@ -2971,7 +2971,7 @@
       </ns0:c>
       <ns0:c r="F38" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 메시지·음성·이메일·영상 소통용 API와 소프트웨어 등 고객 참여 플랫폼을 제공한다.</ns0:t>
+          <ns0:t>미국과 해외에서 메시지·음성·이메일·영상 소통 API와 소프트웨어 등 고객 참여 플랫폼을 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G38">
@@ -3050,7 +3050,7 @@
       </ns0:c>
       <ns0:c r="F39" t="inlineStr">
         <ns0:is>
-          <ns0:t>치료제·진단·소재·농업·데이터 저장·학술 연구 등에 쓰이는 합성 DNA 제품을 제조·판매한다.</ns0:t>
+          <ns0:t>치료제·진단·소재·농업·데이터 저장·학술 연구용 합성 DNA 제품 제조·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G39">
@@ -3287,7 +3287,7 @@
       </ns0:c>
       <ns0:c r="F42" t="inlineStr">
         <ns0:is>
-          <ns0:t>유의미한 영업활동 없이 기업 합병·주식 교환·자산 인수 등 사업결합을 추진한다.</ns0:t>
+          <ns0:t>유의미한 영업활동 없이 합병·주식 교환·자산 인수 등 사업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G42">
@@ -3363,7 +3363,7 @@
       </ns0:c>
       <ns0:c r="F43" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술 서비스 분야 기업과의 합병·주식 교환·자산 인수 등 사업결합을 추진한다.</ns0:t>
+          <ns0:t>기술 서비스 기업과의 합병·주식 교환·자산 인수 등 사업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G43">

--- a/technicals/exports/new-highs-history.xlsx
+++ b/technicals/exports/new-highs-history.xlsx
@@ -142,7 +142,7 @@
       </ns0:c>
       <ns0:c r="F2" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 의약품과 치료제를 연구·개발·제조·판매하는 연구 중심 바이오 제약 기업.</ns0:t>
+          <ns0:t>전 세계에서 의약품·치료제를 연구·개발·제조·판매하는 연구 중심 바이오 제약 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G2">
@@ -221,7 +221,7 @@
       </ns0:c>
       <ns0:c r="F3" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 건설·엔지니어링 구조물·운송 시장에 인프라 관련 제품과 솔루션을 제공한다.</ns0:t>
+          <ns0:t>미국 건설·엔지니어링 구조물·운송 시장에 인프라 제품과 솔루션을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G3">
@@ -300,7 +300,7 @@
       </ns0:c>
       <ns0:c r="F4" t="inlineStr">
         <ns0:is>
-          <ns0:t>계열사를 통해 미국 펀드, 기관, 개인 및 고액자산가에게 투자관리·자문 서비스를 제공.</ns0:t>
+          <ns0:t>계열사를 통해 미국 펀드·기관·개인·고액자산가에게 투자관리·자문 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G4">
@@ -379,7 +379,7 @@
       </ns0:c>
       <ns0:c r="F5" t="inlineStr">
         <ns0:is>
-          <ns0:t>디지털 제품의 고객 행동을 분석하는 AI 플랫폼과 실시간 분석·세션 재생 도구를 제공.</ns0:t>
+          <ns0:t>디지털 제품의 고객 행동 분석용 AI 플랫폼과 실시간 분석·세션 재생 도구를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G5">
@@ -537,7 +537,7 @@
       </ns0:c>
       <ns0:c r="F7" t="inlineStr">
         <ns0:is>
-          <ns0:t>다발성경화증, 척수성 근위축증 등 치료제를 연구·개발·제조·공급하는 기업.</ns0:t>
+          <ns0:t>다발성경화증·척수성 근위축증 등 치료제를 연구·개발·제조·공급하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G7">
@@ -616,7 +616,7 @@
       </ns0:c>
       <ns0:c r="F8" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업과의 합병, 주식 교환, 자산 인수 등 사업 결합을 추진하는 기업.</ns0:t>
+          <ns0:t>합병·주식 교환·자산 인수 등 기업과의 사업 결합을 추진하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G8">
@@ -692,7 +692,7 @@
       </ns0:c>
       <ns0:c r="F9" t="inlineStr">
         <ns0:is>
-          <ns0:t>다양한 규모의 조직이 장소와 기기에 관계없이 콘텐츠를 관리하는 클라우드 플랫폼 제공.</ns0:t>
+          <ns0:t>다양한 규모의 조직이 장소·기기에 관계없이 콘텐츠를 관리하는 클라우드 플랫폼 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G9">
@@ -771,7 +771,7 @@
       </ns0:c>
       <ns0:c r="F10" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 선박 보유·용선, 액화석유가스 운송 및 통합 배송 서비스를 제공.</ns0:t>
+          <ns0:t>전 세계에서 선박 보유·용선, 액화석유가스 운송 및 통합 배송 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G10">
@@ -1008,7 +1008,7 @@
       </ns0:c>
       <ns0:c r="F13" t="inlineStr">
         <ns0:is>
-          <ns0:t>벨기에 해운 기업으로 해운·수소 인프라·수소 산업 부문을 운영하며 저탄소·무탄소 선박을 설계·건조·운영.</ns0:t>
+          <ns0:t>해운·수소 인프라·수소 산업을 운영하며 저탄소·무탄소 선박을 설계·건조·운영하는 벨기에 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G13">
@@ -1087,7 +1087,7 @@
       </ns0:c>
       <ns0:c r="F14" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업·공공부문 등에 컴퓨터 시스템과 데이터센터를 포함한 다양한 IT 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>기업·공공부문에 컴퓨터 시스템·데이터센터 등 다양한 IT 솔루션을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G14">
@@ -1166,7 +1166,7 @@
       </ns0:c>
       <ns0:c r="F15" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 직업건강센터와 사업장 내 진료소 등을 통해 직업건강 및 고용주·소비자 건강 서비스를 제공.</ns0:t>
+          <ns0:t>미국에서 직업건강센터와 사업장 내 진료소를 통해 직업건강 및 고용주·소비자 건강 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G15">
@@ -1245,7 +1245,7 @@
       </ns0:c>
       <ns0:c r="F16" t="inlineStr">
         <ns0:is>
-          <ns0:t>컨테이너선과 건화물선을 보유·운영하며 해상 운송 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>컨테이너선·건화물선을 보유·운영하며 해상 운송 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G16">
@@ -1324,7 +1324,7 @@
       </ns0:c>
       <ns0:c r="F17" t="inlineStr">
         <ns0:is>
-          <ns0:t>클라우드 애플리케이션용 관측·보안 플랫폼과 인프라·성능 모니터링, 로그 관리 등을 제공.</ns0:t>
+          <ns0:t>클라우드 앱 관측·보안 플랫폼과 인프라·성능 모니터링, 로그 관리 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G17">
@@ -1403,7 +1403,7 @@
       </ns0:c>
       <ns0:c r="F18" t="inlineStr">
         <ns0:is>
-          <ns0:t>자회사를 통해 원유 운반선을 소유·운영하며 기술 관리 서비스도 제공하는 기업.</ns0:t>
+          <ns0:t>자회사를 통해 원유 운반선을 소유·운영하고 기술 관리 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G18">
@@ -1482,7 +1482,7 @@
       </ns0:c>
       <ns0:c r="F19" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 독립 에너지 기업으로 정유·재생에너지·마케팅·윤활유·미드스트림 사업과 연료 생산·판매를 수행.</ns0:t>
+          <ns0:t>미국 독립 에너지 기업으로 정유·재생에너지·윤활유·미드스트림 사업과 연료 생산·판매 수행.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G19">
@@ -1561,7 +1561,7 @@
       </ns0:c>
       <ns0:c r="F20" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 사이버보안·AI 등 분야 기업과의 합병·인수를 추진하는 기업.</ns0:t>
+          <ns0:t>주요 영업활동 없이 사이버보안·AI 등 분야 기업과의 합병·인수를 추진.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G20">
@@ -1637,7 +1637,7 @@
       </ns0:c>
       <ns0:c r="F21" t="inlineStr">
         <ns0:is>
-          <ns0:t>디지털 기업의 복잡한 디지털 환경을 위한 AI 기반 관측성 플랫폼을 제공하는 기업.</ns0:t>
+          <ns0:t>기업의 복잡한 디지털 환경을 위한 AI 기반 관측성 플랫폼 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G21">
@@ -1874,7 +1874,7 @@
       </ns0:c>
       <ns0:c r="F24" t="inlineStr">
         <ns0:is>
-          <ns0:t>멀티클라우드 애플리케이션 보안·전송 솔루션과 앱 배포·보안·운영용 분산 클라우드 서비스를 제공한다.</ns0:t>
+          <ns0:t>멀티클라우드 앱 보안·전송 솔루션과 앱 배포·보안·운영을 위한 분산 클라우드 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G24">
@@ -1953,7 +1953,7 @@
       </ns0:c>
       <ns0:c r="F25" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 의료용 의류, 신발 등 생활용품을 소비자에게 직접 판매하는 기업.</ns0:t>
+          <ns0:t>미국과 해외에서 의료용 의류·신발 등 생활용품을 소비자에게 직접 판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G25">
@@ -2032,7 +2032,7 @@
       </ns0:c>
       <ns0:c r="F26" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 초대형 원유운반선, 수에즈막스, LR2·아프라막스 등 원유·석유제품 운반선을 보유·운영.</ns0:t>
+          <ns0:t>전 세계에서 초대형·수에즈막스·LR2·아프라막스 원유·석유제품 운반선 보유·운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G26">
@@ -2111,7 +2111,7 @@
       </ns0:c>
       <ns0:c r="F27" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 사이버보안 및 네트워크·보안 통합 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>전 세계에 사이버보안과 네트워크·보안 통합 솔루션을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G27">
@@ -2269,7 +2269,7 @@
       </ns0:c>
       <ns0:c r="F29" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·호주·유럽의 매장과 온라인에서 게임, 수집품, 엔터테인먼트 제품을 판매하는 기업.</ns0:t>
+          <ns0:t>미국·호주·유럽의 매장과 온라인에서 게임·수집품·엔터테인먼트 제품을 판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G29">
@@ -2348,7 +2348,7 @@
       </ns0:c>
       <ns0:c r="F30" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 및 해외에서 에너지 서비스를 제공하며 전력·천연가스 재판매와 재생에너지 사업을 영위.</ns0:t>
+          <ns0:t>미국 및 해외에서 전력·천연가스 재판매와 재생에너지 등 에너지 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G30">
@@ -2427,7 +2427,7 @@
       </ns0:c>
       <ns0:c r="F31" t="inlineStr">
         <ns0:is>
-          <ns0:t>소프트웨어 개발 전 과정을 지원하는 통합 DevSecOps 플랫폼 GitLab을 제공하는 기업.</ns0:t>
+          <ns0:t>소프트웨어 개발 전 과정을 지원하는 통합 DevSecOps 플랫폼 GitLab을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G31">
@@ -2506,7 +2506,7 @@
       </ns0:c>
       <ns0:c r="F32" t="inlineStr">
         <ns0:is>
-          <ns0:t>혈장·혈액센터·병원 부문의 의료기술 기업으로 자동 혈장 채취 시스템과 헌혈자 관리 소프트웨어 등을 제공.</ns0:t>
+          <ns0:t>혈장·혈액센터·병원용 의료기술 기업으로 자동 혈장 채취 시스템과 헌혈자 관리 소프트웨어 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G32">
@@ -2664,7 +2664,7 @@
       </ns0:c>
       <ns0:c r="F34" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다·영국에서 수집용·자동차 애호가용 차량 보험을 제공하며 보험·마켓플레이스 부문을 운영.</ns0:t>
+          <ns0:t>미국·캐나다·영국에서 수집용·자동차 애호가용 차량 보험과 마켓플레이스 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G34">
@@ -2743,7 +2743,7 @@
       </ns0:c>
       <ns0:c r="F35" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국과 해외에서 다양한 형태의 맞춤형 냉간 성형 강재를 제조·판매하는 회사.</ns0:t>
+          <ns0:t>중국과 해외에서 다양한 맞춤형 냉간 성형 강재를 제조·판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G35">
@@ -2822,7 +2822,7 @@
       </ns0:c>
       <ns0:c r="F36" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술로 의료 제공을 확장·자동화하며 급성 부상·만성 통증·수술 후 재활 등 근골격계 관리 플랫폼을 개발하는 기업.</ns0:t>
+          <ns0:t>급성 부상·만성 통증·수술 후 재활 등 근골격계 관리를 위한 의료 자동화 플랫폼 개발 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G36">
@@ -2980,7 +2980,7 @@
       </ns0:c>
       <ns0:c r="F38" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 의료기관에 SaaS 애플리케이션과 의료 제공자 채용·신청·면허 검증 등 관리 도구를 제공.</ns0:t>
+          <ns0:t>미국 의료기관에 SaaS와 의료 제공자 채용·신청·면허 검증 관리 도구를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G38">
@@ -3059,7 +3059,7 @@
       </ns0:c>
       <ns0:c r="F39" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술 기반 고객 경험 솔루션과 고객서비스·기술지원·백오피스 아웃소싱을 제공하는 기업.</ns0:t>
+          <ns0:t>기술 기반 고객 경험 솔루션과 고객서비스·기술지원·백오피스 아웃소싱을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G39">
@@ -3138,7 +3138,7 @@
       </ns0:c>
       <ns0:c r="F40" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·영국 등에서 핀테크 및 통신 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>미국·영국 등에서 핀테크 및 통신 솔루션 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G40">
@@ -3217,7 +3217,7 @@
       </ns0:c>
       <ns0:c r="F41" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업과의 합병, 주식 교환, 자산 인수 등 사업 결합을 추진하는 기업.</ns0:t>
+          <ns0:t>합병·주식 교환·자산 인수 등 사업 결합을 추진하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G41">
@@ -3293,7 +3293,7 @@
       </ns0:c>
       <ns0:c r="F42" t="inlineStr">
         <ns0:is>
-          <ns0:t>원유와 석유제품의 국제 해상 운송을 위해 원유선과 제품 운반선을 보유·운영하는 기업.</ns0:t>
+          <ns0:t>원유선과 석유제품 운반선을 보유·운영하며 원유·석유제품의 국제 해상 운송을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G42">
@@ -3372,7 +3372,7 @@
       </ns0:c>
       <ns0:c r="F43" t="inlineStr">
         <ns0:is>
-          <ns0:t>소셜 서비스와 통신 기술을 제공하며 소셜 라이브 스트리밍 플랫폼 Bigo Live를 운영한다.</ns0:t>
+          <ns0:t>소셜 서비스·통신 기술을 제공하고 소셜 라이브 스트리밍 플랫폼 Bigo Live를 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G43">
@@ -3451,7 +3451,7 @@
       </ns0:c>
       <ns0:c r="F44" t="inlineStr">
         <ns0:is>
-          <ns0:t>외식업용 플라스틱·종이·바이오폴리머·퇴비화 소재 일회용 용기와 포장재를 제조·유통하는 기업.</ns0:t>
+          <ns0:t>외식업용 플라스틱·종이·바이오폴리머·퇴비화 소재 일회용 용기와 포장재를 제조·유통.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G44">
@@ -3530,7 +3530,7 @@
       </ns0:c>
       <ns0:c r="F45" t="inlineStr">
         <ns0:is>
-          <ns0:t>맞춤형 선박을 활용한 해양 탐험과 육상 여행 체험을 전 세계에 제공하는 기업.</ns0:t>
+          <ns0:t>맞춤형 선박을 활용한 해양 탐험과 육상 여행 체험을 전 세계에 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G45">
@@ -3688,7 +3688,7 @@
       </ns0:c>
       <ns0:c r="F47" t="inlineStr">
         <ns0:is>
-          <ns0:t>버뮤다와 해외에서 이중선체 유조선을 보유·운영·용선하며 석유회사와 원유 거래업체에 서비스를 제공.</ns0:t>
+          <ns0:t>버뮤다와 해외에서 이중선체 유조선을 보유·운영·용선하며 석유회사·원유 거래업체에 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G47">
@@ -3846,7 +3846,7 @@
       </ns0:c>
       <ns0:c r="F49" t="inlineStr">
         <ns0:is>
-          <ns0:t>하이브리드·퍼블릭 클라우드 부문에서 데이터 인프라용 기업 소프트웨어·시스템·서비스를 개발하는 기업.</ns0:t>
+          <ns0:t>하이브리드·퍼블릭 클라우드의 데이터 인프라용 기업 소프트웨어·시스템·서비스를 개발.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G49">
@@ -4004,7 +4004,7 @@
       </ns0:c>
       <ns0:c r="F51" t="inlineStr">
         <ns0:is>
-          <ns0:t>자동차 금융·리스, 은행 및 금융서비스 산업용 기업 소프트웨어를 설계·개발·판매하는 회사.</ns0:t>
+          <ns0:t>자동차 금융·리스, 은행·금융서비스용 기업 소프트웨어를 설계·개발·판매하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G51">
@@ -4083,7 +4083,7 @@
       </ns0:c>
       <ns0:c r="F52" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 싱글 사인온과 위험 기반 다중요소 인증 등 신원·접근 보안 서비스를 제공하는 회사.</ns0:t>
+          <ns0:t>미국과 해외에서 싱글 사인온, 위험 기반 다중요소 인증 등 신원·접근 보안 서비스를 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G52">
@@ -4162,7 +4162,7 @@
       </ns0:c>
       <ns0:c r="F53" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 온라인·전화·매장 및 제휴 채널을 통해 개인대출과 신용카드를 제공.</ns0:t>
+          <ns0:t>미국에서 온라인·전화·매장 및 제휴 채널을 통해 개인대출과 신용카드 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G53">
@@ -4241,7 +4241,7 @@
       </ns0:c>
       <ns0:c r="F54" t="inlineStr">
         <ns0:is>
-          <ns0:t>선불카드, 환자 비용 부담 지원, 디지털뱅킹, 생명과학 소프트웨어 및 통합 결제처리를 제공하는 회사.</ns0:t>
+          <ns0:t>선불카드, 환자 비용 지원, 디지털뱅킹, 생명과학 소프트웨어 및 통합 결제처리를 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G54">
@@ -4320,7 +4320,7 @@
       </ns0:c>
       <ns0:c r="F55" t="inlineStr">
         <ns0:is>
-          <ns0:t>브라질과 해외에서 석유·가스를 탐사·생산·판매하며 정유·운송·판매 사업을 운영한다.</ns0:t>
+          <ns0:t>브라질과 해외에서 석유·가스 탐사·생산·판매 및 정유·운송 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G55">
@@ -4399,7 +4399,7 @@
       </ns0:c>
       <ns0:c r="F56" t="inlineStr">
         <ns0:is>
-          <ns0:t>브라질과 해외에서 석유·가스를 탐사·생산·판매하며 정유·운송·판매 사업을 운영한다.</ns0:t>
+          <ns0:t>브라질과 해외에서 석유·가스 탐사·생산·판매 및 정유·운송 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G56">
@@ -4478,7 +4478,7 @@
       </ns0:c>
       <ns0:c r="F57" t="inlineStr">
         <ns0:is>
-          <ns0:t>암 치료 제품을 개발·상용화하는 바이오제약 기업으로 경구용 네라티닙인 NERLYNX를 제공.</ns0:t>
+          <ns0:t>암 치료제를 개발·상용화하는 바이오제약 기업으로 경구용 네라티닙 NERLYNX 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G57">
@@ -4557,7 +4557,7 @@
       </ns0:c>
       <ns0:c r="F58" t="inlineStr">
         <ns0:is>
-          <ns0:t>정보기관의 대테러 조사·작전을 지원하는 소프트웨어 플랫폼을 구축·배포하고 국방 솔루션 제공.</ns0:t>
+          <ns0:t>정보기관의 대테러 조사·작전을 지원하는 소프트웨어 플랫폼과 국방 솔루션을 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G58">
@@ -4715,7 +4715,7 @@
       </ns0:c>
       <ns0:c r="F60" t="inlineStr">
         <ns0:is>
-          <ns0:t>당좌·저축·정기예금과 개인·기업·농업·상업용 부동산·주택담보 대출 등 은행 서비스를 제공한다.</ns0:t>
+          <ns0:t>당좌·저축·정기예금과 개인·기업·농업·상업용 부동산·주택담보 대출 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G60">
@@ -4873,7 +4873,7 @@
       </ns0:c>
       <ns0:c r="F62" t="inlineStr">
         <ns0:is>
-          <ns0:t>텍사스·뉴멕시코에서 석유·천연가스·천연가스액 자산을 인수·탐사·개발·생산.</ns0:t>
+          <ns0:t>텍사스·뉴멕시코에서 석유·천연가스·천연가스액 자산을 인수·탐사·개발·생산한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G62">
@@ -4952,7 +4952,7 @@
       </ns0:c>
       <ns0:c r="F63" t="inlineStr">
         <ns0:is>
-          <ns0:t>온라인 판매자와 소비자의 신뢰 관계 구축을 돕는 전자상거래 위험 분석 플랫폼을 개발·제공한다.</ns0:t>
+          <ns0:t>온라인 판매자와 소비자의 신뢰 구축을 돕는 전자상거래 위험 분석 플랫폼을 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G63">
@@ -5031,7 +5031,7 @@
       </ns0:c>
       <ns0:c r="F64" t="inlineStr">
         <ns0:is>
-          <ns0:t>세계 각지에서 통합 가스, 자원 개발·생산, 마케팅, 화학·제품, 재생에너지 사업을 운영한다.</ns0:t>
+          <ns0:t>전 세계에서 통합 가스, 자원 개발·생산, 마케팅, 화학·제품, 재생에너지 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G64">
@@ -5110,7 +5110,7 @@
       </ns0:c>
       <ns0:c r="F65" t="inlineStr">
         <ns0:is>
-          <ns0:t>실질적인 영업활동 없이 합병, 주식 교환, 자산 인수 등 기업결합을 추진하는 회사.</ns0:t>
+          <ns0:t>실질적 영업활동 없이 합병·주식교환·자산인수 등 기업결합을 추진.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G65">
@@ -5186,7 +5186,7 @@
       </ns0:c>
       <ns0:c r="F66" t="inlineStr">
         <ns0:is>
-          <ns0:t>남아공 등에서 화학·에너지 사업을 운영하며 역청, 연료, 나프타, 윤활유, 액화석유가스 등을 공급한다.</ns0:t>
+          <ns0:t>남아공 등에서 화학·에너지 사업을 운영하며 역청·연료·나프타·윤활유·액화석유가스를 공급한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G66">
@@ -5265,7 +5265,7 @@
       </ns0:c>
       <ns0:c r="F67" t="inlineStr">
         <ns0:is>
-          <ns0:t>캐나다·미국 등에서 오일샌드, 석유 탐사·생산, 정유·판매 사업을 영위하는 종합 에너지 기업.</ns0:t>
+          <ns0:t>캐나다·미국 등에서 오일샌드, 석유 탐사·생산, 정유·판매 사업을 운영하는 종합 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G67">
@@ -5502,7 +5502,7 @@
       </ns0:c>
       <ns0:c r="F70" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 원유 해상운송과 해양 서비스를 제공하며 원유·정유제품 운반선을 보유·운영한다.</ns0:t>
+          <ns0:t>세계적으로 원유 해상운송·해양 서비스를 제공하며 원유·정유제품 운반선을 보유·운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G70">
@@ -5581,7 +5581,7 @@
       </ns0:c>
       <ns0:c r="F71" t="inlineStr">
         <ns0:is>
-          <ns0:t>석유업계에 해상 운송, 항해·기간 용선, 해상 선박 간 화물 이송 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>석유업계에 해상 운송·항해 및 기간 용선·해상 선박 간 화물 이송 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G71">
@@ -5739,7 +5739,7 @@
       </ns0:c>
       <ns0:c r="F73" t="inlineStr">
         <ns0:is>
-          <ns0:t>실질적인 영업활동 없이 다른 기업과의 합병·주식교환·자산인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>실질적 영업활동 없이 합병·주식교환·자산인수 등 다른 기업과의 기업결합을 추진.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G73">
@@ -5815,7 +5815,7 @@
       </ns0:c>
       <ns0:c r="F74" t="inlineStr">
         <ns0:is>
-          <ns0:t>결제 승인·청산·정산 네트워크 VisaNet을 운영하고 신용·직불·선불카드 상품을 제공.</ns0:t>
+          <ns0:t>결제 승인·청산·정산 네트워크 VisaNet을 운영하고 신용·직불·선불카드 상품을 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G74">
@@ -5894,7 +5894,7 @@
       </ns0:c>
       <ns0:c r="F75" t="inlineStr">
         <ns0:is>
-          <ns0:t>파키스탄·우크라이나·카자흐스탄·방글라데시·우즈베키스탄에서 이동통신과 디지털 서비스를 제공.</ns0:t>
+          <ns0:t>파키스탄·우크라이나·카자흐스탄·방글라데시·우즈베키스탄에서 이동통신·디지털 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G75">
@@ -6131,7 +6131,7 @@
       </ns0:c>
       <ns0:c r="F78" t="inlineStr">
         <ns0:is>
-          <ns0:t>자회사 Win-Fung을 통해 말레이시아 등에서 유리섬유 강화 플라스틱 제품과 탱크·라이닝 제품을 제조·공급한다.</ns0:t>
+          <ns0:t>자회사 Win-Fung을 통해 말레이시아 등에서 유리섬유 강화 플라스틱·탱크·라이닝 제품을 제조·공급한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G78">
@@ -6210,7 +6210,7 @@
       </ns0:c>
       <ns0:c r="F79" t="inlineStr">
         <ns0:is>
-          <ns0:t>브라질에서 개방형 투자 플랫폼을 통해 증권·채권·펀드 등 금융상품과 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>브라질의 개방형 투자 플랫폼으로 증권·채권·펀드 등 금융상품과 서비스를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G79">
@@ -6289,7 +6289,7 @@
       </ns0:c>
       <ns0:c r="F80" t="inlineStr">
         <ns0:is>
-          <ns0:t>이스라엘과 해외에서 컨테이너 해운과 문전·항만 간 운송 등 관련 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>이스라엘과 해외에서 컨테이너 해운 및 문전·항만 간 운송 서비스를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G80">

--- a/technicals/exports/new-highs-history.xlsx
+++ b/technicals/exports/new-highs-history.xlsx
@@ -142,7 +142,7 @@
       </ns0:c>
       <ns0:c r="F2" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 스마트폰, 개인용 컴퓨터, 태블릿, 웨어러블 및 액세서리를 설계·제조·판매.</ns0:t>
+          <ns0:t>전 세계에서 스마트폰·PC·태블릿·웨어러블·액세서리를 설계·제조·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G2">
@@ -221,7 +221,7 @@
       </ns0:c>
       <ns0:c r="F3" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 의약품과 치료제를 연구·개발·제조·판매하는 연구 중심 바이오 제약 기업.</ns0:t>
+          <ns0:t>전 세계에서 의약품·치료제를 연구·개발·제조·판매하는 연구 중심 바이오 제약 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G3">
@@ -300,7 +300,7 @@
       </ns0:c>
       <ns0:c r="F4" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 건설·엔지니어링 구조물·운송 시장에 인프라 관련 제품과 솔루션을 제공한다.</ns0:t>
+          <ns0:t>미국 건설·엔지니어링 구조물·운송 시장에 인프라 제품과 솔루션을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G4">
@@ -379,7 +379,7 @@
       </ns0:c>
       <ns0:c r="F5" t="inlineStr">
         <ns0:is>
-          <ns0:t>미주·유럽·중동·아시아 등에서 소비자용, 학교용, 기술 및 사무용 제품을 설계·제조·판매.</ns0:t>
+          <ns0:t>미주·유럽·중동·아시아 등에서 소비자·학교·기술·사무용 제품을 설계·제조·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G5">
@@ -458,7 +458,7 @@
       </ns0:c>
       <ns0:c r="F6" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·이집트·북해에서 천연가스, 원유 및 천연가스액을 탐사·개발·생산하는 독립 에너지 기업.</ns0:t>
+          <ns0:t>미국·이집트·북해에서 천연가스·원유·천연가스액을 탐사·개발·생산하는 독립 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G6">
@@ -537,7 +537,7 @@
       </ns0:c>
       <ns0:c r="F7" t="inlineStr">
         <ns0:is>
-          <ns0:t>북미·유럽 등에서 온라인 데이팅·소셜 네트워킹 앱을 운영하며 구독과 앱 내 구매를 제공.</ns0:t>
+          <ns0:t>북미·유럽 등에서 데이팅·소셜 네트워킹 앱을 운영하며 구독과 앱 내 구매 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G7">
@@ -616,7 +616,7 @@
       </ns0:c>
       <ns0:c r="F8" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 석유·가스 사업을 운영하며 가스·저탄소 에너지, 석유 생산 및 고객·제품 부문을 영위.</ns0:t>
+          <ns0:t>전 세계에서 가스·저탄소 에너지, 석유 생산, 고객·제품 부문 등 석유·가스 사업 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G8">
@@ -695,7 +695,7 @@
       </ns0:c>
       <ns0:c r="F9" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 의료기술 기업으로 급성기 환자용 현장 뇌파검사 플랫폼인 Ceribell System을 개발.</ns0:t>
+          <ns0:t>급성기 환자용 현장 뇌파검사 플랫폼 Ceribell System을 개발하는 미국 의료기술 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G9">
@@ -932,7 +932,7 @@
       </ns0:c>
       <ns0:c r="F12" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 보험 보장이 부족한 가정과 기업에 프로그램·서비스를 제공하는 관리형 의료 기업.</ns0:t>
+          <ns0:t>미국 내 보험 보장이 부족한 가정·기업에 프로그램과 서비스를 제공하는 관리형 의료 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G12">
@@ -1011,7 +1011,7 @@
       </ns0:c>
       <ns0:c r="F13" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업·공공부문 등에 컴퓨터 시스템과 데이터센터를 포함한 다양한 IT 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>기업·공공부문에 컴퓨터 시스템·데이터센터 등 다양한 IT 솔루션을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G13">
@@ -1090,7 +1090,7 @@
       </ns0:c>
       <ns0:c r="F14" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 직업건강센터와 사업장 내 진료소 등을 통해 직업건강 및 고용주·소비자 건강 서비스를 제공.</ns0:t>
+          <ns0:t>미국에서 직업건강센터와 사업장 내 진료소를 통해 직업건강 및 고용주·소비자 건강 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G14">
@@ -1169,7 +1169,7 @@
       </ns0:c>
       <ns0:c r="F15" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 재생연료, 석유 정제·판매 및 질소비료 제조 사업을 영위하는 기업.</ns0:t>
+          <ns0:t>미국에서 재생연료, 석유 정제·판매, 질소비료 제조 사업을 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G15">
@@ -1248,7 +1248,7 @@
       </ns0:c>
       <ns0:c r="F16" t="inlineStr">
         <ns0:is>
-          <ns0:t>원유·천연가스 탐사, 개발, 생산, 운송 등을 포함한 통합 에너지 및 화학 사업을 영위.</ns0:t>
+          <ns0:t>원유·천연가스 탐사·개발·생산·운송 등을 포함한 통합 에너지·화학 사업 영위.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G16">
@@ -1327,7 +1327,7 @@
       </ns0:c>
       <ns0:c r="F17" t="inlineStr">
         <ns0:is>
-          <ns0:t>한국·미국 등에서 캐주얼 게임과 모바일 앱을 개발·배급하며 소셜 카지노 게임 및 iGaming 사업 운영.</ns0:t>
+          <ns0:t>한국·미국 등에서 캐주얼 게임·모바일 앱을 개발·배급하고 소셜 카지노와 iGaming 사업을 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G17">
@@ -1406,7 +1406,7 @@
       </ns0:c>
       <ns0:c r="F18" t="inlineStr">
         <ns0:is>
-          <ns0:t>자회사를 통해 원유 운반선을 소유·운영하며 기술 관리 서비스도 제공하는 기업.</ns0:t>
+          <ns0:t>자회사를 통해 원유 운반선을 소유·운영하고 기술 관리 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G18">
@@ -1485,7 +1485,7 @@
       </ns0:c>
       <ns0:c r="F19" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 독립 에너지 기업으로 정유·재생에너지·마케팅·윤활유·미드스트림 사업과 연료 생산·판매를 수행.</ns0:t>
+          <ns0:t>미국 독립 에너지 기업으로 정유·재생에너지·윤활유·미드스트림 사업과 연료 생산·판매 수행.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G19">
@@ -1564,7 +1564,7 @@
       </ns0:c>
       <ns0:c r="F20" t="inlineStr">
         <ns0:is>
-          <ns0:t>디지털 기업의 복잡한 디지털 환경을 위한 AI 기반 관측성 플랫폼을 제공하는 기업.</ns0:t>
+          <ns0:t>기업의 복잡한 디지털 환경을 위한 AI 기반 관측성 플랫폼 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G20">
@@ -1722,7 +1722,7 @@
       </ns0:c>
       <ns0:c r="F22" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 부실 소비자 채권을 할인 매입·관리하며 채무 회수 솔루션과 관련 서비스를 제공.</ns0:t>
+          <ns0:t>전 세계 부실 소비자 채권을 할인 매입·관리하며 채무 회수 솔루션과 관련 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G22">
@@ -1880,7 +1880,7 @@
       </ns0:c>
       <ns0:c r="F24" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 의료용 의류, 신발 등 생활용품을 소비자에게 직접 판매하는 기업.</ns0:t>
+          <ns0:t>미국과 해외에서 의료용 의류·신발 등 생활용품을 소비자에게 직접 판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G24">
@@ -1959,7 +1959,7 @@
       </ns0:c>
       <ns0:c r="F25" t="inlineStr">
         <ns0:is>
-          <ns0:t>시계·스마트워치·주얼리·핸드백·가죽 소품·벨트·선글라스 등 패션 액세서리를 설계·개발·유통.</ns0:t>
+          <ns0:t>시계·스마트워치·주얼리·핸드백·가죽 소품·벨트·선글라스 등 패션 액세서리 설계·개발·유통.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G25">
@@ -2038,7 +2038,7 @@
       </ns0:c>
       <ns0:c r="F26" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 초대형 원유운반선, 수에즈막스, LR2·아프라막스 등 원유·석유제품 운반선을 보유·운영.</ns0:t>
+          <ns0:t>전 세계에서 초대형·수에즈막스·LR2·아프라막스 원유·석유제품 운반선 보유·운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G26">
@@ -2117,7 +2117,7 @@
       </ns0:c>
       <ns0:c r="F27" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 사이버보안 및 네트워크·보안 통합 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>전 세계에 사이버보안과 네트워크·보안 통합 솔루션을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G27">
@@ -2275,7 +2275,7 @@
       </ns0:c>
       <ns0:c r="F29" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·호주·유럽의 매장과 온라인에서 게임, 수집품, 엔터테인먼트 제품을 판매하는 기업.</ns0:t>
+          <ns0:t>미국·호주·유럽의 매장과 온라인에서 게임·수집품·엔터테인먼트 제품을 판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G29">
@@ -2354,7 +2354,7 @@
       </ns0:c>
       <ns0:c r="F30" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 및 해외에서 에너지 서비스를 제공하며 전력·천연가스 재판매와 재생에너지 사업을 영위.</ns0:t>
+          <ns0:t>미국 및 해외에서 전력·천연가스 재판매와 재생에너지 등 에너지 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G30">
@@ -2433,7 +2433,7 @@
       </ns0:c>
       <ns0:c r="F31" t="inlineStr">
         <ns0:is>
-          <ns0:t>소프트웨어 개발 전 과정을 지원하는 통합 DevSecOps 플랫폼 GitLab을 제공하는 기업.</ns0:t>
+          <ns0:t>소프트웨어 개발 전 과정을 지원하는 통합 DevSecOps 플랫폼 GitLab을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G31">
@@ -2512,7 +2512,7 @@
       </ns0:c>
       <ns0:c r="F32" t="inlineStr">
         <ns0:is>
-          <ns0:t>혈장·혈액센터·병원 부문의 의료기술 기업으로 자동 혈장 채취 시스템과 헌혈자 관리 소프트웨어 등을 제공.</ns0:t>
+          <ns0:t>혈장·혈액센터·병원용 의료기술 기업으로 자동 혈장 채취 시스템과 헌혈자 관리 소프트웨어 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G32">
@@ -2591,7 +2591,7 @@
       </ns0:c>
       <ns0:c r="F33" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다·영국에서 수집용·자동차 애호가용 차량 보험을 제공하며 보험·마켓플레이스 부문을 운영.</ns0:t>
+          <ns0:t>미국·캐나다·영국에서 수집용·자동차 애호가용 차량 보험과 마켓플레이스 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G33">
@@ -2670,7 +2670,7 @@
       </ns0:c>
       <ns0:c r="F34" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국과 해외에서 다양한 형태의 맞춤형 냉간 성형 강재를 제조·판매하는 회사.</ns0:t>
+          <ns0:t>중국과 해외에서 다양한 맞춤형 냉간 성형 강재를 제조·판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G34">
@@ -2749,7 +2749,7 @@
       </ns0:c>
       <ns0:c r="F35" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술로 의료 제공을 확장·자동화하며 급성 부상·만성 통증·수술 후 재활 등 근골격계 관리 플랫폼을 개발하는 기업.</ns0:t>
+          <ns0:t>급성 부상·만성 통증·수술 후 재활 등 근골격계 관리를 위한 의료 자동화 플랫폼 개발 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G35">
@@ -2907,7 +2907,7 @@
       </ns0:c>
       <ns0:c r="F37" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 의료기관에 SaaS 애플리케이션과 의료 제공자 채용·신청·면허 검증 등 관리 도구를 제공.</ns0:t>
+          <ns0:t>미국 의료기관에 SaaS와 의료 제공자 채용·신청·면허 검증 관리 도구를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G37">
@@ -2986,7 +2986,7 @@
       </ns0:c>
       <ns0:c r="F38" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술 기반 고객 경험 솔루션과 고객서비스·기술지원·백오피스 아웃소싱을 제공하는 기업.</ns0:t>
+          <ns0:t>기술 기반 고객 경험 솔루션과 고객서비스·기술지원·백오피스 아웃소싱을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G38">
@@ -3065,7 +3065,7 @@
       </ns0:c>
       <ns0:c r="F39" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 소비재 브랜드 등의 디지털 판촉을 제휴 매체 네트워크를 통해 소비자에게 제공.</ns0:t>
+          <ns0:t>미국 소비재 브랜드 등의 디지털 판촉을 제휴 매체 네트워크로 소비자에게 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G39">
@@ -3144,7 +3144,7 @@
       </ns0:c>
       <ns0:c r="F40" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·영국 등에서 핀테크 및 통신 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>미국·영국 등에서 핀테크 및 통신 솔루션 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G40">
@@ -3223,7 +3223,7 @@
       </ns0:c>
       <ns0:c r="F41" t="inlineStr">
         <ns0:is>
-          <ns0:t>싱가포르·동남아에서 재생·신규 용기를 판매하고 강철·플라스틱 드럼 등 용기 재생 서비스를 제공.</ns0:t>
+          <ns0:t>싱가포르·동남아에서 재생·신규 용기를 판매하고 강철·플라스틱 드럼 등의 재생 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G41">
@@ -3299,7 +3299,7 @@
       </ns0:c>
       <ns0:c r="F42" t="inlineStr">
         <ns0:is>
-          <ns0:t>소셜 서비스와 통신 기술을 제공하며 소셜 라이브 스트리밍 플랫폼 Bigo Live를 운영한다.</ns0:t>
+          <ns0:t>소셜 서비스·통신 기술을 제공하고 소셜 라이브 스트리밍 플랫폼 Bigo Live를 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G42">
@@ -3457,7 +3457,7 @@
       </ns0:c>
       <ns0:c r="F44" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병·주식 교환·자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G44">
@@ -3533,7 +3533,7 @@
       </ns0:c>
       <ns0:c r="F45" t="inlineStr">
         <ns0:is>
-          <ns0:t>맞춤형 선박을 활용한 해양 탐험과 육상 여행 체험을 전 세계에 제공하는 기업.</ns0:t>
+          <ns0:t>맞춤형 선박을 활용한 해양 탐험과 육상 여행 체험을 전 세계에 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G45">
@@ -3612,7 +3612,7 @@
       </ns0:c>
       <ns0:c r="F46" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 거래 처리 및 결제 관련 제품·서비스를 소비자, 가맹점, 금융기관 등에 제공.</ns0:t>
+          <ns0:t>미국과 해외에서 소비자·가맹점·금융기관 등에 거래 처리와 결제 제품·서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G46">
@@ -3691,7 +3691,7 @@
       </ns0:c>
       <ns0:c r="F47" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 보험, 연금, 임직원 복리후생 및 자산관리 서비스를 제공하는 금융서비스 기업.</ns0:t>
+          <ns0:t>전 세계에서 보험·연금·임직원 복리후생·자산관리 서비스를 제공하는 금융서비스 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G47">
@@ -3770,7 +3770,7 @@
       </ns0:c>
       <ns0:c r="F48" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국의 통합 다운스트림 에너지 기업으로 정유·판매, 미드스트림, 재생 디젤 사업을 운영한다.</ns0:t>
+          <ns0:t>미국에서 정유·판매, 미드스트림, 재생 디젤 사업을 운영하는 통합 다운스트림 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G48">
@@ -3849,7 +3849,7 @@
       </ns0:c>
       <ns0:c r="F49" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다·멕시코·영국 등에서 금속가공 및 유지보수·수리·운영용 제품과 서비스를 유통한다.</ns0:t>
+          <ns0:t>미국·캐나다·멕시코·영국 등에서 금속가공 및 유지보수·수리·운영용 제품과 서비스를 유통.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G49">
@@ -3928,7 +3928,7 @@
       </ns0:c>
       <ns0:c r="F50" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 실험실용 기기 등 정밀기기를 제조·공급하고 관련 서비스를 제공한다.</ns0:t>
+          <ns0:t>전 세계에 실험실용 기기 등 정밀기기를 제조·공급하고 관련 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G50">
@@ -4007,7 +4007,7 @@
       </ns0:c>
       <ns0:c r="F51" t="inlineStr">
         <ns0:is>
-          <ns0:t>버뮤다와 해외에서 이중선체 유조선을 보유·운영·용선하며 석유회사와 원유 거래업체에 서비스를 제공.</ns0:t>
+          <ns0:t>버뮤다와 해외에서 이중선체 유조선을 보유·운영·용선하며 석유회사·원유 거래업체에 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G51">
@@ -4086,7 +4086,7 @@
       </ns0:c>
       <ns0:c r="F52" t="inlineStr">
         <ns0:is>
-          <ns0:t>아시아·유럽·북미·호주에서 건화물선과 유조선을 보유·운영하며 액체·건화물 해상운송을 제공.</ns0:t>
+          <ns0:t>아시아·유럽·북미·호주에서 건화물선·유조선을 보유·운영하며 액체·건화물 해상운송 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G52">
@@ -4165,7 +4165,7 @@
       </ns0:c>
       <ns0:c r="F53" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 IT 하드웨어·소프트웨어·서비스 및 클라우드·데이터 관리 지원 솔루션 제공.</ns0:t>
+          <ns0:t>미국과 해외에서 IT 하드웨어·소프트웨어·서비스와 클라우드·데이터 관리 지원 솔루션 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G53">
@@ -4244,7 +4244,7 @@
       </ns0:c>
       <ns0:c r="F54" t="inlineStr">
         <ns0:is>
-          <ns0:t>하이브리드·퍼블릭 클라우드 부문에서 데이터 인프라용 기업 소프트웨어·시스템·서비스를 개발하는 기업.</ns0:t>
+          <ns0:t>하이브리드·퍼블릭 클라우드의 데이터 인프라용 기업 소프트웨어·시스템·서비스를 개발.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G54">
@@ -4323,7 +4323,7 @@
       </ns0:c>
       <ns0:c r="F55" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 온라인·전화·매장 및 제휴 채널을 통해 개인대출과 신용카드를 제공.</ns0:t>
+          <ns0:t>미국에서 온라인·전화·매장 및 제휴 채널을 통해 개인대출과 신용카드 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G55">
@@ -4402,7 +4402,7 @@
       </ns0:c>
       <ns0:c r="F56" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 의료 기술 기업으로 개인·가족·직원·소규모 단체용 건강보험과 의료 시스템용 플랫폼 제공.</ns0:t>
+          <ns0:t>미국에서 개인·가족·직원·소규모 단체용 건강보험과 의료 시스템용 플랫폼을 제공하는 의료 기술 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G56">
@@ -4481,7 +4481,7 @@
       </ns0:c>
       <ns0:c r="F57" t="inlineStr">
         <ns0:is>
-          <ns0:t>데이터 저장·관리 기술과 제품, 서비스를 제공하며 데이터 축소·보호·암호화 소프트웨어를 공급한다.</ns0:t>
+          <ns0:t>데이터 저장·관리 기술과 제품·서비스, 데이터 축소·보호·암호화 소프트웨어 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G57">
@@ -4560,7 +4560,7 @@
       </ns0:c>
       <ns0:c r="F58" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 재생·기존 연료를 공급하며 정유, 소매, 물류 사업을 운영한다.</ns0:t>
+          <ns0:t>미국에서 재생·기존 연료를 공급하며 정유·소매·물류 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G58">
@@ -4639,7 +4639,7 @@
       </ns0:c>
       <ns0:c r="F59" t="inlineStr">
         <ns0:is>
-          <ns0:t>선불카드, 환자 비용 부담 지원, 디지털뱅킹, 생명과학 소프트웨어 및 통합 결제처리를 제공하는 회사.</ns0:t>
+          <ns0:t>선불카드, 환자 비용 지원, 디지털뱅킹, 생명과학 소프트웨어 및 통합 결제처리를 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G59">
@@ -4718,7 +4718,7 @@
       </ns0:c>
       <ns0:c r="F60" t="inlineStr">
         <ns0:is>
-          <ns0:t>정유·물류 사업을 통해 휘발유·경유·항공유·윤활유·석유화학제품·아스팔트 등을 생산·공급하는 기업.</ns0:t>
+          <ns0:t>정유·물류 사업을 통해 휘발유·경유·항공유·윤활유·석유화학제품·아스팔트를 생산·공급한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G60">
@@ -4955,7 +4955,7 @@
       </ns0:c>
       <ns0:c r="F63" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 등에서 미드스트림·화학·정유·마케팅 및 특수제품·재생연료 사업을 운영하는 통합 다운스트림 에너지 기업.</ns0:t>
+          <ns0:t>미국 등에서 미드스트림·화학·정유·마케팅·특수제품·재생연료 사업을 운영하는 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G63">
@@ -5034,7 +5034,7 @@
       </ns0:c>
       <ns0:c r="F64" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 유조선·건화물선 사업을 운영하며 정제 석유제품 등을 운송하는 해운사.</ns0:t>
+          <ns0:t>미국과 해외에서 유조선·건화물선을 운영하며 정제 석유제품 등을 운송하는 해운사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G64">
@@ -5189,7 +5189,7 @@
       </ns0:c>
       <ns0:c r="F66" t="inlineStr">
         <ns0:is>
-          <ns0:t>텍사스·뉴멕시코에서 석유·천연가스·천연가스액 자산을 인수·탐사·개발·생산.</ns0:t>
+          <ns0:t>텍사스·뉴멕시코에서 석유·천연가스·천연가스액 자산을 인수·탐사·개발·생산한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G66">
@@ -5268,7 +5268,7 @@
       </ns0:c>
       <ns0:c r="F67" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 생명·건강 및 자산집약형 재보험을 제공하며 장애·장기요양 관련 보장도 취급.</ns0:t>
+          <ns0:t>전 세계에서 생명·건강·자산집약형 재보험을 제공하고 장애·장기요양 관련 보장도 취급.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G67">
@@ -5347,7 +5347,7 @@
       </ns0:c>
       <ns0:c r="F68" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 재산·상해·특종 보험과 재보험을 제공하며 재산 재해 초과손해 재보험을 취급.</ns0:t>
+          <ns0:t>미국과 해외에서 재산·상해·특종 보험 및 재보험을 제공하고 재산 재해 초과손해 재보험 취급.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G68">
@@ -5505,7 +5505,7 @@
       </ns0:c>
       <ns0:c r="F70" t="inlineStr">
         <ns0:is>
-          <ns0:t>일본·베트남·미국·싱가포르의 미용 시술 센터에 광고·마케팅·인력관리 등 경영 서비스를 제공한다.</ns0:t>
+          <ns0:t>일본·베트남·미국·싱가포르 미용 시술 센터에 광고·마케팅·인력관리 등 경영 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G70">
@@ -5584,7 +5584,7 @@
       </ns0:c>
       <ns0:c r="F71" t="inlineStr">
         <ns0:is>
-          <ns0:t>세계 각지에서 통합 가스, 자원 개발·생산, 마케팅, 화학·제품, 재생에너지 사업을 운영한다.</ns0:t>
+          <ns0:t>전 세계에서 통합 가스, 자원 개발·생산, 마케팅, 화학·제품, 재생에너지 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G71">
@@ -5663,7 +5663,7 @@
       </ns0:c>
       <ns0:c r="F72" t="inlineStr">
         <ns0:is>
-          <ns0:t>남아공 등에서 화학·에너지 사업을 운영하며 역청, 연료, 나프타, 윤활유, 액화석유가스 등을 공급한다.</ns0:t>
+          <ns0:t>남아공 등에서 화학·에너지 사업을 운영하며 역청·연료·나프타·윤활유·액화석유가스를 공급한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G72">
@@ -5742,7 +5742,7 @@
       </ns0:c>
       <ns0:c r="F73" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·영국 등에서 디지털 전환, 마케팅·미디어·커머스, 마케팅 클라우드와 커뮤니케이션 서비스 제공.</ns0:t>
+          <ns0:t>미국·영국 등에서 디지털 전환, 마케팅·미디어·커머스, 마케팅 클라우드·커뮤니케이션 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G73">
@@ -5821,7 +5821,7 @@
       </ns0:c>
       <ns0:c r="F74" t="inlineStr">
         <ns0:is>
-          <ns0:t>캐나다·미국 등에서 오일샌드, 석유 탐사·생산, 정유·판매 사업을 영위하는 종합 에너지 기업.</ns0:t>
+          <ns0:t>캐나다·미국 등에서 오일샌드, 석유 탐사·생산, 정유·판매 사업을 운영하는 종합 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G74">
@@ -6134,7 +6134,7 @@
       </ns0:c>
       <ns0:c r="F78" t="inlineStr">
         <ns0:is>
-          <ns0:t>그리스와 해외에서 원유·석유제품 해상 운송 서비스를 제공하며 다양한 유조선과 LNG 운반선 등을 운영.</ns0:t>
+          <ns0:t>그리스와 해외에서 원유·석유제품 해상운송을 제공하며 다양한 유조선과 LNG 운반선 등을 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G78">
@@ -6213,7 +6213,7 @@
       </ns0:c>
       <ns0:c r="F79" t="inlineStr">
         <ns0:is>
-          <ns0:t>실질적인 영업활동 없이 다른 기업과의 합병·주식교환·자산인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>실질적 영업활동 없이 합병·주식교환·자산인수 등 다른 기업과의 기업결합을 추진.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G79">
@@ -6289,7 +6289,7 @@
       </ns0:c>
       <ns0:c r="F80" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 재산·상해보험과 보증보험을 제공하며 화재·배상책임·자동차·산재보험 등을 취급.</ns0:t>
+          <ns0:t>미국에서 재산·상해·보증보험을 제공하며 화재·배상책임·자동차·산재보험 등을 취급.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G80">
@@ -6368,7 +6368,7 @@
       </ns0:c>
       <ns0:c r="F81" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 소매·도매·구독 사업으로 의류·신발·액세서리 등 라이프스타일 상품과 서비스 제공.</ns0:t>
+          <ns0:t>미국과 해외에서 소매·도매·구독 사업을 통해 의류·신발·액세서리 등 라이프스타일 상품·서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G81">
@@ -6447,7 +6447,7 @@
       </ns0:c>
       <ns0:c r="F82" t="inlineStr">
         <ns0:is>
-          <ns0:t>결제 승인·청산·정산 네트워크 VisaNet을 운영하고 신용·직불·선불카드 상품을 제공.</ns0:t>
+          <ns0:t>결제 승인·청산·정산 네트워크 VisaNet을 운영하고 신용·직불·선불카드 상품을 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G82">
@@ -6526,7 +6526,7 @@
       </ns0:c>
       <ns0:c r="F83" t="inlineStr">
         <ns0:is>
-          <ns0:t>버지니아 내 상업·개인 금융 서비스를 제공하는 은행의 지주회사로 은행 및 신탁·상속재산 서비스 운영.</ns0:t>
+          <ns0:t>버지니아에서 상업·개인 금융과 신탁·상속재산 서비스를 운영하는 은행 지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G83">
@@ -6605,7 +6605,7 @@
       </ns0:c>
       <ns0:c r="F84" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계 생명과학 산업에 클라우드 소프트웨어를 제공하며 제약·바이오 기업용 CRM 제품군 등을 제공.</ns0:t>
+          <ns0:t>전 세계 생명과학 산업에 클라우드 소프트웨어와 제약·바이오 기업용 CRM 제품군 등을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G84">
@@ -6684,7 +6684,7 @@
       </ns0:c>
       <ns0:c r="F85" t="inlineStr">
         <ns0:is>
-          <ns0:t>석유 기반·저탄소 운송용 액체 연료와 석유화학 제품을 제조·판매하는 기업.</ns0:t>
+          <ns0:t>석유 기반·저탄소 운송용 액체 연료와 석유화학 제품을 제조·판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G85">
@@ -6921,7 +6921,7 @@
       </ns0:c>
       <ns0:c r="F88" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외 기업에 소비자 인텔리전스와 마케팅 자동화 소프트웨어를 제공하는 옴니채널 데이터 기반 플랫폼 운영.</ns0:t>
+          <ns0:t>미국과 해외 기업에 소비자 인텔리전스·마케팅 자동화 소프트웨어를 제공하는 옴니채널 데이터 기반 플랫폼 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G88">

--- a/technicals/exports/new-highs-history.xlsx
+++ b/technicals/exports/new-highs-history.xlsx
@@ -122,55 +122,55 @@
       </ns0:c>
       <ns0:c r="B2" t="inlineStr">
         <ns0:is>
-          <ns0:t>ATKR</ns0:t>
+          <ns0:t>ABBV</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C2" t="inlineStr">
         <ns0:is>
-          <ns0:t>Atkore Inc</ns0:t>
+          <ns0:t>Abbvie Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D2" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E2" t="inlineStr">
         <ns0:is>
-          <ns0:t>Electrical Equipment &amp; Parts</ns0:t>
+          <ns0:t>Drug Manufacturers - General</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F2" t="inlineStr">
         <ns0:is>
-          <ns0:t>전기·기계·안전·인프라 제품과 솔루션을 제조·판매하는 기업.</ns0:t>
+          <ns0:t>전 세계에서 의약품·치료제를 연구·개발·제조·판매하는 연구 중심 바이오 제약 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G2">
-        <ns0:v>94.93000030517578</ns0:v>
+        <ns0:v>283.4800109863281</ns0:v>
       </ns0:c>
       <ns0:c r="H2">
-        <ns0:v>0.052701362990403844</ns0:v>
+        <ns0:v>3.3241092439479925</ns0:v>
       </ns0:c>
       <ns0:c r="I2">
-        <ns0:v>94.9000015258789</ns0:v>
+        <ns0:v>283.42999267578125</ns0:v>
       </ns0:c>
       <ns0:c r="J2">
-        <ns0:v>0.0316109365801065</ns0:v>
+        <ns0:v>0.017647500913597902</ns0:v>
       </ns0:c>
       <ns0:c r="K2">
-        <ns0:v>1.149775972643658</ns0:v>
+        <ns0:v>1.201887444117473</ns0:v>
       </ns0:c>
       <ns0:c r="L2">
-        <ns0:v>72.23885089238354</ns0:v>
+        <ns0:v>69.68325183031487</ns0:v>
       </ns0:c>
       <ns0:c r="M2">
-        <ns0:v>94.67849960327149</ns0:v>
+        <ns0:v>267.8889984130859</ns0:v>
       </ns0:c>
       <ns0:c r="N2">
-        <ns0:v>94.14320022583007</ns0:v>
+        <ns0:v>260.8753985595703</ns0:v>
       </ns0:c>
       <ns0:c r="O2">
-        <ns0:v>76.60020009994507</ns0:v>
+        <ns0:v>233.40449935913085</ns0:v>
       </ns0:c>
       <ns0:c r="P2" t="inlineStr">
         <ns0:is>
@@ -189,7 +189,7 @@
       </ns0:c>
       <ns0:c r="T2" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/ATKR/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ABBV/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -201,55 +201,52 @@
       </ns0:c>
       <ns0:c r="B3" t="inlineStr">
         <ns0:is>
-          <ns0:t>ABBV</ns0:t>
+          <ns0:t>ALDF</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C3" t="inlineStr">
         <ns0:is>
-          <ns0:t>Abbvie Inc</ns0:t>
+          <ns0:t>Aldel Financial II Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D3" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E3" t="inlineStr">
         <ns0:is>
-          <ns0:t>Drug Manufacturers - General</ns0:t>
+          <ns0:t>Shell Companies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F3" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 의약품과 치료제를 연구·개발·제조·판매하는 연구 중심 바이오 제약 기업.</ns0:t>
+          <ns0:t>주요 영업활동 없이 합병·주식교환·자산인수 등 사업결합을 추진하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G3">
-        <ns0:v>283.4800109863281</ns0:v>
+        <ns0:v>10.979999542236328</ns0:v>
       </ns0:c>
       <ns0:c r="H3">
-        <ns0:v>3.3241092439479925</ns0:v>
+        <ns0:v>1.4787416998601755</ns0:v>
       </ns0:c>
       <ns0:c r="I3">
-        <ns0:v>283.42999267578125</ns0:v>
+        <ns0:v>10.859999656677246</ns0:v>
       </ns0:c>
       <ns0:c r="J3">
-        <ns0:v>0.017647500913597902</ns0:v>
-      </ns0:c>
-      <ns0:c r="K3">
-        <ns0:v>1.201887444117473</ns0:v>
+        <ns0:v>1.1049713568388686</ns0:v>
       </ns0:c>
       <ns0:c r="L3">
-        <ns0:v>69.68325183031487</ns0:v>
+        <ns0:v>94.11871785465019</ns0:v>
       </ns0:c>
       <ns0:c r="M3">
-        <ns0:v>267.8889984130859</ns0:v>
+        <ns0:v>10.829999732971192</ns0:v>
       </ns0:c>
       <ns0:c r="N3">
-        <ns0:v>260.8753985595703</ns0:v>
+        <ns0:v>10.801599884033203</ns0:v>
       </ns0:c>
       <ns0:c r="O3">
-        <ns0:v>233.40449935913085</ns0:v>
+        <ns0:v>10.65395495414734</ns0:v>
       </ns0:c>
       <ns0:c r="P3" t="inlineStr">
         <ns0:is>
@@ -268,7 +265,7 @@
       </ns0:c>
       <ns0:c r="T3" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/ABBV/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ALDF/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -280,56 +277,59 @@
       </ns0:c>
       <ns0:c r="B4" t="inlineStr">
         <ns0:is>
-          <ns0:t>ALDF</ns0:t>
+          <ns0:t>APA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C4" t="inlineStr">
         <ns0:is>
-          <ns0:t>Aldel Financial II Inc</ns0:t>
+          <ns0:t>APA Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D4" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E4" t="inlineStr">
         <ns0:is>
-          <ns0:t>Shell Companies</ns0:t>
+          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F4" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 기업과의 합병, 주식 교환, 자산 인수 등 사업결합을 추진.</ns0:t>
+          <ns0:t>미국·이집트·북해에서 천연가스·원유·천연가스액을 탐사·개발·생산하는 독립 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G4">
-        <ns0:v>10.979999542236328</ns0:v>
+        <ns0:v>47.369998931884766</ns0:v>
       </ns0:c>
       <ns0:c r="H4">
-        <ns0:v>1.4787416998601755</ns0:v>
+        <ns0:v>-1.3330543887175805</ns0:v>
       </ns0:c>
       <ns0:c r="I4">
-        <ns0:v>10.859999656677246</ns0:v>
+        <ns0:v>48.08000183105469</ns0:v>
       </ns0:c>
       <ns0:c r="J4">
-        <ns0:v>1.1049713568388686</ns0:v>
+        <ns0:v>-1.4767114644977708</ns0:v>
+      </ns0:c>
+      <ns0:c r="K4">
+        <ns0:v>0.8837884965251704</ns0:v>
       </ns0:c>
       <ns0:c r="L4">
-        <ns0:v>94.11871785465019</ns0:v>
+        <ns0:v>64.69187965552572</ns0:v>
       </ns0:c>
       <ns0:c r="M4">
-        <ns0:v>10.829999732971192</ns0:v>
+        <ns0:v>44.24850006103516</ns0:v>
       </ns0:c>
       <ns0:c r="N4">
-        <ns0:v>10.801599884033203</ns0:v>
+        <ns0:v>43.109000015258786</ns0:v>
       </ns0:c>
       <ns0:c r="O4">
-        <ns0:v>10.65395495414734</ns0:v>
+        <ns0:v>36.19505007743835</ns0:v>
       </ns0:c>
       <ns0:c r="P4" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q4" t="inlineStr">
@@ -344,7 +344,7 @@
       </ns0:c>
       <ns0:c r="T4" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/ALDF/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/APA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -356,55 +356,55 @@
       </ns0:c>
       <ns0:c r="B5" t="inlineStr">
         <ns0:is>
-          <ns0:t>APA</ns0:t>
+          <ns0:t>ASC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C5" t="inlineStr">
         <ns0:is>
-          <ns0:t>APA Corp</ns0:t>
+          <ns0:t>Ardmore Shipping Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas E&amp;P</ns0:t>
+          <ns0:t>Marine Shipping</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F5" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·이집트·북해에서 천연가스, 원유 및 천연가스액을 탐사·개발·생산하는 독립 에너지 기업.</ns0:t>
+          <ns0:t>전 세계에서 석유제품과 화학제품을 해상 운송하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G5">
-        <ns0:v>47.369998931884766</ns0:v>
+        <ns0:v>19.670000076293945</ns0:v>
       </ns0:c>
       <ns0:c r="H5">
-        <ns0:v>-1.3330543887175805</ns0:v>
+        <ns0:v>-2.2851420946365275</ns0:v>
       </ns0:c>
       <ns0:c r="I5">
-        <ns0:v>48.08000183105469</ns0:v>
+        <ns0:v>20.149999618530273</ns0:v>
       </ns0:c>
       <ns0:c r="J5">
-        <ns0:v>-1.4767114644977708</ns0:v>
+        <ns0:v>-2.382131768354534</ns0:v>
       </ns0:c>
       <ns0:c r="K5">
-        <ns0:v>0.8837884965251704</ns0:v>
+        <ns0:v>1.3509094790462801</ns0:v>
       </ns0:c>
       <ns0:c r="L5">
-        <ns0:v>64.69187965552572</ns0:v>
+        <ns0:v>59.93280844247997</ns0:v>
       </ns0:c>
       <ns0:c r="M5">
-        <ns0:v>44.24850006103516</ns0:v>
+        <ns0:v>18.82599992752075</ns0:v>
       </ns0:c>
       <ns0:c r="N5">
-        <ns0:v>43.109000015258786</ns0:v>
+        <ns0:v>18.188199882507323</ns0:v>
       </ns0:c>
       <ns0:c r="O5">
-        <ns0:v>36.19505007743835</ns0:v>
+        <ns0:v>16.08799996852875</ns0:v>
       </ns0:c>
       <ns0:c r="P5" t="inlineStr">
         <ns0:is>
@@ -423,7 +423,7 @@
       </ns0:c>
       <ns0:c r="T5" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/APA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ASC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -435,12 +435,12 @@
       </ns0:c>
       <ns0:c r="B6" t="inlineStr">
         <ns0:is>
-          <ns0:t>ASC</ns0:t>
+          <ns0:t>ATKR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C6" t="inlineStr">
         <ns0:is>
-          <ns0:t>Ardmore Shipping Corp</ns0:t>
+          <ns0:t>Atkore Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D6" t="inlineStr">
@@ -450,44 +450,44 @@
       </ns0:c>
       <ns0:c r="E6" t="inlineStr">
         <ns0:is>
-          <ns0:t>Marine Shipping</ns0:t>
+          <ns0:t>Electrical Equipment &amp; Parts</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F6" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 석유제품과 화학제품을 해상 운송하는 기업.</ns0:t>
+          <ns0:t>전기·기계·안전·인프라 제품과 솔루션을 제조·판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G6">
-        <ns0:v>19.670000076293945</ns0:v>
+        <ns0:v>94.93000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="H6">
-        <ns0:v>-2.2851420946365275</ns0:v>
+        <ns0:v>0.052701362990403844</ns0:v>
       </ns0:c>
       <ns0:c r="I6">
-        <ns0:v>20.149999618530273</ns0:v>
+        <ns0:v>94.9000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="J6">
-        <ns0:v>-2.382131768354534</ns0:v>
+        <ns0:v>0.0316109365801065</ns0:v>
       </ns0:c>
       <ns0:c r="K6">
-        <ns0:v>1.3509094790462801</ns0:v>
+        <ns0:v>1.149775972643658</ns0:v>
       </ns0:c>
       <ns0:c r="L6">
-        <ns0:v>59.93280844247997</ns0:v>
+        <ns0:v>72.23885089238354</ns0:v>
       </ns0:c>
       <ns0:c r="M6">
-        <ns0:v>18.82599992752075</ns0:v>
+        <ns0:v>94.67849960327149</ns0:v>
       </ns0:c>
       <ns0:c r="N6">
-        <ns0:v>18.188199882507323</ns0:v>
+        <ns0:v>94.14320022583007</ns0:v>
       </ns0:c>
       <ns0:c r="O6">
-        <ns0:v>16.08799996852875</ns0:v>
+        <ns0:v>76.60020009994507</ns0:v>
       </ns0:c>
       <ns0:c r="P6" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q6" t="inlineStr">
@@ -502,7 +502,7 @@
       </ns0:c>
       <ns0:c r="T6" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/ASC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ATKR/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -534,7 +534,7 @@
       </ns0:c>
       <ns0:c r="F7" t="inlineStr">
         <ns0:is>
-          <ns0:t>다양한 규모의 조직이 장소와 기기에 관계없이 콘텐츠를 관리하는 클라우드 플랫폼 제공.</ns0:t>
+          <ns0:t>다양한 규모의 조직이 장소·기기에 관계없이 콘텐츠를 관리하는 클라우드 플랫폼 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G7">
@@ -613,7 +613,7 @@
       </ns0:c>
       <ns0:c r="F8" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 석유·가스 사업을 운영하며 가스·저탄소 에너지, 석유 생산 및 고객·제품 부문을 영위.</ns0:t>
+          <ns0:t>전 세계에서 가스·저탄소 에너지, 석유 생산, 고객·제품 부문 등 석유·가스 사업 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G8">
@@ -692,7 +692,7 @@
       </ns0:c>
       <ns0:c r="F9" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 의료기술 기업으로 급성기 환자용 현장 뇌파검사 플랫폼인 Ceribell System을 개발.</ns0:t>
+          <ns0:t>급성기 환자용 현장 뇌파검사 플랫폼 Ceribell System을 개발하는 미국 의료기술 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G9">
@@ -850,7 +850,7 @@
       </ns0:c>
       <ns0:c r="F11" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 싱가포르에서 광고판·포스터 등을 활용한 옥외 및 공항 광고 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>미국·싱가포르에서 광고판·포스터 등을 활용한 옥외·공항 광고 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G11">
@@ -929,7 +929,7 @@
       </ns0:c>
       <ns0:c r="F12" t="inlineStr">
         <ns0:is>
-          <ns0:t>대만과 해외에서 개인·기업 고객에게 이동통신·유선통신 등 통합 통신 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>대만과 해외 개인·기업 고객에게 이동통신·유선통신 등 통합 통신 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G12">
@@ -1008,7 +1008,7 @@
       </ns0:c>
       <ns0:c r="F13" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 보험 보장이 부족한 가정과 기업에 프로그램·서비스를 제공하는 관리형 의료 기업.</ns0:t>
+          <ns0:t>미국 내 보험 보장이 부족한 가정·기업에 프로그램과 서비스를 제공하는 관리형 의료 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G13">
@@ -1087,7 +1087,7 @@
       </ns0:c>
       <ns0:c r="F14" t="inlineStr">
         <ns0:is>
-          <ns0:t>캐나다 서부·영국 북해·아프리카 해상에서 원유·천연가스·천연가스액을 탐사·개발·생산·판매하는 기업.</ns0:t>
+          <ns0:t>캐나다 서부·영국 북해·아프리카 해상에서 원유·천연가스·천연가스액을 탐사·개발·생산·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G14">
@@ -1166,7 +1166,7 @@
       </ns0:c>
       <ns0:c r="F15" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 직업건강센터와 사업장 내 진료소 등을 통해 직업건강 및 고용주·소비자 건강 서비스를 제공.</ns0:t>
+          <ns0:t>미국에서 직업건강센터와 사업장 내 진료소를 통해 직업건강 및 고용주·소비자 건강 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G15">
@@ -1245,7 +1245,7 @@
       </ns0:c>
       <ns0:c r="F16" t="inlineStr">
         <ns0:is>
-          <ns0:t>원유·역청·천연가스·액화천연가스·천연가스액을 탐사·생산·운송·판매하는 기업.</ns0:t>
+          <ns0:t>원유·역청·천연가스·액화천연가스·천연가스액을 탐사·생산·운송·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G16">
@@ -1324,7 +1324,7 @@
       </ns0:c>
       <ns0:c r="F17" t="inlineStr">
         <ns0:is>
-          <ns0:t>AI 등 기술을 활용해 산재보상·일반 및 자동차 배상책임 관리와 병원비 심사·지급 적정성 솔루션을 제공.</ns0:t>
+          <ns0:t>AI 등을 활용해 산재보상·일반 및 자동차 배상책임 관리, 병원비 심사·지급 적정성 솔루션을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G17">
@@ -1403,7 +1403,7 @@
       </ns0:c>
       <ns0:c r="F18" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 재생연료, 석유 정제·판매 및 질소비료 제조 사업을 영위하는 기업.</ns0:t>
+          <ns0:t>미국에서 재생연료, 석유 정제·판매, 질소비료 제조 사업을 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G18">
@@ -1482,7 +1482,7 @@
       </ns0:c>
       <ns0:c r="F19" t="inlineStr">
         <ns0:is>
-          <ns0:t>원유·천연가스 탐사, 개발, 생산, 운송 등을 포함한 통합 에너지 및 화학 사업을 영위.</ns0:t>
+          <ns0:t>원유·천연가스 탐사·개발·생산·운송 등을 포함한 통합 에너지·화학 사업 영위.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G19">
@@ -1561,7 +1561,7 @@
       </ns0:c>
       <ns0:c r="F20" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국에서 학습 서비스·스마트 기기·온라인 마케팅을 비롯한 인터넷 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>중국에서 학습 서비스·스마트 기기·온라인 마케팅 등 인터넷 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G20">
@@ -1640,7 +1640,7 @@
       </ns0:c>
       <ns0:c r="F21" t="inlineStr">
         <ns0:is>
-          <ns0:t>자회사를 통해 원유 운반선을 소유·운영하며 기술 관리 서비스도 제공하는 기업.</ns0:t>
+          <ns0:t>자회사를 통해 원유 운반선을 소유·운영하고 기술 관리 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G21">
@@ -1719,7 +1719,7 @@
       </ns0:c>
       <ns0:c r="F22" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 독립 에너지 기업으로 정유·재생에너지·마케팅·윤활유·미드스트림 사업과 연료 생산·판매를 수행.</ns0:t>
+          <ns0:t>미국 독립 에너지 기업으로 정유·재생에너지·윤활유·미드스트림 사업과 연료 생산·판매 수행.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G22">
@@ -1877,7 +1877,7 @@
       </ns0:c>
       <ns0:c r="F24" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·트리니다드토바고 등에서 원유·천연가스액·천연가스를 탐사·개발·생산·판매하는 기업.</ns0:t>
+          <ns0:t>미국·트리니다드토바고 등에서 원유·천연가스액·천연가스를 탐사·개발·생산·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G24">
@@ -2035,7 +2035,7 @@
       </ns0:c>
       <ns0:c r="F26" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·호주·유럽의 매장과 온라인에서 게임, 수집품, 엔터테인먼트 제품을 판매하는 기업.</ns0:t>
+          <ns0:t>미국·호주·유럽의 매장과 온라인에서 게임·수집품·엔터테인먼트 제품을 판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G26">
@@ -2114,7 +2114,7 @@
       </ns0:c>
       <ns0:c r="F27" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 및 해외에서 에너지 서비스를 제공하며 전력·천연가스 재판매와 재생에너지 사업을 영위.</ns0:t>
+          <ns0:t>미국 및 해외에서 전력·천연가스 재판매와 재생에너지 등 에너지 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G27">
@@ -2193,7 +2193,7 @@
       </ns0:c>
       <ns0:c r="F28" t="inlineStr">
         <ns0:is>
-          <ns0:t>독자 효소와 기기를 연구·개발·상용화하며 재조합 인간 히알루로니다아제 기반 제품을 보유한 바이오제약사.</ns0:t>
+          <ns0:t>독자 효소·기기를 연구·개발·상용화하며 재조합 인간 히알루로니다아제 기반 제품을 보유한 바이오제약사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G28">
@@ -2272,7 +2272,7 @@
       </ns0:c>
       <ns0:c r="F29" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국과 해외에서 다양한 형태의 맞춤형 냉간 성형 강재를 제조·판매하는 회사.</ns0:t>
+          <ns0:t>중국과 해외에서 다양한 맞춤형 냉간 성형 강재를 제조·판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G29">
@@ -2351,7 +2351,7 @@
       </ns0:c>
       <ns0:c r="F30" t="inlineStr">
         <ns0:is>
-          <ns0:t>세계 각지에서 오토바이·자동차·동력 제품을 개발·제조·유통하고 금융 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>세계 각지에서 오토바이·자동차·동력 제품을 개발·제조·유통하고 금융 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G30">
@@ -2430,7 +2430,7 @@
       </ns0:c>
       <ns0:c r="F31" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술 기반 고객 경험 솔루션과 고객서비스·기술지원·백오피스 아웃소싱을 제공하는 기업.</ns0:t>
+          <ns0:t>기술 기반 고객 경험 솔루션과 고객서비스·기술지원·백오피스 아웃소싱을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G31">
@@ -2509,7 +2509,7 @@
       </ns0:c>
       <ns0:c r="F32" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 소비재 브랜드 등의 디지털 판촉을 제휴 매체 네트워크를 통해 소비자에게 제공.</ns0:t>
+          <ns0:t>미국 소비재 브랜드 등의 디지털 판촉을 제휴 매체 네트워크로 소비자에게 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G32">
@@ -2588,7 +2588,7 @@
       </ns0:c>
       <ns0:c r="F33" t="inlineStr">
         <ns0:is>
-          <ns0:t>식품·음료·건강 및 바이오과학·향료와 관련 제품을 제조·판매하는 글로벌 기업.</ns0:t>
+          <ns0:t>식품·음료·건강·바이오과학·향료 관련 제품을 제조·판매하는 글로벌 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G33">
@@ -2667,7 +2667,7 @@
       </ns0:c>
       <ns0:c r="F34" t="inlineStr">
         <ns0:is>
-          <ns0:t>원유와 석유제품의 국제 해상 운송을 위해 원유선과 제품 운반선을 보유·운영하는 기업.</ns0:t>
+          <ns0:t>원유선과 석유제품 운반선을 보유·운영하며 원유·석유제품의 국제 해상 운송을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G34">
@@ -2746,7 +2746,7 @@
       </ns0:c>
       <ns0:c r="F35" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국에서 푸시 알림·메신저·분석·문자·원클릭 인증 등 개발자 서비스와 산업별 앱을 제공하는 기업.</ns0:t>
+          <ns0:t>중국에서 푸시 알림·메신저·분석·문자·원클릭 인증 등 개발자 서비스와 산업별 앱을 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G35">
@@ -2825,7 +2825,7 @@
       </ns0:c>
       <ns0:c r="F36" t="inlineStr">
         <ns0:is>
-          <ns0:t>소셜 서비스와 통신 기술을 제공하며 소셜 라이브 스트리밍 플랫폼 Bigo Live를 운영한다.</ns0:t>
+          <ns0:t>소셜 서비스·통신 기술을 제공하고 소셜 라이브 스트리밍 플랫폼 Bigo Live를 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G36">
@@ -3062,7 +3062,7 @@
       </ns0:c>
       <ns0:c r="F39" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 석유·천연가스 자산의 광물권과 로열티 권익을 보유·취득하는 기업.</ns0:t>
+          <ns0:t>미국 석유·천연가스 자산의 광물권과 로열티 권익을 보유·취득.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G39">
@@ -3141,7 +3141,7 @@
       </ns0:c>
       <ns0:c r="F40" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 거래 처리 및 결제 관련 제품·서비스를 소비자, 가맹점, 금융기관 등에 제공.</ns0:t>
+          <ns0:t>미국과 해외에서 소비자·가맹점·금융기관 등에 거래 처리와 결제 제품·서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G40">
@@ -3220,7 +3220,7 @@
       </ns0:c>
       <ns0:c r="F41" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국의 통합 다운스트림 에너지 기업으로 정유·판매, 미드스트림, 재생 디젤 사업을 운영한다.</ns0:t>
+          <ns0:t>미국에서 정유·판매, 미드스트림, 재생 디젤 사업을 운영하는 통합 다운스트림 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G41">
@@ -3299,7 +3299,7 @@
       </ns0:c>
       <ns0:c r="F42" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다·멕시코·영국 등에서 금속가공 및 유지보수·수리·운영용 제품과 서비스를 유통한다.</ns0:t>
+          <ns0:t>미국·캐나다·멕시코·영국 등에서 금속가공 및 유지보수·수리·운영용 제품과 서비스를 유통.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G42">
@@ -3378,7 +3378,7 @@
       </ns0:c>
       <ns0:c r="F43" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 실험실용 기기 등 정밀기기를 제조·공급하고 관련 서비스를 제공한다.</ns0:t>
+          <ns0:t>전 세계에 실험실용 기기 등 정밀기기를 제조·공급하고 관련 서비스 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G43">
@@ -3457,7 +3457,7 @@
       </ns0:c>
       <ns0:c r="F44" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 식음료 판매, 컨설팅, 전자폐기물 자재 판매 등 공급망 사업을 운영한다.</ns0:t>
+          <ns0:t>미국에서 식음료 판매, 컨설팅, 전자폐기물 자재 판매 등 공급망 사업을 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G44">
@@ -3536,7 +3536,7 @@
       </ns0:c>
       <ns0:c r="F45" t="inlineStr">
         <ns0:is>
-          <ns0:t>자동차 금융·리스, 은행 및 금융서비스 산업용 기업 소프트웨어를 설계·개발·판매하는 회사.</ns0:t>
+          <ns0:t>자동차 금융·리스, 은행·금융서비스용 기업 소프트웨어를 설계·개발·판매하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G45">
@@ -3691,7 +3691,7 @@
       </ns0:c>
       <ns0:c r="F47" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 재생·기존 연료를 공급하며 정유, 소매, 물류 사업을 운영한다.</ns0:t>
+          <ns0:t>미국에서 재생·기존 연료를 공급하며 정유·소매·물류 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G47">
@@ -3770,7 +3770,7 @@
       </ns0:c>
       <ns0:c r="F48" t="inlineStr">
         <ns0:is>
-          <ns0:t>정유·물류 사업을 통해 휘발유·경유·항공유·윤활유·석유화학제품·아스팔트 등을 생산·공급하는 기업.</ns0:t>
+          <ns0:t>정유·물류 사업을 통해 휘발유·경유·항공유·윤활유·석유화학제품·아스팔트를 생산·공급한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G48">
@@ -3849,7 +3849,7 @@
       </ns0:c>
       <ns0:c r="F49" t="inlineStr">
         <ns0:is>
-          <ns0:t>브라질과 해외에서 석유·가스를 탐사·생산·판매하며 정유·운송·판매 사업을 운영한다.</ns0:t>
+          <ns0:t>브라질과 해외에서 석유·가스 탐사·생산·판매 및 정유·운송 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G49">
@@ -3928,7 +3928,7 @@
       </ns0:c>
       <ns0:c r="F50" t="inlineStr">
         <ns0:is>
-          <ns0:t>브라질과 해외에서 석유·가스를 탐사·생산·판매하며 정유·운송·판매 사업을 운영한다.</ns0:t>
+          <ns0:t>브라질과 해외에서 석유·가스 탐사·생산·판매 및 정유·운송 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G50">
@@ -4007,7 +4007,7 @@
       </ns0:c>
       <ns0:c r="F51" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 의료진 대상 비마약성 통증관리·재생건강 솔루션을 개발·제조·판매하며 수술 후 통증관리 주사제를 제공.</ns0:t>
+          <ns0:t>비마약성 통증관리·재생건강 솔루션과 수술 후 통증관리 주사제를 개발·제조·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G51">
@@ -4086,7 +4086,7 @@
       </ns0:c>
       <ns0:c r="F52" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 바이오의약품을 발굴·개발·제조·마케팅·유통·판매하는 기업.</ns0:t>
+          <ns0:t>미국과 해외에서 바이오의약품을 발굴·개발·제조·마케팅·유통·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G52">
@@ -4165,7 +4165,7 @@
       </ns0:c>
       <ns0:c r="F53" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 등에서 미드스트림·화학·정유·마케팅 및 특수제품·재생연료 사업을 운영하는 통합 다운스트림 에너지 기업.</ns0:t>
+          <ns0:t>미국 등에서 미드스트림·화학·정유·마케팅·특수제품·재생연료 사업을 운영하는 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G53">
@@ -4244,7 +4244,7 @@
       </ns0:c>
       <ns0:c r="F54" t="inlineStr">
         <ns0:is>
-          <ns0:t>텍사스·뉴멕시코에서 석유·천연가스·천연가스액 자산을 인수·탐사·개발·생산.</ns0:t>
+          <ns0:t>텍사스·뉴멕시코에서 석유·천연가스·천연가스액 자산을 인수·탐사·개발·생산한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G54">
@@ -4323,7 +4323,7 @@
       </ns0:c>
       <ns0:c r="F55" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에서 생명·건강 및 자산집약형 재보험을 제공하며 장애·장기요양 관련 보장도 취급.</ns0:t>
+          <ns0:t>전 세계에서 생명·건강·자산집약형 재보험을 제공하고 장애·장기요양 관련 보장도 취급.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G55">
@@ -4402,7 +4402,7 @@
       </ns0:c>
       <ns0:c r="F56" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 재산·상해·특종 보험과 재보험을 제공하며 재산 재해 초과손해 재보험을 취급.</ns0:t>
+          <ns0:t>미국과 해외에서 재산·상해·특종 보험 및 재보험을 제공하고 재산 재해 초과손해 재보험 취급.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G56">
@@ -4481,7 +4481,7 @@
       </ns0:c>
       <ns0:c r="F57" t="inlineStr">
         <ns0:is>
-          <ns0:t>세계 각지에서 통합 가스, 자원 개발·생산, 마케팅, 화학·제품, 재생에너지 사업을 운영한다.</ns0:t>
+          <ns0:t>전 세계에서 통합 가스, 자원 개발·생산, 마케팅, 화학·제품, 재생에너지 사업을 운영한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G57">
@@ -4560,7 +4560,7 @@
       </ns0:c>
       <ns0:c r="F58" t="inlineStr">
         <ns0:is>
-          <ns0:t>캐나다·미국 등에서 오일샌드, 석유 탐사·생산, 정유·판매 사업을 영위하는 종합 에너지 기업.</ns0:t>
+          <ns0:t>캐나다·미국 등에서 오일샌드, 석유 탐사·생산, 정유·판매 사업을 운영하는 종합 에너지 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G58">
@@ -4639,7 +4639,7 @@
       </ns0:c>
       <ns0:c r="F59" t="inlineStr">
         <ns0:is>
-          <ns0:t>그리스와 해외에서 원유·석유제품 해상 운송 서비스를 제공하며 다양한 유조선과 LNG 운반선 등을 운영.</ns0:t>
+          <ns0:t>그리스와 해외에서 원유·석유제품 해상운송을 제공하며 다양한 유조선과 LNG 운반선 등을 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G59">
@@ -4797,7 +4797,7 @@
       </ns0:c>
       <ns0:c r="F61" t="inlineStr">
         <ns0:is>
-          <ns0:t>버지니아 내 상업·개인 금융 서비스를 제공하는 은행의 지주회사로 은행 및 신탁·상속재산 서비스 운영.</ns0:t>
+          <ns0:t>버지니아에서 상업·개인 금융과 신탁·상속재산 서비스를 운영하는 은행 지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G61">
@@ -4876,7 +4876,7 @@
       </ns0:c>
       <ns0:c r="F62" t="inlineStr">
         <ns0:is>
-          <ns0:t>주식·뮤추얼펀드·ETF·옵션 등을 다루는 투자 정기간행물과 관련 출판물을 제작·판매.</ns0:t>
+          <ns0:t>주식·뮤추얼펀드·ETF·옵션 관련 투자 정기간행물과 출판물을 제작·판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G62">
@@ -4955,7 +4955,7 @@
       </ns0:c>
       <ns0:c r="F63" t="inlineStr">
         <ns0:is>
-          <ns0:t>석유 기반·저탄소 운송용 액체 연료와 석유화학 제품을 제조·판매하는 기업.</ns0:t>
+          <ns0:t>석유 기반·저탄소 운송용 액체 연료와 석유화학 제품을 제조·판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G63">
@@ -5113,7 +5113,7 @@
       </ns0:c>
       <ns0:c r="F65" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다 등에서 원유·천연가스를 탐사·생산하며 에너지·화학·특수제품 사업을 운영한다.</ns0:t>
+          <ns0:t>미국·캐나다 등에서 원유·천연가스를 탐사·생산하며 에너지·화학·특수제품 사업 운영.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G65">
